--- a/build/dts/P2437-HV-DTS-003 REV0.xlsx
+++ b/build/dts/P2437-HV-DTS-003 REV0.xlsx
@@ -22,7 +22,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.00000000000000"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -146,6 +146,11 @@
       <b val="1"/>
       <color rgb="001F4E78"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00404040"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
@@ -488,10 +493,10 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3218,7 +3223,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O86"/>
+  <dimension ref="A1:O77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30.61328125" customWidth="1" min="1" max="1"/>
@@ -3450,15 +3455,24 @@
           <t>Campo</t>
         </is>
       </c>
-      <c r="B10" s="59" t="inlineStr">
-        <is>
-          <t>Valor</t>
-        </is>
-      </c>
+      <c r="B10" s="59" t="n"/>
       <c r="C10" s="59" t="n"/>
       <c r="D10" s="59" t="n"/>
       <c r="E10" s="59" t="n"/>
       <c r="F10" s="59" t="n"/>
+      <c r="G10" s="59" t="n"/>
+      <c r="H10" s="59" t="n"/>
+      <c r="I10" s="59" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="J10" s="59" t="n"/>
+      <c r="K10" s="59" t="n"/>
+      <c r="L10" s="59" t="n"/>
+      <c r="M10" s="59" t="n"/>
+      <c r="N10" s="59" t="n"/>
+      <c r="O10" s="59" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="60" t="inlineStr">
@@ -3466,15 +3480,24 @@
           <t>Código</t>
         </is>
       </c>
-      <c r="B11" s="60" t="inlineStr">
-        <is>
-          <t>HD-REJ-001</t>
-        </is>
-      </c>
+      <c r="B11" s="61" t="n"/>
       <c r="C11" s="61" t="n"/>
       <c r="D11" s="61" t="n"/>
       <c r="E11" s="61" t="n"/>
       <c r="F11" s="61" t="n"/>
+      <c r="G11" s="61" t="n"/>
+      <c r="H11" s="61" t="n"/>
+      <c r="I11" s="60" t="inlineStr">
+        <is>
+          <t>HD-REJ-001</t>
+        </is>
+      </c>
+      <c r="J11" s="61" t="n"/>
+      <c r="K11" s="61" t="n"/>
+      <c r="L11" s="61" t="n"/>
+      <c r="M11" s="61" t="n"/>
+      <c r="N11" s="61" t="n"/>
+      <c r="O11" s="61" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="60" t="inlineStr">
@@ -3482,15 +3505,24 @@
           <t>Revisión</t>
         </is>
       </c>
-      <c r="B12" s="60" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="B12" s="61" t="n"/>
       <c r="C12" s="61" t="n"/>
       <c r="D12" s="61" t="n"/>
       <c r="E12" s="61" t="n"/>
       <c r="F12" s="61" t="n"/>
+      <c r="G12" s="61" t="n"/>
+      <c r="H12" s="61" t="n"/>
+      <c r="I12" s="60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J12" s="61" t="n"/>
+      <c r="K12" s="61" t="n"/>
+      <c r="L12" s="61" t="n"/>
+      <c r="M12" s="61" t="n"/>
+      <c r="N12" s="61" t="n"/>
+      <c r="O12" s="61" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="60" t="inlineStr">
@@ -3498,15 +3530,24 @@
           <t>Fecha</t>
         </is>
       </c>
-      <c r="B13" s="60" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
+      <c r="B13" s="61" t="n"/>
       <c r="C13" s="61" t="n"/>
       <c r="D13" s="61" t="n"/>
       <c r="E13" s="61" t="n"/>
       <c r="F13" s="61" t="n"/>
+      <c r="G13" s="61" t="n"/>
+      <c r="H13" s="61" t="n"/>
+      <c r="I13" s="60" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="J13" s="61" t="n"/>
+      <c r="K13" s="61" t="n"/>
+      <c r="L13" s="61" t="n"/>
+      <c r="M13" s="61" t="n"/>
+      <c r="N13" s="61" t="n"/>
+      <c r="O13" s="61" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="60" t="inlineStr">
@@ -3514,15 +3555,24 @@
           <t>Proyecto</t>
         </is>
       </c>
-      <c r="B14" s="60" t="inlineStr">
-        <is>
-          <t>P2437-HV-INF-001 — BRINSA, laboratorio de análisis industrial, Cajicá</t>
-        </is>
-      </c>
+      <c r="B14" s="61" t="n"/>
       <c r="C14" s="61" t="n"/>
       <c r="D14" s="61" t="n"/>
       <c r="E14" s="61" t="n"/>
       <c r="F14" s="61" t="n"/>
+      <c r="G14" s="61" t="n"/>
+      <c r="H14" s="61" t="n"/>
+      <c r="I14" s="60" t="inlineStr">
+        <is>
+          <t>P2437-HV-INF-001 — BRINSA, laboratorio de análisis industrial, Cajicá</t>
+        </is>
+      </c>
+      <c r="J14" s="61" t="n"/>
+      <c r="K14" s="61" t="n"/>
+      <c r="L14" s="61" t="n"/>
+      <c r="M14" s="61" t="n"/>
+      <c r="N14" s="61" t="n"/>
+      <c r="O14" s="61" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="60" t="inlineStr">
@@ -3530,15 +3580,24 @@
           <t>Etiqueta de equipo</t>
         </is>
       </c>
-      <c r="B15" s="60" t="inlineStr">
-        <is>
-          <t>REJ-001 a REJ-003 (rejillas de exfiltración)</t>
-        </is>
-      </c>
+      <c r="B15" s="61" t="n"/>
       <c r="C15" s="61" t="n"/>
       <c r="D15" s="61" t="n"/>
       <c r="E15" s="61" t="n"/>
       <c r="F15" s="61" t="n"/>
+      <c r="G15" s="61" t="n"/>
+      <c r="H15" s="61" t="n"/>
+      <c r="I15" s="60" t="inlineStr">
+        <is>
+          <t>REJ-001 a REJ-003 (rejillas de exfiltración)</t>
+        </is>
+      </c>
+      <c r="J15" s="61" t="n"/>
+      <c r="K15" s="61" t="n"/>
+      <c r="L15" s="61" t="n"/>
+      <c r="M15" s="61" t="n"/>
+      <c r="N15" s="61" t="n"/>
+      <c r="O15" s="61" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="62" t="inlineStr">
@@ -3557,621 +3616,888 @@
     <row r="20"/>
     <row r="21"/>
     <row r="22"/>
-    <row r="23"/>
+    <row r="24">
+      <c r="A24" s="62" t="inlineStr">
+        <is>
+          <t>2. Condiciones de operación y desempeño</t>
+        </is>
+      </c>
+    </row>
     <row r="25">
-      <c r="A25" s="62" t="inlineStr">
-        <is>
-          <t>2. Condiciones de operación y desempeño</t>
+      <c r="A25" s="64" t="inlineStr">
+        <is>
+          <t>Tabla 1. Condiciones de diseño (valores congelados de la memoria de cálculo).</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="64" t="inlineStr">
-        <is>
-          <t>Tabla 1. Condiciones de diseño (valores congelados de la memoria de cálculo).</t>
-        </is>
-      </c>
+      <c r="A26" s="59" t="inlineStr">
+        <is>
+          <t>Parámetro</t>
+        </is>
+      </c>
+      <c r="B26" s="59" t="n"/>
+      <c r="C26" s="59" t="n"/>
+      <c r="D26" s="59" t="n"/>
+      <c r="E26" s="59" t="n"/>
+      <c r="F26" s="59" t="n"/>
+      <c r="G26" s="59" t="n"/>
+      <c r="H26" s="59" t="n"/>
+      <c r="I26" s="59" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="J26" s="59" t="n"/>
+      <c r="K26" s="59" t="n"/>
+      <c r="L26" s="59" t="n"/>
+      <c r="M26" s="59" t="n"/>
+      <c r="N26" s="59" t="n"/>
+      <c r="O26" s="59" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="59" t="inlineStr">
-        <is>
-          <t>Parámetro</t>
-        </is>
-      </c>
-      <c r="B27" s="59" t="inlineStr">
-        <is>
-          <t>Valor</t>
-        </is>
-      </c>
-      <c r="C27" s="59" t="n"/>
-      <c r="D27" s="59" t="n"/>
-      <c r="E27" s="59" t="n"/>
-      <c r="F27" s="59" t="n"/>
+      <c r="A27" s="60" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="B27" s="61" t="n"/>
+      <c r="C27" s="61" t="n"/>
+      <c r="D27" s="61" t="n"/>
+      <c r="E27" s="61" t="n"/>
+      <c r="F27" s="61" t="n"/>
+      <c r="G27" s="61" t="n"/>
+      <c r="H27" s="61" t="n"/>
+      <c r="I27" s="60" t="inlineStr">
+        <is>
+          <t>3 unidades</t>
+        </is>
+      </c>
+      <c r="J27" s="61" t="n"/>
+      <c r="K27" s="61" t="n"/>
+      <c r="L27" s="61" t="n"/>
+      <c r="M27" s="61" t="n"/>
+      <c r="N27" s="61" t="n"/>
+      <c r="O27" s="61" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="60" t="inlineStr">
         <is>
-          <t>Cantidad</t>
-        </is>
-      </c>
-      <c r="B28" s="60" t="inlineStr">
-        <is>
-          <t>3 unidades</t>
-        </is>
-      </c>
+          <t>Dimensiones faciales (unitarias)</t>
+        </is>
+      </c>
+      <c r="B28" s="61" t="n"/>
       <c r="C28" s="61" t="n"/>
       <c r="D28" s="61" t="n"/>
       <c r="E28" s="61" t="n"/>
       <c r="F28" s="61" t="n"/>
+      <c r="G28" s="61" t="n"/>
+      <c r="H28" s="61" t="n"/>
+      <c r="I28" s="60" t="inlineStr">
+        <is>
+          <t>353×336 mm (área facial 0.1187 m²)</t>
+        </is>
+      </c>
+      <c r="J28" s="61" t="n"/>
+      <c r="K28" s="61" t="n"/>
+      <c r="L28" s="61" t="n"/>
+      <c r="M28" s="61" t="n"/>
+      <c r="N28" s="61" t="n"/>
+      <c r="O28" s="61" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="60" t="inlineStr">
         <is>
-          <t>Dimensiones faciales (unitarias)</t>
-        </is>
-      </c>
-      <c r="B29" s="60" t="inlineStr">
-        <is>
-          <t>353×336 mm (área facial 0.1187 m²)</t>
-        </is>
-      </c>
+          <t>Caudal total de exfiltración</t>
+        </is>
+      </c>
+      <c r="B29" s="61" t="n"/>
       <c r="C29" s="61" t="n"/>
       <c r="D29" s="61" t="n"/>
       <c r="E29" s="61" t="n"/>
       <c r="F29" s="61" t="n"/>
+      <c r="G29" s="61" t="n"/>
+      <c r="H29" s="61" t="n"/>
+      <c r="I29" s="60" t="inlineStr">
+        <is>
+          <t>3 840 m³/h (1.0667 m³/s)</t>
+        </is>
+      </c>
+      <c r="J29" s="61" t="n"/>
+      <c r="K29" s="61" t="n"/>
+      <c r="L29" s="61" t="n"/>
+      <c r="M29" s="61" t="n"/>
+      <c r="N29" s="61" t="n"/>
+      <c r="O29" s="61" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="60" t="inlineStr">
         <is>
-          <t>Caudal total de exfiltración</t>
-        </is>
-      </c>
-      <c r="B30" s="60" t="inlineStr">
-        <is>
-          <t>3 840 m³/h (1.0667 m³/s)</t>
-        </is>
-      </c>
+          <t>Velocidad facial</t>
+        </is>
+      </c>
+      <c r="B30" s="61" t="n"/>
       <c r="C30" s="61" t="n"/>
       <c r="D30" s="61" t="n"/>
       <c r="E30" s="61" t="n"/>
       <c r="F30" s="61" t="n"/>
+      <c r="G30" s="61" t="n"/>
+      <c r="H30" s="61" t="n"/>
+      <c r="I30" s="60" t="inlineStr">
+        <is>
+          <t>3 m/s</t>
+        </is>
+      </c>
+      <c r="J30" s="61" t="n"/>
+      <c r="K30" s="61" t="n"/>
+      <c r="L30" s="61" t="n"/>
+      <c r="M30" s="61" t="n"/>
+      <c r="N30" s="61" t="n"/>
+      <c r="O30" s="61" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="60" t="inlineStr">
         <is>
-          <t>Velocidad facial</t>
-        </is>
-      </c>
-      <c r="B31" s="60" t="inlineStr">
-        <is>
-          <t>3 m/s</t>
-        </is>
-      </c>
+          <t>ΔP unitaria (cierre de orificio, C_d = 0.60, en el sitio)</t>
+        </is>
+      </c>
+      <c r="B31" s="61" t="n"/>
       <c r="C31" s="61" t="n"/>
       <c r="D31" s="61" t="n"/>
       <c r="E31" s="61" t="n"/>
       <c r="F31" s="61" t="n"/>
+      <c r="G31" s="61" t="n"/>
+      <c r="H31" s="61" t="n"/>
+      <c r="I31" s="60" t="inlineStr">
+        <is>
+          <t>11 Pa</t>
+        </is>
+      </c>
+      <c r="J31" s="61" t="n"/>
+      <c r="K31" s="61" t="n"/>
+      <c r="L31" s="61" t="n"/>
+      <c r="M31" s="61" t="n"/>
+      <c r="N31" s="61" t="n"/>
+      <c r="O31" s="61" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="60" t="inlineStr">
         <is>
-          <t>ΔP unitaria (cierre de orificio, C_d = 0.60, en el sitio)</t>
-        </is>
-      </c>
-      <c r="B32" s="60" t="inlineStr">
-        <is>
-          <t>11 Pa</t>
-        </is>
-      </c>
+          <t>ΔP equivalente a densidad estándar (ρ = 1.2 kg/m³)</t>
+        </is>
+      </c>
+      <c r="B32" s="61" t="n"/>
       <c r="C32" s="61" t="n"/>
       <c r="D32" s="61" t="n"/>
       <c r="E32" s="61" t="n"/>
       <c r="F32" s="61" t="n"/>
+      <c r="G32" s="61" t="n"/>
+      <c r="H32" s="61" t="n"/>
+      <c r="I32" s="60" t="inlineStr">
+        <is>
+          <t>15 Pa</t>
+        </is>
+      </c>
+      <c r="J32" s="61" t="n"/>
+      <c r="K32" s="61" t="n"/>
+      <c r="L32" s="61" t="n"/>
+      <c r="M32" s="61" t="n"/>
+      <c r="N32" s="61" t="n"/>
+      <c r="O32" s="61" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="60" t="inlineStr">
         <is>
-          <t>ΔP equivalente a densidad estándar (ρ = 1.2 kg/m³)</t>
-        </is>
-      </c>
-      <c r="B33" s="60" t="inlineStr">
-        <is>
-          <t>15 Pa</t>
-        </is>
-      </c>
+          <t>Densidad del aire de diseño</t>
+        </is>
+      </c>
+      <c r="B33" s="61" t="n"/>
       <c r="C33" s="61" t="n"/>
       <c r="D33" s="61" t="n"/>
       <c r="E33" s="61" t="n"/>
       <c r="F33" s="61" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="60" t="inlineStr">
-        <is>
-          <t>Densidad del aire de diseño</t>
-        </is>
-      </c>
-      <c r="B34" s="60" t="inlineStr">
+      <c r="G33" s="61" t="n"/>
+      <c r="H33" s="61" t="n"/>
+      <c r="I33" s="60" t="inlineStr">
         <is>
           <t>0.88 kg/m³ (2 558 msnm, 74.1 kPa)</t>
         </is>
       </c>
-      <c r="C34" s="61" t="n"/>
-      <c r="D34" s="61" t="n"/>
-      <c r="E34" s="61" t="n"/>
-      <c r="F34" s="61" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="63" t="inlineStr">
+      <c r="J33" s="61" t="n"/>
+      <c r="K33" s="61" t="n"/>
+      <c r="L33" s="61" t="n"/>
+      <c r="M33" s="61" t="n"/>
+      <c r="N33" s="61" t="n"/>
+      <c r="O33" s="61" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="63" t="inlineStr">
         <is>
           <t>2.1. Nota de contexto: la configuración sin damper de alivio (rejillas a 4 m/s) solo alcanzaría 19.6 Pa de presurización a esta altitud; cerrar el balance a 25 Pa sin damper requeriría un área total de 0.236 m² (0.079 m² por rejilla ≈ 280×281 mm a 4.5 m/s). El sistema adoptado conserva las tres rejillas de 353×336 mm y cierra el balance con el damper barométrico (componente obligatorio; ver HD-INST-001 e informe_investigacion.md §3.2.4).</t>
         </is>
       </c>
     </row>
+    <row r="36"/>
     <row r="37"/>
     <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
+    <row r="40">
+      <c r="A40" s="62" t="inlineStr">
+        <is>
+          <t>3. Construcción y áreas netas</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="64" t="inlineStr">
+        <is>
+          <t>Tabla 2. Especificación constructiva.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="59" t="inlineStr">
+        <is>
+          <t>Característica</t>
+        </is>
+      </c>
+      <c r="B42" s="59" t="n"/>
+      <c r="C42" s="59" t="n"/>
+      <c r="D42" s="59" t="n"/>
+      <c r="E42" s="59" t="n"/>
+      <c r="F42" s="59" t="n"/>
+      <c r="G42" s="59" t="n"/>
+      <c r="H42" s="59" t="n"/>
+      <c r="I42" s="59" t="inlineStr">
+        <is>
+          <t>Especificación</t>
+        </is>
+      </c>
+      <c r="J42" s="59" t="n"/>
+      <c r="K42" s="59" t="n"/>
+      <c r="L42" s="59" t="n"/>
+      <c r="M42" s="59" t="n"/>
+      <c r="N42" s="59" t="n"/>
+      <c r="O42" s="59" t="n"/>
+    </row>
     <row r="43">
-      <c r="A43" s="62" t="inlineStr">
-        <is>
-          <t>3. Construcción y áreas netas</t>
-        </is>
-      </c>
+      <c r="A43" s="60" t="inlineStr">
+        <is>
+          <t>Tipo de núcleo</t>
+        </is>
+      </c>
+      <c r="B43" s="61" t="n"/>
+      <c r="C43" s="61" t="n"/>
+      <c r="D43" s="61" t="n"/>
+      <c r="E43" s="61" t="n"/>
+      <c r="F43" s="61" t="n"/>
+      <c r="G43" s="61" t="n"/>
+      <c r="H43" s="61" t="n"/>
+      <c r="I43" s="60" t="inlineStr">
+        <is>
+          <t>Eggcrate (panal) ½×½×½ in (12.7 mm), máxima área libre</t>
+        </is>
+      </c>
+      <c r="J43" s="61" t="n"/>
+      <c r="K43" s="61" t="n"/>
+      <c r="L43" s="61" t="n"/>
+      <c r="M43" s="61" t="n"/>
+      <c r="N43" s="61" t="n"/>
+      <c r="O43" s="61" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="64" t="inlineStr">
-        <is>
-          <t>Tabla 2. Especificación constructiva.</t>
-        </is>
-      </c>
+      <c r="A44" s="60" t="inlineStr">
+        <is>
+          <t>Área libre del núcleo</t>
+        </is>
+      </c>
+      <c r="B44" s="61" t="n"/>
+      <c r="C44" s="61" t="n"/>
+      <c r="D44" s="61" t="n"/>
+      <c r="E44" s="61" t="n"/>
+      <c r="F44" s="61" t="n"/>
+      <c r="G44" s="61" t="n"/>
+      <c r="H44" s="61" t="n"/>
+      <c r="I44" s="60" t="inlineStr">
+        <is>
+          <t>≥ 90 % (cifra repetida en catálogos del tipo; Airfoil RC-FCR5 (https://airfoil.com.au/product/removable-core-fixing-clip-eggcrate-grille-rc-fcr5/), consulta 2026-07-23)</t>
+        </is>
+      </c>
+      <c r="J44" s="61" t="n"/>
+      <c r="K44" s="61" t="n"/>
+      <c r="L44" s="61" t="n"/>
+      <c r="M44" s="61" t="n"/>
+      <c r="N44" s="61" t="n"/>
+      <c r="O44" s="61" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="59" t="inlineStr">
-        <is>
-          <t>Característica</t>
-        </is>
-      </c>
-      <c r="B45" s="59" t="inlineStr">
-        <is>
-          <t>Especificación</t>
-        </is>
-      </c>
-      <c r="C45" s="59" t="n"/>
-      <c r="D45" s="59" t="n"/>
-      <c r="E45" s="59" t="n"/>
-      <c r="F45" s="59" t="n"/>
+      <c r="A45" s="60" t="inlineStr">
+        <is>
+          <t>Malla anti-insectos</t>
+        </is>
+      </c>
+      <c r="B45" s="61" t="n"/>
+      <c r="C45" s="61" t="n"/>
+      <c r="D45" s="61" t="n"/>
+      <c r="E45" s="61" t="n"/>
+      <c r="F45" s="61" t="n"/>
+      <c r="G45" s="61" t="n"/>
+      <c r="H45" s="61" t="n"/>
+      <c r="I45" s="60" t="inlineStr">
+        <is>
+          <t>Tejido 18×18, abertura ≈1 mm, alambre 0.45 mm, área abierta ≥ 48 % (tabla Industrial Metal Mesh (https://www.industrialmetalmesh.com/sale-54819921-micron-304-316l-stainless-steel-wire-mesh-screen-filter-mesh.html), consulta 2026-07-23); excluye insectos comunes</t>
+        </is>
+      </c>
+      <c r="J45" s="61" t="n"/>
+      <c r="K45" s="61" t="n"/>
+      <c r="L45" s="61" t="n"/>
+      <c r="M45" s="61" t="n"/>
+      <c r="N45" s="61" t="n"/>
+      <c r="O45" s="61" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="60" t="inlineStr">
         <is>
-          <t>Tipo de núcleo</t>
-        </is>
-      </c>
-      <c r="B46" s="60" t="inlineStr">
-        <is>
-          <t>Eggcrate (panal) ½×½×½ in (12.7 mm), máxima área libre</t>
-        </is>
-      </c>
+          <t>Área neta combinada (núcleo + malla)</t>
+        </is>
+      </c>
+      <c r="B46" s="61" t="n"/>
       <c r="C46" s="61" t="n"/>
       <c r="D46" s="61" t="n"/>
       <c r="E46" s="61" t="n"/>
       <c r="F46" s="61" t="n"/>
+      <c r="G46" s="61" t="n"/>
+      <c r="H46" s="61" t="n"/>
+      <c r="I46" s="60" t="inlineStr">
+        <is>
+          <t>≈ 45 % del área facial (dato típico: 0.90 × 0.50)</t>
+        </is>
+      </c>
+      <c r="J46" s="61" t="n"/>
+      <c r="K46" s="61" t="n"/>
+      <c r="L46" s="61" t="n"/>
+      <c r="M46" s="61" t="n"/>
+      <c r="N46" s="61" t="n"/>
+      <c r="O46" s="61" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="60" t="inlineStr">
         <is>
-          <t>Área libre del núcleo</t>
-        </is>
-      </c>
-      <c r="B47" s="60" t="inlineStr">
-        <is>
-          <t>≥ 90 % (cifra repetida en catálogos del tipo; Airfoil RC-FCR5 (https://airfoil.com.au/product/removable-core-fixing-clip-eggcrate-grille-rc-fcr5/), consulta 2026-07-23)</t>
-        </is>
-      </c>
+          <t>Material de la rejilla</t>
+        </is>
+      </c>
+      <c r="B47" s="61" t="n"/>
       <c r="C47" s="61" t="n"/>
       <c r="D47" s="61" t="n"/>
       <c r="E47" s="61" t="n"/>
       <c r="F47" s="61" t="n"/>
+      <c r="G47" s="61" t="n"/>
+      <c r="H47" s="61" t="n"/>
+      <c r="I47" s="60" t="inlineStr">
+        <is>
+          <t>Inox 316L (primera opción) o aluminio anodizado 6063-T5 (alternativa)</t>
+        </is>
+      </c>
+      <c r="J47" s="61" t="n"/>
+      <c r="K47" s="61" t="n"/>
+      <c r="L47" s="61" t="n"/>
+      <c r="M47" s="61" t="n"/>
+      <c r="N47" s="61" t="n"/>
+      <c r="O47" s="61" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="60" t="inlineStr">
         <is>
-          <t>Malla anti-insectos</t>
-        </is>
-      </c>
-      <c r="B48" s="60" t="inlineStr">
-        <is>
-          <t>Tejido 18×18, abertura ≈1 mm, alambre 0.45 mm, área abierta ≥ 48 % (tabla Industrial Metal Mesh (https://www.industrialmetalmesh.com/sale-54819921-micron-304-316l-stainless-steel-wire-mesh-screen-filter-mesh.html), consulta 2026-07-23); excluye insectos comunes</t>
-        </is>
-      </c>
+          <t>Material de la malla</t>
+        </is>
+      </c>
+      <c r="B48" s="61" t="n"/>
       <c r="C48" s="61" t="n"/>
       <c r="D48" s="61" t="n"/>
       <c r="E48" s="61" t="n"/>
       <c r="F48" s="61" t="n"/>
+      <c r="G48" s="61" t="n"/>
+      <c r="H48" s="61" t="n"/>
+      <c r="I48" s="60" t="inlineStr">
+        <is>
+          <t>Inox 316</t>
+        </is>
+      </c>
+      <c r="J48" s="61" t="n"/>
+      <c r="K48" s="61" t="n"/>
+      <c r="L48" s="61" t="n"/>
+      <c r="M48" s="61" t="n"/>
+      <c r="N48" s="61" t="n"/>
+      <c r="O48" s="61" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="60" t="inlineStr">
         <is>
-          <t>Área neta combinada (núcleo + malla)</t>
-        </is>
-      </c>
-      <c r="B49" s="60" t="inlineStr">
-        <is>
-          <t>≈ 45 % del área facial (dato típico: 0.90 × 0.50)</t>
-        </is>
-      </c>
+          <t>Montaje de la malla</t>
+        </is>
+      </c>
+      <c r="B49" s="61" t="n"/>
       <c r="C49" s="61" t="n"/>
       <c r="D49" s="61" t="n"/>
       <c r="E49" s="61" t="n"/>
       <c r="F49" s="61" t="n"/>
+      <c r="G49" s="61" t="n"/>
+      <c r="H49" s="61" t="n"/>
+      <c r="I49" s="60" t="inlineStr">
+        <is>
+          <t>Marco desmontable para limpieza periódica</t>
+        </is>
+      </c>
+      <c r="J49" s="61" t="n"/>
+      <c r="K49" s="61" t="n"/>
+      <c r="L49" s="61" t="n"/>
+      <c r="M49" s="61" t="n"/>
+      <c r="N49" s="61" t="n"/>
+      <c r="O49" s="61" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="60" t="inlineStr">
         <is>
-          <t>Material de la rejilla</t>
-        </is>
-      </c>
-      <c r="B50" s="60" t="inlineStr">
-        <is>
-          <t>Inox 316L (primera opción) o aluminio anodizado 6063-T5 (alternativa)</t>
-        </is>
-      </c>
+          <t>Par galvánico</t>
+        </is>
+      </c>
+      <c r="B50" s="61" t="n"/>
       <c r="C50" s="61" t="n"/>
       <c r="D50" s="61" t="n"/>
       <c r="E50" s="61" t="n"/>
       <c r="F50" s="61" t="n"/>
+      <c r="G50" s="61" t="n"/>
+      <c r="H50" s="61" t="n"/>
+      <c r="I50" s="60" t="inlineStr">
+        <is>
+          <t>Si se combina marco de aluminio con malla inox, aislamiento dieléctrico (dato típico de ingeniería)</t>
+        </is>
+      </c>
+      <c r="J50" s="61" t="n"/>
+      <c r="K50" s="61" t="n"/>
+      <c r="L50" s="61" t="n"/>
+      <c r="M50" s="61" t="n"/>
+      <c r="N50" s="61" t="n"/>
+      <c r="O50" s="61" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="60" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
-        </is>
-      </c>
-      <c r="B51" s="60" t="inlineStr">
-        <is>
-          <t>Inox 316</t>
-        </is>
-      </c>
+          <t>Ensayo de desempeño</t>
+        </is>
+      </c>
+      <c r="B51" s="61" t="n"/>
       <c r="C51" s="61" t="n"/>
       <c r="D51" s="61" t="n"/>
       <c r="E51" s="61" t="n"/>
       <c r="F51" s="61" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="60" t="inlineStr">
-        <is>
-          <t>Montaje de la malla</t>
-        </is>
-      </c>
-      <c r="B52" s="60" t="inlineStr">
-        <is>
-          <t>Marco desmontable para limpieza periódica</t>
-        </is>
-      </c>
-      <c r="C52" s="61" t="n"/>
-      <c r="D52" s="61" t="n"/>
-      <c r="E52" s="61" t="n"/>
-      <c r="F52" s="61" t="n"/>
+      <c r="G51" s="61" t="n"/>
+      <c r="H51" s="61" t="n"/>
+      <c r="I51" s="60" t="inlineStr">
+        <is>
+          <t>ASHRAE 70 (medición de rejillas)</t>
+        </is>
+      </c>
+      <c r="J51" s="61" t="n"/>
+      <c r="K51" s="61" t="n"/>
+      <c r="L51" s="61" t="n"/>
+      <c r="M51" s="61" t="n"/>
+      <c r="N51" s="61" t="n"/>
+      <c r="O51" s="61" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="60" t="inlineStr">
-        <is>
-          <t>Par galvánico</t>
-        </is>
-      </c>
-      <c r="B53" s="60" t="inlineStr">
-        <is>
-          <t>Si se combina marco de aluminio con malla inox, aislamiento dieléctrico (dato típico de ingeniería)</t>
-        </is>
-      </c>
-      <c r="C53" s="61" t="n"/>
-      <c r="D53" s="61" t="n"/>
-      <c r="E53" s="61" t="n"/>
-      <c r="F53" s="61" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="60" t="inlineStr">
-        <is>
-          <t>Ensayo de desempeño</t>
-        </is>
-      </c>
-      <c r="B54" s="60" t="inlineStr">
-        <is>
-          <t>ASHRAE 70 (medición de rejillas)</t>
-        </is>
-      </c>
-      <c r="C54" s="61" t="n"/>
-      <c r="D54" s="61" t="n"/>
-      <c r="E54" s="61" t="n"/>
-      <c r="F54" s="61" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="63" t="inlineStr">
+      <c r="A53" s="63" t="inlineStr">
         <is>
           <t>3.1. La malla domina la pérdida del conjunto; el dimensionamiento por área neta combinada y la ΔP calculada por cierre de orificio (11 Pa) deben verificarse contra el área efectiva (Ak) del fabricante seleccionado (por confirmar con proveedor).</t>
         </is>
       </c>
     </row>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="57">
+      <c r="A57" s="62" t="inlineStr">
+        <is>
+          <t>4. Candidatos comerciales</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="64" t="inlineStr">
+        <is>
+          <t>Tabla 3. Candidatos (consulta 2026-07-23).</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="59" t="inlineStr">
+        <is>
+          <t>Producto</t>
+        </is>
+      </c>
+      <c r="B59" s="59" t="n"/>
+      <c r="C59" s="59" t="n"/>
+      <c r="D59" s="59" t="inlineStr">
+        <is>
+          <t>Tipo / material</t>
+        </is>
+      </c>
+      <c r="E59" s="59" t="n"/>
+      <c r="F59" s="59" t="n"/>
+      <c r="G59" s="59" t="inlineStr">
+        <is>
+          <t>Pros</t>
+        </is>
+      </c>
+      <c r="H59" s="59" t="n"/>
+      <c r="I59" s="59" t="n"/>
+      <c r="J59" s="59" t="inlineStr">
+        <is>
+          <t>Contras</t>
+        </is>
+      </c>
+      <c r="K59" s="59" t="n"/>
+      <c r="L59" s="59" t="n"/>
+      <c r="M59" s="59" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="N59" s="59" t="n"/>
+      <c r="O59" s="59" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="60" t="inlineStr">
+        <is>
+          <t>Titus 50F / 50R</t>
+        </is>
+      </c>
+      <c r="B60" s="61" t="n"/>
+      <c r="C60" s="61" t="n"/>
+      <c r="D60" s="60" t="inlineStr">
+        <is>
+          <t>Eggcrate ½ in; aluminio, con versión íntegramente inox de fábrica</t>
+        </is>
+      </c>
+      <c r="E60" s="61" t="n"/>
+      <c r="F60" s="61" t="n"/>
+      <c r="G60" s="60" t="inlineStr">
+        <is>
+          <t>«Highest free area of any return grille»; única opción inox de catálogo</t>
+        </is>
+      </c>
+      <c r="H60" s="61" t="n"/>
+      <c r="I60" s="61" t="n"/>
+      <c r="J60" s="60" t="inlineStr">
+        <is>
+          <t>Importación; tamaño 353×336 por pedido</t>
+        </is>
+      </c>
+      <c r="K60" s="61" t="n"/>
+      <c r="L60" s="61" t="n"/>
+      <c r="M60" s="60" t="inlineStr">
+        <is>
+          <t>Titus 50F (PDF) (https://www.titus-hvac.com/file/1228/50F_50Rrprod_specialized_2017.pdf)</t>
+        </is>
+      </c>
+      <c r="N60" s="61" t="n"/>
+      <c r="O60" s="61" t="n"/>
+    </row>
     <row r="61">
-      <c r="A61" s="62" t="inlineStr">
-        <is>
-          <t>4. Candidatos comerciales</t>
-        </is>
-      </c>
+      <c r="A61" s="60" t="inlineStr">
+        <is>
+          <t>Krueger EGC5</t>
+        </is>
+      </c>
+      <c r="B61" s="61" t="n"/>
+      <c r="C61" s="61" t="n"/>
+      <c r="D61" s="60" t="inlineStr">
+        <is>
+          <t>Eggcrate ½ in; aluminio</t>
+        </is>
+      </c>
+      <c r="E61" s="61" t="n"/>
+      <c r="F61" s="61" t="n"/>
+      <c r="G61" s="60" t="inlineStr">
+        <is>
+          <t>Amplia gama de tamaños (6×4 in a 96×96 in)</t>
+        </is>
+      </c>
+      <c r="H61" s="61" t="n"/>
+      <c r="I61" s="61" t="n"/>
+      <c r="J61" s="60" t="inlineStr">
+        <is>
+          <t>Sin ejecución inox</t>
+        </is>
+      </c>
+      <c r="K61" s="61" t="n"/>
+      <c r="L61" s="61" t="n"/>
+      <c r="M61" s="60" t="inlineStr">
+        <is>
+          <t>Krueger EGC5 (https://www.krueger-hvac.com/Catalog%20Home/Grilles/Grilles%20-%20Return/EGC5)</t>
+        </is>
+      </c>
+      <c r="N61" s="61" t="n"/>
+      <c r="O61" s="61" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="64" t="inlineStr">
-        <is>
-          <t>Tabla 3. Candidatos (consulta 2026-07-23).</t>
-        </is>
-      </c>
+      <c r="A62" s="60" t="inlineStr">
+        <is>
+          <t>ProAire S.A.S (Bogotá)</t>
+        </is>
+      </c>
+      <c r="B62" s="61" t="n"/>
+      <c r="C62" s="61" t="n"/>
+      <c r="D62" s="60" t="inlineStr">
+        <is>
+          <t>Fabricación a medida con corte láser, inox 316</t>
+        </is>
+      </c>
+      <c r="E62" s="61" t="n"/>
+      <c r="F62" s="61" t="n"/>
+      <c r="G62" s="60" t="inlineStr">
+        <is>
+          <t>Medida exacta 353×336 y ejecución inox 316L local; vía recomendada</t>
+        </is>
+      </c>
+      <c r="H62" s="61" t="n"/>
+      <c r="I62" s="61" t="n"/>
+      <c r="J62" s="60" t="inlineStr">
+        <is>
+          <t>Submittal y Ak por confirmar con proveedor</t>
+        </is>
+      </c>
+      <c r="K62" s="61" t="n"/>
+      <c r="L62" s="61" t="n"/>
+      <c r="M62" s="60" t="inlineStr">
+        <is>
+          <t>proairecolombia.com (https://www.proairecolombia.com/productos/rejillas-y-difusores.html)</t>
+        </is>
+      </c>
+      <c r="N62" s="61" t="n"/>
+      <c r="O62" s="61" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="59" t="inlineStr">
-        <is>
-          <t>Producto</t>
-        </is>
-      </c>
-      <c r="B63" s="59" t="inlineStr">
-        <is>
-          <t>Tipo / material</t>
-        </is>
-      </c>
-      <c r="C63" s="59" t="inlineStr">
-        <is>
-          <t>Pros</t>
-        </is>
-      </c>
-      <c r="D63" s="59" t="inlineStr">
-        <is>
-          <t>Contras</t>
-        </is>
-      </c>
-      <c r="E63" s="59" t="inlineStr">
-        <is>
-          <t>Fuente</t>
-        </is>
-      </c>
-      <c r="F63" s="59" t="n"/>
+      <c r="A63" s="60" t="inlineStr">
+        <is>
+          <t>Laminaire (Colombia)</t>
+        </is>
+      </c>
+      <c r="B63" s="61" t="n"/>
+      <c r="C63" s="61" t="n"/>
+      <c r="D63" s="60" t="inlineStr">
+        <is>
+          <t>Rejillas y difusores en aluminio a pedido</t>
+        </is>
+      </c>
+      <c r="E63" s="61" t="n"/>
+      <c r="F63" s="61" t="n"/>
+      <c r="G63" s="60" t="inlineStr">
+        <is>
+          <t>Fabricación local con software de selección; marco para malla a pedido</t>
+        </is>
+      </c>
+      <c r="H63" s="61" t="n"/>
+      <c r="I63" s="61" t="n"/>
+      <c r="J63" s="60" t="inlineStr">
+        <is>
+          <t>Confirmar ejecución inox</t>
+        </is>
+      </c>
+      <c r="K63" s="61" t="n"/>
+      <c r="L63" s="61" t="n"/>
+      <c r="M63" s="60" t="inlineStr">
+        <is>
+          <t>laminaire.net (https://laminaire.net/)</t>
+        </is>
+      </c>
+      <c r="N63" s="61" t="n"/>
+      <c r="O63" s="61" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="60" t="inlineStr">
         <is>
-          <t>Titus 50F / 50R</t>
-        </is>
-      </c>
-      <c r="B64" s="60" t="inlineStr">
-        <is>
-          <t>Eggcrate ½ in; aluminio, con versión íntegramente inox de fábrica</t>
-        </is>
-      </c>
-      <c r="C64" s="60" t="inlineStr">
-        <is>
-          <t>«Highest free area of any return grille»; única opción inox de catálogo</t>
-        </is>
-      </c>
+          <t>CL Ingeniería (Bogotá)</t>
+        </is>
+      </c>
+      <c r="B64" s="61" t="n"/>
+      <c r="C64" s="61" t="n"/>
       <c r="D64" s="60" t="inlineStr">
         <is>
-          <t>Importación; tamaño 353×336 por pedido</t>
-        </is>
-      </c>
-      <c r="E64" s="60" t="inlineStr">
-        <is>
-          <t>Titus 50F (PDF) (https://www.titus-hvac.com/file/1228/50F_50Rrprod_specialized_2017.pdf)</t>
-        </is>
-      </c>
+          <t>Rejillas, dampers y accesorios HVAC</t>
+        </is>
+      </c>
+      <c r="E64" s="61" t="n"/>
       <c r="F64" s="61" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="60" t="inlineStr">
-        <is>
-          <t>Krueger EGC5</t>
-        </is>
-      </c>
-      <c r="B65" s="60" t="inlineStr">
-        <is>
-          <t>Eggcrate ½ in; aluminio</t>
-        </is>
-      </c>
-      <c r="C65" s="60" t="inlineStr">
-        <is>
-          <t>Amplia gama de tamaños (6×4 in a 96×96 in)</t>
-        </is>
-      </c>
-      <c r="D65" s="60" t="inlineStr">
-        <is>
-          <t>Sin ejecución inox</t>
-        </is>
-      </c>
-      <c r="E65" s="60" t="inlineStr">
-        <is>
-          <t>Krueger EGC5 (https://www.krueger-hvac.com/Catalog%20Home/Grilles/Grilles%20-%20Return/EGC5)</t>
-        </is>
-      </c>
-      <c r="F65" s="61" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="60" t="inlineStr">
-        <is>
-          <t>ProAire S.A.S (Bogotá)</t>
-        </is>
-      </c>
-      <c r="B66" s="60" t="inlineStr">
-        <is>
-          <t>Fabricación a medida con corte láser, inox 316</t>
-        </is>
-      </c>
-      <c r="C66" s="60" t="inlineStr">
-        <is>
-          <t>Medida exacta 353×336 y ejecución inox 316L local; vía recomendada</t>
-        </is>
-      </c>
-      <c r="D66" s="60" t="inlineStr">
-        <is>
-          <t>Submittal y Ak por confirmar con proveedor</t>
-        </is>
-      </c>
-      <c r="E66" s="60" t="inlineStr">
-        <is>
-          <t>proairecolombia.com (https://www.proairecolombia.com/productos/rejillas-y-difusores.html)</t>
-        </is>
-      </c>
-      <c r="F66" s="61" t="n"/>
+      <c r="G64" s="60" t="inlineStr">
+        <is>
+          <t>Canal local adicional</t>
+        </is>
+      </c>
+      <c r="H64" s="61" t="n"/>
+      <c r="I64" s="61" t="n"/>
+      <c r="J64" s="60" t="inlineStr">
+        <is>
+          <t>Catálogo genérico</t>
+        </is>
+      </c>
+      <c r="K64" s="61" t="n"/>
+      <c r="L64" s="61" t="n"/>
+      <c r="M64" s="60" t="inlineStr">
+        <is>
+          <t>clingenieria.co (https://clingenieria.co/)</t>
+        </is>
+      </c>
+      <c r="N64" s="61" t="n"/>
+      <c r="O64" s="61" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="60" t="inlineStr">
-        <is>
-          <t>Laminaire (Colombia)</t>
-        </is>
-      </c>
-      <c r="B67" s="60" t="inlineStr">
-        <is>
-          <t>Rejillas y difusores en aluminio a pedido</t>
-        </is>
-      </c>
-      <c r="C67" s="60" t="inlineStr">
-        <is>
-          <t>Fabricación local con software de selección; marco para malla a pedido</t>
-        </is>
-      </c>
-      <c r="D67" s="60" t="inlineStr">
-        <is>
-          <t>Confirmar ejecución inox</t>
-        </is>
-      </c>
-      <c r="E67" s="60" t="inlineStr">
-        <is>
-          <t>laminaire.net (https://laminaire.net/)</t>
-        </is>
-      </c>
-      <c r="F67" s="61" t="n"/>
+      <c r="A67" s="62" t="inlineStr">
+        <is>
+          <t>5. Instalación</t>
+        </is>
+      </c>
     </row>
     <row r="68">
-      <c r="A68" s="60" t="inlineStr">
-        <is>
-          <t>CL Ingeniería (Bogotá)</t>
-        </is>
-      </c>
-      <c r="B68" s="60" t="inlineStr">
-        <is>
-          <t>Rejillas, dampers y accesorios HVAC</t>
-        </is>
-      </c>
-      <c r="C68" s="60" t="inlineStr">
-        <is>
-          <t>Canal local adicional</t>
-        </is>
-      </c>
-      <c r="D68" s="60" t="inlineStr">
-        <is>
-          <t>Catálogo genérico</t>
-        </is>
-      </c>
-      <c r="E68" s="60" t="inlineStr">
-        <is>
-          <t>clingenieria.co (https://clingenieria.co/)</t>
-        </is>
-      </c>
-      <c r="F68" s="61" t="n"/>
-    </row>
+      <c r="A68" s="63" t="inlineStr">
+        <is>
+          <t>5.1. Montaje a ras de muro exterior con marco perimetral sellado con silicona RTV neutra (compatible con hipoclorito; Chemical Resistance of RTV Silicone Sealants (PDF) (https://irp.cdn-website.com/63168859/files/uploaded/Chemical%20Resistance%20of%20RTV%20Silicone%20Sealants%20Chart.pdf), consulta 2026-07-23) y ferretería inox 316 (A4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="69"/>
+    <row r="70"/>
     <row r="71">
-      <c r="A71" s="62" t="inlineStr">
-        <is>
-          <t>5. Instalación</t>
+      <c r="A71" s="63" t="inlineStr">
+        <is>
+          <t>5.2. Las bocas exteriores se orientan preferentemente a sotavento respecto de las fuentes de cloro de la planta.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="63" t="inlineStr">
         <is>
-          <t>5.1. Montaje a ras de muro exterior con marco perimetral sellado con silicona RTV neutra (compatible con hipoclorito; Chemical Resistance of RTV Silicone Sealants (PDF) (https://irp.cdn-website.com/63168859/files/uploaded/Chemical%20Resistance%20of%20RTV%20Silicone%20Sealants%20Chart.pdf), consulta 2026-07-23) y ferretería inox 316 (A4). 5.2. Las bocas exteriores se orientan preferentemente a sotavento respecto de las fuentes de cloro de la planta. 5.3. Programa de limpieza de la malla según carga de polvo observada en comisionamiento (dato típico de operación).</t>
-        </is>
-      </c>
-    </row>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
+          <t>5.3. Programa de limpieza de la malla según carga de polvo observada en comisionamiento (dato típico de operación).</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="62" t="inlineStr">
+        <is>
+          <t>6. Normas aplicables</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="63" t="inlineStr">
+        <is>
+          <t>6.1. ASHRAE 70 (método de ensayo y reporte de desempeño de rejillas); correlación de área libre para transferencia de aire según Building Science BA-0006 (https://buildingscience.com/sites/default/files/migrate/pdf/BA-0006_Discuss_transfer_grilles.pdf) (consulta 2026-07-23); ISO 12944 / NACE-AMPP para la selección de materiales en el ambiente clorado.</t>
+        </is>
+      </c>
+    </row>
     <row r="76"/>
     <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="81">
-      <c r="A81" s="62" t="inlineStr">
-        <is>
-          <t>6. Normas aplicables</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="63" t="inlineStr">
-        <is>
-          <t>6.1. ASHRAE 70 (método de ensayo y reporte de desempeño de rejillas); correlación de área libre para transferencia de aire según Building Science BA-0006 (https://buildingscience.com/sites/default/files/migrate/pdf/BA-0006_Discuss_transfer_grilles.pdf) (consulta 2026-07-23); ISO 12944 / NACE-AMPP para la selección de materiales en el ambiente clorado.</t>
-        </is>
-      </c>
-    </row>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
   </sheetData>
-  <mergeCells count="53">
-    <mergeCell ref="A82:F86"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B54:F54"/>
-    <mergeCell ref="E68:F68"/>
+  <mergeCells count="101">
+    <mergeCell ref="I44:O44"/>
+    <mergeCell ref="G62:I62"/>
+    <mergeCell ref="A49:H49"/>
+    <mergeCell ref="A19:O22"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="A35:O38"/>
+    <mergeCell ref="I30:O30"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="I46:O46"/>
+    <mergeCell ref="C2:L3"/>
+    <mergeCell ref="G63:I63"/>
+    <mergeCell ref="A50:H50"/>
+    <mergeCell ref="A63:C63"/>
+    <mergeCell ref="J61:L61"/>
+    <mergeCell ref="A32:H32"/>
+    <mergeCell ref="I32:O32"/>
+    <mergeCell ref="A40:O40"/>
+    <mergeCell ref="A67:O67"/>
+    <mergeCell ref="A24:O24"/>
+    <mergeCell ref="A29:H29"/>
+    <mergeCell ref="I43:O43"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A44:H44"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="B1:B5"/>
+    <mergeCell ref="I33:O33"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A51:H51"/>
+    <mergeCell ref="I10:O10"/>
+    <mergeCell ref="A18:O18"/>
+    <mergeCell ref="I50:O50"/>
+    <mergeCell ref="J63:L63"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="G64:I64"/>
+    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="I11:O11"/>
+    <mergeCell ref="I45:O45"/>
+    <mergeCell ref="A42:H42"/>
+    <mergeCell ref="D60:F60"/>
+    <mergeCell ref="A47:H47"/>
+    <mergeCell ref="I47:O47"/>
+    <mergeCell ref="I28:O28"/>
+    <mergeCell ref="A60:C60"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="J60:L60"/>
+    <mergeCell ref="A28:H28"/>
     <mergeCell ref="N4:O4"/>
-    <mergeCell ref="E67:F67"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="B46:F46"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="E64:F64"/>
-    <mergeCell ref="B52:F52"/>
-    <mergeCell ref="A72:F79"/>
-    <mergeCell ref="A71:F71"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="N3:O3"/>
-    <mergeCell ref="B48:F48"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="E63:F63"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="N5:O5"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="E65:F65"/>
-    <mergeCell ref="A43:F43"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="A81:F81"/>
-    <mergeCell ref="C2:L3"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="A36:F41"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="A56:F59"/>
+    <mergeCell ref="A48:H48"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="I51:O51"/>
+    <mergeCell ref="A74:O74"/>
+    <mergeCell ref="M61:O61"/>
+    <mergeCell ref="A62:C62"/>
+    <mergeCell ref="M62:O62"/>
+    <mergeCell ref="I49:O49"/>
+    <mergeCell ref="I27:O27"/>
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="D59:F59"/>
+    <mergeCell ref="A53:O55"/>
+    <mergeCell ref="A59:C59"/>
+    <mergeCell ref="A9:O9"/>
     <mergeCell ref="A1:A5"/>
     <mergeCell ref="C1:L1"/>
-    <mergeCell ref="B49:F49"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="A19:F23"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="M59:O59"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="J59:L59"/>
+    <mergeCell ref="I12:O12"/>
+    <mergeCell ref="M60:O60"/>
+    <mergeCell ref="I14:O14"/>
+    <mergeCell ref="I48:O48"/>
+    <mergeCell ref="D61:F61"/>
+    <mergeCell ref="I29:O29"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A45:H45"/>
+    <mergeCell ref="A75:O77"/>
+    <mergeCell ref="I13:O13"/>
+    <mergeCell ref="A57:O57"/>
+    <mergeCell ref="I31:O31"/>
+    <mergeCell ref="D62:F62"/>
+    <mergeCell ref="I15:O15"/>
+    <mergeCell ref="A46:H46"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="D64:F64"/>
+    <mergeCell ref="J62:L62"/>
+    <mergeCell ref="M63:O63"/>
+    <mergeCell ref="G60:I60"/>
+    <mergeCell ref="I26:O26"/>
+    <mergeCell ref="A68:O70"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="G59:I59"/>
+    <mergeCell ref="J64:L64"/>
+    <mergeCell ref="D63:F63"/>
     <mergeCell ref="C4:L6"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="B51:F51"/>
-    <mergeCell ref="A61:F61"/>
-    <mergeCell ref="B45:F45"/>
-    <mergeCell ref="E66:F66"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="B50:F50"/>
-    <mergeCell ref="B1:B5"/>
-    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="A43:H43"/>
+    <mergeCell ref="G61:I61"/>
+    <mergeCell ref="M64:O64"/>
+    <mergeCell ref="I42:O42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/build/dts/P2437-HV-DTS-003 REV0.xlsx
+++ b/build/dts/P2437-HV-DTS-003 REV0.xlsx
@@ -3223,7 +3223,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O77"/>
+  <dimension ref="A1:O76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30.61328125" customWidth="1" min="1" max="1"/>
@@ -3445,7 +3445,7 @@
     <row r="9">
       <c r="A9" s="58" t="inlineStr">
         <is>
-          <t>Hoja de datos: rejillas de exfiltración con malla anti-insectos</t>
+          <t>Hoja de datos: rejillas de descarga con malla anti-insectos</t>
         </is>
       </c>
     </row>
@@ -3514,7 +3514,7 @@
       <c r="H12" s="61" t="n"/>
       <c r="I12" s="60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" s="61" t="n"/>
@@ -3539,7 +3539,7 @@
       <c r="H13" s="61" t="n"/>
       <c r="I13" s="60" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="J13" s="61" t="n"/>
@@ -3589,7 +3589,7 @@
       <c r="H15" s="61" t="n"/>
       <c r="I15" s="60" t="inlineStr">
         <is>
-          <t>REJ-001 a REJ-003 (rejillas de exfiltración)</t>
+          <t>REJ-001 a REJ-003 (rejillas de descarga)</t>
         </is>
       </c>
       <c r="J15" s="61" t="n"/>
@@ -3609,7 +3609,7 @@
     <row r="19">
       <c r="A19" s="63" t="inlineStr">
         <is>
-          <t>1.1. Descarga del caudal de exfiltración del laboratorio presurizado (+25 Pa) hacia el exterior, a través de la envolvente del recinto. Las rejillas son la trayectoria de salida permanente del aire y, con el sistema detenido, una vía potencial de ingreso: por ello incorporan malla anti-insectos. Ambiente exterior corrosivo (atmósfera clorada de planta de hipoclorito de calcio).</t>
+          <t>1.1. Descarga libre a la atmósfera del caudal de ventilación del laboratorio, a través de la envolvente del recinto. Las rejillas son la trayectoria de salida permanente del aire y, con el sistema detenido, una vía potencial de ingreso: por ello incorporan malla anti-insectos. Ambiente exterior corrosivo (atmósfera clorada de planta de hipoclorito de calcio).</t>
         </is>
       </c>
     </row>
@@ -3708,7 +3708,7 @@
     <row r="29">
       <c r="A29" s="60" t="inlineStr">
         <is>
-          <t>Caudal total de exfiltración</t>
+          <t>Caudal total de descarga</t>
         </is>
       </c>
       <c r="B29" s="61" t="n"/>
@@ -3833,56 +3833,80 @@
     <row r="35">
       <c r="A35" s="63" t="inlineStr">
         <is>
-          <t>2.1. Nota de contexto: la configuración sin damper de alivio (rejillas a 4 m/s) solo alcanzaría 19.6 Pa de presurización a esta altitud; cerrar el balance a 25 Pa sin damper requeriría un área total de 0.236 m² (0.079 m² por rejilla ≈ 280×281 mm a 4.5 m/s). El sistema adoptado conserva las tres rejillas de 353×336 mm y cierra el balance con el damper barométrico (componente obligatorio; ver HD-INST-001 e informe_investigacion.md §3.2.4).</t>
+          <t>2.1. Nota de contexto: la ΔP unitaria de 11 Pa (cierre de orificio, C_d = 0.60, a 3 m/s) es la pérdida de descarga libre a la atmósfera y se suma a la caída de presión de la etapa filtrante para definir el punto de trabajo del ventilador; no existe consigna de presión interior que sostener.</t>
         </is>
       </c>
     </row>
     <row r="36"/>
     <row r="37"/>
-    <row r="38"/>
+    <row r="39">
+      <c r="A39" s="62" t="inlineStr">
+        <is>
+          <t>3. Construcción y áreas netas</t>
+        </is>
+      </c>
+    </row>
     <row r="40">
-      <c r="A40" s="62" t="inlineStr">
-        <is>
-          <t>3. Construcción y áreas netas</t>
+      <c r="A40" s="64" t="inlineStr">
+        <is>
+          <t>Tabla 2. Especificación constructiva.</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="64" t="inlineStr">
-        <is>
-          <t>Tabla 2. Especificación constructiva.</t>
-        </is>
-      </c>
+      <c r="A41" s="59" t="inlineStr">
+        <is>
+          <t>Característica</t>
+        </is>
+      </c>
+      <c r="B41" s="59" t="n"/>
+      <c r="C41" s="59" t="n"/>
+      <c r="D41" s="59" t="n"/>
+      <c r="E41" s="59" t="n"/>
+      <c r="F41" s="59" t="n"/>
+      <c r="G41" s="59" t="n"/>
+      <c r="H41" s="59" t="n"/>
+      <c r="I41" s="59" t="inlineStr">
+        <is>
+          <t>Especificación</t>
+        </is>
+      </c>
+      <c r="J41" s="59" t="n"/>
+      <c r="K41" s="59" t="n"/>
+      <c r="L41" s="59" t="n"/>
+      <c r="M41" s="59" t="n"/>
+      <c r="N41" s="59" t="n"/>
+      <c r="O41" s="59" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="59" t="inlineStr">
-        <is>
-          <t>Característica</t>
-        </is>
-      </c>
-      <c r="B42" s="59" t="n"/>
-      <c r="C42" s="59" t="n"/>
-      <c r="D42" s="59" t="n"/>
-      <c r="E42" s="59" t="n"/>
-      <c r="F42" s="59" t="n"/>
-      <c r="G42" s="59" t="n"/>
-      <c r="H42" s="59" t="n"/>
-      <c r="I42" s="59" t="inlineStr">
-        <is>
-          <t>Especificación</t>
-        </is>
-      </c>
-      <c r="J42" s="59" t="n"/>
-      <c r="K42" s="59" t="n"/>
-      <c r="L42" s="59" t="n"/>
-      <c r="M42" s="59" t="n"/>
-      <c r="N42" s="59" t="n"/>
-      <c r="O42" s="59" t="n"/>
+      <c r="A42" s="60" t="inlineStr">
+        <is>
+          <t>Tipo de núcleo</t>
+        </is>
+      </c>
+      <c r="B42" s="61" t="n"/>
+      <c r="C42" s="61" t="n"/>
+      <c r="D42" s="61" t="n"/>
+      <c r="E42" s="61" t="n"/>
+      <c r="F42" s="61" t="n"/>
+      <c r="G42" s="61" t="n"/>
+      <c r="H42" s="61" t="n"/>
+      <c r="I42" s="60" t="inlineStr">
+        <is>
+          <t>Eggcrate (panal) ½×½×½ in (12.7 mm), máxima área libre</t>
+        </is>
+      </c>
+      <c r="J42" s="61" t="n"/>
+      <c r="K42" s="61" t="n"/>
+      <c r="L42" s="61" t="n"/>
+      <c r="M42" s="61" t="n"/>
+      <c r="N42" s="61" t="n"/>
+      <c r="O42" s="61" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="60" t="inlineStr">
         <is>
-          <t>Tipo de núcleo</t>
+          <t>Área libre del núcleo</t>
         </is>
       </c>
       <c r="B43" s="61" t="n"/>
@@ -3894,7 +3918,7 @@
       <c r="H43" s="61" t="n"/>
       <c r="I43" s="60" t="inlineStr">
         <is>
-          <t>Eggcrate (panal) ½×½×½ in (12.7 mm), máxima área libre</t>
+          <t>≥ 90 % (cifra repetida en catálogos del tipo; Airfoil RC-FCR5 (https://airfoil.com.au/product/removable-core-fixing-clip-eggcrate-grille-rc-fcr5/), consulta 2026-07-23)</t>
         </is>
       </c>
       <c r="J43" s="61" t="n"/>
@@ -3907,7 +3931,7 @@
     <row r="44">
       <c r="A44" s="60" t="inlineStr">
         <is>
-          <t>Área libre del núcleo</t>
+          <t>Malla anti-insectos</t>
         </is>
       </c>
       <c r="B44" s="61" t="n"/>
@@ -3919,7 +3943,7 @@
       <c r="H44" s="61" t="n"/>
       <c r="I44" s="60" t="inlineStr">
         <is>
-          <t>≥ 90 % (cifra repetida en catálogos del tipo; Airfoil RC-FCR5 (https://airfoil.com.au/product/removable-core-fixing-clip-eggcrate-grille-rc-fcr5/), consulta 2026-07-23)</t>
+          <t>Tejido 18×18, abertura ≈1 mm, alambre 0.45 mm, área abierta ≥ 48 % (tabla Industrial Metal Mesh (https://www.industrialmetalmesh.com/sale-54819921-micron-304-316l-stainless-steel-wire-mesh-screen-filter-mesh.html), consulta 2026-07-23); excluye insectos comunes</t>
         </is>
       </c>
       <c r="J44" s="61" t="n"/>
@@ -3932,7 +3956,7 @@
     <row r="45">
       <c r="A45" s="60" t="inlineStr">
         <is>
-          <t>Malla anti-insectos</t>
+          <t>Área neta combinada (núcleo + malla)</t>
         </is>
       </c>
       <c r="B45" s="61" t="n"/>
@@ -3944,7 +3968,7 @@
       <c r="H45" s="61" t="n"/>
       <c r="I45" s="60" t="inlineStr">
         <is>
-          <t>Tejido 18×18, abertura ≈1 mm, alambre 0.45 mm, área abierta ≥ 48 % (tabla Industrial Metal Mesh (https://www.industrialmetalmesh.com/sale-54819921-micron-304-316l-stainless-steel-wire-mesh-screen-filter-mesh.html), consulta 2026-07-23); excluye insectos comunes</t>
+          <t>≈ 45 % del área facial (dato típico: 0.90 × 0.50)</t>
         </is>
       </c>
       <c r="J45" s="61" t="n"/>
@@ -3957,7 +3981,7 @@
     <row r="46">
       <c r="A46" s="60" t="inlineStr">
         <is>
-          <t>Área neta combinada (núcleo + malla)</t>
+          <t>Material de la rejilla</t>
         </is>
       </c>
       <c r="B46" s="61" t="n"/>
@@ -3969,7 +3993,7 @@
       <c r="H46" s="61" t="n"/>
       <c r="I46" s="60" t="inlineStr">
         <is>
-          <t>≈ 45 % del área facial (dato típico: 0.90 × 0.50)</t>
+          <t>Inox 316L (primera opción) o aluminio anodizado 6063-T5 (alternativa)</t>
         </is>
       </c>
       <c r="J46" s="61" t="n"/>
@@ -3982,7 +4006,7 @@
     <row r="47">
       <c r="A47" s="60" t="inlineStr">
         <is>
-          <t>Material de la rejilla</t>
+          <t>Material de la malla</t>
         </is>
       </c>
       <c r="B47" s="61" t="n"/>
@@ -3994,7 +4018,7 @@
       <c r="H47" s="61" t="n"/>
       <c r="I47" s="60" t="inlineStr">
         <is>
-          <t>Inox 316L (primera opción) o aluminio anodizado 6063-T5 (alternativa)</t>
+          <t>Inox 316</t>
         </is>
       </c>
       <c r="J47" s="61" t="n"/>
@@ -4007,7 +4031,7 @@
     <row r="48">
       <c r="A48" s="60" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Montaje de la malla</t>
         </is>
       </c>
       <c r="B48" s="61" t="n"/>
@@ -4019,7 +4043,7 @@
       <c r="H48" s="61" t="n"/>
       <c r="I48" s="60" t="inlineStr">
         <is>
-          <t>Inox 316</t>
+          <t>Marco desmontable para limpieza periódica</t>
         </is>
       </c>
       <c r="J48" s="61" t="n"/>
@@ -4032,7 +4056,7 @@
     <row r="49">
       <c r="A49" s="60" t="inlineStr">
         <is>
-          <t>Montaje de la malla</t>
+          <t>Par galvánico</t>
         </is>
       </c>
       <c r="B49" s="61" t="n"/>
@@ -4044,7 +4068,7 @@
       <c r="H49" s="61" t="n"/>
       <c r="I49" s="60" t="inlineStr">
         <is>
-          <t>Marco desmontable para limpieza periódica</t>
+          <t>Si se combina marco de aluminio con malla inox, aislamiento dieléctrico (dato típico de ingeniería)</t>
         </is>
       </c>
       <c r="J49" s="61" t="n"/>
@@ -4057,7 +4081,7 @@
     <row r="50">
       <c r="A50" s="60" t="inlineStr">
         <is>
-          <t>Par galvánico</t>
+          <t>Ensayo de desempeño</t>
         </is>
       </c>
       <c r="B50" s="61" t="n"/>
@@ -4069,7 +4093,7 @@
       <c r="H50" s="61" t="n"/>
       <c r="I50" s="60" t="inlineStr">
         <is>
-          <t>Si se combina marco de aluminio con malla inox, aislamiento dieléctrico (dato típico de ingeniería)</t>
+          <t>ASHRAE 70 (medición de rejillas)</t>
         </is>
       </c>
       <c r="J50" s="61" t="n"/>
@@ -4079,123 +4103,135 @@
       <c r="N50" s="61" t="n"/>
       <c r="O50" s="61" t="n"/>
     </row>
-    <row r="51">
-      <c r="A51" s="60" t="inlineStr">
-        <is>
-          <t>Ensayo de desempeño</t>
-        </is>
-      </c>
-      <c r="B51" s="61" t="n"/>
-      <c r="C51" s="61" t="n"/>
-      <c r="D51" s="61" t="n"/>
-      <c r="E51" s="61" t="n"/>
-      <c r="F51" s="61" t="n"/>
-      <c r="G51" s="61" t="n"/>
-      <c r="H51" s="61" t="n"/>
-      <c r="I51" s="60" t="inlineStr">
-        <is>
-          <t>ASHRAE 70 (medición de rejillas)</t>
-        </is>
-      </c>
-      <c r="J51" s="61" t="n"/>
-      <c r="K51" s="61" t="n"/>
-      <c r="L51" s="61" t="n"/>
-      <c r="M51" s="61" t="n"/>
-      <c r="N51" s="61" t="n"/>
-      <c r="O51" s="61" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="63" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="63" t="inlineStr">
         <is>
           <t>3.1. La malla domina la pérdida del conjunto; el dimensionamiento por área neta combinada y la ΔP calculada por cierre de orificio (11 Pa) deben verificarse contra el área efectiva (Ak) del fabricante seleccionado (por confirmar con proveedor).</t>
         </is>
       </c>
     </row>
+    <row r="53"/>
     <row r="54"/>
-    <row r="55"/>
+    <row r="56">
+      <c r="A56" s="62" t="inlineStr">
+        <is>
+          <t>4. Candidatos comerciales</t>
+        </is>
+      </c>
+    </row>
     <row r="57">
-      <c r="A57" s="62" t="inlineStr">
-        <is>
-          <t>4. Candidatos comerciales</t>
+      <c r="A57" s="64" t="inlineStr">
+        <is>
+          <t>Tabla 3. Candidatos (consulta 2026-07-23).</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="64" t="inlineStr">
-        <is>
-          <t>Tabla 3. Candidatos (consulta 2026-07-23).</t>
-        </is>
-      </c>
+      <c r="A58" s="59" t="inlineStr">
+        <is>
+          <t>Producto</t>
+        </is>
+      </c>
+      <c r="B58" s="59" t="n"/>
+      <c r="C58" s="59" t="n"/>
+      <c r="D58" s="59" t="inlineStr">
+        <is>
+          <t>Tipo / material</t>
+        </is>
+      </c>
+      <c r="E58" s="59" t="n"/>
+      <c r="F58" s="59" t="n"/>
+      <c r="G58" s="59" t="inlineStr">
+        <is>
+          <t>Pros</t>
+        </is>
+      </c>
+      <c r="H58" s="59" t="n"/>
+      <c r="I58" s="59" t="n"/>
+      <c r="J58" s="59" t="inlineStr">
+        <is>
+          <t>Contras</t>
+        </is>
+      </c>
+      <c r="K58" s="59" t="n"/>
+      <c r="L58" s="59" t="n"/>
+      <c r="M58" s="59" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="N58" s="59" t="n"/>
+      <c r="O58" s="59" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="59" t="inlineStr">
-        <is>
-          <t>Producto</t>
-        </is>
-      </c>
-      <c r="B59" s="59" t="n"/>
-      <c r="C59" s="59" t="n"/>
-      <c r="D59" s="59" t="inlineStr">
-        <is>
-          <t>Tipo / material</t>
-        </is>
-      </c>
-      <c r="E59" s="59" t="n"/>
-      <c r="F59" s="59" t="n"/>
-      <c r="G59" s="59" t="inlineStr">
-        <is>
-          <t>Pros</t>
-        </is>
-      </c>
-      <c r="H59" s="59" t="n"/>
-      <c r="I59" s="59" t="n"/>
-      <c r="J59" s="59" t="inlineStr">
-        <is>
-          <t>Contras</t>
-        </is>
-      </c>
-      <c r="K59" s="59" t="n"/>
-      <c r="L59" s="59" t="n"/>
-      <c r="M59" s="59" t="inlineStr">
-        <is>
-          <t>Fuente</t>
-        </is>
-      </c>
-      <c r="N59" s="59" t="n"/>
-      <c r="O59" s="59" t="n"/>
+      <c r="A59" s="60" t="inlineStr">
+        <is>
+          <t>Titus 50F / 50R</t>
+        </is>
+      </c>
+      <c r="B59" s="61" t="n"/>
+      <c r="C59" s="61" t="n"/>
+      <c r="D59" s="60" t="inlineStr">
+        <is>
+          <t>Eggcrate ½ in; aluminio, con versión íntegramente inox de fábrica</t>
+        </is>
+      </c>
+      <c r="E59" s="61" t="n"/>
+      <c r="F59" s="61" t="n"/>
+      <c r="G59" s="60" t="inlineStr">
+        <is>
+          <t>«Highest free area of any return grille»; única opción inox de catálogo</t>
+        </is>
+      </c>
+      <c r="H59" s="61" t="n"/>
+      <c r="I59" s="61" t="n"/>
+      <c r="J59" s="60" t="inlineStr">
+        <is>
+          <t>Importación; tamaño 353×336 por pedido</t>
+        </is>
+      </c>
+      <c r="K59" s="61" t="n"/>
+      <c r="L59" s="61" t="n"/>
+      <c r="M59" s="60" t="inlineStr">
+        <is>
+          <t>Titus 50F (PDF) (https://www.titus-hvac.com/file/1228/50F_50Rrprod_specialized_2017.pdf)</t>
+        </is>
+      </c>
+      <c r="N59" s="61" t="n"/>
+      <c r="O59" s="61" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="60" t="inlineStr">
         <is>
-          <t>Titus 50F / 50R</t>
+          <t>Krueger EGC5</t>
         </is>
       </c>
       <c r="B60" s="61" t="n"/>
       <c r="C60" s="61" t="n"/>
       <c r="D60" s="60" t="inlineStr">
         <is>
-          <t>Eggcrate ½ in; aluminio, con versión íntegramente inox de fábrica</t>
+          <t>Eggcrate ½ in; aluminio</t>
         </is>
       </c>
       <c r="E60" s="61" t="n"/>
       <c r="F60" s="61" t="n"/>
       <c r="G60" s="60" t="inlineStr">
         <is>
-          <t>«Highest free area of any return grille»; única opción inox de catálogo</t>
+          <t>Amplia gama de tamaños (6×4 in a 96×96 in)</t>
         </is>
       </c>
       <c r="H60" s="61" t="n"/>
       <c r="I60" s="61" t="n"/>
       <c r="J60" s="60" t="inlineStr">
         <is>
-          <t>Importación; tamaño 353×336 por pedido</t>
+          <t>Sin ejecución inox</t>
         </is>
       </c>
       <c r="K60" s="61" t="n"/>
       <c r="L60" s="61" t="n"/>
       <c r="M60" s="60" t="inlineStr">
         <is>
-          <t>Titus 50F (PDF) (https://www.titus-hvac.com/file/1228/50F_50Rrprod_specialized_2017.pdf)</t>
+          <t>Krueger EGC5 (https://www.krueger-hvac.com/Catalog%20Home/Grilles/Grilles%20-%20Return/EGC5)</t>
         </is>
       </c>
       <c r="N60" s="61" t="n"/>
@@ -4204,35 +4240,35 @@
     <row r="61">
       <c r="A61" s="60" t="inlineStr">
         <is>
-          <t>Krueger EGC5</t>
+          <t>ProAire S.A.S (Bogotá)</t>
         </is>
       </c>
       <c r="B61" s="61" t="n"/>
       <c r="C61" s="61" t="n"/>
       <c r="D61" s="60" t="inlineStr">
         <is>
-          <t>Eggcrate ½ in; aluminio</t>
+          <t>Fabricación a medida con corte láser, inox 316</t>
         </is>
       </c>
       <c r="E61" s="61" t="n"/>
       <c r="F61" s="61" t="n"/>
       <c r="G61" s="60" t="inlineStr">
         <is>
-          <t>Amplia gama de tamaños (6×4 in a 96×96 in)</t>
+          <t>Medida exacta 353×336 y ejecución inox 316L local; vía recomendada</t>
         </is>
       </c>
       <c r="H61" s="61" t="n"/>
       <c r="I61" s="61" t="n"/>
       <c r="J61" s="60" t="inlineStr">
         <is>
-          <t>Sin ejecución inox</t>
+          <t>Submittal y Ak por confirmar con proveedor</t>
         </is>
       </c>
       <c r="K61" s="61" t="n"/>
       <c r="L61" s="61" t="n"/>
       <c r="M61" s="60" t="inlineStr">
         <is>
-          <t>Krueger EGC5 (https://www.krueger-hvac.com/Catalog%20Home/Grilles/Grilles%20-%20Return/EGC5)</t>
+          <t>proairecolombia.com (https://www.proairecolombia.com/productos/rejillas-y-difusores.html)</t>
         </is>
       </c>
       <c r="N61" s="61" t="n"/>
@@ -4241,35 +4277,35 @@
     <row r="62">
       <c r="A62" s="60" t="inlineStr">
         <is>
-          <t>ProAire S.A.S (Bogotá)</t>
+          <t>Laminaire (Colombia)</t>
         </is>
       </c>
       <c r="B62" s="61" t="n"/>
       <c r="C62" s="61" t="n"/>
       <c r="D62" s="60" t="inlineStr">
         <is>
-          <t>Fabricación a medida con corte láser, inox 316</t>
+          <t>Rejillas y difusores en aluminio a pedido</t>
         </is>
       </c>
       <c r="E62" s="61" t="n"/>
       <c r="F62" s="61" t="n"/>
       <c r="G62" s="60" t="inlineStr">
         <is>
-          <t>Medida exacta 353×336 y ejecución inox 316L local; vía recomendada</t>
+          <t>Fabricación local con software de selección; marco para malla a pedido</t>
         </is>
       </c>
       <c r="H62" s="61" t="n"/>
       <c r="I62" s="61" t="n"/>
       <c r="J62" s="60" t="inlineStr">
         <is>
-          <t>Submittal y Ak por confirmar con proveedor</t>
+          <t>Confirmar ejecución inox</t>
         </is>
       </c>
       <c r="K62" s="61" t="n"/>
       <c r="L62" s="61" t="n"/>
       <c r="M62" s="60" t="inlineStr">
         <is>
-          <t>proairecolombia.com (https://www.proairecolombia.com/productos/rejillas-y-difusores.html)</t>
+          <t>laminaire.net (https://laminaire.net/)</t>
         </is>
       </c>
       <c r="N62" s="61" t="n"/>
@@ -4278,131 +4314,94 @@
     <row r="63">
       <c r="A63" s="60" t="inlineStr">
         <is>
-          <t>Laminaire (Colombia)</t>
+          <t>CL Ingeniería (Bogotá)</t>
         </is>
       </c>
       <c r="B63" s="61" t="n"/>
       <c r="C63" s="61" t="n"/>
       <c r="D63" s="60" t="inlineStr">
         <is>
-          <t>Rejillas y difusores en aluminio a pedido</t>
+          <t>Rejillas y accesorios HVAC</t>
         </is>
       </c>
       <c r="E63" s="61" t="n"/>
       <c r="F63" s="61" t="n"/>
       <c r="G63" s="60" t="inlineStr">
         <is>
-          <t>Fabricación local con software de selección; marco para malla a pedido</t>
+          <t>Canal local adicional</t>
         </is>
       </c>
       <c r="H63" s="61" t="n"/>
       <c r="I63" s="61" t="n"/>
       <c r="J63" s="60" t="inlineStr">
         <is>
-          <t>Confirmar ejecución inox</t>
+          <t>Catálogo genérico</t>
         </is>
       </c>
       <c r="K63" s="61" t="n"/>
       <c r="L63" s="61" t="n"/>
       <c r="M63" s="60" t="inlineStr">
         <is>
-          <t>laminaire.net (https://laminaire.net/)</t>
+          <t>clingenieria.co (https://clingenieria.co/)</t>
         </is>
       </c>
       <c r="N63" s="61" t="n"/>
       <c r="O63" s="61" t="n"/>
     </row>
-    <row r="64">
-      <c r="A64" s="60" t="inlineStr">
-        <is>
-          <t>CL Ingeniería (Bogotá)</t>
-        </is>
-      </c>
-      <c r="B64" s="61" t="n"/>
-      <c r="C64" s="61" t="n"/>
-      <c r="D64" s="60" t="inlineStr">
-        <is>
-          <t>Rejillas, dampers y accesorios HVAC</t>
-        </is>
-      </c>
-      <c r="E64" s="61" t="n"/>
-      <c r="F64" s="61" t="n"/>
-      <c r="G64" s="60" t="inlineStr">
-        <is>
-          <t>Canal local adicional</t>
-        </is>
-      </c>
-      <c r="H64" s="61" t="n"/>
-      <c r="I64" s="61" t="n"/>
-      <c r="J64" s="60" t="inlineStr">
-        <is>
-          <t>Catálogo genérico</t>
-        </is>
-      </c>
-      <c r="K64" s="61" t="n"/>
-      <c r="L64" s="61" t="n"/>
-      <c r="M64" s="60" t="inlineStr">
-        <is>
-          <t>clingenieria.co (https://clingenieria.co/)</t>
-        </is>
-      </c>
-      <c r="N64" s="61" t="n"/>
-      <c r="O64" s="61" t="n"/>
+    <row r="66">
+      <c r="A66" s="62" t="inlineStr">
+        <is>
+          <t>5. Instalación</t>
+        </is>
+      </c>
     </row>
     <row r="67">
-      <c r="A67" s="62" t="inlineStr">
-        <is>
-          <t>5. Instalación</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="63" t="inlineStr">
+      <c r="A67" s="63" t="inlineStr">
         <is>
           <t>5.1. Montaje a ras de muro exterior con marco perimetral sellado con silicona RTV neutra (compatible con hipoclorito; Chemical Resistance of RTV Silicone Sealants (PDF) (https://irp.cdn-website.com/63168859/files/uploaded/Chemical%20Resistance%20of%20RTV%20Silicone%20Sealants%20Chart.pdf), consulta 2026-07-23) y ferretería inox 316 (A4).</t>
         </is>
       </c>
     </row>
+    <row r="68"/>
     <row r="69"/>
-    <row r="70"/>
+    <row r="70">
+      <c r="A70" s="63" t="inlineStr">
+        <is>
+          <t>5.2. Las bocas exteriores se orientan preferentemente a sotavento respecto de las fuentes de cloro de la planta.</t>
+        </is>
+      </c>
+    </row>
     <row r="71">
       <c r="A71" s="63" t="inlineStr">
         <is>
-          <t>5.2. Las bocas exteriores se orientan preferentemente a sotavento respecto de las fuentes de cloro de la planta.</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="63" t="inlineStr">
-        <is>
           <t>5.3. Programa de limpieza de la malla según carga de polvo observada en comisionamiento (dato típico de operación).</t>
         </is>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" s="62" t="inlineStr">
+        <is>
+          <t>6. Normas aplicables</t>
+        </is>
+      </c>
+    </row>
     <row r="74">
-      <c r="A74" s="62" t="inlineStr">
-        <is>
-          <t>6. Normas aplicables</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="63" t="inlineStr">
+      <c r="A74" s="63" t="inlineStr">
         <is>
           <t>6.1. ASHRAE 70 (método de ensayo y reporte de desempeño de rejillas); correlación de área libre para transferencia de aire según Building Science BA-0006 (https://buildingscience.com/sites/default/files/migrate/pdf/BA-0006_Discuss_transfer_grilles.pdf) (consulta 2026-07-23); ISO 12944 / NACE-AMPP para la selección de materiales en el ambiente clorado.</t>
         </is>
       </c>
     </row>
+    <row r="75"/>
     <row r="76"/>
-    <row r="77"/>
   </sheetData>
   <mergeCells count="101">
+    <mergeCell ref="A66:O66"/>
     <mergeCell ref="I44:O44"/>
     <mergeCell ref="G62:I62"/>
     <mergeCell ref="A49:H49"/>
     <mergeCell ref="A19:O22"/>
     <mergeCell ref="N3:O3"/>
-    <mergeCell ref="A35:O38"/>
     <mergeCell ref="I30:O30"/>
     <mergeCell ref="N5:O5"/>
     <mergeCell ref="I46:O46"/>
@@ -4413,9 +4412,9 @@
     <mergeCell ref="J61:L61"/>
     <mergeCell ref="A32:H32"/>
     <mergeCell ref="I32:O32"/>
-    <mergeCell ref="A40:O40"/>
-    <mergeCell ref="A67:O67"/>
+    <mergeCell ref="I41:O41"/>
     <mergeCell ref="A24:O24"/>
+    <mergeCell ref="A73:O73"/>
     <mergeCell ref="A29:H29"/>
     <mergeCell ref="I43:O43"/>
     <mergeCell ref="A13:H13"/>
@@ -4424,20 +4423,21 @@
     <mergeCell ref="B1:B5"/>
     <mergeCell ref="I33:O33"/>
     <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A51:H51"/>
     <mergeCell ref="I10:O10"/>
     <mergeCell ref="A18:O18"/>
+    <mergeCell ref="A74:O76"/>
     <mergeCell ref="I50:O50"/>
     <mergeCell ref="J63:L63"/>
     <mergeCell ref="N2:O2"/>
-    <mergeCell ref="G64:I64"/>
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="I11:O11"/>
     <mergeCell ref="I45:O45"/>
+    <mergeCell ref="A58:C58"/>
     <mergeCell ref="A42:H42"/>
     <mergeCell ref="D60:F60"/>
     <mergeCell ref="A47:H47"/>
     <mergeCell ref="I47:O47"/>
+    <mergeCell ref="M58:O58"/>
     <mergeCell ref="I28:O28"/>
     <mergeCell ref="A60:C60"/>
     <mergeCell ref="N6:O6"/>
@@ -4446,22 +4446,26 @@
     <mergeCell ref="N4:O4"/>
     <mergeCell ref="A48:H48"/>
     <mergeCell ref="A30:H30"/>
-    <mergeCell ref="I51:O51"/>
-    <mergeCell ref="A74:O74"/>
+    <mergeCell ref="A56:O56"/>
+    <mergeCell ref="G58:I58"/>
+    <mergeCell ref="D58:F58"/>
+    <mergeCell ref="A41:H41"/>
     <mergeCell ref="M61:O61"/>
     <mergeCell ref="A62:C62"/>
     <mergeCell ref="M62:O62"/>
     <mergeCell ref="I49:O49"/>
     <mergeCell ref="I27:O27"/>
     <mergeCell ref="A26:H26"/>
+    <mergeCell ref="J58:L58"/>
     <mergeCell ref="A33:H33"/>
     <mergeCell ref="D59:F59"/>
-    <mergeCell ref="A53:O55"/>
+    <mergeCell ref="A35:O37"/>
     <mergeCell ref="A59:C59"/>
     <mergeCell ref="A9:O9"/>
+    <mergeCell ref="A67:O69"/>
     <mergeCell ref="A1:A5"/>
     <mergeCell ref="C1:L1"/>
-    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="A39:O39"/>
     <mergeCell ref="M59:O59"/>
     <mergeCell ref="A61:C61"/>
     <mergeCell ref="A10:H10"/>
@@ -4474,29 +4478,24 @@
     <mergeCell ref="I29:O29"/>
     <mergeCell ref="A11:H11"/>
     <mergeCell ref="A45:H45"/>
-    <mergeCell ref="A75:O77"/>
     <mergeCell ref="I13:O13"/>
-    <mergeCell ref="A57:O57"/>
     <mergeCell ref="I31:O31"/>
     <mergeCell ref="D62:F62"/>
     <mergeCell ref="I15:O15"/>
     <mergeCell ref="A46:H46"/>
     <mergeCell ref="N1:O1"/>
     <mergeCell ref="A12:H12"/>
-    <mergeCell ref="D64:F64"/>
     <mergeCell ref="J62:L62"/>
     <mergeCell ref="M63:O63"/>
     <mergeCell ref="G60:I60"/>
     <mergeCell ref="I26:O26"/>
-    <mergeCell ref="A68:O70"/>
     <mergeCell ref="A14:H14"/>
     <mergeCell ref="G59:I59"/>
-    <mergeCell ref="J64:L64"/>
     <mergeCell ref="D63:F63"/>
+    <mergeCell ref="A52:O54"/>
     <mergeCell ref="C4:L6"/>
     <mergeCell ref="A43:H43"/>
     <mergeCell ref="G61:I61"/>
-    <mergeCell ref="M64:O64"/>
     <mergeCell ref="I42:O42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/build/dts/P2437-HV-DTS-003 REV0.xlsx
+++ b/build/dts/P2437-HV-DTS-003 REV0.xlsx
@@ -22,7 +22,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.00000000000000"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="32">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -133,28 +133,87 @@
       <sz val="16"/>
     </font>
     <font>
+      <name val="Times New Roman"/>
       <b val="1"/>
       <color rgb="001F4E78"/>
       <sz val="14"/>
     </font>
     <font>
+      <name val="Times New Roman"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
+      <name val="Times New Roman"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
       <b val="1"/>
       <color rgb="001F4E78"/>
       <sz val="12"/>
     </font>
     <font>
+      <name val="Times New Roman"/>
       <i val="1"/>
       <color rgb="00404040"/>
       <sz val="10"/>
     </font>
     <font>
+      <name val="Times New Roman"/>
       <b val="1"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <i val="1"/>
+      <color theme="1"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <color theme="1"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <color rgb="FF00B050"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <color theme="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="6">
@@ -342,7 +401,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
@@ -460,6 +519,14 @@
     <xf numFmtId="164" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -470,33 +537,74 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="1" hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="5" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1070,96 +1178,96 @@
   </cols>
   <sheetData>
     <row r="1" ht="25" customFormat="1" customHeight="1" s="2">
-      <c r="A1" s="29" t="n"/>
-      <c r="B1" s="44" t="n"/>
-      <c r="C1" s="44" t="n"/>
-      <c r="D1" s="44" t="n"/>
-      <c r="E1" s="44" t="n"/>
-      <c r="F1" s="44" t="n"/>
-      <c r="G1" s="44" t="n"/>
-      <c r="H1" s="44" t="n"/>
-      <c r="I1" s="44" t="n"/>
-      <c r="J1" s="44" t="n"/>
-      <c r="K1" s="44" t="n"/>
-      <c r="L1" s="44" t="n"/>
-      <c r="M1" s="45" t="n"/>
-      <c r="N1" s="30" t="n"/>
-      <c r="O1" s="44" t="n"/>
-      <c r="P1" s="44" t="n"/>
-      <c r="Q1" s="44" t="n"/>
-      <c r="R1" s="44" t="n"/>
-      <c r="S1" s="44" t="n"/>
-      <c r="T1" s="44" t="n"/>
-      <c r="U1" s="44" t="n"/>
-      <c r="V1" s="44" t="n"/>
-      <c r="W1" s="44" t="n"/>
-      <c r="X1" s="44" t="n"/>
-      <c r="Y1" s="45" t="n"/>
+      <c r="A1" s="44" t="n"/>
+      <c r="B1" s="45" t="n"/>
+      <c r="C1" s="45" t="n"/>
+      <c r="D1" s="45" t="n"/>
+      <c r="E1" s="45" t="n"/>
+      <c r="F1" s="45" t="n"/>
+      <c r="G1" s="45" t="n"/>
+      <c r="H1" s="45" t="n"/>
+      <c r="I1" s="45" t="n"/>
+      <c r="J1" s="45" t="n"/>
+      <c r="K1" s="45" t="n"/>
+      <c r="L1" s="45" t="n"/>
+      <c r="M1" s="46" t="n"/>
+      <c r="N1" s="47" t="n"/>
+      <c r="O1" s="45" t="n"/>
+      <c r="P1" s="48" t="n"/>
+      <c r="Q1" s="48" t="n"/>
+      <c r="R1" s="48" t="n"/>
+      <c r="S1" s="48" t="n"/>
+      <c r="T1" s="48" t="n"/>
+      <c r="U1" s="48" t="n"/>
+      <c r="V1" s="48" t="n"/>
+      <c r="W1" s="48" t="n"/>
+      <c r="X1" s="48" t="n"/>
+      <c r="Y1" s="49" t="n"/>
       <c r="Z1" s="27" t="inlineStr">
         <is>
           <t>DISEÑO DE INGENIERÍA</t>
         </is>
       </c>
-      <c r="AA1" s="44" t="n"/>
-      <c r="AB1" s="44" t="n"/>
-      <c r="AC1" s="44" t="n"/>
-      <c r="AD1" s="44" t="n"/>
-      <c r="AE1" s="44" t="n"/>
-      <c r="AF1" s="44" t="n"/>
-      <c r="AG1" s="44" t="n"/>
-      <c r="AH1" s="44" t="n"/>
-      <c r="AI1" s="44" t="n"/>
-      <c r="AJ1" s="44" t="n"/>
-      <c r="AK1" s="44" t="n"/>
-      <c r="AL1" s="44" t="n"/>
-      <c r="AM1" s="44" t="n"/>
-      <c r="AN1" s="44" t="n"/>
-      <c r="AO1" s="44" t="n"/>
-      <c r="AP1" s="44" t="n"/>
-      <c r="AQ1" s="44" t="n"/>
-      <c r="AR1" s="44" t="n"/>
-      <c r="AS1" s="44" t="n"/>
-      <c r="AT1" s="44" t="n"/>
-      <c r="AU1" s="44" t="n"/>
-      <c r="AV1" s="44" t="n"/>
-      <c r="AW1" s="44" t="n"/>
-      <c r="AX1" s="44" t="n"/>
-      <c r="AY1" s="44" t="n"/>
-      <c r="AZ1" s="44" t="n"/>
-      <c r="BA1" s="44" t="n"/>
-      <c r="BB1" s="45" t="n"/>
+      <c r="AA1" s="48" t="n"/>
+      <c r="AB1" s="48" t="n"/>
+      <c r="AC1" s="48" t="n"/>
+      <c r="AD1" s="48" t="n"/>
+      <c r="AE1" s="48" t="n"/>
+      <c r="AF1" s="48" t="n"/>
+      <c r="AG1" s="48" t="n"/>
+      <c r="AH1" s="48" t="n"/>
+      <c r="AI1" s="48" t="n"/>
+      <c r="AJ1" s="48" t="n"/>
+      <c r="AK1" s="48" t="n"/>
+      <c r="AL1" s="48" t="n"/>
+      <c r="AM1" s="48" t="n"/>
+      <c r="AN1" s="48" t="n"/>
+      <c r="AO1" s="48" t="n"/>
+      <c r="AP1" s="48" t="n"/>
+      <c r="AQ1" s="48" t="n"/>
+      <c r="AR1" s="48" t="n"/>
+      <c r="AS1" s="48" t="n"/>
+      <c r="AT1" s="48" t="n"/>
+      <c r="AU1" s="48" t="n"/>
+      <c r="AV1" s="48" t="n"/>
+      <c r="AW1" s="48" t="n"/>
+      <c r="AX1" s="48" t="n"/>
+      <c r="AY1" s="48" t="n"/>
+      <c r="AZ1" s="48" t="n"/>
+      <c r="BA1" s="48" t="n"/>
+      <c r="BB1" s="49" t="n"/>
       <c r="BC1" s="26" t="inlineStr">
         <is>
           <t>CODIGO:</t>
         </is>
       </c>
-      <c r="BD1" s="46" t="n"/>
-      <c r="BE1" s="46" t="n"/>
-      <c r="BF1" s="46" t="n"/>
-      <c r="BG1" s="46" t="n"/>
-      <c r="BH1" s="46" t="n"/>
-      <c r="BI1" s="46" t="n"/>
-      <c r="BJ1" s="46" t="n"/>
-      <c r="BK1" s="46" t="n"/>
-      <c r="BL1" s="46" t="n"/>
-      <c r="BM1" s="46" t="n"/>
-      <c r="BN1" s="47" t="n"/>
+      <c r="BD1" s="50" t="n"/>
+      <c r="BE1" s="50" t="n"/>
+      <c r="BF1" s="50" t="n"/>
+      <c r="BG1" s="50" t="n"/>
+      <c r="BH1" s="50" t="n"/>
+      <c r="BI1" s="50" t="n"/>
+      <c r="BJ1" s="50" t="n"/>
+      <c r="BK1" s="50" t="n"/>
+      <c r="BL1" s="50" t="n"/>
+      <c r="BM1" s="50" t="n"/>
+      <c r="BN1" s="51" t="n"/>
       <c r="BO1" s="25" t="inlineStr">
         <is>
           <t>P2437-HV-DTS-003</t>
         </is>
       </c>
-      <c r="BP1" s="48" t="n"/>
-      <c r="BQ1" s="48" t="n"/>
-      <c r="BR1" s="48" t="n"/>
-      <c r="BS1" s="48" t="n"/>
-      <c r="BT1" s="48" t="n"/>
-      <c r="BU1" s="48" t="n"/>
-      <c r="BV1" s="48" t="n"/>
-      <c r="BW1" s="48" t="n"/>
-      <c r="BX1" s="48" t="n"/>
-      <c r="BY1" s="48" t="n"/>
-      <c r="BZ1" s="49" t="n"/>
+      <c r="BP1" s="52" t="n"/>
+      <c r="BQ1" s="52" t="n"/>
+      <c r="BR1" s="52" t="n"/>
+      <c r="BS1" s="52" t="n"/>
+      <c r="BT1" s="52" t="n"/>
+      <c r="BU1" s="52" t="n"/>
+      <c r="BV1" s="52" t="n"/>
+      <c r="BW1" s="52" t="n"/>
+      <c r="BX1" s="52" t="n"/>
+      <c r="BY1" s="52" t="n"/>
+      <c r="BZ1" s="53" t="n"/>
       <c r="CB1" s="15" t="inlineStr">
         <is>
           <t>REVIZADO</t>
@@ -1172,71 +1280,83 @@
       </c>
     </row>
     <row r="2" ht="25" customFormat="1" customHeight="1" s="2">
-      <c r="A2" s="50" t="n"/>
-      <c r="M2" s="51" t="n"/>
-      <c r="N2" s="50" t="n"/>
-      <c r="Y2" s="51" t="n"/>
-      <c r="Z2" s="52" t="n"/>
-      <c r="AA2" s="53" t="n"/>
-      <c r="AB2" s="53" t="n"/>
-      <c r="AC2" s="53" t="n"/>
-      <c r="AD2" s="53" t="n"/>
-      <c r="AE2" s="53" t="n"/>
-      <c r="AF2" s="53" t="n"/>
-      <c r="AG2" s="53" t="n"/>
-      <c r="AH2" s="53" t="n"/>
-      <c r="AI2" s="53" t="n"/>
-      <c r="AJ2" s="53" t="n"/>
-      <c r="AK2" s="53" t="n"/>
-      <c r="AL2" s="53" t="n"/>
-      <c r="AM2" s="53" t="n"/>
-      <c r="AN2" s="53" t="n"/>
-      <c r="AO2" s="53" t="n"/>
-      <c r="AP2" s="53" t="n"/>
-      <c r="AQ2" s="53" t="n"/>
-      <c r="AR2" s="53" t="n"/>
-      <c r="AS2" s="53" t="n"/>
-      <c r="AT2" s="53" t="n"/>
-      <c r="AU2" s="53" t="n"/>
-      <c r="AV2" s="53" t="n"/>
-      <c r="AW2" s="53" t="n"/>
-      <c r="AX2" s="53" t="n"/>
-      <c r="AY2" s="53" t="n"/>
-      <c r="AZ2" s="53" t="n"/>
-      <c r="BA2" s="53" t="n"/>
-      <c r="BB2" s="54" t="n"/>
+      <c r="A2" s="54" t="n"/>
+      <c r="B2" s="55" t="n"/>
+      <c r="C2" s="55" t="n"/>
+      <c r="D2" s="55" t="n"/>
+      <c r="E2" s="55" t="n"/>
+      <c r="F2" s="55" t="n"/>
+      <c r="G2" s="55" t="n"/>
+      <c r="H2" s="55" t="n"/>
+      <c r="I2" s="55" t="n"/>
+      <c r="J2" s="55" t="n"/>
+      <c r="K2" s="55" t="n"/>
+      <c r="L2" s="55" t="n"/>
+      <c r="M2" s="56" t="n"/>
+      <c r="N2" s="54" t="n"/>
+      <c r="O2" s="55" t="n"/>
+      <c r="Y2" s="57" t="n"/>
+      <c r="Z2" s="58" t="n"/>
+      <c r="AA2" s="59" t="n"/>
+      <c r="AB2" s="59" t="n"/>
+      <c r="AC2" s="59" t="n"/>
+      <c r="AD2" s="59" t="n"/>
+      <c r="AE2" s="59" t="n"/>
+      <c r="AF2" s="59" t="n"/>
+      <c r="AG2" s="59" t="n"/>
+      <c r="AH2" s="59" t="n"/>
+      <c r="AI2" s="59" t="n"/>
+      <c r="AJ2" s="59" t="n"/>
+      <c r="AK2" s="59" t="n"/>
+      <c r="AL2" s="59" t="n"/>
+      <c r="AM2" s="59" t="n"/>
+      <c r="AN2" s="59" t="n"/>
+      <c r="AO2" s="59" t="n"/>
+      <c r="AP2" s="59" t="n"/>
+      <c r="AQ2" s="59" t="n"/>
+      <c r="AR2" s="59" t="n"/>
+      <c r="AS2" s="59" t="n"/>
+      <c r="AT2" s="59" t="n"/>
+      <c r="AU2" s="59" t="n"/>
+      <c r="AV2" s="59" t="n"/>
+      <c r="AW2" s="59" t="n"/>
+      <c r="AX2" s="59" t="n"/>
+      <c r="AY2" s="59" t="n"/>
+      <c r="AZ2" s="59" t="n"/>
+      <c r="BA2" s="59" t="n"/>
+      <c r="BB2" s="60" t="n"/>
       <c r="BC2" s="26" t="inlineStr">
         <is>
           <t>REVISION:</t>
         </is>
       </c>
-      <c r="BD2" s="46" t="n"/>
-      <c r="BE2" s="46" t="n"/>
-      <c r="BF2" s="46" t="n"/>
-      <c r="BG2" s="46" t="n"/>
-      <c r="BH2" s="46" t="n"/>
-      <c r="BI2" s="46" t="n"/>
-      <c r="BJ2" s="46" t="n"/>
-      <c r="BK2" s="46" t="n"/>
-      <c r="BL2" s="46" t="n"/>
-      <c r="BM2" s="46" t="n"/>
-      <c r="BN2" s="47" t="n"/>
+      <c r="BD2" s="50" t="n"/>
+      <c r="BE2" s="50" t="n"/>
+      <c r="BF2" s="50" t="n"/>
+      <c r="BG2" s="50" t="n"/>
+      <c r="BH2" s="50" t="n"/>
+      <c r="BI2" s="50" t="n"/>
+      <c r="BJ2" s="50" t="n"/>
+      <c r="BK2" s="50" t="n"/>
+      <c r="BL2" s="50" t="n"/>
+      <c r="BM2" s="50" t="n"/>
+      <c r="BN2" s="51" t="n"/>
       <c r="BO2" s="25" t="inlineStr">
         <is>
           <t>CERO (0)</t>
         </is>
       </c>
-      <c r="BP2" s="48" t="n"/>
-      <c r="BQ2" s="48" t="n"/>
-      <c r="BR2" s="48" t="n"/>
-      <c r="BS2" s="48" t="n"/>
-      <c r="BT2" s="48" t="n"/>
-      <c r="BU2" s="48" t="n"/>
-      <c r="BV2" s="48" t="n"/>
-      <c r="BW2" s="48" t="n"/>
-      <c r="BX2" s="48" t="n"/>
-      <c r="BY2" s="48" t="n"/>
-      <c r="BZ2" s="49" t="n"/>
+      <c r="BP2" s="52" t="n"/>
+      <c r="BQ2" s="52" t="n"/>
+      <c r="BR2" s="52" t="n"/>
+      <c r="BS2" s="52" t="n"/>
+      <c r="BT2" s="52" t="n"/>
+      <c r="BU2" s="52" t="n"/>
+      <c r="BV2" s="52" t="n"/>
+      <c r="BW2" s="52" t="n"/>
+      <c r="BX2" s="52" t="n"/>
+      <c r="BY2" s="52" t="n"/>
+      <c r="BZ2" s="53" t="n"/>
       <c r="CB2" s="15" t="inlineStr">
         <is>
           <t>APROBADO</t>
@@ -1249,341 +1369,371 @@
       </c>
     </row>
     <row r="3" ht="25" customFormat="1" customHeight="1" s="2">
-      <c r="A3" s="50" t="n"/>
-      <c r="M3" s="51" t="n"/>
-      <c r="N3" s="50" t="n"/>
-      <c r="Y3" s="51" t="n"/>
+      <c r="A3" s="54" t="n"/>
+      <c r="B3" s="55" t="n"/>
+      <c r="C3" s="55" t="n"/>
+      <c r="D3" s="55" t="n"/>
+      <c r="E3" s="55" t="n"/>
+      <c r="F3" s="55" t="n"/>
+      <c r="G3" s="55" t="n"/>
+      <c r="H3" s="55" t="n"/>
+      <c r="I3" s="55" t="n"/>
+      <c r="J3" s="55" t="n"/>
+      <c r="K3" s="55" t="n"/>
+      <c r="L3" s="55" t="n"/>
+      <c r="M3" s="56" t="n"/>
+      <c r="N3" s="54" t="n"/>
+      <c r="O3" s="55" t="n"/>
+      <c r="Y3" s="57" t="n"/>
       <c r="Z3" s="27" t="inlineStr">
         <is>
           <t>SISTEMA HVAC LABORATORIO BRINSA</t>
         </is>
       </c>
-      <c r="AA3" s="44" t="n"/>
-      <c r="AB3" s="44" t="n"/>
-      <c r="AC3" s="44" t="n"/>
-      <c r="AD3" s="44" t="n"/>
-      <c r="AE3" s="44" t="n"/>
-      <c r="AF3" s="44" t="n"/>
-      <c r="AG3" s="44" t="n"/>
-      <c r="AH3" s="44" t="n"/>
-      <c r="AI3" s="44" t="n"/>
-      <c r="AJ3" s="44" t="n"/>
-      <c r="AK3" s="44" t="n"/>
-      <c r="AL3" s="44" t="n"/>
-      <c r="AM3" s="44" t="n"/>
-      <c r="AN3" s="44" t="n"/>
-      <c r="AO3" s="44" t="n"/>
-      <c r="AP3" s="44" t="n"/>
-      <c r="AQ3" s="44" t="n"/>
-      <c r="AR3" s="44" t="n"/>
-      <c r="AS3" s="44" t="n"/>
-      <c r="AT3" s="44" t="n"/>
-      <c r="AU3" s="44" t="n"/>
-      <c r="AV3" s="44" t="n"/>
-      <c r="AW3" s="44" t="n"/>
-      <c r="AX3" s="44" t="n"/>
-      <c r="AY3" s="44" t="n"/>
-      <c r="AZ3" s="44" t="n"/>
-      <c r="BA3" s="44" t="n"/>
-      <c r="BB3" s="45" t="n"/>
+      <c r="AA3" s="48" t="n"/>
+      <c r="AB3" s="48" t="n"/>
+      <c r="AC3" s="48" t="n"/>
+      <c r="AD3" s="48" t="n"/>
+      <c r="AE3" s="48" t="n"/>
+      <c r="AF3" s="48" t="n"/>
+      <c r="AG3" s="48" t="n"/>
+      <c r="AH3" s="48" t="n"/>
+      <c r="AI3" s="48" t="n"/>
+      <c r="AJ3" s="48" t="n"/>
+      <c r="AK3" s="48" t="n"/>
+      <c r="AL3" s="48" t="n"/>
+      <c r="AM3" s="48" t="n"/>
+      <c r="AN3" s="48" t="n"/>
+      <c r="AO3" s="48" t="n"/>
+      <c r="AP3" s="48" t="n"/>
+      <c r="AQ3" s="48" t="n"/>
+      <c r="AR3" s="48" t="n"/>
+      <c r="AS3" s="48" t="n"/>
+      <c r="AT3" s="48" t="n"/>
+      <c r="AU3" s="48" t="n"/>
+      <c r="AV3" s="48" t="n"/>
+      <c r="AW3" s="48" t="n"/>
+      <c r="AX3" s="48" t="n"/>
+      <c r="AY3" s="48" t="n"/>
+      <c r="AZ3" s="48" t="n"/>
+      <c r="BA3" s="48" t="n"/>
+      <c r="BB3" s="49" t="n"/>
       <c r="BC3" s="26" t="inlineStr">
         <is>
           <t>FECHA:</t>
         </is>
       </c>
-      <c r="BD3" s="46" t="n"/>
-      <c r="BE3" s="46" t="n"/>
-      <c r="BF3" s="46" t="n"/>
-      <c r="BG3" s="46" t="n"/>
-      <c r="BH3" s="46" t="n"/>
-      <c r="BI3" s="46" t="n"/>
-      <c r="BJ3" s="46" t="n"/>
-      <c r="BK3" s="46" t="n"/>
-      <c r="BL3" s="46" t="n"/>
-      <c r="BM3" s="46" t="n"/>
-      <c r="BN3" s="47" t="n"/>
+      <c r="BD3" s="50" t="n"/>
+      <c r="BE3" s="50" t="n"/>
+      <c r="BF3" s="50" t="n"/>
+      <c r="BG3" s="50" t="n"/>
+      <c r="BH3" s="50" t="n"/>
+      <c r="BI3" s="50" t="n"/>
+      <c r="BJ3" s="50" t="n"/>
+      <c r="BK3" s="50" t="n"/>
+      <c r="BL3" s="50" t="n"/>
+      <c r="BM3" s="50" t="n"/>
+      <c r="BN3" s="51" t="n"/>
       <c r="BO3" s="25" t="inlineStr">
         <is>
           <t>JULIO 23 DEL 2026</t>
         </is>
       </c>
-      <c r="BP3" s="48" t="n"/>
-      <c r="BQ3" s="48" t="n"/>
-      <c r="BR3" s="48" t="n"/>
-      <c r="BS3" s="48" t="n"/>
-      <c r="BT3" s="48" t="n"/>
-      <c r="BU3" s="48" t="n"/>
-      <c r="BV3" s="48" t="n"/>
-      <c r="BW3" s="48" t="n"/>
-      <c r="BX3" s="48" t="n"/>
-      <c r="BY3" s="48" t="n"/>
-      <c r="BZ3" s="49" t="n"/>
+      <c r="BP3" s="52" t="n"/>
+      <c r="BQ3" s="52" t="n"/>
+      <c r="BR3" s="52" t="n"/>
+      <c r="BS3" s="52" t="n"/>
+      <c r="BT3" s="52" t="n"/>
+      <c r="BU3" s="52" t="n"/>
+      <c r="BV3" s="52" t="n"/>
+      <c r="BW3" s="52" t="n"/>
+      <c r="BX3" s="52" t="n"/>
+      <c r="BY3" s="52" t="n"/>
+      <c r="BZ3" s="53" t="n"/>
     </row>
     <row r="4" ht="25" customFormat="1" customHeight="1" s="2">
-      <c r="A4" s="50" t="n"/>
-      <c r="M4" s="51" t="n"/>
-      <c r="N4" s="50" t="n"/>
-      <c r="Y4" s="51" t="n"/>
-      <c r="Z4" s="52" t="n"/>
-      <c r="AA4" s="53" t="n"/>
-      <c r="AB4" s="53" t="n"/>
-      <c r="AC4" s="53" t="n"/>
-      <c r="AD4" s="53" t="n"/>
-      <c r="AE4" s="53" t="n"/>
-      <c r="AF4" s="53" t="n"/>
-      <c r="AG4" s="53" t="n"/>
-      <c r="AH4" s="53" t="n"/>
-      <c r="AI4" s="53" t="n"/>
-      <c r="AJ4" s="53" t="n"/>
-      <c r="AK4" s="53" t="n"/>
-      <c r="AL4" s="53" t="n"/>
-      <c r="AM4" s="53" t="n"/>
-      <c r="AN4" s="53" t="n"/>
-      <c r="AO4" s="53" t="n"/>
-      <c r="AP4" s="53" t="n"/>
-      <c r="AQ4" s="53" t="n"/>
-      <c r="AR4" s="53" t="n"/>
-      <c r="AS4" s="53" t="n"/>
-      <c r="AT4" s="53" t="n"/>
-      <c r="AU4" s="53" t="n"/>
-      <c r="AV4" s="53" t="n"/>
-      <c r="AW4" s="53" t="n"/>
-      <c r="AX4" s="53" t="n"/>
-      <c r="AY4" s="53" t="n"/>
-      <c r="AZ4" s="53" t="n"/>
-      <c r="BA4" s="53" t="n"/>
-      <c r="BB4" s="54" t="n"/>
+      <c r="A4" s="54" t="n"/>
+      <c r="B4" s="55" t="n"/>
+      <c r="C4" s="55" t="n"/>
+      <c r="D4" s="55" t="n"/>
+      <c r="E4" s="55" t="n"/>
+      <c r="F4" s="55" t="n"/>
+      <c r="G4" s="55" t="n"/>
+      <c r="H4" s="55" t="n"/>
+      <c r="I4" s="55" t="n"/>
+      <c r="J4" s="55" t="n"/>
+      <c r="K4" s="55" t="n"/>
+      <c r="L4" s="55" t="n"/>
+      <c r="M4" s="56" t="n"/>
+      <c r="N4" s="54" t="n"/>
+      <c r="O4" s="55" t="n"/>
+      <c r="Y4" s="57" t="n"/>
+      <c r="Z4" s="58" t="n"/>
+      <c r="AA4" s="59" t="n"/>
+      <c r="AB4" s="59" t="n"/>
+      <c r="AC4" s="59" t="n"/>
+      <c r="AD4" s="59" t="n"/>
+      <c r="AE4" s="59" t="n"/>
+      <c r="AF4" s="59" t="n"/>
+      <c r="AG4" s="59" t="n"/>
+      <c r="AH4" s="59" t="n"/>
+      <c r="AI4" s="59" t="n"/>
+      <c r="AJ4" s="59" t="n"/>
+      <c r="AK4" s="59" t="n"/>
+      <c r="AL4" s="59" t="n"/>
+      <c r="AM4" s="59" t="n"/>
+      <c r="AN4" s="59" t="n"/>
+      <c r="AO4" s="59" t="n"/>
+      <c r="AP4" s="59" t="n"/>
+      <c r="AQ4" s="59" t="n"/>
+      <c r="AR4" s="59" t="n"/>
+      <c r="AS4" s="59" t="n"/>
+      <c r="AT4" s="59" t="n"/>
+      <c r="AU4" s="59" t="n"/>
+      <c r="AV4" s="59" t="n"/>
+      <c r="AW4" s="59" t="n"/>
+      <c r="AX4" s="59" t="n"/>
+      <c r="AY4" s="59" t="n"/>
+      <c r="AZ4" s="59" t="n"/>
+      <c r="BA4" s="59" t="n"/>
+      <c r="BB4" s="60" t="n"/>
       <c r="BC4" s="26" t="inlineStr">
         <is>
           <t>ELABORO:</t>
         </is>
       </c>
-      <c r="BD4" s="46" t="n"/>
-      <c r="BE4" s="46" t="n"/>
-      <c r="BF4" s="46" t="n"/>
-      <c r="BG4" s="46" t="n"/>
-      <c r="BH4" s="46" t="n"/>
-      <c r="BI4" s="46" t="n"/>
-      <c r="BJ4" s="46" t="n"/>
-      <c r="BK4" s="46" t="n"/>
-      <c r="BL4" s="46" t="n"/>
-      <c r="BM4" s="46" t="n"/>
-      <c r="BN4" s="47" t="n"/>
+      <c r="BD4" s="50" t="n"/>
+      <c r="BE4" s="50" t="n"/>
+      <c r="BF4" s="50" t="n"/>
+      <c r="BG4" s="50" t="n"/>
+      <c r="BH4" s="50" t="n"/>
+      <c r="BI4" s="50" t="n"/>
+      <c r="BJ4" s="50" t="n"/>
+      <c r="BK4" s="50" t="n"/>
+      <c r="BL4" s="50" t="n"/>
+      <c r="BM4" s="50" t="n"/>
+      <c r="BN4" s="51" t="n"/>
       <c r="BO4" s="25" t="inlineStr">
         <is>
           <t>J.ARBOLEDA</t>
         </is>
       </c>
-      <c r="BP4" s="48" t="n"/>
-      <c r="BQ4" s="48" t="n"/>
-      <c r="BR4" s="48" t="n"/>
-      <c r="BS4" s="48" t="n"/>
-      <c r="BT4" s="48" t="n"/>
-      <c r="BU4" s="48" t="n"/>
-      <c r="BV4" s="48" t="n"/>
-      <c r="BW4" s="48" t="n"/>
-      <c r="BX4" s="48" t="n"/>
-      <c r="BY4" s="48" t="n"/>
-      <c r="BZ4" s="49" t="n"/>
+      <c r="BP4" s="52" t="n"/>
+      <c r="BQ4" s="52" t="n"/>
+      <c r="BR4" s="52" t="n"/>
+      <c r="BS4" s="52" t="n"/>
+      <c r="BT4" s="52" t="n"/>
+      <c r="BU4" s="52" t="n"/>
+      <c r="BV4" s="52" t="n"/>
+      <c r="BW4" s="52" t="n"/>
+      <c r="BX4" s="52" t="n"/>
+      <c r="BY4" s="52" t="n"/>
+      <c r="BZ4" s="53" t="n"/>
     </row>
     <row r="5" ht="25" customFormat="1" customHeight="1" s="2">
-      <c r="A5" s="52" t="n"/>
-      <c r="B5" s="53" t="n"/>
-      <c r="C5" s="53" t="n"/>
-      <c r="D5" s="53" t="n"/>
-      <c r="E5" s="53" t="n"/>
-      <c r="F5" s="53" t="n"/>
-      <c r="G5" s="53" t="n"/>
-      <c r="H5" s="53" t="n"/>
-      <c r="I5" s="53" t="n"/>
-      <c r="J5" s="53" t="n"/>
-      <c r="K5" s="53" t="n"/>
-      <c r="L5" s="53" t="n"/>
-      <c r="M5" s="54" t="n"/>
-      <c r="N5" s="52" t="n"/>
-      <c r="O5" s="53" t="n"/>
-      <c r="P5" s="53" t="n"/>
-      <c r="Q5" s="53" t="n"/>
-      <c r="R5" s="53" t="n"/>
-      <c r="S5" s="53" t="n"/>
-      <c r="T5" s="53" t="n"/>
-      <c r="U5" s="53" t="n"/>
-      <c r="V5" s="53" t="n"/>
-      <c r="W5" s="53" t="n"/>
-      <c r="X5" s="53" t="n"/>
-      <c r="Y5" s="54" t="n"/>
+      <c r="A5" s="61" t="n"/>
+      <c r="B5" s="62" t="n"/>
+      <c r="C5" s="62" t="n"/>
+      <c r="D5" s="62" t="n"/>
+      <c r="E5" s="62" t="n"/>
+      <c r="F5" s="62" t="n"/>
+      <c r="G5" s="62" t="n"/>
+      <c r="H5" s="62" t="n"/>
+      <c r="I5" s="62" t="n"/>
+      <c r="J5" s="62" t="n"/>
+      <c r="K5" s="62" t="n"/>
+      <c r="L5" s="62" t="n"/>
+      <c r="M5" s="63" t="n"/>
+      <c r="N5" s="61" t="n"/>
+      <c r="O5" s="62" t="n"/>
+      <c r="P5" s="59" t="n"/>
+      <c r="Q5" s="59" t="n"/>
+      <c r="R5" s="59" t="n"/>
+      <c r="S5" s="59" t="n"/>
+      <c r="T5" s="59" t="n"/>
+      <c r="U5" s="59" t="n"/>
+      <c r="V5" s="59" t="n"/>
+      <c r="W5" s="59" t="n"/>
+      <c r="X5" s="59" t="n"/>
+      <c r="Y5" s="60" t="n"/>
       <c r="Z5" s="31" t="inlineStr">
         <is>
           <t>HOJA DE DATOS Y ESPECIFICACIONES TÉCNICAS DE LAS REJILLAS DE EXFILTRACIÓN</t>
         </is>
       </c>
-      <c r="AA5" s="44" t="n"/>
-      <c r="AB5" s="44" t="n"/>
-      <c r="AC5" s="44" t="n"/>
-      <c r="AD5" s="44" t="n"/>
-      <c r="AE5" s="44" t="n"/>
-      <c r="AF5" s="44" t="n"/>
-      <c r="AG5" s="44" t="n"/>
-      <c r="AH5" s="44" t="n"/>
-      <c r="AI5" s="44" t="n"/>
-      <c r="AJ5" s="44" t="n"/>
-      <c r="AK5" s="44" t="n"/>
-      <c r="AL5" s="44" t="n"/>
-      <c r="AM5" s="44" t="n"/>
-      <c r="AN5" s="44" t="n"/>
-      <c r="AO5" s="44" t="n"/>
-      <c r="AP5" s="44" t="n"/>
-      <c r="AQ5" s="44" t="n"/>
-      <c r="AR5" s="44" t="n"/>
-      <c r="AS5" s="44" t="n"/>
-      <c r="AT5" s="44" t="n"/>
-      <c r="AU5" s="44" t="n"/>
-      <c r="AV5" s="44" t="n"/>
-      <c r="AW5" s="44" t="n"/>
-      <c r="AX5" s="44" t="n"/>
-      <c r="AY5" s="44" t="n"/>
-      <c r="AZ5" s="44" t="n"/>
-      <c r="BA5" s="44" t="n"/>
-      <c r="BB5" s="45" t="n"/>
+      <c r="AA5" s="48" t="n"/>
+      <c r="AB5" s="48" t="n"/>
+      <c r="AC5" s="48" t="n"/>
+      <c r="AD5" s="48" t="n"/>
+      <c r="AE5" s="48" t="n"/>
+      <c r="AF5" s="48" t="n"/>
+      <c r="AG5" s="48" t="n"/>
+      <c r="AH5" s="48" t="n"/>
+      <c r="AI5" s="48" t="n"/>
+      <c r="AJ5" s="48" t="n"/>
+      <c r="AK5" s="48" t="n"/>
+      <c r="AL5" s="48" t="n"/>
+      <c r="AM5" s="48" t="n"/>
+      <c r="AN5" s="48" t="n"/>
+      <c r="AO5" s="48" t="n"/>
+      <c r="AP5" s="48" t="n"/>
+      <c r="AQ5" s="48" t="n"/>
+      <c r="AR5" s="48" t="n"/>
+      <c r="AS5" s="48" t="n"/>
+      <c r="AT5" s="48" t="n"/>
+      <c r="AU5" s="48" t="n"/>
+      <c r="AV5" s="48" t="n"/>
+      <c r="AW5" s="48" t="n"/>
+      <c r="AX5" s="48" t="n"/>
+      <c r="AY5" s="48" t="n"/>
+      <c r="AZ5" s="48" t="n"/>
+      <c r="BA5" s="48" t="n"/>
+      <c r="BB5" s="49" t="n"/>
       <c r="BC5" s="26" t="inlineStr">
         <is>
           <t>REVISO:</t>
         </is>
       </c>
-      <c r="BD5" s="46" t="n"/>
-      <c r="BE5" s="46" t="n"/>
-      <c r="BF5" s="46" t="n"/>
-      <c r="BG5" s="46" t="n"/>
-      <c r="BH5" s="46" t="n"/>
-      <c r="BI5" s="46" t="n"/>
-      <c r="BJ5" s="46" t="n"/>
-      <c r="BK5" s="46" t="n"/>
-      <c r="BL5" s="46" t="n"/>
-      <c r="BM5" s="46" t="n"/>
-      <c r="BN5" s="47" t="n"/>
+      <c r="BD5" s="50" t="n"/>
+      <c r="BE5" s="50" t="n"/>
+      <c r="BF5" s="50" t="n"/>
+      <c r="BG5" s="50" t="n"/>
+      <c r="BH5" s="50" t="n"/>
+      <c r="BI5" s="50" t="n"/>
+      <c r="BJ5" s="50" t="n"/>
+      <c r="BK5" s="50" t="n"/>
+      <c r="BL5" s="50" t="n"/>
+      <c r="BM5" s="50" t="n"/>
+      <c r="BN5" s="51" t="n"/>
       <c r="BO5" s="25" t="inlineStr">
         <is>
           <t>F.NAVIA</t>
         </is>
       </c>
-      <c r="BP5" s="48" t="n"/>
-      <c r="BQ5" s="48" t="n"/>
-      <c r="BR5" s="48" t="n"/>
-      <c r="BS5" s="48" t="n"/>
-      <c r="BT5" s="48" t="n"/>
-      <c r="BU5" s="48" t="n"/>
-      <c r="BV5" s="48" t="n"/>
-      <c r="BW5" s="48" t="n"/>
-      <c r="BX5" s="48" t="n"/>
-      <c r="BY5" s="48" t="n"/>
-      <c r="BZ5" s="49" t="n"/>
+      <c r="BP5" s="52" t="n"/>
+      <c r="BQ5" s="52" t="n"/>
+      <c r="BR5" s="52" t="n"/>
+      <c r="BS5" s="52" t="n"/>
+      <c r="BT5" s="52" t="n"/>
+      <c r="BU5" s="52" t="n"/>
+      <c r="BV5" s="52" t="n"/>
+      <c r="BW5" s="52" t="n"/>
+      <c r="BX5" s="52" t="n"/>
+      <c r="BY5" s="52" t="n"/>
+      <c r="BZ5" s="53" t="n"/>
     </row>
     <row r="6" ht="25" customFormat="1" customHeight="1" s="2">
-      <c r="A6" s="28" t="inlineStr">
+      <c r="A6" s="64" t="inlineStr">
         <is>
           <t>PROYECTO</t>
         </is>
       </c>
-      <c r="B6" s="46" t="n"/>
-      <c r="C6" s="46" t="n"/>
-      <c r="D6" s="46" t="n"/>
-      <c r="E6" s="46" t="n"/>
-      <c r="F6" s="46" t="n"/>
-      <c r="G6" s="46" t="n"/>
-      <c r="H6" s="46" t="n"/>
-      <c r="I6" s="46" t="n"/>
-      <c r="J6" s="46" t="n"/>
-      <c r="K6" s="46" t="n"/>
-      <c r="L6" s="46" t="n"/>
-      <c r="M6" s="47" t="n"/>
-      <c r="N6" s="28" t="inlineStr">
+      <c r="B6" s="65" t="n"/>
+      <c r="C6" s="65" t="n"/>
+      <c r="D6" s="65" t="n"/>
+      <c r="E6" s="65" t="n"/>
+      <c r="F6" s="65" t="n"/>
+      <c r="G6" s="65" t="n"/>
+      <c r="H6" s="65" t="n"/>
+      <c r="I6" s="65" t="n"/>
+      <c r="J6" s="65" t="n"/>
+      <c r="K6" s="65" t="n"/>
+      <c r="L6" s="65" t="n"/>
+      <c r="M6" s="66" t="n"/>
+      <c r="N6" s="64" t="inlineStr">
         <is>
           <t>P2437</t>
         </is>
       </c>
-      <c r="O6" s="46" t="n"/>
-      <c r="P6" s="46" t="n"/>
-      <c r="Q6" s="46" t="n"/>
-      <c r="R6" s="46" t="n"/>
-      <c r="S6" s="46" t="n"/>
-      <c r="T6" s="46" t="n"/>
-      <c r="U6" s="46" t="n"/>
-      <c r="V6" s="46" t="n"/>
-      <c r="W6" s="46" t="n"/>
-      <c r="X6" s="46" t="n"/>
-      <c r="Y6" s="47" t="n"/>
-      <c r="Z6" s="52" t="n"/>
-      <c r="AA6" s="53" t="n"/>
-      <c r="AB6" s="53" t="n"/>
-      <c r="AC6" s="53" t="n"/>
-      <c r="AD6" s="53" t="n"/>
-      <c r="AE6" s="53" t="n"/>
-      <c r="AF6" s="53" t="n"/>
-      <c r="AG6" s="53" t="n"/>
-      <c r="AH6" s="53" t="n"/>
-      <c r="AI6" s="53" t="n"/>
-      <c r="AJ6" s="53" t="n"/>
-      <c r="AK6" s="53" t="n"/>
-      <c r="AL6" s="53" t="n"/>
-      <c r="AM6" s="53" t="n"/>
-      <c r="AN6" s="53" t="n"/>
-      <c r="AO6" s="53" t="n"/>
-      <c r="AP6" s="53" t="n"/>
-      <c r="AQ6" s="53" t="n"/>
-      <c r="AR6" s="53" t="n"/>
-      <c r="AS6" s="53" t="n"/>
-      <c r="AT6" s="53" t="n"/>
-      <c r="AU6" s="53" t="n"/>
-      <c r="AV6" s="53" t="n"/>
-      <c r="AW6" s="53" t="n"/>
-      <c r="AX6" s="53" t="n"/>
-      <c r="AY6" s="53" t="n"/>
-      <c r="AZ6" s="53" t="n"/>
-      <c r="BA6" s="53" t="n"/>
-      <c r="BB6" s="54" t="n"/>
+      <c r="O6" s="65" t="n"/>
+      <c r="P6" s="50" t="n"/>
+      <c r="Q6" s="50" t="n"/>
+      <c r="R6" s="50" t="n"/>
+      <c r="S6" s="50" t="n"/>
+      <c r="T6" s="50" t="n"/>
+      <c r="U6" s="50" t="n"/>
+      <c r="V6" s="50" t="n"/>
+      <c r="W6" s="50" t="n"/>
+      <c r="X6" s="50" t="n"/>
+      <c r="Y6" s="51" t="n"/>
+      <c r="Z6" s="58" t="n"/>
+      <c r="AA6" s="59" t="n"/>
+      <c r="AB6" s="59" t="n"/>
+      <c r="AC6" s="59" t="n"/>
+      <c r="AD6" s="59" t="n"/>
+      <c r="AE6" s="59" t="n"/>
+      <c r="AF6" s="59" t="n"/>
+      <c r="AG6" s="59" t="n"/>
+      <c r="AH6" s="59" t="n"/>
+      <c r="AI6" s="59" t="n"/>
+      <c r="AJ6" s="59" t="n"/>
+      <c r="AK6" s="59" t="n"/>
+      <c r="AL6" s="59" t="n"/>
+      <c r="AM6" s="59" t="n"/>
+      <c r="AN6" s="59" t="n"/>
+      <c r="AO6" s="59" t="n"/>
+      <c r="AP6" s="59" t="n"/>
+      <c r="AQ6" s="59" t="n"/>
+      <c r="AR6" s="59" t="n"/>
+      <c r="AS6" s="59" t="n"/>
+      <c r="AT6" s="59" t="n"/>
+      <c r="AU6" s="59" t="n"/>
+      <c r="AV6" s="59" t="n"/>
+      <c r="AW6" s="59" t="n"/>
+      <c r="AX6" s="59" t="n"/>
+      <c r="AY6" s="59" t="n"/>
+      <c r="AZ6" s="59" t="n"/>
+      <c r="BA6" s="59" t="n"/>
+      <c r="BB6" s="60" t="n"/>
       <c r="BC6" s="26" t="inlineStr">
         <is>
           <t>APROBO:</t>
         </is>
       </c>
-      <c r="BD6" s="46" t="n"/>
-      <c r="BE6" s="46" t="n"/>
-      <c r="BF6" s="46" t="n"/>
-      <c r="BG6" s="46" t="n"/>
-      <c r="BH6" s="46" t="n"/>
-      <c r="BI6" s="46" t="n"/>
-      <c r="BJ6" s="46" t="n"/>
-      <c r="BK6" s="46" t="n"/>
-      <c r="BL6" s="46" t="n"/>
-      <c r="BM6" s="46" t="n"/>
-      <c r="BN6" s="47" t="n"/>
+      <c r="BD6" s="50" t="n"/>
+      <c r="BE6" s="50" t="n"/>
+      <c r="BF6" s="50" t="n"/>
+      <c r="BG6" s="50" t="n"/>
+      <c r="BH6" s="50" t="n"/>
+      <c r="BI6" s="50" t="n"/>
+      <c r="BJ6" s="50" t="n"/>
+      <c r="BK6" s="50" t="n"/>
+      <c r="BL6" s="50" t="n"/>
+      <c r="BM6" s="50" t="n"/>
+      <c r="BN6" s="51" t="n"/>
       <c r="BO6" s="25" t="inlineStr">
         <is>
           <t>H.ROSERO</t>
         </is>
       </c>
-      <c r="BP6" s="48" t="n"/>
-      <c r="BQ6" s="48" t="n"/>
-      <c r="BR6" s="48" t="n"/>
-      <c r="BS6" s="48" t="n"/>
-      <c r="BT6" s="48" t="n"/>
-      <c r="BU6" s="48" t="n"/>
-      <c r="BV6" s="48" t="n"/>
-      <c r="BW6" s="48" t="n"/>
-      <c r="BX6" s="48" t="n"/>
-      <c r="BY6" s="48" t="n"/>
-      <c r="BZ6" s="49" t="n"/>
+      <c r="BP6" s="52" t="n"/>
+      <c r="BQ6" s="52" t="n"/>
+      <c r="BR6" s="52" t="n"/>
+      <c r="BS6" s="52" t="n"/>
+      <c r="BT6" s="52" t="n"/>
+      <c r="BU6" s="52" t="n"/>
+      <c r="BV6" s="52" t="n"/>
+      <c r="BW6" s="52" t="n"/>
+      <c r="BX6" s="52" t="n"/>
+      <c r="BY6" s="52" t="n"/>
+      <c r="BZ6" s="53" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="G7" s="21" t="n"/>
-      <c r="H7" s="21" t="n"/>
-      <c r="I7" s="21" t="n"/>
-      <c r="J7" s="21" t="n"/>
-      <c r="K7" s="21" t="n"/>
-      <c r="L7" s="21" t="n"/>
-      <c r="M7" s="21" t="n"/>
-      <c r="N7" s="21" t="n"/>
-      <c r="O7" s="21" t="n"/>
+      <c r="A7" s="55" t="n"/>
+      <c r="B7" s="55" t="n"/>
+      <c r="C7" s="55" t="n"/>
+      <c r="D7" s="55" t="n"/>
+      <c r="E7" s="55" t="n"/>
+      <c r="F7" s="55" t="n"/>
+      <c r="G7" s="67" t="n"/>
+      <c r="H7" s="67" t="n"/>
+      <c r="I7" s="67" t="n"/>
+      <c r="J7" s="67" t="n"/>
+      <c r="K7" s="67" t="n"/>
+      <c r="L7" s="67" t="n"/>
+      <c r="M7" s="67" t="n"/>
+      <c r="N7" s="67" t="n"/>
+      <c r="O7" s="67" t="n"/>
       <c r="P7" s="21" t="n"/>
       <c r="Q7" s="21" t="n"/>
       <c r="R7" s="21" t="n"/>
@@ -1604,15 +1754,21 @@
       <c r="CD7" s="7" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1">
-      <c r="G8" s="21" t="n"/>
-      <c r="H8" s="21" t="n"/>
-      <c r="I8" s="21" t="n"/>
-      <c r="J8" s="21" t="n"/>
-      <c r="K8" s="21" t="n"/>
-      <c r="L8" s="21" t="n"/>
-      <c r="M8" s="21" t="n"/>
-      <c r="N8" s="21" t="n"/>
-      <c r="O8" s="21" t="n"/>
+      <c r="A8" s="55" t="n"/>
+      <c r="B8" s="55" t="n"/>
+      <c r="C8" s="55" t="n"/>
+      <c r="D8" s="55" t="n"/>
+      <c r="E8" s="55" t="n"/>
+      <c r="F8" s="55" t="n"/>
+      <c r="G8" s="67" t="n"/>
+      <c r="H8" s="67" t="n"/>
+      <c r="I8" s="67" t="n"/>
+      <c r="J8" s="67" t="n"/>
+      <c r="K8" s="67" t="n"/>
+      <c r="L8" s="67" t="n"/>
+      <c r="M8" s="67" t="n"/>
+      <c r="N8" s="67" t="n"/>
+      <c r="O8" s="67" t="n"/>
       <c r="P8" s="21" t="n"/>
       <c r="Q8" s="21" t="n"/>
       <c r="R8" s="21" t="n"/>
@@ -1633,15 +1789,21 @@
       <c r="CD8" s="7" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1">
-      <c r="G9" s="21" t="n"/>
-      <c r="H9" s="21" t="n"/>
-      <c r="I9" s="21" t="n"/>
-      <c r="J9" s="21" t="n"/>
-      <c r="K9" s="21" t="n"/>
-      <c r="L9" s="21" t="n"/>
-      <c r="M9" s="21" t="n"/>
-      <c r="N9" s="21" t="n"/>
-      <c r="O9" s="21" t="n"/>
+      <c r="A9" s="55" t="n"/>
+      <c r="B9" s="55" t="n"/>
+      <c r="C9" s="55" t="n"/>
+      <c r="D9" s="55" t="n"/>
+      <c r="E9" s="55" t="n"/>
+      <c r="F9" s="55" t="n"/>
+      <c r="G9" s="67" t="n"/>
+      <c r="H9" s="67" t="n"/>
+      <c r="I9" s="67" t="n"/>
+      <c r="J9" s="67" t="n"/>
+      <c r="K9" s="67" t="n"/>
+      <c r="L9" s="67" t="n"/>
+      <c r="M9" s="67" t="n"/>
+      <c r="N9" s="67" t="n"/>
+      <c r="O9" s="67" t="n"/>
       <c r="P9" s="21" t="n"/>
       <c r="Q9" s="21" t="n"/>
       <c r="R9" s="21" t="n"/>
@@ -1662,15 +1824,21 @@
       <c r="CD9" s="7" t="n"/>
     </row>
     <row r="10" ht="15" customHeight="1">
-      <c r="G10" s="21" t="n"/>
-      <c r="H10" s="21" t="n"/>
-      <c r="I10" s="21" t="n"/>
-      <c r="J10" s="21" t="n"/>
-      <c r="K10" s="21" t="n"/>
-      <c r="L10" s="21" t="n"/>
-      <c r="M10" s="21" t="n"/>
-      <c r="N10" s="21" t="n"/>
-      <c r="O10" s="21" t="n"/>
+      <c r="A10" s="55" t="n"/>
+      <c r="B10" s="55" t="n"/>
+      <c r="C10" s="55" t="n"/>
+      <c r="D10" s="55" t="n"/>
+      <c r="E10" s="55" t="n"/>
+      <c r="F10" s="55" t="n"/>
+      <c r="G10" s="67" t="n"/>
+      <c r="H10" s="67" t="n"/>
+      <c r="I10" s="67" t="n"/>
+      <c r="J10" s="67" t="n"/>
+      <c r="K10" s="67" t="n"/>
+      <c r="L10" s="67" t="n"/>
+      <c r="M10" s="67" t="n"/>
+      <c r="N10" s="67" t="n"/>
+      <c r="O10" s="67" t="n"/>
       <c r="P10" s="21" t="n"/>
       <c r="Q10" s="21" t="n"/>
       <c r="R10" s="21" t="n"/>
@@ -1691,15 +1859,21 @@
       <c r="CD10" s="7" t="n"/>
     </row>
     <row r="11" ht="15" customHeight="1">
-      <c r="G11" s="21" t="n"/>
-      <c r="H11" s="21" t="n"/>
-      <c r="I11" s="21" t="n"/>
-      <c r="J11" s="21" t="n"/>
-      <c r="K11" s="21" t="n"/>
-      <c r="L11" s="21" t="n"/>
-      <c r="M11" s="21" t="n"/>
-      <c r="N11" s="21" t="n"/>
-      <c r="O11" s="21" t="n"/>
+      <c r="A11" s="55" t="n"/>
+      <c r="B11" s="55" t="n"/>
+      <c r="C11" s="55" t="n"/>
+      <c r="D11" s="55" t="n"/>
+      <c r="E11" s="55" t="n"/>
+      <c r="F11" s="55" t="n"/>
+      <c r="G11" s="67" t="n"/>
+      <c r="H11" s="67" t="n"/>
+      <c r="I11" s="67" t="n"/>
+      <c r="J11" s="67" t="n"/>
+      <c r="K11" s="67" t="n"/>
+      <c r="L11" s="67" t="n"/>
+      <c r="M11" s="67" t="n"/>
+      <c r="N11" s="67" t="n"/>
+      <c r="O11" s="67" t="n"/>
       <c r="P11" s="21" t="n"/>
       <c r="Q11" s="21" t="n"/>
       <c r="R11" s="21" t="n"/>
@@ -1720,15 +1894,21 @@
       <c r="CD11" s="7" t="n"/>
     </row>
     <row r="12" ht="15" customHeight="1">
-      <c r="G12" s="21" t="n"/>
-      <c r="H12" s="21" t="n"/>
-      <c r="I12" s="21" t="n"/>
-      <c r="J12" s="21" t="n"/>
-      <c r="K12" s="21" t="n"/>
-      <c r="L12" s="21" t="n"/>
-      <c r="M12" s="21" t="n"/>
-      <c r="N12" s="21" t="n"/>
-      <c r="O12" s="21" t="n"/>
+      <c r="A12" s="55" t="n"/>
+      <c r="B12" s="55" t="n"/>
+      <c r="C12" s="55" t="n"/>
+      <c r="D12" s="55" t="n"/>
+      <c r="E12" s="55" t="n"/>
+      <c r="F12" s="55" t="n"/>
+      <c r="G12" s="67" t="n"/>
+      <c r="H12" s="67" t="n"/>
+      <c r="I12" s="67" t="n"/>
+      <c r="J12" s="67" t="n"/>
+      <c r="K12" s="67" t="n"/>
+      <c r="L12" s="67" t="n"/>
+      <c r="M12" s="67" t="n"/>
+      <c r="N12" s="67" t="n"/>
+      <c r="O12" s="67" t="n"/>
       <c r="P12" s="21" t="n"/>
       <c r="Q12" s="21" t="n"/>
       <c r="R12" s="21" t="n"/>
@@ -1749,15 +1929,21 @@
       <c r="CD12" s="7" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1">
-      <c r="G13" s="21" t="n"/>
-      <c r="H13" s="21" t="n"/>
-      <c r="I13" s="21" t="n"/>
-      <c r="J13" s="21" t="n"/>
-      <c r="K13" s="21" t="n"/>
-      <c r="L13" s="21" t="n"/>
-      <c r="M13" s="21" t="n"/>
-      <c r="N13" s="21" t="n"/>
-      <c r="O13" s="21" t="n"/>
+      <c r="A13" s="55" t="n"/>
+      <c r="B13" s="55" t="n"/>
+      <c r="C13" s="55" t="n"/>
+      <c r="D13" s="55" t="n"/>
+      <c r="E13" s="55" t="n"/>
+      <c r="F13" s="55" t="n"/>
+      <c r="G13" s="67" t="n"/>
+      <c r="H13" s="67" t="n"/>
+      <c r="I13" s="67" t="n"/>
+      <c r="J13" s="67" t="n"/>
+      <c r="K13" s="67" t="n"/>
+      <c r="L13" s="67" t="n"/>
+      <c r="M13" s="67" t="n"/>
+      <c r="N13" s="67" t="n"/>
+      <c r="O13" s="67" t="n"/>
       <c r="P13" s="21" t="n"/>
       <c r="Q13" s="21" t="n"/>
       <c r="R13" s="21" t="n"/>
@@ -1778,15 +1964,21 @@
       <c r="CD13" s="7" t="n"/>
     </row>
     <row r="14" ht="15" customHeight="1">
-      <c r="G14" s="21" t="n"/>
-      <c r="H14" s="21" t="n"/>
-      <c r="I14" s="21" t="n"/>
-      <c r="J14" s="21" t="n"/>
-      <c r="K14" s="21" t="n"/>
-      <c r="L14" s="21" t="n"/>
-      <c r="M14" s="21" t="n"/>
-      <c r="N14" s="21" t="n"/>
-      <c r="O14" s="21" t="n"/>
+      <c r="A14" s="55" t="n"/>
+      <c r="B14" s="55" t="n"/>
+      <c r="C14" s="55" t="n"/>
+      <c r="D14" s="55" t="n"/>
+      <c r="E14" s="55" t="n"/>
+      <c r="F14" s="55" t="n"/>
+      <c r="G14" s="67" t="n"/>
+      <c r="H14" s="67" t="n"/>
+      <c r="I14" s="67" t="n"/>
+      <c r="J14" s="67" t="n"/>
+      <c r="K14" s="67" t="n"/>
+      <c r="L14" s="67" t="n"/>
+      <c r="M14" s="67" t="n"/>
+      <c r="N14" s="67" t="n"/>
+      <c r="O14" s="67" t="n"/>
       <c r="P14" s="21" t="n"/>
       <c r="Q14" s="21" t="n"/>
       <c r="R14" s="21" t="n"/>
@@ -1807,15 +1999,21 @@
       <c r="CD14" s="7" t="n"/>
     </row>
     <row r="15" ht="15" customHeight="1">
-      <c r="G15" s="21" t="n"/>
-      <c r="H15" s="21" t="n"/>
-      <c r="I15" s="21" t="n"/>
-      <c r="J15" s="21" t="n"/>
-      <c r="K15" s="21" t="n"/>
-      <c r="L15" s="21" t="n"/>
-      <c r="M15" s="21" t="n"/>
-      <c r="N15" s="21" t="n"/>
-      <c r="O15" s="21" t="n"/>
+      <c r="A15" s="55" t="n"/>
+      <c r="B15" s="55" t="n"/>
+      <c r="C15" s="55" t="n"/>
+      <c r="D15" s="55" t="n"/>
+      <c r="E15" s="55" t="n"/>
+      <c r="F15" s="55" t="n"/>
+      <c r="G15" s="67" t="n"/>
+      <c r="H15" s="67" t="n"/>
+      <c r="I15" s="67" t="n"/>
+      <c r="J15" s="67" t="n"/>
+      <c r="K15" s="67" t="n"/>
+      <c r="L15" s="67" t="n"/>
+      <c r="M15" s="67" t="n"/>
+      <c r="N15" s="67" t="n"/>
+      <c r="O15" s="67" t="n"/>
       <c r="P15" s="21" t="n"/>
       <c r="Q15" s="21" t="n"/>
       <c r="R15" s="21" t="n"/>
@@ -1836,15 +2034,21 @@
       <c r="CD15" s="7" t="n"/>
     </row>
     <row r="16" ht="15" customHeight="1">
-      <c r="G16" s="21" t="n"/>
-      <c r="H16" s="21" t="n"/>
-      <c r="I16" s="21" t="n"/>
-      <c r="J16" s="21" t="n"/>
-      <c r="K16" s="21" t="n"/>
-      <c r="L16" s="21" t="n"/>
-      <c r="M16" s="21" t="n"/>
-      <c r="N16" s="21" t="n"/>
-      <c r="O16" s="21" t="n"/>
+      <c r="A16" s="55" t="n"/>
+      <c r="B16" s="55" t="n"/>
+      <c r="C16" s="55" t="n"/>
+      <c r="D16" s="55" t="n"/>
+      <c r="E16" s="55" t="n"/>
+      <c r="F16" s="55" t="n"/>
+      <c r="G16" s="67" t="n"/>
+      <c r="H16" s="67" t="n"/>
+      <c r="I16" s="67" t="n"/>
+      <c r="J16" s="67" t="n"/>
+      <c r="K16" s="67" t="n"/>
+      <c r="L16" s="67" t="n"/>
+      <c r="M16" s="67" t="n"/>
+      <c r="N16" s="67" t="n"/>
+      <c r="O16" s="67" t="n"/>
       <c r="P16" s="21" t="n"/>
       <c r="Q16" s="21" t="n"/>
       <c r="R16" s="21" t="n"/>
@@ -1865,15 +2069,21 @@
       <c r="CD16" s="7" t="n"/>
     </row>
     <row r="17" ht="15" customHeight="1">
-      <c r="G17" s="21" t="n"/>
-      <c r="H17" s="21" t="n"/>
-      <c r="I17" s="21" t="n"/>
-      <c r="J17" s="21" t="n"/>
-      <c r="K17" s="21" t="n"/>
-      <c r="L17" s="21" t="n"/>
-      <c r="M17" s="21" t="n"/>
-      <c r="N17" s="21" t="n"/>
-      <c r="O17" s="21" t="n"/>
+      <c r="A17" s="55" t="n"/>
+      <c r="B17" s="55" t="n"/>
+      <c r="C17" s="55" t="n"/>
+      <c r="D17" s="55" t="n"/>
+      <c r="E17" s="55" t="n"/>
+      <c r="F17" s="55" t="n"/>
+      <c r="G17" s="67" t="n"/>
+      <c r="H17" s="67" t="n"/>
+      <c r="I17" s="67" t="n"/>
+      <c r="J17" s="67" t="n"/>
+      <c r="K17" s="67" t="n"/>
+      <c r="L17" s="67" t="n"/>
+      <c r="M17" s="67" t="n"/>
+      <c r="N17" s="67" t="n"/>
+      <c r="O17" s="67" t="n"/>
       <c r="P17" s="21" t="n"/>
       <c r="Q17" s="21" t="n"/>
       <c r="R17" s="21" t="n"/>
@@ -1894,15 +2104,21 @@
       <c r="CD17" s="7" t="n"/>
     </row>
     <row r="18" ht="15" customHeight="1">
-      <c r="G18" s="21" t="n"/>
-      <c r="H18" s="21" t="n"/>
-      <c r="I18" s="21" t="n"/>
-      <c r="J18" s="21" t="n"/>
-      <c r="K18" s="21" t="n"/>
-      <c r="L18" s="21" t="n"/>
-      <c r="M18" s="21" t="n"/>
-      <c r="N18" s="21" t="n"/>
-      <c r="O18" s="21" t="n"/>
+      <c r="A18" s="55" t="n"/>
+      <c r="B18" s="55" t="n"/>
+      <c r="C18" s="55" t="n"/>
+      <c r="D18" s="55" t="n"/>
+      <c r="E18" s="55" t="n"/>
+      <c r="F18" s="55" t="n"/>
+      <c r="G18" s="67" t="n"/>
+      <c r="H18" s="67" t="n"/>
+      <c r="I18" s="67" t="n"/>
+      <c r="J18" s="67" t="n"/>
+      <c r="K18" s="67" t="n"/>
+      <c r="L18" s="67" t="n"/>
+      <c r="M18" s="67" t="n"/>
+      <c r="N18" s="67" t="n"/>
+      <c r="O18" s="67" t="n"/>
       <c r="P18" s="21" t="n"/>
       <c r="Q18" s="21" t="n"/>
       <c r="R18" s="21" t="n"/>
@@ -1923,15 +2139,21 @@
       <c r="CD18" s="7" t="n"/>
     </row>
     <row r="19" ht="15" customHeight="1">
-      <c r="G19" s="21" t="n"/>
-      <c r="H19" s="21" t="n"/>
-      <c r="I19" s="21" t="n"/>
-      <c r="J19" s="21" t="n"/>
-      <c r="K19" s="21" t="n"/>
-      <c r="L19" s="21" t="n"/>
-      <c r="M19" s="21" t="n"/>
-      <c r="N19" s="21" t="n"/>
-      <c r="O19" s="21" t="n"/>
+      <c r="A19" s="55" t="n"/>
+      <c r="B19" s="55" t="n"/>
+      <c r="C19" s="55" t="n"/>
+      <c r="D19" s="55" t="n"/>
+      <c r="E19" s="55" t="n"/>
+      <c r="F19" s="55" t="n"/>
+      <c r="G19" s="67" t="n"/>
+      <c r="H19" s="67" t="n"/>
+      <c r="I19" s="67" t="n"/>
+      <c r="J19" s="67" t="n"/>
+      <c r="K19" s="67" t="n"/>
+      <c r="L19" s="67" t="n"/>
+      <c r="M19" s="67" t="n"/>
+      <c r="N19" s="67" t="n"/>
+      <c r="O19" s="67" t="n"/>
       <c r="P19" s="21" t="n"/>
       <c r="Q19" s="21" t="n"/>
       <c r="R19" s="21" t="n"/>
@@ -1952,15 +2174,21 @@
       <c r="CD19" s="7" t="n"/>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="G20" s="21" t="n"/>
-      <c r="H20" s="21" t="n"/>
-      <c r="I20" s="21" t="n"/>
-      <c r="J20" s="21" t="n"/>
-      <c r="K20" s="21" t="n"/>
-      <c r="L20" s="21" t="n"/>
-      <c r="M20" s="21" t="n"/>
-      <c r="N20" s="21" t="n"/>
-      <c r="O20" s="21" t="n"/>
+      <c r="A20" s="55" t="n"/>
+      <c r="B20" s="55" t="n"/>
+      <c r="C20" s="55" t="n"/>
+      <c r="D20" s="55" t="n"/>
+      <c r="E20" s="55" t="n"/>
+      <c r="F20" s="55" t="n"/>
+      <c r="G20" s="67" t="n"/>
+      <c r="H20" s="67" t="n"/>
+      <c r="I20" s="67" t="n"/>
+      <c r="J20" s="67" t="n"/>
+      <c r="K20" s="67" t="n"/>
+      <c r="L20" s="67" t="n"/>
+      <c r="M20" s="67" t="n"/>
+      <c r="N20" s="67" t="n"/>
+      <c r="O20" s="67" t="n"/>
       <c r="P20" s="21" t="n"/>
       <c r="Q20" s="21" t="n"/>
       <c r="R20" s="21" t="n"/>
@@ -1981,15 +2209,21 @@
       <c r="CD20" s="7" t="n"/>
     </row>
     <row r="21" ht="15" customHeight="1">
-      <c r="G21" s="21" t="n"/>
-      <c r="H21" s="21" t="n"/>
-      <c r="I21" s="21" t="n"/>
-      <c r="J21" s="21" t="n"/>
-      <c r="K21" s="21" t="n"/>
-      <c r="L21" s="21" t="n"/>
-      <c r="M21" s="21" t="n"/>
-      <c r="N21" s="21" t="n"/>
-      <c r="O21" s="21" t="n"/>
+      <c r="A21" s="55" t="n"/>
+      <c r="B21" s="55" t="n"/>
+      <c r="C21" s="55" t="n"/>
+      <c r="D21" s="55" t="n"/>
+      <c r="E21" s="55" t="n"/>
+      <c r="F21" s="55" t="n"/>
+      <c r="G21" s="67" t="n"/>
+      <c r="H21" s="67" t="n"/>
+      <c r="I21" s="67" t="n"/>
+      <c r="J21" s="67" t="n"/>
+      <c r="K21" s="67" t="n"/>
+      <c r="L21" s="67" t="n"/>
+      <c r="M21" s="67" t="n"/>
+      <c r="N21" s="67" t="n"/>
+      <c r="O21" s="67" t="n"/>
       <c r="P21" s="21" t="n"/>
       <c r="Q21" s="21" t="n"/>
       <c r="R21" s="41" t="inlineStr">
@@ -1997,140 +2231,158 @@
           <t>Elaborado por:</t>
         </is>
       </c>
-      <c r="S21" s="44" t="n"/>
-      <c r="T21" s="44" t="n"/>
-      <c r="U21" s="44" t="n"/>
-      <c r="V21" s="44" t="n"/>
-      <c r="W21" s="44" t="n"/>
-      <c r="X21" s="44" t="n"/>
-      <c r="Y21" s="44" t="n"/>
-      <c r="Z21" s="44" t="n"/>
-      <c r="AA21" s="44" t="n"/>
-      <c r="AB21" s="44" t="n"/>
-      <c r="AC21" s="44" t="n"/>
-      <c r="AD21" s="44" t="n"/>
-      <c r="AE21" s="45" t="n"/>
+      <c r="S21" s="48" t="n"/>
+      <c r="T21" s="48" t="n"/>
+      <c r="U21" s="48" t="n"/>
+      <c r="V21" s="48" t="n"/>
+      <c r="W21" s="48" t="n"/>
+      <c r="X21" s="48" t="n"/>
+      <c r="Y21" s="48" t="n"/>
+      <c r="Z21" s="48" t="n"/>
+      <c r="AA21" s="48" t="n"/>
+      <c r="AB21" s="48" t="n"/>
+      <c r="AC21" s="48" t="n"/>
+      <c r="AD21" s="48" t="n"/>
+      <c r="AE21" s="49" t="n"/>
       <c r="AF21" s="41" t="inlineStr">
         <is>
           <t>Revisado por:</t>
         </is>
       </c>
-      <c r="AG21" s="44" t="n"/>
-      <c r="AH21" s="44" t="n"/>
-      <c r="AI21" s="44" t="n"/>
-      <c r="AJ21" s="44" t="n"/>
-      <c r="AK21" s="44" t="n"/>
-      <c r="AL21" s="44" t="n"/>
-      <c r="AM21" s="44" t="n"/>
-      <c r="AN21" s="44" t="n"/>
-      <c r="AO21" s="44" t="n"/>
-      <c r="AP21" s="44" t="n"/>
-      <c r="AQ21" s="44" t="n"/>
-      <c r="AR21" s="44" t="n"/>
-      <c r="AS21" s="45" t="n"/>
+      <c r="AG21" s="48" t="n"/>
+      <c r="AH21" s="48" t="n"/>
+      <c r="AI21" s="48" t="n"/>
+      <c r="AJ21" s="48" t="n"/>
+      <c r="AK21" s="48" t="n"/>
+      <c r="AL21" s="48" t="n"/>
+      <c r="AM21" s="48" t="n"/>
+      <c r="AN21" s="48" t="n"/>
+      <c r="AO21" s="48" t="n"/>
+      <c r="AP21" s="48" t="n"/>
+      <c r="AQ21" s="48" t="n"/>
+      <c r="AR21" s="48" t="n"/>
+      <c r="AS21" s="49" t="n"/>
       <c r="AT21" s="41" t="inlineStr">
         <is>
           <t>Aprobado por:</t>
         </is>
       </c>
-      <c r="AU21" s="44" t="n"/>
-      <c r="AV21" s="44" t="n"/>
-      <c r="AW21" s="44" t="n"/>
-      <c r="AX21" s="44" t="n"/>
-      <c r="AY21" s="44" t="n"/>
-      <c r="AZ21" s="44" t="n"/>
-      <c r="BA21" s="44" t="n"/>
-      <c r="BB21" s="44" t="n"/>
-      <c r="BC21" s="44" t="n"/>
-      <c r="BD21" s="44" t="n"/>
-      <c r="BE21" s="44" t="n"/>
-      <c r="BF21" s="44" t="n"/>
-      <c r="BG21" s="45" t="n"/>
+      <c r="AU21" s="48" t="n"/>
+      <c r="AV21" s="48" t="n"/>
+      <c r="AW21" s="48" t="n"/>
+      <c r="AX21" s="48" t="n"/>
+      <c r="AY21" s="48" t="n"/>
+      <c r="AZ21" s="48" t="n"/>
+      <c r="BA21" s="48" t="n"/>
+      <c r="BB21" s="48" t="n"/>
+      <c r="BC21" s="48" t="n"/>
+      <c r="BD21" s="48" t="n"/>
+      <c r="BE21" s="48" t="n"/>
+      <c r="BF21" s="48" t="n"/>
+      <c r="BG21" s="49" t="n"/>
     </row>
     <row r="22" ht="15" customHeight="1">
-      <c r="G22" s="21" t="n"/>
-      <c r="H22" s="21" t="n"/>
-      <c r="I22" s="21" t="n"/>
-      <c r="J22" s="21" t="n"/>
-      <c r="K22" s="21" t="n"/>
-      <c r="L22" s="21" t="n"/>
-      <c r="M22" s="21" t="n"/>
-      <c r="N22" s="21" t="n"/>
-      <c r="O22" s="21" t="n"/>
+      <c r="A22" s="55" t="n"/>
+      <c r="B22" s="55" t="n"/>
+      <c r="C22" s="55" t="n"/>
+      <c r="D22" s="55" t="n"/>
+      <c r="E22" s="55" t="n"/>
+      <c r="F22" s="55" t="n"/>
+      <c r="G22" s="67" t="n"/>
+      <c r="H22" s="67" t="n"/>
+      <c r="I22" s="67" t="n"/>
+      <c r="J22" s="67" t="n"/>
+      <c r="K22" s="67" t="n"/>
+      <c r="L22" s="67" t="n"/>
+      <c r="M22" s="67" t="n"/>
+      <c r="N22" s="67" t="n"/>
+      <c r="O22" s="67" t="n"/>
       <c r="P22" s="21" t="n"/>
       <c r="Q22" s="21" t="n"/>
-      <c r="R22" s="50" t="n"/>
-      <c r="AE22" s="51" t="n"/>
-      <c r="AF22" s="50" t="n"/>
-      <c r="AS22" s="51" t="n"/>
-      <c r="AT22" s="50" t="n"/>
-      <c r="BG22" s="51" t="n"/>
+      <c r="R22" s="68" t="n"/>
+      <c r="AE22" s="57" t="n"/>
+      <c r="AF22" s="68" t="n"/>
+      <c r="AS22" s="57" t="n"/>
+      <c r="AT22" s="68" t="n"/>
+      <c r="BG22" s="57" t="n"/>
     </row>
     <row r="23" ht="15" customHeight="1">
-      <c r="G23" s="21" t="n"/>
-      <c r="H23" s="21" t="n"/>
-      <c r="I23" s="21" t="n"/>
-      <c r="J23" s="21" t="n"/>
-      <c r="K23" s="21" t="n"/>
-      <c r="L23" s="21" t="n"/>
-      <c r="M23" s="21" t="n"/>
-      <c r="N23" s="21" t="n"/>
-      <c r="O23" s="21" t="n"/>
+      <c r="A23" s="55" t="n"/>
+      <c r="B23" s="55" t="n"/>
+      <c r="C23" s="55" t="n"/>
+      <c r="D23" s="55" t="n"/>
+      <c r="E23" s="55" t="n"/>
+      <c r="F23" s="55" t="n"/>
+      <c r="G23" s="67" t="n"/>
+      <c r="H23" s="67" t="n"/>
+      <c r="I23" s="67" t="n"/>
+      <c r="J23" s="67" t="n"/>
+      <c r="K23" s="67" t="n"/>
+      <c r="L23" s="67" t="n"/>
+      <c r="M23" s="67" t="n"/>
+      <c r="N23" s="67" t="n"/>
+      <c r="O23" s="67" t="n"/>
       <c r="P23" s="21" t="n"/>
       <c r="Q23" s="21" t="n"/>
-      <c r="R23" s="52" t="n"/>
-      <c r="S23" s="53" t="n"/>
-      <c r="T23" s="53" t="n"/>
-      <c r="U23" s="53" t="n"/>
-      <c r="V23" s="53" t="n"/>
-      <c r="W23" s="53" t="n"/>
-      <c r="X23" s="53" t="n"/>
-      <c r="Y23" s="53" t="n"/>
-      <c r="Z23" s="53" t="n"/>
-      <c r="AA23" s="53" t="n"/>
-      <c r="AB23" s="53" t="n"/>
-      <c r="AC23" s="53" t="n"/>
-      <c r="AD23" s="53" t="n"/>
-      <c r="AE23" s="54" t="n"/>
-      <c r="AF23" s="52" t="n"/>
-      <c r="AG23" s="53" t="n"/>
-      <c r="AH23" s="53" t="n"/>
-      <c r="AI23" s="53" t="n"/>
-      <c r="AJ23" s="53" t="n"/>
-      <c r="AK23" s="53" t="n"/>
-      <c r="AL23" s="53" t="n"/>
-      <c r="AM23" s="53" t="n"/>
-      <c r="AN23" s="53" t="n"/>
-      <c r="AO23" s="53" t="n"/>
-      <c r="AP23" s="53" t="n"/>
-      <c r="AQ23" s="53" t="n"/>
-      <c r="AR23" s="53" t="n"/>
-      <c r="AS23" s="54" t="n"/>
-      <c r="AT23" s="52" t="n"/>
-      <c r="AU23" s="53" t="n"/>
-      <c r="AV23" s="53" t="n"/>
-      <c r="AW23" s="53" t="n"/>
-      <c r="AX23" s="53" t="n"/>
-      <c r="AY23" s="53" t="n"/>
-      <c r="AZ23" s="53" t="n"/>
-      <c r="BA23" s="53" t="n"/>
-      <c r="BB23" s="53" t="n"/>
-      <c r="BC23" s="53" t="n"/>
-      <c r="BD23" s="53" t="n"/>
-      <c r="BE23" s="53" t="n"/>
-      <c r="BF23" s="53" t="n"/>
-      <c r="BG23" s="54" t="n"/>
+      <c r="R23" s="58" t="n"/>
+      <c r="S23" s="59" t="n"/>
+      <c r="T23" s="59" t="n"/>
+      <c r="U23" s="59" t="n"/>
+      <c r="V23" s="59" t="n"/>
+      <c r="W23" s="59" t="n"/>
+      <c r="X23" s="59" t="n"/>
+      <c r="Y23" s="59" t="n"/>
+      <c r="Z23" s="59" t="n"/>
+      <c r="AA23" s="59" t="n"/>
+      <c r="AB23" s="59" t="n"/>
+      <c r="AC23" s="59" t="n"/>
+      <c r="AD23" s="59" t="n"/>
+      <c r="AE23" s="60" t="n"/>
+      <c r="AF23" s="58" t="n"/>
+      <c r="AG23" s="59" t="n"/>
+      <c r="AH23" s="59" t="n"/>
+      <c r="AI23" s="59" t="n"/>
+      <c r="AJ23" s="59" t="n"/>
+      <c r="AK23" s="59" t="n"/>
+      <c r="AL23" s="59" t="n"/>
+      <c r="AM23" s="59" t="n"/>
+      <c r="AN23" s="59" t="n"/>
+      <c r="AO23" s="59" t="n"/>
+      <c r="AP23" s="59" t="n"/>
+      <c r="AQ23" s="59" t="n"/>
+      <c r="AR23" s="59" t="n"/>
+      <c r="AS23" s="60" t="n"/>
+      <c r="AT23" s="58" t="n"/>
+      <c r="AU23" s="59" t="n"/>
+      <c r="AV23" s="59" t="n"/>
+      <c r="AW23" s="59" t="n"/>
+      <c r="AX23" s="59" t="n"/>
+      <c r="AY23" s="59" t="n"/>
+      <c r="AZ23" s="59" t="n"/>
+      <c r="BA23" s="59" t="n"/>
+      <c r="BB23" s="59" t="n"/>
+      <c r="BC23" s="59" t="n"/>
+      <c r="BD23" s="59" t="n"/>
+      <c r="BE23" s="59" t="n"/>
+      <c r="BF23" s="59" t="n"/>
+      <c r="BG23" s="60" t="n"/>
     </row>
     <row r="24" ht="15" customHeight="1">
-      <c r="G24" s="21" t="n"/>
-      <c r="H24" s="21" t="n"/>
-      <c r="I24" s="21" t="n"/>
-      <c r="J24" s="21" t="n"/>
-      <c r="K24" s="21" t="n"/>
-      <c r="L24" s="21" t="n"/>
-      <c r="M24" s="21" t="n"/>
-      <c r="N24" s="21" t="n"/>
-      <c r="O24" s="21" t="n"/>
+      <c r="A24" s="55" t="n"/>
+      <c r="B24" s="55" t="n"/>
+      <c r="C24" s="55" t="n"/>
+      <c r="D24" s="55" t="n"/>
+      <c r="E24" s="55" t="n"/>
+      <c r="F24" s="55" t="n"/>
+      <c r="G24" s="67" t="n"/>
+      <c r="H24" s="67" t="n"/>
+      <c r="I24" s="67" t="n"/>
+      <c r="J24" s="67" t="n"/>
+      <c r="K24" s="67" t="n"/>
+      <c r="L24" s="67" t="n"/>
+      <c r="M24" s="67" t="n"/>
+      <c r="N24" s="67" t="n"/>
+      <c r="O24" s="67" t="n"/>
       <c r="P24" s="21" t="n"/>
       <c r="Q24" s="21" t="n"/>
       <c r="R24" s="23" t="inlineStr">
@@ -2138,270 +2390,306 @@
           <t>J.ARBOLEDA</t>
         </is>
       </c>
-      <c r="S24" s="44" t="n"/>
-      <c r="T24" s="44" t="n"/>
-      <c r="U24" s="44" t="n"/>
-      <c r="V24" s="44" t="n"/>
-      <c r="W24" s="44" t="n"/>
-      <c r="X24" s="44" t="n"/>
-      <c r="Y24" s="44" t="n"/>
-      <c r="Z24" s="44" t="n"/>
-      <c r="AA24" s="44" t="n"/>
-      <c r="AB24" s="44" t="n"/>
-      <c r="AC24" s="44" t="n"/>
-      <c r="AD24" s="44" t="n"/>
-      <c r="AE24" s="45" t="n"/>
+      <c r="S24" s="48" t="n"/>
+      <c r="T24" s="48" t="n"/>
+      <c r="U24" s="48" t="n"/>
+      <c r="V24" s="48" t="n"/>
+      <c r="W24" s="48" t="n"/>
+      <c r="X24" s="48" t="n"/>
+      <c r="Y24" s="48" t="n"/>
+      <c r="Z24" s="48" t="n"/>
+      <c r="AA24" s="48" t="n"/>
+      <c r="AB24" s="48" t="n"/>
+      <c r="AC24" s="48" t="n"/>
+      <c r="AD24" s="48" t="n"/>
+      <c r="AE24" s="49" t="n"/>
       <c r="AF24" s="24" t="n"/>
-      <c r="AG24" s="44" t="n"/>
-      <c r="AH24" s="44" t="n"/>
-      <c r="AI24" s="44" t="n"/>
-      <c r="AJ24" s="44" t="n"/>
-      <c r="AK24" s="44" t="n"/>
-      <c r="AL24" s="44" t="n"/>
-      <c r="AM24" s="44" t="n"/>
-      <c r="AN24" s="44" t="n"/>
-      <c r="AO24" s="44" t="n"/>
-      <c r="AP24" s="44" t="n"/>
-      <c r="AQ24" s="44" t="n"/>
-      <c r="AR24" s="44" t="n"/>
-      <c r="AS24" s="45" t="n"/>
+      <c r="AG24" s="48" t="n"/>
+      <c r="AH24" s="48" t="n"/>
+      <c r="AI24" s="48" t="n"/>
+      <c r="AJ24" s="48" t="n"/>
+      <c r="AK24" s="48" t="n"/>
+      <c r="AL24" s="48" t="n"/>
+      <c r="AM24" s="48" t="n"/>
+      <c r="AN24" s="48" t="n"/>
+      <c r="AO24" s="48" t="n"/>
+      <c r="AP24" s="48" t="n"/>
+      <c r="AQ24" s="48" t="n"/>
+      <c r="AR24" s="48" t="n"/>
+      <c r="AS24" s="49" t="n"/>
       <c r="AT24" s="24" t="n"/>
-      <c r="AU24" s="44" t="n"/>
-      <c r="AV24" s="44" t="n"/>
-      <c r="AW24" s="44" t="n"/>
-      <c r="AX24" s="44" t="n"/>
-      <c r="AY24" s="44" t="n"/>
-      <c r="AZ24" s="44" t="n"/>
-      <c r="BA24" s="44" t="n"/>
-      <c r="BB24" s="44" t="n"/>
-      <c r="BC24" s="44" t="n"/>
-      <c r="BD24" s="44" t="n"/>
-      <c r="BE24" s="44" t="n"/>
-      <c r="BF24" s="44" t="n"/>
-      <c r="BG24" s="45" t="n"/>
+      <c r="AU24" s="48" t="n"/>
+      <c r="AV24" s="48" t="n"/>
+      <c r="AW24" s="48" t="n"/>
+      <c r="AX24" s="48" t="n"/>
+      <c r="AY24" s="48" t="n"/>
+      <c r="AZ24" s="48" t="n"/>
+      <c r="BA24" s="48" t="n"/>
+      <c r="BB24" s="48" t="n"/>
+      <c r="BC24" s="48" t="n"/>
+      <c r="BD24" s="48" t="n"/>
+      <c r="BE24" s="48" t="n"/>
+      <c r="BF24" s="48" t="n"/>
+      <c r="BG24" s="49" t="n"/>
     </row>
     <row r="25" ht="15" customHeight="1">
-      <c r="G25" s="21" t="n"/>
-      <c r="H25" s="21" t="n"/>
-      <c r="I25" s="21" t="n"/>
-      <c r="J25" s="21" t="n"/>
-      <c r="K25" s="21" t="n"/>
-      <c r="L25" s="21" t="n"/>
-      <c r="M25" s="21" t="n"/>
-      <c r="N25" s="21" t="n"/>
-      <c r="O25" s="21" t="n"/>
+      <c r="A25" s="55" t="n"/>
+      <c r="B25" s="55" t="n"/>
+      <c r="C25" s="55" t="n"/>
+      <c r="D25" s="55" t="n"/>
+      <c r="E25" s="55" t="n"/>
+      <c r="F25" s="55" t="n"/>
+      <c r="G25" s="67" t="n"/>
+      <c r="H25" s="67" t="n"/>
+      <c r="I25" s="67" t="n"/>
+      <c r="J25" s="67" t="n"/>
+      <c r="K25" s="67" t="n"/>
+      <c r="L25" s="67" t="n"/>
+      <c r="M25" s="67" t="n"/>
+      <c r="N25" s="67" t="n"/>
+      <c r="O25" s="67" t="n"/>
       <c r="P25" s="21" t="n"/>
       <c r="Q25" s="21" t="n"/>
-      <c r="R25" s="50" t="n"/>
-      <c r="AE25" s="51" t="n"/>
-      <c r="AF25" s="50" t="n"/>
-      <c r="AS25" s="51" t="n"/>
-      <c r="AT25" s="50" t="n"/>
-      <c r="BG25" s="51" t="n"/>
+      <c r="R25" s="68" t="n"/>
+      <c r="AE25" s="57" t="n"/>
+      <c r="AF25" s="68" t="n"/>
+      <c r="AS25" s="57" t="n"/>
+      <c r="AT25" s="68" t="n"/>
+      <c r="BG25" s="57" t="n"/>
     </row>
     <row r="26" ht="15" customHeight="1">
-      <c r="G26" s="21" t="n"/>
-      <c r="H26" s="21" t="n"/>
-      <c r="I26" s="21" t="n"/>
-      <c r="J26" s="21" t="n"/>
-      <c r="K26" s="21" t="n"/>
-      <c r="L26" s="21" t="n"/>
-      <c r="M26" s="21" t="n"/>
-      <c r="N26" s="21" t="n"/>
-      <c r="O26" s="21" t="n"/>
+      <c r="A26" s="55" t="n"/>
+      <c r="B26" s="55" t="n"/>
+      <c r="C26" s="55" t="n"/>
+      <c r="D26" s="55" t="n"/>
+      <c r="E26" s="55" t="n"/>
+      <c r="F26" s="55" t="n"/>
+      <c r="G26" s="67" t="n"/>
+      <c r="H26" s="67" t="n"/>
+      <c r="I26" s="67" t="n"/>
+      <c r="J26" s="67" t="n"/>
+      <c r="K26" s="67" t="n"/>
+      <c r="L26" s="67" t="n"/>
+      <c r="M26" s="67" t="n"/>
+      <c r="N26" s="67" t="n"/>
+      <c r="O26" s="67" t="n"/>
       <c r="P26" s="21" t="n"/>
       <c r="Q26" s="21" t="n"/>
-      <c r="R26" s="52" t="n"/>
-      <c r="S26" s="53" t="n"/>
-      <c r="T26" s="53" t="n"/>
-      <c r="U26" s="53" t="n"/>
-      <c r="V26" s="53" t="n"/>
-      <c r="W26" s="53" t="n"/>
-      <c r="X26" s="53" t="n"/>
-      <c r="Y26" s="53" t="n"/>
-      <c r="Z26" s="53" t="n"/>
-      <c r="AA26" s="53" t="n"/>
-      <c r="AB26" s="53" t="n"/>
-      <c r="AC26" s="53" t="n"/>
-      <c r="AD26" s="53" t="n"/>
-      <c r="AE26" s="54" t="n"/>
-      <c r="AF26" s="52" t="n"/>
-      <c r="AG26" s="53" t="n"/>
-      <c r="AH26" s="53" t="n"/>
-      <c r="AI26" s="53" t="n"/>
-      <c r="AJ26" s="53" t="n"/>
-      <c r="AK26" s="53" t="n"/>
-      <c r="AL26" s="53" t="n"/>
-      <c r="AM26" s="53" t="n"/>
-      <c r="AN26" s="53" t="n"/>
-      <c r="AO26" s="53" t="n"/>
-      <c r="AP26" s="53" t="n"/>
-      <c r="AQ26" s="53" t="n"/>
-      <c r="AR26" s="53" t="n"/>
-      <c r="AS26" s="54" t="n"/>
-      <c r="AT26" s="52" t="n"/>
-      <c r="AU26" s="53" t="n"/>
-      <c r="AV26" s="53" t="n"/>
-      <c r="AW26" s="53" t="n"/>
-      <c r="AX26" s="53" t="n"/>
-      <c r="AY26" s="53" t="n"/>
-      <c r="AZ26" s="53" t="n"/>
-      <c r="BA26" s="53" t="n"/>
-      <c r="BB26" s="53" t="n"/>
-      <c r="BC26" s="53" t="n"/>
-      <c r="BD26" s="53" t="n"/>
-      <c r="BE26" s="53" t="n"/>
-      <c r="BF26" s="53" t="n"/>
-      <c r="BG26" s="54" t="n"/>
+      <c r="R26" s="58" t="n"/>
+      <c r="S26" s="59" t="n"/>
+      <c r="T26" s="59" t="n"/>
+      <c r="U26" s="59" t="n"/>
+      <c r="V26" s="59" t="n"/>
+      <c r="W26" s="59" t="n"/>
+      <c r="X26" s="59" t="n"/>
+      <c r="Y26" s="59" t="n"/>
+      <c r="Z26" s="59" t="n"/>
+      <c r="AA26" s="59" t="n"/>
+      <c r="AB26" s="59" t="n"/>
+      <c r="AC26" s="59" t="n"/>
+      <c r="AD26" s="59" t="n"/>
+      <c r="AE26" s="60" t="n"/>
+      <c r="AF26" s="58" t="n"/>
+      <c r="AG26" s="59" t="n"/>
+      <c r="AH26" s="59" t="n"/>
+      <c r="AI26" s="59" t="n"/>
+      <c r="AJ26" s="59" t="n"/>
+      <c r="AK26" s="59" t="n"/>
+      <c r="AL26" s="59" t="n"/>
+      <c r="AM26" s="59" t="n"/>
+      <c r="AN26" s="59" t="n"/>
+      <c r="AO26" s="59" t="n"/>
+      <c r="AP26" s="59" t="n"/>
+      <c r="AQ26" s="59" t="n"/>
+      <c r="AR26" s="59" t="n"/>
+      <c r="AS26" s="60" t="n"/>
+      <c r="AT26" s="58" t="n"/>
+      <c r="AU26" s="59" t="n"/>
+      <c r="AV26" s="59" t="n"/>
+      <c r="AW26" s="59" t="n"/>
+      <c r="AX26" s="59" t="n"/>
+      <c r="AY26" s="59" t="n"/>
+      <c r="AZ26" s="59" t="n"/>
+      <c r="BA26" s="59" t="n"/>
+      <c r="BB26" s="59" t="n"/>
+      <c r="BC26" s="59" t="n"/>
+      <c r="BD26" s="59" t="n"/>
+      <c r="BE26" s="59" t="n"/>
+      <c r="BF26" s="59" t="n"/>
+      <c r="BG26" s="60" t="n"/>
     </row>
     <row r="27" ht="15" customHeight="1">
-      <c r="G27" s="21" t="n"/>
-      <c r="H27" s="21" t="n"/>
-      <c r="I27" s="21" t="n"/>
-      <c r="J27" s="21" t="n"/>
-      <c r="K27" s="21" t="n"/>
-      <c r="L27" s="21" t="n"/>
-      <c r="M27" s="21" t="n"/>
-      <c r="N27" s="21" t="n"/>
-      <c r="O27" s="21" t="n"/>
+      <c r="A27" s="55" t="n"/>
+      <c r="B27" s="55" t="n"/>
+      <c r="C27" s="55" t="n"/>
+      <c r="D27" s="55" t="n"/>
+      <c r="E27" s="55" t="n"/>
+      <c r="F27" s="55" t="n"/>
+      <c r="G27" s="67" t="n"/>
+      <c r="H27" s="67" t="n"/>
+      <c r="I27" s="67" t="n"/>
+      <c r="J27" s="67" t="n"/>
+      <c r="K27" s="67" t="n"/>
+      <c r="L27" s="67" t="n"/>
+      <c r="M27" s="67" t="n"/>
+      <c r="N27" s="67" t="n"/>
+      <c r="O27" s="67" t="n"/>
       <c r="P27" s="21" t="n"/>
       <c r="Q27" s="21" t="n"/>
       <c r="R27" s="24">
         <f>"Fecha :"&amp;BO3</f>
         <v/>
       </c>
-      <c r="S27" s="44" t="n"/>
-      <c r="T27" s="44" t="n"/>
-      <c r="U27" s="44" t="n"/>
-      <c r="V27" s="44" t="n"/>
-      <c r="W27" s="44" t="n"/>
-      <c r="X27" s="44" t="n"/>
-      <c r="Y27" s="44" t="n"/>
-      <c r="Z27" s="44" t="n"/>
-      <c r="AA27" s="44" t="n"/>
-      <c r="AB27" s="44" t="n"/>
-      <c r="AC27" s="44" t="n"/>
-      <c r="AD27" s="44" t="n"/>
-      <c r="AE27" s="45" t="n"/>
+      <c r="S27" s="48" t="n"/>
+      <c r="T27" s="48" t="n"/>
+      <c r="U27" s="48" t="n"/>
+      <c r="V27" s="48" t="n"/>
+      <c r="W27" s="48" t="n"/>
+      <c r="X27" s="48" t="n"/>
+      <c r="Y27" s="48" t="n"/>
+      <c r="Z27" s="48" t="n"/>
+      <c r="AA27" s="48" t="n"/>
+      <c r="AB27" s="48" t="n"/>
+      <c r="AC27" s="48" t="n"/>
+      <c r="AD27" s="48" t="n"/>
+      <c r="AE27" s="49" t="n"/>
       <c r="AF27" s="24">
         <f>"Fecha :"&amp;CC1</f>
         <v/>
       </c>
-      <c r="AG27" s="44" t="n"/>
-      <c r="AH27" s="44" t="n"/>
-      <c r="AI27" s="44" t="n"/>
-      <c r="AJ27" s="44" t="n"/>
-      <c r="AK27" s="44" t="n"/>
-      <c r="AL27" s="44" t="n"/>
-      <c r="AM27" s="44" t="n"/>
-      <c r="AN27" s="44" t="n"/>
-      <c r="AO27" s="44" t="n"/>
-      <c r="AP27" s="44" t="n"/>
-      <c r="AQ27" s="44" t="n"/>
-      <c r="AR27" s="44" t="n"/>
-      <c r="AS27" s="45" t="n"/>
+      <c r="AG27" s="48" t="n"/>
+      <c r="AH27" s="48" t="n"/>
+      <c r="AI27" s="48" t="n"/>
+      <c r="AJ27" s="48" t="n"/>
+      <c r="AK27" s="48" t="n"/>
+      <c r="AL27" s="48" t="n"/>
+      <c r="AM27" s="48" t="n"/>
+      <c r="AN27" s="48" t="n"/>
+      <c r="AO27" s="48" t="n"/>
+      <c r="AP27" s="48" t="n"/>
+      <c r="AQ27" s="48" t="n"/>
+      <c r="AR27" s="48" t="n"/>
+      <c r="AS27" s="49" t="n"/>
       <c r="AT27" s="24">
         <f>"Fecha :"&amp;CC2</f>
         <v/>
       </c>
-      <c r="AU27" s="44" t="n"/>
-      <c r="AV27" s="44" t="n"/>
-      <c r="AW27" s="44" t="n"/>
-      <c r="AX27" s="44" t="n"/>
-      <c r="AY27" s="44" t="n"/>
-      <c r="AZ27" s="44" t="n"/>
-      <c r="BA27" s="44" t="n"/>
-      <c r="BB27" s="44" t="n"/>
-      <c r="BC27" s="44" t="n"/>
-      <c r="BD27" s="44" t="n"/>
-      <c r="BE27" s="44" t="n"/>
-      <c r="BF27" s="44" t="n"/>
-      <c r="BG27" s="45" t="n"/>
+      <c r="AU27" s="48" t="n"/>
+      <c r="AV27" s="48" t="n"/>
+      <c r="AW27" s="48" t="n"/>
+      <c r="AX27" s="48" t="n"/>
+      <c r="AY27" s="48" t="n"/>
+      <c r="AZ27" s="48" t="n"/>
+      <c r="BA27" s="48" t="n"/>
+      <c r="BB27" s="48" t="n"/>
+      <c r="BC27" s="48" t="n"/>
+      <c r="BD27" s="48" t="n"/>
+      <c r="BE27" s="48" t="n"/>
+      <c r="BF27" s="48" t="n"/>
+      <c r="BG27" s="49" t="n"/>
     </row>
     <row r="28" ht="15" customHeight="1">
-      <c r="G28" s="21" t="n"/>
-      <c r="H28" s="21" t="n"/>
-      <c r="I28" s="21" t="n"/>
-      <c r="J28" s="21" t="n"/>
-      <c r="K28" s="21" t="n"/>
-      <c r="L28" s="21" t="n"/>
-      <c r="M28" s="21" t="n"/>
-      <c r="N28" s="21" t="n"/>
-      <c r="O28" s="21" t="n"/>
+      <c r="A28" s="55" t="n"/>
+      <c r="B28" s="55" t="n"/>
+      <c r="C28" s="55" t="n"/>
+      <c r="D28" s="55" t="n"/>
+      <c r="E28" s="55" t="n"/>
+      <c r="F28" s="55" t="n"/>
+      <c r="G28" s="67" t="n"/>
+      <c r="H28" s="67" t="n"/>
+      <c r="I28" s="67" t="n"/>
+      <c r="J28" s="67" t="n"/>
+      <c r="K28" s="67" t="n"/>
+      <c r="L28" s="67" t="n"/>
+      <c r="M28" s="67" t="n"/>
+      <c r="N28" s="67" t="n"/>
+      <c r="O28" s="67" t="n"/>
       <c r="P28" s="21" t="n"/>
       <c r="Q28" s="21" t="n"/>
-      <c r="R28" s="50" t="n"/>
-      <c r="AE28" s="51" t="n"/>
-      <c r="AF28" s="50" t="n"/>
-      <c r="AS28" s="51" t="n"/>
-      <c r="AT28" s="50" t="n"/>
-      <c r="BG28" s="51" t="n"/>
+      <c r="R28" s="68" t="n"/>
+      <c r="AE28" s="57" t="n"/>
+      <c r="AF28" s="68" t="n"/>
+      <c r="AS28" s="57" t="n"/>
+      <c r="AT28" s="68" t="n"/>
+      <c r="BG28" s="57" t="n"/>
     </row>
     <row r="29" ht="15" customHeight="1">
-      <c r="G29" s="21" t="n"/>
-      <c r="H29" s="21" t="n"/>
-      <c r="I29" s="21" t="n"/>
-      <c r="J29" s="21" t="n"/>
-      <c r="K29" s="21" t="n"/>
-      <c r="L29" s="21" t="n"/>
-      <c r="M29" s="21" t="n"/>
-      <c r="N29" s="21" t="n"/>
-      <c r="O29" s="21" t="n"/>
+      <c r="A29" s="55" t="n"/>
+      <c r="B29" s="55" t="n"/>
+      <c r="C29" s="55" t="n"/>
+      <c r="D29" s="55" t="n"/>
+      <c r="E29" s="55" t="n"/>
+      <c r="F29" s="55" t="n"/>
+      <c r="G29" s="67" t="n"/>
+      <c r="H29" s="67" t="n"/>
+      <c r="I29" s="67" t="n"/>
+      <c r="J29" s="67" t="n"/>
+      <c r="K29" s="67" t="n"/>
+      <c r="L29" s="67" t="n"/>
+      <c r="M29" s="67" t="n"/>
+      <c r="N29" s="67" t="n"/>
+      <c r="O29" s="67" t="n"/>
       <c r="P29" s="21" t="n"/>
       <c r="Q29" s="21" t="n"/>
-      <c r="R29" s="52" t="n"/>
-      <c r="S29" s="53" t="n"/>
-      <c r="T29" s="53" t="n"/>
-      <c r="U29" s="53" t="n"/>
-      <c r="V29" s="53" t="n"/>
-      <c r="W29" s="53" t="n"/>
-      <c r="X29" s="53" t="n"/>
-      <c r="Y29" s="53" t="n"/>
-      <c r="Z29" s="53" t="n"/>
-      <c r="AA29" s="53" t="n"/>
-      <c r="AB29" s="53" t="n"/>
-      <c r="AC29" s="53" t="n"/>
-      <c r="AD29" s="53" t="n"/>
-      <c r="AE29" s="54" t="n"/>
-      <c r="AF29" s="52" t="n"/>
-      <c r="AG29" s="53" t="n"/>
-      <c r="AH29" s="53" t="n"/>
-      <c r="AI29" s="53" t="n"/>
-      <c r="AJ29" s="53" t="n"/>
-      <c r="AK29" s="53" t="n"/>
-      <c r="AL29" s="53" t="n"/>
-      <c r="AM29" s="53" t="n"/>
-      <c r="AN29" s="53" t="n"/>
-      <c r="AO29" s="53" t="n"/>
-      <c r="AP29" s="53" t="n"/>
-      <c r="AQ29" s="53" t="n"/>
-      <c r="AR29" s="53" t="n"/>
-      <c r="AS29" s="54" t="n"/>
-      <c r="AT29" s="52" t="n"/>
-      <c r="AU29" s="53" t="n"/>
-      <c r="AV29" s="53" t="n"/>
-      <c r="AW29" s="53" t="n"/>
-      <c r="AX29" s="53" t="n"/>
-      <c r="AY29" s="53" t="n"/>
-      <c r="AZ29" s="53" t="n"/>
-      <c r="BA29" s="53" t="n"/>
-      <c r="BB29" s="53" t="n"/>
-      <c r="BC29" s="53" t="n"/>
-      <c r="BD29" s="53" t="n"/>
-      <c r="BE29" s="53" t="n"/>
-      <c r="BF29" s="53" t="n"/>
-      <c r="BG29" s="54" t="n"/>
+      <c r="R29" s="58" t="n"/>
+      <c r="S29" s="59" t="n"/>
+      <c r="T29" s="59" t="n"/>
+      <c r="U29" s="59" t="n"/>
+      <c r="V29" s="59" t="n"/>
+      <c r="W29" s="59" t="n"/>
+      <c r="X29" s="59" t="n"/>
+      <c r="Y29" s="59" t="n"/>
+      <c r="Z29" s="59" t="n"/>
+      <c r="AA29" s="59" t="n"/>
+      <c r="AB29" s="59" t="n"/>
+      <c r="AC29" s="59" t="n"/>
+      <c r="AD29" s="59" t="n"/>
+      <c r="AE29" s="60" t="n"/>
+      <c r="AF29" s="58" t="n"/>
+      <c r="AG29" s="59" t="n"/>
+      <c r="AH29" s="59" t="n"/>
+      <c r="AI29" s="59" t="n"/>
+      <c r="AJ29" s="59" t="n"/>
+      <c r="AK29" s="59" t="n"/>
+      <c r="AL29" s="59" t="n"/>
+      <c r="AM29" s="59" t="n"/>
+      <c r="AN29" s="59" t="n"/>
+      <c r="AO29" s="59" t="n"/>
+      <c r="AP29" s="59" t="n"/>
+      <c r="AQ29" s="59" t="n"/>
+      <c r="AR29" s="59" t="n"/>
+      <c r="AS29" s="60" t="n"/>
+      <c r="AT29" s="58" t="n"/>
+      <c r="AU29" s="59" t="n"/>
+      <c r="AV29" s="59" t="n"/>
+      <c r="AW29" s="59" t="n"/>
+      <c r="AX29" s="59" t="n"/>
+      <c r="AY29" s="59" t="n"/>
+      <c r="AZ29" s="59" t="n"/>
+      <c r="BA29" s="59" t="n"/>
+      <c r="BB29" s="59" t="n"/>
+      <c r="BC29" s="59" t="n"/>
+      <c r="BD29" s="59" t="n"/>
+      <c r="BE29" s="59" t="n"/>
+      <c r="BF29" s="59" t="n"/>
+      <c r="BG29" s="60" t="n"/>
     </row>
     <row r="30" ht="15" customHeight="1">
-      <c r="G30" s="21" t="n"/>
-      <c r="H30" s="21" t="n"/>
-      <c r="I30" s="21" t="n"/>
-      <c r="J30" s="21" t="n"/>
-      <c r="K30" s="21" t="n"/>
-      <c r="L30" s="21" t="n"/>
-      <c r="M30" s="21" t="n"/>
-      <c r="N30" s="21" t="n"/>
-      <c r="O30" s="21" t="n"/>
+      <c r="A30" s="55" t="n"/>
+      <c r="B30" s="55" t="n"/>
+      <c r="C30" s="55" t="n"/>
+      <c r="D30" s="55" t="n"/>
+      <c r="E30" s="55" t="n"/>
+      <c r="F30" s="55" t="n"/>
+      <c r="G30" s="67" t="n"/>
+      <c r="H30" s="67" t="n"/>
+      <c r="I30" s="67" t="n"/>
+      <c r="J30" s="67" t="n"/>
+      <c r="K30" s="67" t="n"/>
+      <c r="L30" s="67" t="n"/>
+      <c r="M30" s="67" t="n"/>
+      <c r="N30" s="67" t="n"/>
+      <c r="O30" s="67" t="n"/>
       <c r="P30" s="21" t="n"/>
       <c r="Q30" s="21" t="n"/>
       <c r="R30" s="21" t="n"/>
@@ -2421,15 +2709,21 @@
       <c r="AF30" s="21" t="n"/>
     </row>
     <row r="31" ht="15" customHeight="1">
-      <c r="G31" s="21" t="n"/>
-      <c r="H31" s="21" t="n"/>
-      <c r="I31" s="21" t="n"/>
-      <c r="J31" s="21" t="n"/>
-      <c r="K31" s="21" t="n"/>
-      <c r="L31" s="21" t="n"/>
-      <c r="M31" s="21" t="n"/>
-      <c r="N31" s="21" t="n"/>
-      <c r="O31" s="21" t="n"/>
+      <c r="A31" s="55" t="n"/>
+      <c r="B31" s="55" t="n"/>
+      <c r="C31" s="55" t="n"/>
+      <c r="D31" s="55" t="n"/>
+      <c r="E31" s="55" t="n"/>
+      <c r="F31" s="55" t="n"/>
+      <c r="G31" s="67" t="n"/>
+      <c r="H31" s="67" t="n"/>
+      <c r="I31" s="67" t="n"/>
+      <c r="J31" s="67" t="n"/>
+      <c r="K31" s="67" t="n"/>
+      <c r="L31" s="67" t="n"/>
+      <c r="M31" s="67" t="n"/>
+      <c r="N31" s="67" t="n"/>
+      <c r="O31" s="67" t="n"/>
       <c r="P31" s="21" t="n"/>
       <c r="Q31" s="21" t="n"/>
       <c r="R31" s="21" t="n"/>
@@ -2449,15 +2743,21 @@
       <c r="AF31" s="21" t="n"/>
     </row>
     <row r="32" ht="15" customHeight="1">
-      <c r="G32" s="21" t="n"/>
-      <c r="H32" s="21" t="n"/>
-      <c r="I32" s="21" t="n"/>
-      <c r="J32" s="21" t="n"/>
-      <c r="K32" s="21" t="n"/>
-      <c r="L32" s="21" t="n"/>
-      <c r="M32" s="21" t="n"/>
-      <c r="N32" s="21" t="n"/>
-      <c r="O32" s="21" t="n"/>
+      <c r="A32" s="55" t="n"/>
+      <c r="B32" s="55" t="n"/>
+      <c r="C32" s="55" t="n"/>
+      <c r="D32" s="55" t="n"/>
+      <c r="E32" s="55" t="n"/>
+      <c r="F32" s="55" t="n"/>
+      <c r="G32" s="67" t="n"/>
+      <c r="H32" s="67" t="n"/>
+      <c r="I32" s="67" t="n"/>
+      <c r="J32" s="67" t="n"/>
+      <c r="K32" s="67" t="n"/>
+      <c r="L32" s="67" t="n"/>
+      <c r="M32" s="67" t="n"/>
+      <c r="N32" s="67" t="n"/>
+      <c r="O32" s="67" t="n"/>
       <c r="P32" s="21" t="n"/>
       <c r="Q32" s="21" t="n"/>
       <c r="R32" s="21" t="n"/>
@@ -2477,15 +2777,21 @@
       <c r="AF32" s="21" t="n"/>
     </row>
     <row r="33" ht="15" customHeight="1">
-      <c r="G33" s="21" t="n"/>
-      <c r="H33" s="21" t="n"/>
-      <c r="I33" s="21" t="n"/>
-      <c r="J33" s="21" t="n"/>
-      <c r="K33" s="21" t="n"/>
-      <c r="L33" s="21" t="n"/>
-      <c r="M33" s="21" t="n"/>
-      <c r="N33" s="21" t="n"/>
-      <c r="O33" s="21" t="n"/>
+      <c r="A33" s="55" t="n"/>
+      <c r="B33" s="55" t="n"/>
+      <c r="C33" s="55" t="n"/>
+      <c r="D33" s="55" t="n"/>
+      <c r="E33" s="55" t="n"/>
+      <c r="F33" s="55" t="n"/>
+      <c r="G33" s="67" t="n"/>
+      <c r="H33" s="67" t="n"/>
+      <c r="I33" s="67" t="n"/>
+      <c r="J33" s="67" t="n"/>
+      <c r="K33" s="67" t="n"/>
+      <c r="L33" s="67" t="n"/>
+      <c r="M33" s="67" t="n"/>
+      <c r="N33" s="67" t="n"/>
+      <c r="O33" s="67" t="n"/>
       <c r="P33" s="21" t="n"/>
       <c r="Q33" s="21" t="n"/>
       <c r="R33" s="21" t="n"/>
@@ -2505,15 +2811,21 @@
       <c r="AF33" s="21" t="n"/>
     </row>
     <row r="34" ht="15" customHeight="1">
-      <c r="G34" s="21" t="n"/>
-      <c r="H34" s="21" t="n"/>
-      <c r="I34" s="21" t="n"/>
-      <c r="J34" s="21" t="n"/>
-      <c r="K34" s="21" t="n"/>
-      <c r="L34" s="21" t="n"/>
-      <c r="M34" s="21" t="n"/>
-      <c r="N34" s="21" t="n"/>
-      <c r="O34" s="21" t="n"/>
+      <c r="A34" s="55" t="n"/>
+      <c r="B34" s="55" t="n"/>
+      <c r="C34" s="55" t="n"/>
+      <c r="D34" s="55" t="n"/>
+      <c r="E34" s="55" t="n"/>
+      <c r="F34" s="55" t="n"/>
+      <c r="G34" s="67" t="n"/>
+      <c r="H34" s="67" t="n"/>
+      <c r="I34" s="67" t="n"/>
+      <c r="J34" s="67" t="n"/>
+      <c r="K34" s="67" t="n"/>
+      <c r="L34" s="67" t="n"/>
+      <c r="M34" s="67" t="n"/>
+      <c r="N34" s="67" t="n"/>
+      <c r="O34" s="67" t="n"/>
       <c r="P34" s="21" t="n"/>
       <c r="Q34" s="21" t="n"/>
       <c r="R34" s="21" t="n"/>
@@ -2533,15 +2845,21 @@
       <c r="AF34" s="21" t="n"/>
     </row>
     <row r="35" ht="15" customHeight="1">
-      <c r="G35" s="21" t="n"/>
-      <c r="H35" s="21" t="n"/>
-      <c r="I35" s="21" t="n"/>
-      <c r="J35" s="21" t="n"/>
-      <c r="K35" s="21" t="n"/>
-      <c r="L35" s="21" t="n"/>
-      <c r="M35" s="21" t="n"/>
-      <c r="N35" s="21" t="n"/>
-      <c r="O35" s="21" t="n"/>
+      <c r="A35" s="55" t="n"/>
+      <c r="B35" s="55" t="n"/>
+      <c r="C35" s="55" t="n"/>
+      <c r="D35" s="55" t="n"/>
+      <c r="E35" s="55" t="n"/>
+      <c r="F35" s="55" t="n"/>
+      <c r="G35" s="67" t="n"/>
+      <c r="H35" s="67" t="n"/>
+      <c r="I35" s="67" t="n"/>
+      <c r="J35" s="67" t="n"/>
+      <c r="K35" s="67" t="n"/>
+      <c r="L35" s="67" t="n"/>
+      <c r="M35" s="67" t="n"/>
+      <c r="N35" s="67" t="n"/>
+      <c r="O35" s="67" t="n"/>
       <c r="P35" s="21" t="n"/>
       <c r="Q35" s="21" t="n"/>
       <c r="R35" s="21" t="n"/>
@@ -2561,15 +2879,21 @@
       <c r="AF35" s="21" t="n"/>
     </row>
     <row r="36" ht="15" customHeight="1">
-      <c r="G36" s="21" t="n"/>
-      <c r="H36" s="21" t="n"/>
-      <c r="I36" s="21" t="n"/>
-      <c r="J36" s="21" t="n"/>
-      <c r="K36" s="21" t="n"/>
-      <c r="L36" s="21" t="n"/>
-      <c r="M36" s="21" t="n"/>
-      <c r="N36" s="21" t="n"/>
-      <c r="O36" s="21" t="n"/>
+      <c r="A36" s="55" t="n"/>
+      <c r="B36" s="55" t="n"/>
+      <c r="C36" s="55" t="n"/>
+      <c r="D36" s="55" t="n"/>
+      <c r="E36" s="55" t="n"/>
+      <c r="F36" s="55" t="n"/>
+      <c r="G36" s="67" t="n"/>
+      <c r="H36" s="67" t="n"/>
+      <c r="I36" s="67" t="n"/>
+      <c r="J36" s="67" t="n"/>
+      <c r="K36" s="67" t="n"/>
+      <c r="L36" s="67" t="n"/>
+      <c r="M36" s="67" t="n"/>
+      <c r="N36" s="67" t="n"/>
+      <c r="O36" s="67" t="n"/>
       <c r="P36" s="21" t="n"/>
       <c r="Q36" s="21" t="n"/>
       <c r="R36" s="21" t="n"/>
@@ -2590,15 +2914,21 @@
       <c r="BK36" s="21" t="n"/>
     </row>
     <row r="37" ht="15" customHeight="1">
-      <c r="G37" s="21" t="n"/>
-      <c r="H37" s="21" t="n"/>
-      <c r="I37" s="21" t="n"/>
-      <c r="J37" s="21" t="n"/>
-      <c r="K37" s="21" t="n"/>
-      <c r="L37" s="21" t="n"/>
-      <c r="M37" s="21" t="n"/>
-      <c r="N37" s="21" t="n"/>
-      <c r="O37" s="21" t="n"/>
+      <c r="A37" s="55" t="n"/>
+      <c r="B37" s="55" t="n"/>
+      <c r="C37" s="55" t="n"/>
+      <c r="D37" s="55" t="n"/>
+      <c r="E37" s="55" t="n"/>
+      <c r="F37" s="55" t="n"/>
+      <c r="G37" s="67" t="n"/>
+      <c r="H37" s="67" t="n"/>
+      <c r="I37" s="67" t="n"/>
+      <c r="J37" s="67" t="n"/>
+      <c r="K37" s="67" t="n"/>
+      <c r="L37" s="67" t="n"/>
+      <c r="M37" s="67" t="n"/>
+      <c r="N37" s="67" t="n"/>
+      <c r="O37" s="67" t="n"/>
       <c r="P37" s="21" t="n"/>
       <c r="Q37" s="21" t="n"/>
       <c r="R37" s="21" t="n"/>
@@ -2618,15 +2948,21 @@
       <c r="AF37" s="21" t="n"/>
     </row>
     <row r="38" ht="15" customHeight="1">
-      <c r="G38" s="21" t="n"/>
-      <c r="H38" s="21" t="n"/>
-      <c r="I38" s="21" t="n"/>
-      <c r="J38" s="21" t="n"/>
-      <c r="K38" s="21" t="n"/>
-      <c r="L38" s="21" t="n"/>
-      <c r="M38" s="21" t="n"/>
-      <c r="N38" s="21" t="n"/>
-      <c r="O38" s="21" t="n"/>
+      <c r="A38" s="55" t="n"/>
+      <c r="B38" s="55" t="n"/>
+      <c r="C38" s="55" t="n"/>
+      <c r="D38" s="55" t="n"/>
+      <c r="E38" s="55" t="n"/>
+      <c r="F38" s="55" t="n"/>
+      <c r="G38" s="67" t="n"/>
+      <c r="H38" s="67" t="n"/>
+      <c r="I38" s="67" t="n"/>
+      <c r="J38" s="67" t="n"/>
+      <c r="K38" s="67" t="n"/>
+      <c r="L38" s="67" t="n"/>
+      <c r="M38" s="67" t="n"/>
+      <c r="N38" s="67" t="n"/>
+      <c r="O38" s="67" t="n"/>
       <c r="P38" s="21" t="n"/>
       <c r="Q38" s="21" t="n"/>
       <c r="R38" s="21" t="n"/>
@@ -2646,476 +2982,608 @@
       <c r="AF38" s="21" t="n"/>
     </row>
     <row r="39" ht="15" customHeight="1">
-      <c r="G39" s="21" t="n"/>
-      <c r="H39" s="21" t="n"/>
-      <c r="I39" s="21" t="n"/>
-      <c r="J39" s="21" t="n"/>
-      <c r="K39" s="21" t="n"/>
-      <c r="L39" s="21" t="n"/>
-      <c r="M39" s="21" t="n"/>
-      <c r="N39" s="21" t="n"/>
-      <c r="O39" s="42" t="inlineStr">
+      <c r="A39" s="55" t="n"/>
+      <c r="B39" s="55" t="n"/>
+      <c r="C39" s="55" t="n"/>
+      <c r="D39" s="55" t="n"/>
+      <c r="E39" s="55" t="n"/>
+      <c r="F39" s="55" t="n"/>
+      <c r="G39" s="67" t="n"/>
+      <c r="H39" s="67" t="n"/>
+      <c r="I39" s="67" t="n"/>
+      <c r="J39" s="67" t="n"/>
+      <c r="K39" s="67" t="n"/>
+      <c r="L39" s="67" t="n"/>
+      <c r="M39" s="67" t="n"/>
+      <c r="N39" s="67" t="n"/>
+      <c r="O39" s="69" t="inlineStr">
         <is>
           <t>Versión</t>
         </is>
       </c>
-      <c r="P39" s="44" t="n"/>
-      <c r="Q39" s="44" t="n"/>
-      <c r="R39" s="44" t="n"/>
-      <c r="S39" s="44" t="n"/>
-      <c r="T39" s="44" t="n"/>
-      <c r="U39" s="45" t="n"/>
+      <c r="P39" s="48" t="n"/>
+      <c r="Q39" s="48" t="n"/>
+      <c r="R39" s="48" t="n"/>
+      <c r="S39" s="48" t="n"/>
+      <c r="T39" s="48" t="n"/>
+      <c r="U39" s="49" t="n"/>
       <c r="V39" s="42" t="inlineStr">
         <is>
           <t>Autor</t>
         </is>
       </c>
-      <c r="W39" s="44" t="n"/>
-      <c r="X39" s="44" t="n"/>
-      <c r="Y39" s="44" t="n"/>
-      <c r="Z39" s="44" t="n"/>
-      <c r="AA39" s="44" t="n"/>
-      <c r="AB39" s="45" t="n"/>
+      <c r="W39" s="48" t="n"/>
+      <c r="X39" s="48" t="n"/>
+      <c r="Y39" s="48" t="n"/>
+      <c r="Z39" s="48" t="n"/>
+      <c r="AA39" s="48" t="n"/>
+      <c r="AB39" s="49" t="n"/>
       <c r="AC39" s="43" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
       </c>
-      <c r="AD39" s="44" t="n"/>
-      <c r="AE39" s="44" t="n"/>
-      <c r="AF39" s="44" t="n"/>
-      <c r="AG39" s="44" t="n"/>
-      <c r="AH39" s="44" t="n"/>
-      <c r="AI39" s="44" t="n"/>
-      <c r="AJ39" s="44" t="n"/>
-      <c r="AK39" s="44" t="n"/>
-      <c r="AL39" s="44" t="n"/>
-      <c r="AM39" s="44" t="n"/>
-      <c r="AN39" s="44" t="n"/>
-      <c r="AO39" s="45" t="n"/>
+      <c r="AD39" s="48" t="n"/>
+      <c r="AE39" s="48" t="n"/>
+      <c r="AF39" s="48" t="n"/>
+      <c r="AG39" s="48" t="n"/>
+      <c r="AH39" s="48" t="n"/>
+      <c r="AI39" s="48" t="n"/>
+      <c r="AJ39" s="48" t="n"/>
+      <c r="AK39" s="48" t="n"/>
+      <c r="AL39" s="48" t="n"/>
+      <c r="AM39" s="48" t="n"/>
+      <c r="AN39" s="48" t="n"/>
+      <c r="AO39" s="49" t="n"/>
       <c r="AP39" s="42" t="inlineStr">
         <is>
           <t>Fecha de elaboración</t>
         </is>
       </c>
-      <c r="AQ39" s="44" t="n"/>
-      <c r="AR39" s="44" t="n"/>
-      <c r="AS39" s="44" t="n"/>
-      <c r="AT39" s="44" t="n"/>
-      <c r="AU39" s="44" t="n"/>
-      <c r="AV39" s="45" t="n"/>
+      <c r="AQ39" s="48" t="n"/>
+      <c r="AR39" s="48" t="n"/>
+      <c r="AS39" s="48" t="n"/>
+      <c r="AT39" s="48" t="n"/>
+      <c r="AU39" s="48" t="n"/>
+      <c r="AV39" s="49" t="n"/>
       <c r="AW39" s="42" t="inlineStr">
         <is>
           <t>Fecha de revisión</t>
         </is>
       </c>
-      <c r="AX39" s="44" t="n"/>
-      <c r="AY39" s="44" t="n"/>
-      <c r="AZ39" s="44" t="n"/>
-      <c r="BA39" s="44" t="n"/>
-      <c r="BB39" s="44" t="n"/>
-      <c r="BC39" s="45" t="n"/>
+      <c r="AX39" s="48" t="n"/>
+      <c r="AY39" s="48" t="n"/>
+      <c r="AZ39" s="48" t="n"/>
+      <c r="BA39" s="48" t="n"/>
+      <c r="BB39" s="48" t="n"/>
+      <c r="BC39" s="49" t="n"/>
       <c r="BD39" s="42" t="inlineStr">
         <is>
           <t>Revisado por</t>
         </is>
       </c>
-      <c r="BE39" s="44" t="n"/>
-      <c r="BF39" s="44" t="n"/>
-      <c r="BG39" s="44" t="n"/>
-      <c r="BH39" s="44" t="n"/>
-      <c r="BI39" s="44" t="n"/>
-      <c r="BJ39" s="45" t="n"/>
+      <c r="BE39" s="48" t="n"/>
+      <c r="BF39" s="48" t="n"/>
+      <c r="BG39" s="48" t="n"/>
+      <c r="BH39" s="48" t="n"/>
+      <c r="BI39" s="48" t="n"/>
+      <c r="BJ39" s="49" t="n"/>
     </row>
     <row r="40" ht="15" customHeight="1">
-      <c r="G40" s="21" t="n"/>
-      <c r="H40" s="21" t="n"/>
-      <c r="I40" s="21" t="n"/>
-      <c r="J40" s="21" t="n"/>
-      <c r="K40" s="21" t="n"/>
-      <c r="L40" s="21" t="n"/>
-      <c r="M40" s="21" t="n"/>
-      <c r="N40" s="21" t="n"/>
-      <c r="O40" s="50" t="n"/>
-      <c r="U40" s="51" t="n"/>
-      <c r="V40" s="50" t="n"/>
-      <c r="AB40" s="51" t="n"/>
-      <c r="AC40" s="50" t="n"/>
-      <c r="AO40" s="51" t="n"/>
-      <c r="AP40" s="50" t="n"/>
-      <c r="AV40" s="51" t="n"/>
-      <c r="AW40" s="50" t="n"/>
-      <c r="BC40" s="51" t="n"/>
-      <c r="BD40" s="50" t="n"/>
-      <c r="BJ40" s="51" t="n"/>
+      <c r="A40" s="55" t="n"/>
+      <c r="B40" s="55" t="n"/>
+      <c r="C40" s="55" t="n"/>
+      <c r="D40" s="55" t="n"/>
+      <c r="E40" s="55" t="n"/>
+      <c r="F40" s="55" t="n"/>
+      <c r="G40" s="67" t="n"/>
+      <c r="H40" s="67" t="n"/>
+      <c r="I40" s="67" t="n"/>
+      <c r="J40" s="67" t="n"/>
+      <c r="K40" s="67" t="n"/>
+      <c r="L40" s="67" t="n"/>
+      <c r="M40" s="67" t="n"/>
+      <c r="N40" s="67" t="n"/>
+      <c r="O40" s="54" t="n"/>
+      <c r="U40" s="57" t="n"/>
+      <c r="V40" s="68" t="n"/>
+      <c r="AB40" s="57" t="n"/>
+      <c r="AC40" s="68" t="n"/>
+      <c r="AO40" s="57" t="n"/>
+      <c r="AP40" s="68" t="n"/>
+      <c r="AV40" s="57" t="n"/>
+      <c r="AW40" s="68" t="n"/>
+      <c r="BC40" s="57" t="n"/>
+      <c r="BD40" s="68" t="n"/>
+      <c r="BJ40" s="57" t="n"/>
     </row>
     <row r="41" ht="15" customHeight="1">
-      <c r="G41" s="21" t="n"/>
-      <c r="H41" s="21" t="n"/>
-      <c r="I41" s="21" t="n"/>
-      <c r="J41" s="21" t="n"/>
-      <c r="K41" s="21" t="n"/>
-      <c r="L41" s="21" t="n"/>
-      <c r="M41" s="21" t="n"/>
-      <c r="N41" s="21" t="n"/>
-      <c r="O41" s="52" t="n"/>
-      <c r="P41" s="53" t="n"/>
-      <c r="Q41" s="53" t="n"/>
-      <c r="R41" s="53" t="n"/>
-      <c r="S41" s="53" t="n"/>
-      <c r="T41" s="53" t="n"/>
-      <c r="U41" s="54" t="n"/>
-      <c r="V41" s="52" t="n"/>
-      <c r="W41" s="53" t="n"/>
-      <c r="X41" s="53" t="n"/>
-      <c r="Y41" s="53" t="n"/>
-      <c r="Z41" s="53" t="n"/>
-      <c r="AA41" s="53" t="n"/>
-      <c r="AB41" s="54" t="n"/>
-      <c r="AC41" s="52" t="n"/>
-      <c r="AD41" s="53" t="n"/>
-      <c r="AE41" s="53" t="n"/>
-      <c r="AF41" s="53" t="n"/>
-      <c r="AG41" s="53" t="n"/>
-      <c r="AH41" s="53" t="n"/>
-      <c r="AI41" s="53" t="n"/>
-      <c r="AJ41" s="53" t="n"/>
-      <c r="AK41" s="53" t="n"/>
-      <c r="AL41" s="53" t="n"/>
-      <c r="AM41" s="53" t="n"/>
-      <c r="AN41" s="53" t="n"/>
-      <c r="AO41" s="54" t="n"/>
-      <c r="AP41" s="52" t="n"/>
-      <c r="AQ41" s="53" t="n"/>
-      <c r="AR41" s="53" t="n"/>
-      <c r="AS41" s="53" t="n"/>
-      <c r="AT41" s="53" t="n"/>
-      <c r="AU41" s="53" t="n"/>
-      <c r="AV41" s="54" t="n"/>
-      <c r="AW41" s="52" t="n"/>
-      <c r="AX41" s="53" t="n"/>
-      <c r="AY41" s="53" t="n"/>
-      <c r="AZ41" s="53" t="n"/>
-      <c r="BA41" s="53" t="n"/>
-      <c r="BB41" s="53" t="n"/>
-      <c r="BC41" s="54" t="n"/>
-      <c r="BD41" s="52" t="n"/>
-      <c r="BE41" s="53" t="n"/>
-      <c r="BF41" s="53" t="n"/>
-      <c r="BG41" s="53" t="n"/>
-      <c r="BH41" s="53" t="n"/>
-      <c r="BI41" s="53" t="n"/>
-      <c r="BJ41" s="54" t="n"/>
+      <c r="A41" s="55" t="n"/>
+      <c r="B41" s="55" t="n"/>
+      <c r="C41" s="55" t="n"/>
+      <c r="D41" s="55" t="n"/>
+      <c r="E41" s="55" t="n"/>
+      <c r="F41" s="55" t="n"/>
+      <c r="G41" s="67" t="n"/>
+      <c r="H41" s="67" t="n"/>
+      <c r="I41" s="67" t="n"/>
+      <c r="J41" s="67" t="n"/>
+      <c r="K41" s="67" t="n"/>
+      <c r="L41" s="67" t="n"/>
+      <c r="M41" s="67" t="n"/>
+      <c r="N41" s="67" t="n"/>
+      <c r="O41" s="61" t="n"/>
+      <c r="P41" s="59" t="n"/>
+      <c r="Q41" s="59" t="n"/>
+      <c r="R41" s="59" t="n"/>
+      <c r="S41" s="59" t="n"/>
+      <c r="T41" s="59" t="n"/>
+      <c r="U41" s="60" t="n"/>
+      <c r="V41" s="58" t="n"/>
+      <c r="W41" s="59" t="n"/>
+      <c r="X41" s="59" t="n"/>
+      <c r="Y41" s="59" t="n"/>
+      <c r="Z41" s="59" t="n"/>
+      <c r="AA41" s="59" t="n"/>
+      <c r="AB41" s="60" t="n"/>
+      <c r="AC41" s="58" t="n"/>
+      <c r="AD41" s="59" t="n"/>
+      <c r="AE41" s="59" t="n"/>
+      <c r="AF41" s="59" t="n"/>
+      <c r="AG41" s="59" t="n"/>
+      <c r="AH41" s="59" t="n"/>
+      <c r="AI41" s="59" t="n"/>
+      <c r="AJ41" s="59" t="n"/>
+      <c r="AK41" s="59" t="n"/>
+      <c r="AL41" s="59" t="n"/>
+      <c r="AM41" s="59" t="n"/>
+      <c r="AN41" s="59" t="n"/>
+      <c r="AO41" s="60" t="n"/>
+      <c r="AP41" s="58" t="n"/>
+      <c r="AQ41" s="59" t="n"/>
+      <c r="AR41" s="59" t="n"/>
+      <c r="AS41" s="59" t="n"/>
+      <c r="AT41" s="59" t="n"/>
+      <c r="AU41" s="59" t="n"/>
+      <c r="AV41" s="60" t="n"/>
+      <c r="AW41" s="58" t="n"/>
+      <c r="AX41" s="59" t="n"/>
+      <c r="AY41" s="59" t="n"/>
+      <c r="AZ41" s="59" t="n"/>
+      <c r="BA41" s="59" t="n"/>
+      <c r="BB41" s="59" t="n"/>
+      <c r="BC41" s="60" t="n"/>
+      <c r="BD41" s="58" t="n"/>
+      <c r="BE41" s="59" t="n"/>
+      <c r="BF41" s="59" t="n"/>
+      <c r="BG41" s="59" t="n"/>
+      <c r="BH41" s="59" t="n"/>
+      <c r="BI41" s="59" t="n"/>
+      <c r="BJ41" s="60" t="n"/>
     </row>
     <row r="42" ht="15" customHeight="1">
-      <c r="G42" s="21" t="n"/>
-      <c r="H42" s="21" t="n"/>
-      <c r="I42" s="21" t="n"/>
-      <c r="J42" s="21" t="n"/>
-      <c r="K42" s="21" t="n"/>
-      <c r="L42" s="21" t="n"/>
-      <c r="M42" s="21" t="n"/>
-      <c r="N42" s="21" t="n"/>
-      <c r="O42" s="37" t="inlineStr">
+      <c r="A42" s="55" t="n"/>
+      <c r="B42" s="55" t="n"/>
+      <c r="C42" s="55" t="n"/>
+      <c r="D42" s="55" t="n"/>
+      <c r="E42" s="55" t="n"/>
+      <c r="F42" s="55" t="n"/>
+      <c r="G42" s="67" t="n"/>
+      <c r="H42" s="67" t="n"/>
+      <c r="I42" s="67" t="n"/>
+      <c r="J42" s="67" t="n"/>
+      <c r="K42" s="67" t="n"/>
+      <c r="L42" s="67" t="n"/>
+      <c r="M42" s="67" t="n"/>
+      <c r="N42" s="67" t="n"/>
+      <c r="O42" s="70" t="inlineStr">
         <is>
           <t>CERO (0)</t>
         </is>
       </c>
-      <c r="P42" s="44" t="n"/>
-      <c r="Q42" s="44" t="n"/>
-      <c r="R42" s="44" t="n"/>
-      <c r="S42" s="44" t="n"/>
-      <c r="T42" s="44" t="n"/>
-      <c r="U42" s="45" t="n"/>
+      <c r="P42" s="48" t="n"/>
+      <c r="Q42" s="48" t="n"/>
+      <c r="R42" s="48" t="n"/>
+      <c r="S42" s="48" t="n"/>
+      <c r="T42" s="48" t="n"/>
+      <c r="U42" s="49" t="n"/>
       <c r="V42" s="37" t="inlineStr">
         <is>
           <t>J.ARBOLEDA</t>
         </is>
       </c>
-      <c r="W42" s="44" t="n"/>
-      <c r="X42" s="44" t="n"/>
-      <c r="Y42" s="44" t="n"/>
-      <c r="Z42" s="44" t="n"/>
-      <c r="AA42" s="44" t="n"/>
-      <c r="AB42" s="45" t="n"/>
+      <c r="W42" s="48" t="n"/>
+      <c r="X42" s="48" t="n"/>
+      <c r="Y42" s="48" t="n"/>
+      <c r="Z42" s="48" t="n"/>
+      <c r="AA42" s="48" t="n"/>
+      <c r="AB42" s="49" t="n"/>
       <c r="AC42" s="38" t="inlineStr">
         <is>
           <t>Emitido para cotizacion</t>
         </is>
       </c>
-      <c r="AD42" s="44" t="n"/>
-      <c r="AE42" s="44" t="n"/>
-      <c r="AF42" s="44" t="n"/>
-      <c r="AG42" s="44" t="n"/>
-      <c r="AH42" s="44" t="n"/>
-      <c r="AI42" s="44" t="n"/>
-      <c r="AJ42" s="44" t="n"/>
-      <c r="AK42" s="44" t="n"/>
-      <c r="AL42" s="44" t="n"/>
-      <c r="AM42" s="44" t="n"/>
-      <c r="AN42" s="44" t="n"/>
-      <c r="AO42" s="45" t="n"/>
+      <c r="AD42" s="48" t="n"/>
+      <c r="AE42" s="48" t="n"/>
+      <c r="AF42" s="48" t="n"/>
+      <c r="AG42" s="48" t="n"/>
+      <c r="AH42" s="48" t="n"/>
+      <c r="AI42" s="48" t="n"/>
+      <c r="AJ42" s="48" t="n"/>
+      <c r="AK42" s="48" t="n"/>
+      <c r="AL42" s="48" t="n"/>
+      <c r="AM42" s="48" t="n"/>
+      <c r="AN42" s="48" t="n"/>
+      <c r="AO42" s="49" t="n"/>
       <c r="AP42" s="39">
         <f>BO3</f>
         <v/>
       </c>
-      <c r="AQ42" s="44" t="n"/>
-      <c r="AR42" s="44" t="n"/>
-      <c r="AS42" s="44" t="n"/>
-      <c r="AT42" s="44" t="n"/>
-      <c r="AU42" s="44" t="n"/>
-      <c r="AV42" s="45" t="n"/>
+      <c r="AQ42" s="48" t="n"/>
+      <c r="AR42" s="48" t="n"/>
+      <c r="AS42" s="48" t="n"/>
+      <c r="AT42" s="48" t="n"/>
+      <c r="AU42" s="48" t="n"/>
+      <c r="AV42" s="49" t="n"/>
       <c r="AW42" s="39">
         <f>AT27</f>
         <v/>
       </c>
-      <c r="AX42" s="44" t="n"/>
-      <c r="AY42" s="44" t="n"/>
-      <c r="AZ42" s="44" t="n"/>
-      <c r="BA42" s="44" t="n"/>
-      <c r="BB42" s="44" t="n"/>
-      <c r="BC42" s="45" t="n"/>
+      <c r="AX42" s="48" t="n"/>
+      <c r="AY42" s="48" t="n"/>
+      <c r="AZ42" s="48" t="n"/>
+      <c r="BA42" s="48" t="n"/>
+      <c r="BB42" s="48" t="n"/>
+      <c r="BC42" s="49" t="n"/>
       <c r="BD42" s="40">
         <f>BO5</f>
         <v/>
       </c>
-      <c r="BE42" s="44" t="n"/>
-      <c r="BF42" s="44" t="n"/>
-      <c r="BG42" s="44" t="n"/>
-      <c r="BH42" s="44" t="n"/>
-      <c r="BI42" s="44" t="n"/>
-      <c r="BJ42" s="45" t="n"/>
+      <c r="BE42" s="48" t="n"/>
+      <c r="BF42" s="48" t="n"/>
+      <c r="BG42" s="48" t="n"/>
+      <c r="BH42" s="48" t="n"/>
+      <c r="BI42" s="48" t="n"/>
+      <c r="BJ42" s="49" t="n"/>
     </row>
     <row r="43" ht="15" customHeight="1">
-      <c r="G43" s="21" t="n"/>
-      <c r="H43" s="21" t="n"/>
-      <c r="I43" s="21" t="n"/>
-      <c r="J43" s="21" t="n"/>
-      <c r="K43" s="21" t="n"/>
-      <c r="L43" s="21" t="n"/>
-      <c r="M43" s="21" t="n"/>
-      <c r="N43" s="21" t="n"/>
-      <c r="O43" s="50" t="n"/>
-      <c r="U43" s="51" t="n"/>
-      <c r="V43" s="50" t="n"/>
-      <c r="AB43" s="51" t="n"/>
-      <c r="AC43" s="50" t="n"/>
-      <c r="AO43" s="51" t="n"/>
-      <c r="AP43" s="50" t="n"/>
-      <c r="AV43" s="51" t="n"/>
-      <c r="AW43" s="50" t="n"/>
-      <c r="BC43" s="51" t="n"/>
-      <c r="BD43" s="50" t="n"/>
-      <c r="BJ43" s="51" t="n"/>
+      <c r="A43" s="55" t="n"/>
+      <c r="B43" s="55" t="n"/>
+      <c r="C43" s="55" t="n"/>
+      <c r="D43" s="55" t="n"/>
+      <c r="E43" s="55" t="n"/>
+      <c r="F43" s="55" t="n"/>
+      <c r="G43" s="67" t="n"/>
+      <c r="H43" s="67" t="n"/>
+      <c r="I43" s="67" t="n"/>
+      <c r="J43" s="67" t="n"/>
+      <c r="K43" s="67" t="n"/>
+      <c r="L43" s="67" t="n"/>
+      <c r="M43" s="67" t="n"/>
+      <c r="N43" s="67" t="n"/>
+      <c r="O43" s="54" t="n"/>
+      <c r="U43" s="57" t="n"/>
+      <c r="V43" s="68" t="n"/>
+      <c r="AB43" s="57" t="n"/>
+      <c r="AC43" s="68" t="n"/>
+      <c r="AO43" s="57" t="n"/>
+      <c r="AP43" s="68" t="n"/>
+      <c r="AV43" s="57" t="n"/>
+      <c r="AW43" s="68" t="n"/>
+      <c r="BC43" s="57" t="n"/>
+      <c r="BD43" s="68" t="n"/>
+      <c r="BJ43" s="57" t="n"/>
       <c r="BP43" s="21" t="n"/>
     </row>
     <row r="44" ht="15" customHeight="1">
-      <c r="G44" s="21" t="n"/>
-      <c r="H44" s="21" t="n"/>
-      <c r="I44" s="21" t="n"/>
-      <c r="J44" s="21" t="n"/>
-      <c r="K44" s="21" t="n"/>
-      <c r="L44" s="21" t="n"/>
-      <c r="M44" s="21" t="n"/>
-      <c r="N44" s="21" t="n"/>
-      <c r="O44" s="52" t="n"/>
-      <c r="P44" s="53" t="n"/>
-      <c r="Q44" s="53" t="n"/>
-      <c r="R44" s="53" t="n"/>
-      <c r="S44" s="53" t="n"/>
-      <c r="T44" s="53" t="n"/>
-      <c r="U44" s="54" t="n"/>
-      <c r="V44" s="52" t="n"/>
-      <c r="W44" s="53" t="n"/>
-      <c r="X44" s="53" t="n"/>
-      <c r="Y44" s="53" t="n"/>
-      <c r="Z44" s="53" t="n"/>
-      <c r="AA44" s="53" t="n"/>
-      <c r="AB44" s="54" t="n"/>
-      <c r="AC44" s="52" t="n"/>
-      <c r="AD44" s="53" t="n"/>
-      <c r="AE44" s="53" t="n"/>
-      <c r="AF44" s="53" t="n"/>
-      <c r="AG44" s="53" t="n"/>
-      <c r="AH44" s="53" t="n"/>
-      <c r="AI44" s="53" t="n"/>
-      <c r="AJ44" s="53" t="n"/>
-      <c r="AK44" s="53" t="n"/>
-      <c r="AL44" s="53" t="n"/>
-      <c r="AM44" s="53" t="n"/>
-      <c r="AN44" s="53" t="n"/>
-      <c r="AO44" s="54" t="n"/>
-      <c r="AP44" s="52" t="n"/>
-      <c r="AQ44" s="53" t="n"/>
-      <c r="AR44" s="53" t="n"/>
-      <c r="AS44" s="53" t="n"/>
-      <c r="AT44" s="53" t="n"/>
-      <c r="AU44" s="53" t="n"/>
-      <c r="AV44" s="54" t="n"/>
-      <c r="AW44" s="52" t="n"/>
-      <c r="AX44" s="53" t="n"/>
-      <c r="AY44" s="53" t="n"/>
-      <c r="AZ44" s="53" t="n"/>
-      <c r="BA44" s="53" t="n"/>
-      <c r="BB44" s="53" t="n"/>
-      <c r="BC44" s="54" t="n"/>
-      <c r="BD44" s="52" t="n"/>
-      <c r="BE44" s="53" t="n"/>
-      <c r="BF44" s="53" t="n"/>
-      <c r="BG44" s="53" t="n"/>
-      <c r="BH44" s="53" t="n"/>
-      <c r="BI44" s="53" t="n"/>
-      <c r="BJ44" s="54" t="n"/>
+      <c r="A44" s="55" t="n"/>
+      <c r="B44" s="55" t="n"/>
+      <c r="C44" s="55" t="n"/>
+      <c r="D44" s="55" t="n"/>
+      <c r="E44" s="55" t="n"/>
+      <c r="F44" s="55" t="n"/>
+      <c r="G44" s="67" t="n"/>
+      <c r="H44" s="67" t="n"/>
+      <c r="I44" s="67" t="n"/>
+      <c r="J44" s="67" t="n"/>
+      <c r="K44" s="67" t="n"/>
+      <c r="L44" s="67" t="n"/>
+      <c r="M44" s="67" t="n"/>
+      <c r="N44" s="67" t="n"/>
+      <c r="O44" s="61" t="n"/>
+      <c r="P44" s="59" t="n"/>
+      <c r="Q44" s="59" t="n"/>
+      <c r="R44" s="59" t="n"/>
+      <c r="S44" s="59" t="n"/>
+      <c r="T44" s="59" t="n"/>
+      <c r="U44" s="60" t="n"/>
+      <c r="V44" s="58" t="n"/>
+      <c r="W44" s="59" t="n"/>
+      <c r="X44" s="59" t="n"/>
+      <c r="Y44" s="59" t="n"/>
+      <c r="Z44" s="59" t="n"/>
+      <c r="AA44" s="59" t="n"/>
+      <c r="AB44" s="60" t="n"/>
+      <c r="AC44" s="58" t="n"/>
+      <c r="AD44" s="59" t="n"/>
+      <c r="AE44" s="59" t="n"/>
+      <c r="AF44" s="59" t="n"/>
+      <c r="AG44" s="59" t="n"/>
+      <c r="AH44" s="59" t="n"/>
+      <c r="AI44" s="59" t="n"/>
+      <c r="AJ44" s="59" t="n"/>
+      <c r="AK44" s="59" t="n"/>
+      <c r="AL44" s="59" t="n"/>
+      <c r="AM44" s="59" t="n"/>
+      <c r="AN44" s="59" t="n"/>
+      <c r="AO44" s="60" t="n"/>
+      <c r="AP44" s="58" t="n"/>
+      <c r="AQ44" s="59" t="n"/>
+      <c r="AR44" s="59" t="n"/>
+      <c r="AS44" s="59" t="n"/>
+      <c r="AT44" s="59" t="n"/>
+      <c r="AU44" s="59" t="n"/>
+      <c r="AV44" s="60" t="n"/>
+      <c r="AW44" s="58" t="n"/>
+      <c r="AX44" s="59" t="n"/>
+      <c r="AY44" s="59" t="n"/>
+      <c r="AZ44" s="59" t="n"/>
+      <c r="BA44" s="59" t="n"/>
+      <c r="BB44" s="59" t="n"/>
+      <c r="BC44" s="60" t="n"/>
+      <c r="BD44" s="58" t="n"/>
+      <c r="BE44" s="59" t="n"/>
+      <c r="BF44" s="59" t="n"/>
+      <c r="BG44" s="59" t="n"/>
+      <c r="BH44" s="59" t="n"/>
+      <c r="BI44" s="59" t="n"/>
+      <c r="BJ44" s="60" t="n"/>
     </row>
     <row r="45" ht="15" customHeight="1">
-      <c r="G45" s="21" t="n"/>
-      <c r="H45" s="21" t="n"/>
-      <c r="I45" s="21" t="n"/>
-      <c r="J45" s="21" t="n"/>
-      <c r="K45" s="21" t="n"/>
-      <c r="L45" s="21" t="n"/>
-      <c r="M45" s="21" t="n"/>
-      <c r="N45" s="21" t="n"/>
-      <c r="O45" s="20" t="n"/>
-      <c r="P45" s="44" t="n"/>
-      <c r="Q45" s="44" t="n"/>
-      <c r="R45" s="44" t="n"/>
-      <c r="S45" s="44" t="n"/>
-      <c r="T45" s="44" t="n"/>
-      <c r="U45" s="45" t="n"/>
+      <c r="A45" s="55" t="n"/>
+      <c r="B45" s="55" t="n"/>
+      <c r="C45" s="55" t="n"/>
+      <c r="D45" s="55" t="n"/>
+      <c r="E45" s="55" t="n"/>
+      <c r="F45" s="55" t="n"/>
+      <c r="G45" s="67" t="n"/>
+      <c r="H45" s="67" t="n"/>
+      <c r="I45" s="67" t="n"/>
+      <c r="J45" s="67" t="n"/>
+      <c r="K45" s="67" t="n"/>
+      <c r="L45" s="67" t="n"/>
+      <c r="M45" s="67" t="n"/>
+      <c r="N45" s="67" t="n"/>
+      <c r="O45" s="71" t="n"/>
+      <c r="P45" s="48" t="n"/>
+      <c r="Q45" s="48" t="n"/>
+      <c r="R45" s="48" t="n"/>
+      <c r="S45" s="48" t="n"/>
+      <c r="T45" s="48" t="n"/>
+      <c r="U45" s="49" t="n"/>
       <c r="V45" s="20" t="n"/>
-      <c r="W45" s="44" t="n"/>
-      <c r="X45" s="44" t="n"/>
-      <c r="Y45" s="44" t="n"/>
-      <c r="Z45" s="44" t="n"/>
-      <c r="AA45" s="44" t="n"/>
-      <c r="AB45" s="45" t="n"/>
+      <c r="W45" s="48" t="n"/>
+      <c r="X45" s="48" t="n"/>
+      <c r="Y45" s="48" t="n"/>
+      <c r="Z45" s="48" t="n"/>
+      <c r="AA45" s="48" t="n"/>
+      <c r="AB45" s="49" t="n"/>
       <c r="AC45" s="22" t="n"/>
-      <c r="AD45" s="44" t="n"/>
-      <c r="AE45" s="44" t="n"/>
-      <c r="AF45" s="44" t="n"/>
-      <c r="AG45" s="44" t="n"/>
-      <c r="AH45" s="44" t="n"/>
-      <c r="AI45" s="44" t="n"/>
-      <c r="AJ45" s="44" t="n"/>
-      <c r="AK45" s="44" t="n"/>
-      <c r="AL45" s="44" t="n"/>
-      <c r="AM45" s="44" t="n"/>
-      <c r="AN45" s="44" t="n"/>
-      <c r="AO45" s="45" t="n"/>
+      <c r="AD45" s="48" t="n"/>
+      <c r="AE45" s="48" t="n"/>
+      <c r="AF45" s="48" t="n"/>
+      <c r="AG45" s="48" t="n"/>
+      <c r="AH45" s="48" t="n"/>
+      <c r="AI45" s="48" t="n"/>
+      <c r="AJ45" s="48" t="n"/>
+      <c r="AK45" s="48" t="n"/>
+      <c r="AL45" s="48" t="n"/>
+      <c r="AM45" s="48" t="n"/>
+      <c r="AN45" s="48" t="n"/>
+      <c r="AO45" s="49" t="n"/>
       <c r="AP45" s="20" t="n"/>
-      <c r="AQ45" s="44" t="n"/>
-      <c r="AR45" s="44" t="n"/>
-      <c r="AS45" s="44" t="n"/>
-      <c r="AT45" s="44" t="n"/>
-      <c r="AU45" s="44" t="n"/>
-      <c r="AV45" s="45" t="n"/>
+      <c r="AQ45" s="48" t="n"/>
+      <c r="AR45" s="48" t="n"/>
+      <c r="AS45" s="48" t="n"/>
+      <c r="AT45" s="48" t="n"/>
+      <c r="AU45" s="48" t="n"/>
+      <c r="AV45" s="49" t="n"/>
       <c r="AW45" s="20" t="n"/>
-      <c r="AX45" s="44" t="n"/>
-      <c r="AY45" s="44" t="n"/>
-      <c r="AZ45" s="44" t="n"/>
-      <c r="BA45" s="44" t="n"/>
-      <c r="BB45" s="44" t="n"/>
-      <c r="BC45" s="45" t="n"/>
+      <c r="AX45" s="48" t="n"/>
+      <c r="AY45" s="48" t="n"/>
+      <c r="AZ45" s="48" t="n"/>
+      <c r="BA45" s="48" t="n"/>
+      <c r="BB45" s="48" t="n"/>
+      <c r="BC45" s="49" t="n"/>
       <c r="BD45" s="20" t="n"/>
-      <c r="BE45" s="44" t="n"/>
-      <c r="BF45" s="44" t="n"/>
-      <c r="BG45" s="44" t="n"/>
-      <c r="BH45" s="44" t="n"/>
-      <c r="BI45" s="44" t="n"/>
-      <c r="BJ45" s="45" t="n"/>
+      <c r="BE45" s="48" t="n"/>
+      <c r="BF45" s="48" t="n"/>
+      <c r="BG45" s="48" t="n"/>
+      <c r="BH45" s="48" t="n"/>
+      <c r="BI45" s="48" t="n"/>
+      <c r="BJ45" s="49" t="n"/>
     </row>
     <row r="46" ht="15" customHeight="1">
-      <c r="G46" s="21" t="n"/>
-      <c r="H46" s="21" t="n"/>
-      <c r="I46" s="21" t="n"/>
-      <c r="J46" s="21" t="n"/>
-      <c r="K46" s="21" t="n"/>
-      <c r="L46" s="21" t="n"/>
-      <c r="M46" s="21" t="n"/>
-      <c r="N46" s="21" t="n"/>
-      <c r="O46" s="50" t="n"/>
-      <c r="U46" s="51" t="n"/>
-      <c r="V46" s="50" t="n"/>
-      <c r="AB46" s="51" t="n"/>
-      <c r="AC46" s="50" t="n"/>
-      <c r="AO46" s="51" t="n"/>
-      <c r="AP46" s="50" t="n"/>
-      <c r="AV46" s="51" t="n"/>
-      <c r="AW46" s="50" t="n"/>
-      <c r="BC46" s="51" t="n"/>
-      <c r="BD46" s="50" t="n"/>
-      <c r="BJ46" s="51" t="n"/>
+      <c r="A46" s="55" t="n"/>
+      <c r="B46" s="55" t="n"/>
+      <c r="C46" s="55" t="n"/>
+      <c r="D46" s="55" t="n"/>
+      <c r="E46" s="55" t="n"/>
+      <c r="F46" s="55" t="n"/>
+      <c r="G46" s="67" t="n"/>
+      <c r="H46" s="67" t="n"/>
+      <c r="I46" s="67" t="n"/>
+      <c r="J46" s="67" t="n"/>
+      <c r="K46" s="67" t="n"/>
+      <c r="L46" s="67" t="n"/>
+      <c r="M46" s="67" t="n"/>
+      <c r="N46" s="67" t="n"/>
+      <c r="O46" s="54" t="n"/>
+      <c r="U46" s="57" t="n"/>
+      <c r="V46" s="68" t="n"/>
+      <c r="AB46" s="57" t="n"/>
+      <c r="AC46" s="68" t="n"/>
+      <c r="AO46" s="57" t="n"/>
+      <c r="AP46" s="68" t="n"/>
+      <c r="AV46" s="57" t="n"/>
+      <c r="AW46" s="68" t="n"/>
+      <c r="BC46" s="57" t="n"/>
+      <c r="BD46" s="68" t="n"/>
+      <c r="BJ46" s="57" t="n"/>
     </row>
     <row r="47" ht="15" customHeight="1">
-      <c r="G47" s="21" t="n"/>
-      <c r="H47" s="21" t="n"/>
-      <c r="I47" s="21" t="n"/>
-      <c r="J47" s="21" t="n"/>
-      <c r="K47" s="21" t="n"/>
-      <c r="L47" s="21" t="n"/>
-      <c r="M47" s="21" t="n"/>
-      <c r="N47" s="21" t="n"/>
-      <c r="O47" s="52" t="n"/>
-      <c r="P47" s="53" t="n"/>
-      <c r="Q47" s="53" t="n"/>
-      <c r="R47" s="53" t="n"/>
-      <c r="S47" s="53" t="n"/>
-      <c r="T47" s="53" t="n"/>
-      <c r="U47" s="54" t="n"/>
-      <c r="V47" s="52" t="n"/>
-      <c r="W47" s="53" t="n"/>
-      <c r="X47" s="53" t="n"/>
-      <c r="Y47" s="53" t="n"/>
-      <c r="Z47" s="53" t="n"/>
-      <c r="AA47" s="53" t="n"/>
-      <c r="AB47" s="54" t="n"/>
-      <c r="AC47" s="52" t="n"/>
-      <c r="AD47" s="53" t="n"/>
-      <c r="AE47" s="53" t="n"/>
-      <c r="AF47" s="53" t="n"/>
-      <c r="AG47" s="53" t="n"/>
-      <c r="AH47" s="53" t="n"/>
-      <c r="AI47" s="53" t="n"/>
-      <c r="AJ47" s="53" t="n"/>
-      <c r="AK47" s="53" t="n"/>
-      <c r="AL47" s="53" t="n"/>
-      <c r="AM47" s="53" t="n"/>
-      <c r="AN47" s="53" t="n"/>
-      <c r="AO47" s="54" t="n"/>
-      <c r="AP47" s="52" t="n"/>
-      <c r="AQ47" s="53" t="n"/>
-      <c r="AR47" s="53" t="n"/>
-      <c r="AS47" s="53" t="n"/>
-      <c r="AT47" s="53" t="n"/>
-      <c r="AU47" s="53" t="n"/>
-      <c r="AV47" s="54" t="n"/>
-      <c r="AW47" s="52" t="n"/>
-      <c r="AX47" s="53" t="n"/>
-      <c r="AY47" s="53" t="n"/>
-      <c r="AZ47" s="53" t="n"/>
-      <c r="BA47" s="53" t="n"/>
-      <c r="BB47" s="53" t="n"/>
-      <c r="BC47" s="54" t="n"/>
-      <c r="BD47" s="52" t="n"/>
-      <c r="BE47" s="53" t="n"/>
-      <c r="BF47" s="53" t="n"/>
-      <c r="BG47" s="53" t="n"/>
-      <c r="BH47" s="53" t="n"/>
-      <c r="BI47" s="53" t="n"/>
-      <c r="BJ47" s="54" t="n"/>
+      <c r="A47" s="55" t="n"/>
+      <c r="B47" s="55" t="n"/>
+      <c r="C47" s="55" t="n"/>
+      <c r="D47" s="55" t="n"/>
+      <c r="E47" s="55" t="n"/>
+      <c r="F47" s="55" t="n"/>
+      <c r="G47" s="67" t="n"/>
+      <c r="H47" s="67" t="n"/>
+      <c r="I47" s="67" t="n"/>
+      <c r="J47" s="67" t="n"/>
+      <c r="K47" s="67" t="n"/>
+      <c r="L47" s="67" t="n"/>
+      <c r="M47" s="67" t="n"/>
+      <c r="N47" s="67" t="n"/>
+      <c r="O47" s="61" t="n"/>
+      <c r="P47" s="59" t="n"/>
+      <c r="Q47" s="59" t="n"/>
+      <c r="R47" s="59" t="n"/>
+      <c r="S47" s="59" t="n"/>
+      <c r="T47" s="59" t="n"/>
+      <c r="U47" s="60" t="n"/>
+      <c r="V47" s="58" t="n"/>
+      <c r="W47" s="59" t="n"/>
+      <c r="X47" s="59" t="n"/>
+      <c r="Y47" s="59" t="n"/>
+      <c r="Z47" s="59" t="n"/>
+      <c r="AA47" s="59" t="n"/>
+      <c r="AB47" s="60" t="n"/>
+      <c r="AC47" s="58" t="n"/>
+      <c r="AD47" s="59" t="n"/>
+      <c r="AE47" s="59" t="n"/>
+      <c r="AF47" s="59" t="n"/>
+      <c r="AG47" s="59" t="n"/>
+      <c r="AH47" s="59" t="n"/>
+      <c r="AI47" s="59" t="n"/>
+      <c r="AJ47" s="59" t="n"/>
+      <c r="AK47" s="59" t="n"/>
+      <c r="AL47" s="59" t="n"/>
+      <c r="AM47" s="59" t="n"/>
+      <c r="AN47" s="59" t="n"/>
+      <c r="AO47" s="60" t="n"/>
+      <c r="AP47" s="58" t="n"/>
+      <c r="AQ47" s="59" t="n"/>
+      <c r="AR47" s="59" t="n"/>
+      <c r="AS47" s="59" t="n"/>
+      <c r="AT47" s="59" t="n"/>
+      <c r="AU47" s="59" t="n"/>
+      <c r="AV47" s="60" t="n"/>
+      <c r="AW47" s="58" t="n"/>
+      <c r="AX47" s="59" t="n"/>
+      <c r="AY47" s="59" t="n"/>
+      <c r="AZ47" s="59" t="n"/>
+      <c r="BA47" s="59" t="n"/>
+      <c r="BB47" s="59" t="n"/>
+      <c r="BC47" s="60" t="n"/>
+      <c r="BD47" s="58" t="n"/>
+      <c r="BE47" s="59" t="n"/>
+      <c r="BF47" s="59" t="n"/>
+      <c r="BG47" s="59" t="n"/>
+      <c r="BH47" s="59" t="n"/>
+      <c r="BI47" s="59" t="n"/>
+      <c r="BJ47" s="60" t="n"/>
     </row>
     <row r="48" ht="15" customHeight="1">
-      <c r="O48" s="19" t="n"/>
+      <c r="A48" s="55" t="n"/>
+      <c r="B48" s="55" t="n"/>
+      <c r="C48" s="55" t="n"/>
+      <c r="D48" s="55" t="n"/>
+      <c r="E48" s="55" t="n"/>
+      <c r="F48" s="55" t="n"/>
+      <c r="G48" s="55" t="n"/>
+      <c r="H48" s="55" t="n"/>
+      <c r="I48" s="55" t="n"/>
+      <c r="J48" s="55" t="n"/>
+      <c r="K48" s="55" t="n"/>
+      <c r="L48" s="55" t="n"/>
+      <c r="M48" s="55" t="n"/>
+      <c r="N48" s="55" t="n"/>
+      <c r="O48" s="72" t="n"/>
       <c r="V48" s="19" t="n"/>
       <c r="AC48" s="19" t="n"/>
       <c r="AP48" s="19" t="n"/>
       <c r="AW48" s="19" t="n"/>
       <c r="BD48" s="19" t="n"/>
     </row>
-    <row r="49" ht="15" customHeight="1"/>
-    <row r="50" ht="15" customHeight="1"/>
+    <row r="49" ht="15" customHeight="1">
+      <c r="A49" s="55" t="n"/>
+      <c r="B49" s="55" t="n"/>
+      <c r="C49" s="55" t="n"/>
+      <c r="D49" s="55" t="n"/>
+      <c r="E49" s="55" t="n"/>
+      <c r="F49" s="55" t="n"/>
+      <c r="G49" s="55" t="n"/>
+      <c r="H49" s="55" t="n"/>
+      <c r="I49" s="55" t="n"/>
+      <c r="J49" s="55" t="n"/>
+      <c r="K49" s="55" t="n"/>
+      <c r="L49" s="55" t="n"/>
+      <c r="M49" s="55" t="n"/>
+      <c r="N49" s="55" t="n"/>
+      <c r="O49" s="55" t="n"/>
+    </row>
+    <row r="50" ht="15" customHeight="1">
+      <c r="A50" s="55" t="n"/>
+      <c r="B50" s="55" t="n"/>
+      <c r="C50" s="55" t="n"/>
+      <c r="D50" s="55" t="n"/>
+      <c r="E50" s="55" t="n"/>
+      <c r="F50" s="55" t="n"/>
+      <c r="G50" s="55" t="n"/>
+      <c r="H50" s="55" t="n"/>
+      <c r="I50" s="55" t="n"/>
+      <c r="J50" s="55" t="n"/>
+      <c r="K50" s="55" t="n"/>
+      <c r="L50" s="55" t="n"/>
+      <c r="M50" s="55" t="n"/>
+      <c r="N50" s="55" t="n"/>
+      <c r="O50" s="55" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="55" t="n"/>
+      <c r="B51" s="55" t="n"/>
+      <c r="C51" s="55" t="n"/>
+      <c r="D51" s="55" t="n"/>
+      <c r="E51" s="55" t="n"/>
+      <c r="F51" s="55" t="n"/>
+      <c r="G51" s="55" t="n"/>
+      <c r="H51" s="55" t="n"/>
+      <c r="I51" s="55" t="n"/>
+      <c r="J51" s="55" t="n"/>
+      <c r="K51" s="55" t="n"/>
+      <c r="L51" s="55" t="n"/>
+      <c r="M51" s="55" t="n"/>
+      <c r="N51" s="55" t="n"/>
+      <c r="O51" s="55" t="n"/>
+    </row>
     <row r="52" ht="15" customHeight="1">
+      <c r="A52" s="55" t="n"/>
+      <c r="B52" s="55" t="n"/>
+      <c r="C52" s="55" t="n"/>
+      <c r="D52" s="55" t="n"/>
+      <c r="E52" s="55" t="n"/>
+      <c r="F52" s="55" t="n"/>
+      <c r="G52" s="55" t="n"/>
+      <c r="H52" s="55" t="n"/>
+      <c r="I52" s="55" t="n"/>
+      <c r="J52" s="55" t="n"/>
+      <c r="K52" s="55" t="n"/>
+      <c r="L52" s="55" t="n"/>
+      <c r="M52" s="55" t="n"/>
+      <c r="N52" s="55" t="n"/>
+      <c r="O52" s="55" t="n"/>
       <c r="BH52" s="8" t="n"/>
       <c r="BI52" s="8" t="n"/>
       <c r="BJ52" s="8" t="n"/>
@@ -3128,22 +3596,54 @@
       <c r="BQ52" s="9" t="n"/>
       <c r="BR52" s="9" t="n"/>
     </row>
+    <row r="53">
+      <c r="A53" s="55" t="n"/>
+      <c r="B53" s="55" t="n"/>
+      <c r="C53" s="55" t="n"/>
+      <c r="D53" s="55" t="n"/>
+      <c r="E53" s="55" t="n"/>
+      <c r="F53" s="55" t="n"/>
+      <c r="G53" s="55" t="n"/>
+      <c r="H53" s="55" t="n"/>
+      <c r="I53" s="55" t="n"/>
+      <c r="J53" s="55" t="n"/>
+      <c r="K53" s="55" t="n"/>
+      <c r="L53" s="55" t="n"/>
+      <c r="M53" s="55" t="n"/>
+      <c r="N53" s="55" t="n"/>
+      <c r="O53" s="55" t="n"/>
+    </row>
     <row r="54" ht="15" customHeight="1">
-      <c r="AA54" s="55" t="n"/>
-      <c r="AB54" s="55" t="n"/>
-      <c r="AC54" s="55" t="n"/>
-      <c r="AD54" s="55" t="n"/>
-      <c r="AE54" s="55" t="n"/>
-      <c r="AF54" s="55" t="n"/>
-      <c r="AG54" s="55" t="n"/>
-      <c r="AH54" s="55" t="n"/>
-      <c r="AI54" s="55" t="n"/>
-      <c r="AJ54" s="55" t="n"/>
-      <c r="AK54" s="55" t="n"/>
-      <c r="AL54" s="55" t="n"/>
-      <c r="AM54" s="55" t="n"/>
-      <c r="AN54" s="55" t="n"/>
-      <c r="AO54" s="55" t="n"/>
+      <c r="A54" s="55" t="n"/>
+      <c r="B54" s="55" t="n"/>
+      <c r="C54" s="55" t="n"/>
+      <c r="D54" s="55" t="n"/>
+      <c r="E54" s="55" t="n"/>
+      <c r="F54" s="55" t="n"/>
+      <c r="G54" s="55" t="n"/>
+      <c r="H54" s="55" t="n"/>
+      <c r="I54" s="55" t="n"/>
+      <c r="J54" s="55" t="n"/>
+      <c r="K54" s="55" t="n"/>
+      <c r="L54" s="55" t="n"/>
+      <c r="M54" s="55" t="n"/>
+      <c r="N54" s="55" t="n"/>
+      <c r="O54" s="55" t="n"/>
+      <c r="AA54" s="73" t="n"/>
+      <c r="AB54" s="73" t="n"/>
+      <c r="AC54" s="73" t="n"/>
+      <c r="AD54" s="73" t="n"/>
+      <c r="AE54" s="73" t="n"/>
+      <c r="AF54" s="73" t="n"/>
+      <c r="AG54" s="73" t="n"/>
+      <c r="AH54" s="73" t="n"/>
+      <c r="AI54" s="73" t="n"/>
+      <c r="AJ54" s="73" t="n"/>
+      <c r="AK54" s="73" t="n"/>
+      <c r="AL54" s="73" t="n"/>
+      <c r="AM54" s="73" t="n"/>
+      <c r="AN54" s="73" t="n"/>
+      <c r="AO54" s="73" t="n"/>
       <c r="AP54" s="11" t="n"/>
       <c r="AQ54" s="11" t="n"/>
       <c r="AR54" s="11" t="n"/>
@@ -3223,1280 +3723,1378 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O76"/>
+  <dimension ref="A1:O90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30.61328125" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="30.6" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="23" max="23"/>
+    <col width="13" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="26" max="26"/>
+    <col width="13" customWidth="1" min="27" max="27"/>
+    <col width="13" customWidth="1" min="28" max="28"/>
+    <col width="13" customWidth="1" min="29" max="29"/>
+    <col width="13" customWidth="1" min="30" max="30"/>
+    <col width="13" customWidth="1" min="31" max="31"/>
+    <col width="13" customWidth="1" min="32" max="32"/>
+    <col width="13" customWidth="1" min="33" max="33"/>
+    <col width="13" customWidth="1" min="34" max="34"/>
+    <col width="13" customWidth="1" min="35" max="35"/>
+    <col width="13" customWidth="1" min="36" max="36"/>
+    <col width="13" customWidth="1" min="38" max="38"/>
+    <col width="13" customWidth="1" min="39" max="39"/>
+    <col width="13" customWidth="1" min="40" max="40"/>
+    <col width="13" customWidth="1" min="41" max="41"/>
+    <col width="13" customWidth="1" min="42" max="42"/>
+    <col width="13" customWidth="1" min="44" max="44"/>
+    <col width="13" customWidth="1" min="46" max="46"/>
+    <col width="13" customWidth="1" min="47" max="47"/>
+    <col width="13" customWidth="1" min="48" max="48"/>
+    <col width="13" customWidth="1" min="49" max="49"/>
+    <col width="13" customWidth="1" min="50" max="50"/>
+    <col width="13" customWidth="1" min="51" max="51"/>
+    <col width="13" customWidth="1" min="52" max="52"/>
+    <col width="13" customWidth="1" min="53" max="53"/>
+    <col width="13" customWidth="1" min="54" max="54"/>
+    <col width="13" customWidth="1" min="55" max="55"/>
+    <col width="13" customWidth="1" min="57" max="57"/>
+    <col width="13" customWidth="1" min="58" max="58"/>
+    <col width="13" customWidth="1" min="59" max="59"/>
+    <col width="13" customWidth="1" min="60" max="60"/>
+    <col width="13" customWidth="1" min="62" max="62"/>
+    <col width="13" customWidth="1" min="64" max="64"/>
+    <col width="13" customWidth="1" min="65" max="65"/>
+    <col width="13" customWidth="1" min="66" max="66"/>
+    <col width="13" customWidth="1" min="67" max="67"/>
+    <col width="13" customWidth="1" min="68" max="68"/>
+    <col width="13" customWidth="1" min="69" max="69"/>
+    <col width="13" customWidth="1" min="72" max="72"/>
+    <col width="13" customWidth="1" min="73" max="73"/>
+    <col width="13" customWidth="1" min="74" max="74"/>
+    <col width="13" customWidth="1" min="75" max="75"/>
+    <col width="13" customWidth="1" min="76" max="76"/>
+    <col width="13" customWidth="1" min="77" max="77"/>
+    <col width="13" customWidth="1" min="78" max="78"/>
+    <col width="13" customWidth="1" min="79" max="79"/>
+    <col width="13" customWidth="1" min="80" max="80"/>
+    <col width="13" customWidth="1" min="81" max="81"/>
+    <col width="13" customWidth="1" min="82" max="82"/>
+    <col width="13" customWidth="1" min="84" max="84"/>
+    <col width="13" customWidth="1" min="85" max="85"/>
+    <col width="13" customWidth="1" min="86" max="86"/>
+    <col width="13" customWidth="1" min="87" max="87"/>
+    <col width="13" customWidth="1" min="88" max="88"/>
+    <col width="13" customWidth="1" min="89" max="89"/>
+    <col width="13" customWidth="1" min="90" max="90"/>
   </cols>
   <sheetData>
     <row r="1" ht="29.25" customHeight="1">
-      <c r="A1" s="35" t="n"/>
-      <c r="B1" s="36" t="n"/>
-      <c r="C1" s="35">
+      <c r="A1" s="74" t="n"/>
+      <c r="B1" s="75" t="n"/>
+      <c r="C1" s="74">
         <f>PORTADA!Z1</f>
         <v/>
       </c>
-      <c r="D1" s="46" t="n"/>
-      <c r="E1" s="46" t="n"/>
-      <c r="F1" s="46" t="n"/>
-      <c r="G1" s="46" t="n"/>
-      <c r="H1" s="46" t="n"/>
-      <c r="I1" s="46" t="n"/>
-      <c r="J1" s="46" t="n"/>
-      <c r="K1" s="46" t="n"/>
-      <c r="L1" s="47" t="n"/>
-      <c r="M1" s="12" t="inlineStr">
+      <c r="D1" s="65" t="n"/>
+      <c r="E1" s="65" t="n"/>
+      <c r="F1" s="65" t="n"/>
+      <c r="G1" s="65" t="n"/>
+      <c r="H1" s="65" t="n"/>
+      <c r="I1" s="65" t="n"/>
+      <c r="J1" s="65" t="n"/>
+      <c r="K1" s="65" t="n"/>
+      <c r="L1" s="66" t="n"/>
+      <c r="M1" s="76" t="inlineStr">
         <is>
           <t>CODIGO:</t>
         </is>
       </c>
-      <c r="N1" s="32">
+      <c r="N1" s="77">
         <f>PORTADA!BO1</f>
         <v/>
       </c>
-      <c r="O1" s="47" t="n"/>
+      <c r="O1" s="66" t="n"/>
     </row>
     <row r="2" ht="29.25" customHeight="1">
-      <c r="A2" s="56" t="n"/>
-      <c r="B2" s="56" t="n"/>
-      <c r="C2" s="35">
+      <c r="A2" s="78" t="n"/>
+      <c r="B2" s="78" t="n"/>
+      <c r="C2" s="74">
         <f>PORTADA!Z3</f>
         <v/>
       </c>
-      <c r="D2" s="44" t="n"/>
-      <c r="E2" s="44" t="n"/>
-      <c r="F2" s="44" t="n"/>
-      <c r="G2" s="44" t="n"/>
-      <c r="H2" s="44" t="n"/>
-      <c r="I2" s="44" t="n"/>
-      <c r="J2" s="44" t="n"/>
-      <c r="K2" s="44" t="n"/>
-      <c r="L2" s="45" t="n"/>
-      <c r="M2" s="12" t="inlineStr">
+      <c r="D2" s="45" t="n"/>
+      <c r="E2" s="45" t="n"/>
+      <c r="F2" s="45" t="n"/>
+      <c r="G2" s="45" t="n"/>
+      <c r="H2" s="45" t="n"/>
+      <c r="I2" s="45" t="n"/>
+      <c r="J2" s="45" t="n"/>
+      <c r="K2" s="45" t="n"/>
+      <c r="L2" s="46" t="n"/>
+      <c r="M2" s="76" t="inlineStr">
         <is>
           <t>REVISION:</t>
         </is>
       </c>
-      <c r="N2" s="32">
+      <c r="N2" s="77">
         <f>PORTADA!BO2</f>
         <v/>
       </c>
-      <c r="O2" s="47" t="n"/>
+      <c r="O2" s="66" t="n"/>
     </row>
     <row r="3" ht="29.25" customHeight="1">
-      <c r="A3" s="56" t="n"/>
-      <c r="B3" s="56" t="n"/>
-      <c r="C3" s="52" t="n"/>
-      <c r="D3" s="53" t="n"/>
-      <c r="E3" s="53" t="n"/>
-      <c r="F3" s="53" t="n"/>
-      <c r="G3" s="53" t="n"/>
-      <c r="H3" s="53" t="n"/>
-      <c r="I3" s="53" t="n"/>
-      <c r="J3" s="53" t="n"/>
-      <c r="K3" s="53" t="n"/>
-      <c r="L3" s="54" t="n"/>
-      <c r="M3" s="12" t="inlineStr">
+      <c r="A3" s="78" t="n"/>
+      <c r="B3" s="78" t="n"/>
+      <c r="C3" s="61" t="n"/>
+      <c r="D3" s="62" t="n"/>
+      <c r="E3" s="62" t="n"/>
+      <c r="F3" s="62" t="n"/>
+      <c r="G3" s="62" t="n"/>
+      <c r="H3" s="62" t="n"/>
+      <c r="I3" s="62" t="n"/>
+      <c r="J3" s="62" t="n"/>
+      <c r="K3" s="62" t="n"/>
+      <c r="L3" s="63" t="n"/>
+      <c r="M3" s="76" t="inlineStr">
         <is>
           <t>FECHA:</t>
         </is>
       </c>
-      <c r="N3" s="32">
+      <c r="N3" s="77">
         <f>PORTADA!BO3</f>
         <v/>
       </c>
-      <c r="O3" s="47" t="n"/>
+      <c r="O3" s="66" t="n"/>
     </row>
     <row r="4" ht="29.25" customHeight="1">
-      <c r="A4" s="56" t="n"/>
-      <c r="B4" s="56" t="n"/>
-      <c r="C4" s="35">
+      <c r="A4" s="78" t="n"/>
+      <c r="B4" s="78" t="n"/>
+      <c r="C4" s="74">
         <f>PORTADA!Z5</f>
         <v/>
       </c>
-      <c r="D4" s="44" t="n"/>
-      <c r="E4" s="44" t="n"/>
-      <c r="F4" s="44" t="n"/>
-      <c r="G4" s="44" t="n"/>
-      <c r="H4" s="44" t="n"/>
-      <c r="I4" s="44" t="n"/>
-      <c r="J4" s="44" t="n"/>
-      <c r="K4" s="44" t="n"/>
-      <c r="L4" s="45" t="n"/>
-      <c r="M4" s="12" t="inlineStr">
+      <c r="D4" s="45" t="n"/>
+      <c r="E4" s="45" t="n"/>
+      <c r="F4" s="45" t="n"/>
+      <c r="G4" s="45" t="n"/>
+      <c r="H4" s="45" t="n"/>
+      <c r="I4" s="45" t="n"/>
+      <c r="J4" s="45" t="n"/>
+      <c r="K4" s="45" t="n"/>
+      <c r="L4" s="46" t="n"/>
+      <c r="M4" s="76" t="inlineStr">
         <is>
           <t>ELABORO:</t>
         </is>
       </c>
-      <c r="N4" s="32">
+      <c r="N4" s="77">
         <f>PORTADA!BO4</f>
         <v/>
       </c>
-      <c r="O4" s="47" t="n"/>
+      <c r="O4" s="66" t="n"/>
     </row>
     <row r="5" ht="29.25" customHeight="1">
-      <c r="A5" s="57" t="n"/>
-      <c r="B5" s="57" t="n"/>
-      <c r="C5" s="50" t="n"/>
-      <c r="L5" s="51" t="n"/>
-      <c r="M5" s="12" t="inlineStr">
+      <c r="A5" s="79" t="n"/>
+      <c r="B5" s="79" t="n"/>
+      <c r="C5" s="54" t="n"/>
+      <c r="D5" s="55" t="n"/>
+      <c r="E5" s="55" t="n"/>
+      <c r="F5" s="55" t="n"/>
+      <c r="G5" s="55" t="n"/>
+      <c r="H5" s="55" t="n"/>
+      <c r="I5" s="55" t="n"/>
+      <c r="J5" s="55" t="n"/>
+      <c r="K5" s="55" t="n"/>
+      <c r="L5" s="56" t="n"/>
+      <c r="M5" s="76" t="inlineStr">
         <is>
           <t xml:space="preserve">REVISO:      </t>
         </is>
       </c>
-      <c r="N5" s="32">
+      <c r="N5" s="77">
         <f>PORTADA!BO5</f>
         <v/>
       </c>
-      <c r="O5" s="47" t="n"/>
+      <c r="O5" s="66" t="n"/>
     </row>
     <row r="6" ht="29.25" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="76" t="inlineStr">
         <is>
           <t>PROYECTO:</t>
         </is>
       </c>
-      <c r="B6" s="35">
+      <c r="B6" s="74">
         <f>PORTADA!N6</f>
         <v/>
       </c>
-      <c r="C6" s="52" t="n"/>
-      <c r="D6" s="53" t="n"/>
-      <c r="E6" s="53" t="n"/>
-      <c r="F6" s="53" t="n"/>
-      <c r="G6" s="53" t="n"/>
-      <c r="H6" s="53" t="n"/>
-      <c r="I6" s="53" t="n"/>
-      <c r="J6" s="53" t="n"/>
-      <c r="K6" s="53" t="n"/>
-      <c r="L6" s="54" t="n"/>
-      <c r="M6" s="12" t="inlineStr">
+      <c r="C6" s="61" t="n"/>
+      <c r="D6" s="62" t="n"/>
+      <c r="E6" s="62" t="n"/>
+      <c r="F6" s="62" t="n"/>
+      <c r="G6" s="62" t="n"/>
+      <c r="H6" s="62" t="n"/>
+      <c r="I6" s="62" t="n"/>
+      <c r="J6" s="62" t="n"/>
+      <c r="K6" s="62" t="n"/>
+      <c r="L6" s="63" t="n"/>
+      <c r="M6" s="76" t="inlineStr">
         <is>
           <t>APROBO:</t>
         </is>
       </c>
-      <c r="N6" s="32">
+      <c r="N6" s="77">
         <f>PORTADA!BO6</f>
         <v/>
       </c>
-      <c r="O6" s="47" t="n"/>
+      <c r="O6" s="66" t="n"/>
     </row>
     <row r="7" ht="25" customHeight="1">
-      <c r="A7" s="18" t="n">
+      <c r="A7" s="80" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="18" t="n">
+      <c r="B7" s="80" t="n">
         <v>2</v>
       </c>
-      <c r="C7" s="18" t="n">
+      <c r="C7" s="80" t="n">
         <v>3</v>
       </c>
-      <c r="D7" s="18" t="n">
+      <c r="D7" s="80" t="n">
         <v>4</v>
       </c>
-      <c r="E7" s="18" t="n">
+      <c r="E7" s="80" t="n">
         <v>5</v>
       </c>
-      <c r="F7" s="18" t="n">
+      <c r="F7" s="80" t="n">
         <v>6</v>
       </c>
-      <c r="G7" s="18" t="n">
+      <c r="G7" s="80" t="n">
         <v>7</v>
       </c>
-      <c r="H7" s="18" t="n">
+      <c r="H7" s="80" t="n">
         <v>8</v>
       </c>
-      <c r="I7" s="18" t="n">
+      <c r="I7" s="80" t="n">
         <v>9</v>
       </c>
-      <c r="J7" s="18" t="n">
+      <c r="J7" s="80" t="n">
         <v>10</v>
       </c>
-      <c r="K7" s="18" t="n">
+      <c r="K7" s="80" t="n">
         <v>11</v>
       </c>
-      <c r="L7" s="18" t="n">
+      <c r="L7" s="80" t="n">
         <v>12</v>
       </c>
-      <c r="M7" s="18" t="n">
+      <c r="M7" s="80" t="n">
         <v>13</v>
       </c>
-      <c r="N7" s="18" t="n">
+      <c r="N7" s="80" t="n">
         <v>14</v>
       </c>
-      <c r="O7" s="18" t="n">
+      <c r="O7" s="80" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="58" t="inlineStr">
+    <row r="9" ht="345" customHeight="1">
+      <c r="A9" s="81" t="inlineStr">
         <is>
           <t>Hoja de datos: rejillas de descarga con malla anti-insectos</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="59" t="inlineStr">
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="82" t="inlineStr">
         <is>
           <t>Campo</t>
         </is>
       </c>
-      <c r="B10" s="59" t="n"/>
-      <c r="C10" s="59" t="n"/>
-      <c r="D10" s="59" t="n"/>
-      <c r="E10" s="59" t="n"/>
-      <c r="F10" s="59" t="n"/>
-      <c r="G10" s="59" t="n"/>
-      <c r="H10" s="59" t="n"/>
-      <c r="I10" s="59" t="inlineStr">
+      <c r="B10" s="82" t="n"/>
+      <c r="C10" s="82" t="n"/>
+      <c r="D10" s="82" t="n"/>
+      <c r="E10" s="82" t="n"/>
+      <c r="F10" s="82" t="n"/>
+      <c r="G10" s="82" t="n"/>
+      <c r="H10" s="82" t="n"/>
+      <c r="I10" s="82" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
       </c>
-      <c r="J10" s="59" t="n"/>
-      <c r="K10" s="59" t="n"/>
-      <c r="L10" s="59" t="n"/>
-      <c r="M10" s="59" t="n"/>
-      <c r="N10" s="59" t="n"/>
-      <c r="O10" s="59" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="60" t="inlineStr">
+      <c r="J10" s="82" t="n"/>
+      <c r="K10" s="82" t="n"/>
+      <c r="L10" s="82" t="n"/>
+      <c r="M10" s="82" t="n"/>
+      <c r="N10" s="82" t="n"/>
+      <c r="O10" s="82" t="n"/>
+    </row>
+    <row r="11" ht="45" customHeight="1">
+      <c r="A11" s="83" t="inlineStr">
         <is>
           <t>Código</t>
         </is>
       </c>
-      <c r="B11" s="61" t="n"/>
-      <c r="C11" s="61" t="n"/>
-      <c r="D11" s="61" t="n"/>
-      <c r="E11" s="61" t="n"/>
-      <c r="F11" s="61" t="n"/>
-      <c r="G11" s="61" t="n"/>
-      <c r="H11" s="61" t="n"/>
-      <c r="I11" s="60" t="inlineStr">
+      <c r="B11" s="84" t="n"/>
+      <c r="C11" s="84" t="n"/>
+      <c r="D11" s="84" t="n"/>
+      <c r="E11" s="84" t="n"/>
+      <c r="F11" s="84" t="n"/>
+      <c r="G11" s="84" t="n"/>
+      <c r="H11" s="84" t="n"/>
+      <c r="I11" s="83" t="inlineStr">
         <is>
           <t>HD-REJ-001</t>
         </is>
       </c>
-      <c r="J11" s="61" t="n"/>
-      <c r="K11" s="61" t="n"/>
-      <c r="L11" s="61" t="n"/>
-      <c r="M11" s="61" t="n"/>
-      <c r="N11" s="61" t="n"/>
-      <c r="O11" s="61" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="60" t="inlineStr">
+      <c r="J11" s="84" t="n"/>
+      <c r="K11" s="84" t="n"/>
+      <c r="L11" s="84" t="n"/>
+      <c r="M11" s="84" t="n"/>
+      <c r="N11" s="84" t="n"/>
+      <c r="O11" s="84" t="n"/>
+    </row>
+    <row r="12" ht="45" customHeight="1">
+      <c r="A12" s="83" t="inlineStr">
         <is>
           <t>Revisión</t>
         </is>
       </c>
-      <c r="B12" s="61" t="n"/>
-      <c r="C12" s="61" t="n"/>
-      <c r="D12" s="61" t="n"/>
-      <c r="E12" s="61" t="n"/>
-      <c r="F12" s="61" t="n"/>
-      <c r="G12" s="61" t="n"/>
-      <c r="H12" s="61" t="n"/>
-      <c r="I12" s="60" t="inlineStr">
+      <c r="B12" s="84" t="n"/>
+      <c r="C12" s="84" t="n"/>
+      <c r="D12" s="84" t="n"/>
+      <c r="E12" s="84" t="n"/>
+      <c r="F12" s="84" t="n"/>
+      <c r="G12" s="84" t="n"/>
+      <c r="H12" s="84" t="n"/>
+      <c r="I12" s="83" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J12" s="61" t="n"/>
-      <c r="K12" s="61" t="n"/>
-      <c r="L12" s="61" t="n"/>
-      <c r="M12" s="61" t="n"/>
-      <c r="N12" s="61" t="n"/>
-      <c r="O12" s="61" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="60" t="inlineStr">
+      <c r="J12" s="84" t="n"/>
+      <c r="K12" s="84" t="n"/>
+      <c r="L12" s="84" t="n"/>
+      <c r="M12" s="84" t="n"/>
+      <c r="N12" s="84" t="n"/>
+      <c r="O12" s="84" t="n"/>
+    </row>
+    <row r="13" ht="45" customHeight="1">
+      <c r="A13" s="83" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
       </c>
-      <c r="B13" s="61" t="n"/>
-      <c r="C13" s="61" t="n"/>
-      <c r="D13" s="61" t="n"/>
-      <c r="E13" s="61" t="n"/>
-      <c r="F13" s="61" t="n"/>
-      <c r="G13" s="61" t="n"/>
-      <c r="H13" s="61" t="n"/>
-      <c r="I13" s="60" t="inlineStr">
+      <c r="B13" s="84" t="n"/>
+      <c r="C13" s="84" t="n"/>
+      <c r="D13" s="84" t="n"/>
+      <c r="E13" s="84" t="n"/>
+      <c r="F13" s="84" t="n"/>
+      <c r="G13" s="84" t="n"/>
+      <c r="H13" s="84" t="n"/>
+      <c r="I13" s="83" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="J13" s="61" t="n"/>
-      <c r="K13" s="61" t="n"/>
-      <c r="L13" s="61" t="n"/>
-      <c r="M13" s="61" t="n"/>
-      <c r="N13" s="61" t="n"/>
-      <c r="O13" s="61" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="60" t="inlineStr">
+      <c r="J13" s="84" t="n"/>
+      <c r="K13" s="84" t="n"/>
+      <c r="L13" s="84" t="n"/>
+      <c r="M13" s="84" t="n"/>
+      <c r="N13" s="84" t="n"/>
+      <c r="O13" s="84" t="n"/>
+    </row>
+    <row r="14" ht="240" customHeight="1">
+      <c r="A14" s="83" t="inlineStr">
         <is>
           <t>Proyecto</t>
         </is>
       </c>
-      <c r="B14" s="61" t="n"/>
-      <c r="C14" s="61" t="n"/>
-      <c r="D14" s="61" t="n"/>
-      <c r="E14" s="61" t="n"/>
-      <c r="F14" s="61" t="n"/>
-      <c r="G14" s="61" t="n"/>
-      <c r="H14" s="61" t="n"/>
-      <c r="I14" s="60" t="inlineStr">
+      <c r="B14" s="84" t="n"/>
+      <c r="C14" s="84" t="n"/>
+      <c r="D14" s="84" t="n"/>
+      <c r="E14" s="84" t="n"/>
+      <c r="F14" s="84" t="n"/>
+      <c r="G14" s="84" t="n"/>
+      <c r="H14" s="84" t="n"/>
+      <c r="I14" s="83" t="inlineStr">
         <is>
           <t>P2437-HV-INF-001 — BRINSA, laboratorio de análisis industrial, Cajicá</t>
         </is>
       </c>
-      <c r="J14" s="61" t="n"/>
-      <c r="K14" s="61" t="n"/>
-      <c r="L14" s="61" t="n"/>
-      <c r="M14" s="61" t="n"/>
-      <c r="N14" s="61" t="n"/>
-      <c r="O14" s="61" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="60" t="inlineStr">
+      <c r="J14" s="84" t="n"/>
+      <c r="K14" s="84" t="n"/>
+      <c r="L14" s="84" t="n"/>
+      <c r="M14" s="84" t="n"/>
+      <c r="N14" s="84" t="n"/>
+      <c r="O14" s="84" t="n"/>
+    </row>
+    <row r="15" ht="150" customHeight="1">
+      <c r="A15" s="83" t="inlineStr">
         <is>
           <t>Etiqueta de equipo</t>
         </is>
       </c>
-      <c r="B15" s="61" t="n"/>
-      <c r="C15" s="61" t="n"/>
-      <c r="D15" s="61" t="n"/>
-      <c r="E15" s="61" t="n"/>
-      <c r="F15" s="61" t="n"/>
-      <c r="G15" s="61" t="n"/>
-      <c r="H15" s="61" t="n"/>
-      <c r="I15" s="60" t="inlineStr">
+      <c r="B15" s="84" t="n"/>
+      <c r="C15" s="84" t="n"/>
+      <c r="D15" s="84" t="n"/>
+      <c r="E15" s="84" t="n"/>
+      <c r="F15" s="84" t="n"/>
+      <c r="G15" s="84" t="n"/>
+      <c r="H15" s="84" t="n"/>
+      <c r="I15" s="83" t="inlineStr">
         <is>
           <t>REJ-001 a REJ-003 (rejillas de descarga)</t>
         </is>
       </c>
-      <c r="J15" s="61" t="n"/>
-      <c r="K15" s="61" t="n"/>
-      <c r="L15" s="61" t="n"/>
-      <c r="M15" s="61" t="n"/>
-      <c r="N15" s="61" t="n"/>
-      <c r="O15" s="61" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="62" t="inlineStr">
+      <c r="J15" s="84" t="n"/>
+      <c r="K15" s="84" t="n"/>
+      <c r="L15" s="84" t="n"/>
+      <c r="M15" s="84" t="n"/>
+      <c r="N15" s="84" t="n"/>
+      <c r="O15" s="84" t="n"/>
+    </row>
+    <row r="16" ht="15" customHeight="1"/>
+    <row r="17" ht="15" customHeight="1"/>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="85" t="inlineStr">
         <is>
           <t>1. Servicio</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="63" t="inlineStr">
+    <row r="19" ht="165" customHeight="1">
+      <c r="A19" s="86" t="inlineStr">
         <is>
           <t>1.1. Descarga libre a la atmósfera del caudal de ventilación del laboratorio, a través de la envolvente del recinto. Las rejillas son la trayectoria de salida permanente del aire y, con el sistema detenido, una vía potencial de ingreso: por ello incorporan malla anti-insectos. Ambiente exterior corrosivo (atmósfera clorada de planta de hipoclorito de calcio).</t>
         </is>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="24">
-      <c r="A24" s="62" t="inlineStr">
+    <row r="20" ht="15" customHeight="1"/>
+    <row r="21" ht="15" customHeight="1"/>
+    <row r="22" ht="15" customHeight="1"/>
+    <row r="23" ht="15" customHeight="1"/>
+    <row r="24" ht="15" customHeight="1"/>
+    <row r="25" ht="15" customHeight="1"/>
+    <row r="26" ht="105" customHeight="1">
+      <c r="A26" s="85" t="inlineStr">
         <is>
           <t>2. Condiciones de operación y desempeño</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="64" t="inlineStr">
+    <row r="27" ht="105" customHeight="1">
+      <c r="A27" s="87" t="inlineStr">
         <is>
           <t>Tabla 1. Condiciones de diseño (valores congelados de la memoria de cálculo).</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="59" t="inlineStr">
+    <row r="28" ht="15" customHeight="1"/>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="82" t="inlineStr">
         <is>
           <t>Parámetro</t>
         </is>
       </c>
-      <c r="B26" s="59" t="n"/>
-      <c r="C26" s="59" t="n"/>
-      <c r="D26" s="59" t="n"/>
-      <c r="E26" s="59" t="n"/>
-      <c r="F26" s="59" t="n"/>
-      <c r="G26" s="59" t="n"/>
-      <c r="H26" s="59" t="n"/>
-      <c r="I26" s="59" t="inlineStr">
+      <c r="B29" s="82" t="n"/>
+      <c r="C29" s="82" t="n"/>
+      <c r="D29" s="82" t="n"/>
+      <c r="E29" s="82" t="n"/>
+      <c r="F29" s="82" t="n"/>
+      <c r="G29" s="82" t="n"/>
+      <c r="H29" s="82" t="n"/>
+      <c r="I29" s="82" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
       </c>
-      <c r="J26" s="59" t="n"/>
-      <c r="K26" s="59" t="n"/>
-      <c r="L26" s="59" t="n"/>
-      <c r="M26" s="59" t="n"/>
-      <c r="N26" s="59" t="n"/>
-      <c r="O26" s="59" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="60" t="inlineStr">
+      <c r="J29" s="82" t="n"/>
+      <c r="K29" s="82" t="n"/>
+      <c r="L29" s="82" t="n"/>
+      <c r="M29" s="82" t="n"/>
+      <c r="N29" s="82" t="n"/>
+      <c r="O29" s="82" t="n"/>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="83" t="inlineStr">
         <is>
           <t>Cantidad</t>
         </is>
       </c>
-      <c r="B27" s="61" t="n"/>
-      <c r="C27" s="61" t="n"/>
-      <c r="D27" s="61" t="n"/>
-      <c r="E27" s="61" t="n"/>
-      <c r="F27" s="61" t="n"/>
-      <c r="G27" s="61" t="n"/>
-      <c r="H27" s="61" t="n"/>
-      <c r="I27" s="60" t="inlineStr">
+      <c r="B30" s="84" t="n"/>
+      <c r="C30" s="84" t="n"/>
+      <c r="D30" s="84" t="n"/>
+      <c r="E30" s="84" t="n"/>
+      <c r="F30" s="84" t="n"/>
+      <c r="G30" s="84" t="n"/>
+      <c r="H30" s="84" t="n"/>
+      <c r="I30" s="83" t="inlineStr">
         <is>
           <t>3 unidades</t>
         </is>
       </c>
-      <c r="J27" s="61" t="n"/>
-      <c r="K27" s="61" t="n"/>
-      <c r="L27" s="61" t="n"/>
-      <c r="M27" s="61" t="n"/>
-      <c r="N27" s="61" t="n"/>
-      <c r="O27" s="61" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="60" t="inlineStr">
+      <c r="J30" s="84" t="n"/>
+      <c r="K30" s="84" t="n"/>
+      <c r="L30" s="84" t="n"/>
+      <c r="M30" s="84" t="n"/>
+      <c r="N30" s="84" t="n"/>
+      <c r="O30" s="84" t="n"/>
+    </row>
+    <row r="31" ht="105" customHeight="1">
+      <c r="A31" s="83" t="inlineStr">
         <is>
           <t>Dimensiones faciales (unitarias)</t>
         </is>
       </c>
-      <c r="B28" s="61" t="n"/>
-      <c r="C28" s="61" t="n"/>
-      <c r="D28" s="61" t="n"/>
-      <c r="E28" s="61" t="n"/>
-      <c r="F28" s="61" t="n"/>
-      <c r="G28" s="61" t="n"/>
-      <c r="H28" s="61" t="n"/>
-      <c r="I28" s="60" t="inlineStr">
+      <c r="B31" s="84" t="n"/>
+      <c r="C31" s="84" t="n"/>
+      <c r="D31" s="84" t="n"/>
+      <c r="E31" s="84" t="n"/>
+      <c r="F31" s="84" t="n"/>
+      <c r="G31" s="84" t="n"/>
+      <c r="H31" s="84" t="n"/>
+      <c r="I31" s="83" t="inlineStr">
         <is>
           <t>353×336 mm (área facial 0.1187 m²)</t>
         </is>
       </c>
-      <c r="J28" s="61" t="n"/>
-      <c r="K28" s="61" t="n"/>
-      <c r="L28" s="61" t="n"/>
-      <c r="M28" s="61" t="n"/>
-      <c r="N28" s="61" t="n"/>
-      <c r="O28" s="61" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="60" t="inlineStr">
+      <c r="J31" s="84" t="n"/>
+      <c r="K31" s="84" t="n"/>
+      <c r="L31" s="84" t="n"/>
+      <c r="M31" s="84" t="n"/>
+      <c r="N31" s="84" t="n"/>
+      <c r="O31" s="84" t="n"/>
+    </row>
+    <row r="32" ht="75" customHeight="1">
+      <c r="A32" s="83" t="inlineStr">
         <is>
           <t>Caudal total de descarga</t>
         </is>
       </c>
-      <c r="B29" s="61" t="n"/>
-      <c r="C29" s="61" t="n"/>
-      <c r="D29" s="61" t="n"/>
-      <c r="E29" s="61" t="n"/>
-      <c r="F29" s="61" t="n"/>
-      <c r="G29" s="61" t="n"/>
-      <c r="H29" s="61" t="n"/>
-      <c r="I29" s="60" t="inlineStr">
+      <c r="B32" s="84" t="n"/>
+      <c r="C32" s="84" t="n"/>
+      <c r="D32" s="84" t="n"/>
+      <c r="E32" s="84" t="n"/>
+      <c r="F32" s="84" t="n"/>
+      <c r="G32" s="84" t="n"/>
+      <c r="H32" s="84" t="n"/>
+      <c r="I32" s="83" t="inlineStr">
         <is>
           <t>3 840 m³/h (1.0667 m³/s)</t>
         </is>
       </c>
-      <c r="J29" s="61" t="n"/>
-      <c r="K29" s="61" t="n"/>
-      <c r="L29" s="61" t="n"/>
-      <c r="M29" s="61" t="n"/>
-      <c r="N29" s="61" t="n"/>
-      <c r="O29" s="61" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="60" t="inlineStr">
+      <c r="J32" s="84" t="n"/>
+      <c r="K32" s="84" t="n"/>
+      <c r="L32" s="84" t="n"/>
+      <c r="M32" s="84" t="n"/>
+      <c r="N32" s="84" t="n"/>
+      <c r="O32" s="84" t="n"/>
+    </row>
+    <row r="33" ht="45" customHeight="1">
+      <c r="A33" s="83" t="inlineStr">
         <is>
           <t>Velocidad facial</t>
         </is>
       </c>
-      <c r="B30" s="61" t="n"/>
-      <c r="C30" s="61" t="n"/>
-      <c r="D30" s="61" t="n"/>
-      <c r="E30" s="61" t="n"/>
-      <c r="F30" s="61" t="n"/>
-      <c r="G30" s="61" t="n"/>
-      <c r="H30" s="61" t="n"/>
-      <c r="I30" s="60" t="inlineStr">
+      <c r="B33" s="84" t="n"/>
+      <c r="C33" s="84" t="n"/>
+      <c r="D33" s="84" t="n"/>
+      <c r="E33" s="84" t="n"/>
+      <c r="F33" s="84" t="n"/>
+      <c r="G33" s="84" t="n"/>
+      <c r="H33" s="84" t="n"/>
+      <c r="I33" s="83" t="inlineStr">
         <is>
           <t>3 m/s</t>
         </is>
       </c>
-      <c r="J30" s="61" t="n"/>
-      <c r="K30" s="61" t="n"/>
-      <c r="L30" s="61" t="n"/>
-      <c r="M30" s="61" t="n"/>
-      <c r="N30" s="61" t="n"/>
-      <c r="O30" s="61" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="60" t="inlineStr">
+      <c r="J33" s="84" t="n"/>
+      <c r="K33" s="84" t="n"/>
+      <c r="L33" s="84" t="n"/>
+      <c r="M33" s="84" t="n"/>
+      <c r="N33" s="84" t="n"/>
+      <c r="O33" s="84" t="n"/>
+    </row>
+    <row r="34" ht="165" customHeight="1">
+      <c r="A34" s="83" t="inlineStr">
         <is>
           <t>ΔP unitaria (cierre de orificio, C_d = 0.60, en el sitio)</t>
         </is>
       </c>
-      <c r="B31" s="61" t="n"/>
-      <c r="C31" s="61" t="n"/>
-      <c r="D31" s="61" t="n"/>
-      <c r="E31" s="61" t="n"/>
-      <c r="F31" s="61" t="n"/>
-      <c r="G31" s="61" t="n"/>
-      <c r="H31" s="61" t="n"/>
-      <c r="I31" s="60" t="inlineStr">
+      <c r="B34" s="84" t="n"/>
+      <c r="C34" s="84" t="n"/>
+      <c r="D34" s="84" t="n"/>
+      <c r="E34" s="84" t="n"/>
+      <c r="F34" s="84" t="n"/>
+      <c r="G34" s="84" t="n"/>
+      <c r="H34" s="84" t="n"/>
+      <c r="I34" s="83" t="inlineStr">
         <is>
           <t>11 Pa</t>
         </is>
       </c>
-      <c r="J31" s="61" t="n"/>
-      <c r="K31" s="61" t="n"/>
-      <c r="L31" s="61" t="n"/>
-      <c r="M31" s="61" t="n"/>
-      <c r="N31" s="61" t="n"/>
-      <c r="O31" s="61" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="60" t="inlineStr">
+      <c r="J34" s="84" t="n"/>
+      <c r="K34" s="84" t="n"/>
+      <c r="L34" s="84" t="n"/>
+      <c r="M34" s="84" t="n"/>
+      <c r="N34" s="84" t="n"/>
+      <c r="O34" s="84" t="n"/>
+    </row>
+    <row r="35" ht="135" customHeight="1">
+      <c r="A35" s="83" t="inlineStr">
         <is>
           <t>ΔP equivalente a densidad estándar (ρ = 1.2 kg/m³)</t>
         </is>
       </c>
-      <c r="B32" s="61" t="n"/>
-      <c r="C32" s="61" t="n"/>
-      <c r="D32" s="61" t="n"/>
-      <c r="E32" s="61" t="n"/>
-      <c r="F32" s="61" t="n"/>
-      <c r="G32" s="61" t="n"/>
-      <c r="H32" s="61" t="n"/>
-      <c r="I32" s="60" t="inlineStr">
+      <c r="B35" s="84" t="n"/>
+      <c r="C35" s="84" t="n"/>
+      <c r="D35" s="84" t="n"/>
+      <c r="E35" s="84" t="n"/>
+      <c r="F35" s="84" t="n"/>
+      <c r="G35" s="84" t="n"/>
+      <c r="H35" s="84" t="n"/>
+      <c r="I35" s="83" t="inlineStr">
         <is>
           <t>15 Pa</t>
         </is>
       </c>
-      <c r="J32" s="61" t="n"/>
-      <c r="K32" s="61" t="n"/>
-      <c r="L32" s="61" t="n"/>
-      <c r="M32" s="61" t="n"/>
-      <c r="N32" s="61" t="n"/>
-      <c r="O32" s="61" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="60" t="inlineStr">
+      <c r="J35" s="84" t="n"/>
+      <c r="K35" s="84" t="n"/>
+      <c r="L35" s="84" t="n"/>
+      <c r="M35" s="84" t="n"/>
+      <c r="N35" s="84" t="n"/>
+      <c r="O35" s="84" t="n"/>
+    </row>
+    <row r="36" ht="90" customHeight="1">
+      <c r="A36" s="83" t="inlineStr">
         <is>
           <t>Densidad del aire de diseño</t>
         </is>
       </c>
-      <c r="B33" s="61" t="n"/>
-      <c r="C33" s="61" t="n"/>
-      <c r="D33" s="61" t="n"/>
-      <c r="E33" s="61" t="n"/>
-      <c r="F33" s="61" t="n"/>
-      <c r="G33" s="61" t="n"/>
-      <c r="H33" s="61" t="n"/>
-      <c r="I33" s="60" t="inlineStr">
+      <c r="B36" s="84" t="n"/>
+      <c r="C36" s="84" t="n"/>
+      <c r="D36" s="84" t="n"/>
+      <c r="E36" s="84" t="n"/>
+      <c r="F36" s="84" t="n"/>
+      <c r="G36" s="84" t="n"/>
+      <c r="H36" s="84" t="n"/>
+      <c r="I36" s="83" t="inlineStr">
         <is>
           <t>0.88 kg/m³ (2 558 msnm, 74.1 kPa)</t>
         </is>
       </c>
-      <c r="J33" s="61" t="n"/>
-      <c r="K33" s="61" t="n"/>
-      <c r="L33" s="61" t="n"/>
-      <c r="M33" s="61" t="n"/>
-      <c r="N33" s="61" t="n"/>
-      <c r="O33" s="61" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="63" t="inlineStr">
+      <c r="J36" s="84" t="n"/>
+      <c r="K36" s="84" t="n"/>
+      <c r="L36" s="84" t="n"/>
+      <c r="M36" s="84" t="n"/>
+      <c r="N36" s="84" t="n"/>
+      <c r="O36" s="84" t="n"/>
+    </row>
+    <row r="37" ht="15" customHeight="1"/>
+    <row r="38" ht="165" customHeight="1">
+      <c r="A38" s="86" t="inlineStr">
         <is>
           <t>2.1. Nota de contexto: la ΔP unitaria de 11 Pa (cierre de orificio, C_d = 0.60, a 3 m/s) es la pérdida de descarga libre a la atmósfera y se suma a la caída de presión de la etapa filtrante para definir el punto de trabajo del ventilador; no existe consigna de presión interior que sostener.</t>
         </is>
       </c>
     </row>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="39">
-      <c r="A39" s="62" t="inlineStr">
+    <row r="39" ht="15" customHeight="1"/>
+    <row r="40" ht="15" customHeight="1"/>
+    <row r="41" ht="15" customHeight="1"/>
+    <row r="42" ht="15" customHeight="1"/>
+    <row r="43" ht="15" customHeight="1"/>
+    <row r="44" ht="90" customHeight="1">
+      <c r="A44" s="85" t="inlineStr">
         <is>
           <t>3. Construcción y áreas netas</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="64" t="inlineStr">
+    <row r="45" ht="45" customHeight="1">
+      <c r="A45" s="87" t="inlineStr">
         <is>
           <t>Tabla 2. Especificación constructiva.</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="59" t="inlineStr">
+    <row r="46" ht="45" customHeight="1">
+      <c r="A46" s="82" t="inlineStr">
         <is>
           <t>Característica</t>
         </is>
       </c>
-      <c r="B41" s="59" t="n"/>
-      <c r="C41" s="59" t="n"/>
-      <c r="D41" s="59" t="n"/>
-      <c r="E41" s="59" t="n"/>
-      <c r="F41" s="59" t="n"/>
-      <c r="G41" s="59" t="n"/>
-      <c r="H41" s="59" t="n"/>
-      <c r="I41" s="59" t="inlineStr">
+      <c r="B46" s="82" t="n"/>
+      <c r="C46" s="82" t="n"/>
+      <c r="D46" s="82" t="n"/>
+      <c r="E46" s="82" t="n"/>
+      <c r="F46" s="82" t="n"/>
+      <c r="G46" s="82" t="n"/>
+      <c r="H46" s="82" t="n"/>
+      <c r="I46" s="82" t="inlineStr">
         <is>
           <t>Especificación</t>
         </is>
       </c>
-      <c r="J41" s="59" t="n"/>
-      <c r="K41" s="59" t="n"/>
-      <c r="L41" s="59" t="n"/>
-      <c r="M41" s="59" t="n"/>
-      <c r="N41" s="59" t="n"/>
-      <c r="O41" s="59" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="60" t="inlineStr">
+      <c r="J46" s="82" t="n"/>
+      <c r="K46" s="82" t="n"/>
+      <c r="L46" s="82" t="n"/>
+      <c r="M46" s="82" t="n"/>
+      <c r="N46" s="82" t="n"/>
+      <c r="O46" s="82" t="n"/>
+    </row>
+    <row r="47" ht="150" customHeight="1">
+      <c r="A47" s="83" t="inlineStr">
         <is>
           <t>Tipo de núcleo</t>
         </is>
       </c>
-      <c r="B42" s="61" t="n"/>
-      <c r="C42" s="61" t="n"/>
-      <c r="D42" s="61" t="n"/>
-      <c r="E42" s="61" t="n"/>
-      <c r="F42" s="61" t="n"/>
-      <c r="G42" s="61" t="n"/>
-      <c r="H42" s="61" t="n"/>
-      <c r="I42" s="60" t="inlineStr">
+      <c r="B47" s="84" t="n"/>
+      <c r="C47" s="84" t="n"/>
+      <c r="D47" s="84" t="n"/>
+      <c r="E47" s="84" t="n"/>
+      <c r="F47" s="84" t="n"/>
+      <c r="G47" s="84" t="n"/>
+      <c r="H47" s="84" t="n"/>
+      <c r="I47" s="83" t="inlineStr">
         <is>
           <t>Eggcrate (panal) ½×½×½ in (12.7 mm), máxima área libre</t>
         </is>
       </c>
-      <c r="J42" s="61" t="n"/>
-      <c r="K42" s="61" t="n"/>
-      <c r="L42" s="61" t="n"/>
-      <c r="M42" s="61" t="n"/>
-      <c r="N42" s="61" t="n"/>
-      <c r="O42" s="61" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="60" t="inlineStr">
+      <c r="J47" s="84" t="n"/>
+      <c r="K47" s="84" t="n"/>
+      <c r="L47" s="84" t="n"/>
+      <c r="M47" s="84" t="n"/>
+      <c r="N47" s="84" t="n"/>
+      <c r="O47" s="84" t="n"/>
+    </row>
+    <row r="48" ht="450" customHeight="1">
+      <c r="A48" s="83" t="inlineStr">
         <is>
           <t>Área libre del núcleo</t>
         </is>
       </c>
-      <c r="B43" s="61" t="n"/>
-      <c r="C43" s="61" t="n"/>
-      <c r="D43" s="61" t="n"/>
-      <c r="E43" s="61" t="n"/>
-      <c r="F43" s="61" t="n"/>
-      <c r="G43" s="61" t="n"/>
-      <c r="H43" s="61" t="n"/>
-      <c r="I43" s="60" t="inlineStr">
+      <c r="B48" s="84" t="n"/>
+      <c r="C48" s="84" t="n"/>
+      <c r="D48" s="84" t="n"/>
+      <c r="E48" s="84" t="n"/>
+      <c r="F48" s="84" t="n"/>
+      <c r="G48" s="84" t="n"/>
+      <c r="H48" s="84" t="n"/>
+      <c r="I48" s="83" t="inlineStr">
         <is>
           <t>≥ 90 % (cifra repetida en catálogos del tipo; Airfoil RC-FCR5 (https://airfoil.com.au/product/removable-core-fixing-clip-eggcrate-grille-rc-fcr5/), consulta 2026-07-23)</t>
         </is>
       </c>
-      <c r="J43" s="61" t="n"/>
-      <c r="K43" s="61" t="n"/>
-      <c r="L43" s="61" t="n"/>
-      <c r="M43" s="61" t="n"/>
-      <c r="N43" s="61" t="n"/>
-      <c r="O43" s="61" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="60" t="inlineStr">
+      <c r="J48" s="84" t="n"/>
+      <c r="K48" s="84" t="n"/>
+      <c r="L48" s="84" t="n"/>
+      <c r="M48" s="84" t="n"/>
+      <c r="N48" s="84" t="n"/>
+      <c r="O48" s="84" t="n"/>
+    </row>
+    <row r="49" ht="705" customHeight="1">
+      <c r="A49" s="83" t="inlineStr">
         <is>
           <t>Malla anti-insectos</t>
         </is>
       </c>
-      <c r="B44" s="61" t="n"/>
-      <c r="C44" s="61" t="n"/>
-      <c r="D44" s="61" t="n"/>
-      <c r="E44" s="61" t="n"/>
-      <c r="F44" s="61" t="n"/>
-      <c r="G44" s="61" t="n"/>
-      <c r="H44" s="61" t="n"/>
-      <c r="I44" s="60" t="inlineStr">
+      <c r="B49" s="84" t="n"/>
+      <c r="C49" s="84" t="n"/>
+      <c r="D49" s="84" t="n"/>
+      <c r="E49" s="84" t="n"/>
+      <c r="F49" s="84" t="n"/>
+      <c r="G49" s="84" t="n"/>
+      <c r="H49" s="84" t="n"/>
+      <c r="I49" s="83" t="inlineStr">
         <is>
           <t>Tejido 18×18, abertura ≈1 mm, alambre 0.45 mm, área abierta ≥ 48 % (tabla Industrial Metal Mesh (https://www.industrialmetalmesh.com/sale-54819921-micron-304-316l-stainless-steel-wire-mesh-screen-filter-mesh.html), consulta 2026-07-23); excluye insectos comunes</t>
         </is>
       </c>
-      <c r="J44" s="61" t="n"/>
-      <c r="K44" s="61" t="n"/>
-      <c r="L44" s="61" t="n"/>
-      <c r="M44" s="61" t="n"/>
-      <c r="N44" s="61" t="n"/>
-      <c r="O44" s="61" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="60" t="inlineStr">
+      <c r="J49" s="84" t="n"/>
+      <c r="K49" s="84" t="n"/>
+      <c r="L49" s="84" t="n"/>
+      <c r="M49" s="84" t="n"/>
+      <c r="N49" s="84" t="n"/>
+      <c r="O49" s="84" t="n"/>
+    </row>
+    <row r="50" ht="135" customHeight="1">
+      <c r="A50" s="83" t="inlineStr">
         <is>
           <t>Área neta combinada (núcleo + malla)</t>
         </is>
       </c>
-      <c r="B45" s="61" t="n"/>
-      <c r="C45" s="61" t="n"/>
-      <c r="D45" s="61" t="n"/>
-      <c r="E45" s="61" t="n"/>
-      <c r="F45" s="61" t="n"/>
-      <c r="G45" s="61" t="n"/>
-      <c r="H45" s="61" t="n"/>
-      <c r="I45" s="60" t="inlineStr">
+      <c r="B50" s="84" t="n"/>
+      <c r="C50" s="84" t="n"/>
+      <c r="D50" s="84" t="n"/>
+      <c r="E50" s="84" t="n"/>
+      <c r="F50" s="84" t="n"/>
+      <c r="G50" s="84" t="n"/>
+      <c r="H50" s="84" t="n"/>
+      <c r="I50" s="83" t="inlineStr">
         <is>
           <t>≈ 45 % del área facial (dato típico: 0.90 × 0.50)</t>
         </is>
       </c>
-      <c r="J45" s="61" t="n"/>
-      <c r="K45" s="61" t="n"/>
-      <c r="L45" s="61" t="n"/>
-      <c r="M45" s="61" t="n"/>
-      <c r="N45" s="61" t="n"/>
-      <c r="O45" s="61" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="60" t="inlineStr">
+      <c r="J50" s="84" t="n"/>
+      <c r="K50" s="84" t="n"/>
+      <c r="L50" s="84" t="n"/>
+      <c r="M50" s="84" t="n"/>
+      <c r="N50" s="84" t="n"/>
+      <c r="O50" s="84" t="n"/>
+    </row>
+    <row r="51" ht="195" customHeight="1">
+      <c r="A51" s="83" t="inlineStr">
         <is>
           <t>Material de la rejilla</t>
         </is>
       </c>
-      <c r="B46" s="61" t="n"/>
-      <c r="C46" s="61" t="n"/>
-      <c r="D46" s="61" t="n"/>
-      <c r="E46" s="61" t="n"/>
-      <c r="F46" s="61" t="n"/>
-      <c r="G46" s="61" t="n"/>
-      <c r="H46" s="61" t="n"/>
-      <c r="I46" s="60" t="inlineStr">
+      <c r="B51" s="84" t="n"/>
+      <c r="C51" s="84" t="n"/>
+      <c r="D51" s="84" t="n"/>
+      <c r="E51" s="84" t="n"/>
+      <c r="F51" s="84" t="n"/>
+      <c r="G51" s="84" t="n"/>
+      <c r="H51" s="84" t="n"/>
+      <c r="I51" s="83" t="inlineStr">
         <is>
           <t>Inox 316L (primera opción) o aluminio anodizado 6063-T5 (alternativa)</t>
         </is>
       </c>
-      <c r="J46" s="61" t="n"/>
-      <c r="K46" s="61" t="n"/>
-      <c r="L46" s="61" t="n"/>
-      <c r="M46" s="61" t="n"/>
-      <c r="N46" s="61" t="n"/>
-      <c r="O46" s="61" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="60" t="inlineStr">
+      <c r="J51" s="84" t="n"/>
+      <c r="K51" s="84" t="n"/>
+      <c r="L51" s="84" t="n"/>
+      <c r="M51" s="84" t="n"/>
+      <c r="N51" s="84" t="n"/>
+      <c r="O51" s="84" t="n"/>
+    </row>
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" s="83" t="inlineStr">
         <is>
           <t>Material de la malla</t>
         </is>
       </c>
-      <c r="B47" s="61" t="n"/>
-      <c r="C47" s="61" t="n"/>
-      <c r="D47" s="61" t="n"/>
-      <c r="E47" s="61" t="n"/>
-      <c r="F47" s="61" t="n"/>
-      <c r="G47" s="61" t="n"/>
-      <c r="H47" s="61" t="n"/>
-      <c r="I47" s="60" t="inlineStr">
+      <c r="B52" s="84" t="n"/>
+      <c r="C52" s="84" t="n"/>
+      <c r="D52" s="84" t="n"/>
+      <c r="E52" s="84" t="n"/>
+      <c r="F52" s="84" t="n"/>
+      <c r="G52" s="84" t="n"/>
+      <c r="H52" s="84" t="n"/>
+      <c r="I52" s="83" t="inlineStr">
         <is>
           <t>Inox 316</t>
         </is>
       </c>
-      <c r="J47" s="61" t="n"/>
-      <c r="K47" s="61" t="n"/>
-      <c r="L47" s="61" t="n"/>
-      <c r="M47" s="61" t="n"/>
-      <c r="N47" s="61" t="n"/>
-      <c r="O47" s="61" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="60" t="inlineStr">
+      <c r="J52" s="84" t="n"/>
+      <c r="K52" s="84" t="n"/>
+      <c r="L52" s="84" t="n"/>
+      <c r="M52" s="84" t="n"/>
+      <c r="N52" s="84" t="n"/>
+      <c r="O52" s="84" t="n"/>
+    </row>
+    <row r="53" ht="120" customHeight="1">
+      <c r="A53" s="83" t="inlineStr">
         <is>
           <t>Montaje de la malla</t>
         </is>
       </c>
-      <c r="B48" s="61" t="n"/>
-      <c r="C48" s="61" t="n"/>
-      <c r="D48" s="61" t="n"/>
-      <c r="E48" s="61" t="n"/>
-      <c r="F48" s="61" t="n"/>
-      <c r="G48" s="61" t="n"/>
-      <c r="H48" s="61" t="n"/>
-      <c r="I48" s="60" t="inlineStr">
+      <c r="B53" s="84" t="n"/>
+      <c r="C53" s="84" t="n"/>
+      <c r="D53" s="84" t="n"/>
+      <c r="E53" s="84" t="n"/>
+      <c r="F53" s="84" t="n"/>
+      <c r="G53" s="84" t="n"/>
+      <c r="H53" s="84" t="n"/>
+      <c r="I53" s="83" t="inlineStr">
         <is>
           <t>Marco desmontable para limpieza periódica</t>
         </is>
       </c>
-      <c r="J48" s="61" t="n"/>
-      <c r="K48" s="61" t="n"/>
-      <c r="L48" s="61" t="n"/>
-      <c r="M48" s="61" t="n"/>
-      <c r="N48" s="61" t="n"/>
-      <c r="O48" s="61" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="60" t="inlineStr">
+      <c r="J53" s="84" t="n"/>
+      <c r="K53" s="84" t="n"/>
+      <c r="L53" s="84" t="n"/>
+      <c r="M53" s="84" t="n"/>
+      <c r="N53" s="84" t="n"/>
+      <c r="O53" s="84" t="n"/>
+    </row>
+    <row r="54" ht="270" customHeight="1">
+      <c r="A54" s="83" t="inlineStr">
         <is>
           <t>Par galvánico</t>
         </is>
       </c>
-      <c r="B49" s="61" t="n"/>
-      <c r="C49" s="61" t="n"/>
-      <c r="D49" s="61" t="n"/>
-      <c r="E49" s="61" t="n"/>
-      <c r="F49" s="61" t="n"/>
-      <c r="G49" s="61" t="n"/>
-      <c r="H49" s="61" t="n"/>
-      <c r="I49" s="60" t="inlineStr">
+      <c r="B54" s="84" t="n"/>
+      <c r="C54" s="84" t="n"/>
+      <c r="D54" s="84" t="n"/>
+      <c r="E54" s="84" t="n"/>
+      <c r="F54" s="84" t="n"/>
+      <c r="G54" s="84" t="n"/>
+      <c r="H54" s="84" t="n"/>
+      <c r="I54" s="83" t="inlineStr">
         <is>
           <t>Si se combina marco de aluminio con malla inox, aislamiento dieléctrico (dato típico de ingeniería)</t>
         </is>
       </c>
-      <c r="J49" s="61" t="n"/>
-      <c r="K49" s="61" t="n"/>
-      <c r="L49" s="61" t="n"/>
-      <c r="M49" s="61" t="n"/>
-      <c r="N49" s="61" t="n"/>
-      <c r="O49" s="61" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="60" t="inlineStr">
+      <c r="J54" s="84" t="n"/>
+      <c r="K54" s="84" t="n"/>
+      <c r="L54" s="84" t="n"/>
+      <c r="M54" s="84" t="n"/>
+      <c r="N54" s="84" t="n"/>
+      <c r="O54" s="84" t="n"/>
+    </row>
+    <row r="55" ht="90" customHeight="1">
+      <c r="A55" s="83" t="inlineStr">
         <is>
           <t>Ensayo de desempeño</t>
         </is>
       </c>
-      <c r="B50" s="61" t="n"/>
-      <c r="C50" s="61" t="n"/>
-      <c r="D50" s="61" t="n"/>
-      <c r="E50" s="61" t="n"/>
-      <c r="F50" s="61" t="n"/>
-      <c r="G50" s="61" t="n"/>
-      <c r="H50" s="61" t="n"/>
-      <c r="I50" s="60" t="inlineStr">
+      <c r="B55" s="84" t="n"/>
+      <c r="C55" s="84" t="n"/>
+      <c r="D55" s="84" t="n"/>
+      <c r="E55" s="84" t="n"/>
+      <c r="F55" s="84" t="n"/>
+      <c r="G55" s="84" t="n"/>
+      <c r="H55" s="84" t="n"/>
+      <c r="I55" s="83" t="inlineStr">
         <is>
           <t>ASHRAE 70 (medición de rejillas)</t>
         </is>
       </c>
-      <c r="J50" s="61" t="n"/>
-      <c r="K50" s="61" t="n"/>
-      <c r="L50" s="61" t="n"/>
-      <c r="M50" s="61" t="n"/>
-      <c r="N50" s="61" t="n"/>
-      <c r="O50" s="61" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="63" t="inlineStr">
+      <c r="J55" s="84" t="n"/>
+      <c r="K55" s="84" t="n"/>
+      <c r="L55" s="84" t="n"/>
+      <c r="M55" s="84" t="n"/>
+      <c r="N55" s="84" t="n"/>
+      <c r="O55" s="84" t="n"/>
+    </row>
+    <row r="56" ht="15" customHeight="1"/>
+    <row r="57" ht="165" customHeight="1">
+      <c r="A57" s="86" t="inlineStr">
         <is>
           <t>3.1. La malla domina la pérdida del conjunto; el dimensionamiento por área neta combinada y la ΔP calculada por cierre de orificio (11 Pa) deben verificarse contra el área efectiva (Ak) del fabricante seleccionado (por confirmar con proveedor).</t>
         </is>
       </c>
     </row>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="56">
-      <c r="A56" s="62" t="inlineStr">
+    <row r="58" ht="15" customHeight="1"/>
+    <row r="59" ht="15" customHeight="1"/>
+    <row r="60" ht="15" customHeight="1"/>
+    <row r="61" ht="15" customHeight="1"/>
+    <row r="62" ht="75" customHeight="1">
+      <c r="A62" s="85" t="inlineStr">
         <is>
           <t>4. Candidatos comerciales</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="64" t="inlineStr">
+    <row r="63" ht="60" customHeight="1">
+      <c r="A63" s="87" t="inlineStr">
         <is>
           <t>Tabla 3. Candidatos (consulta 2026-07-23).</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="59" t="inlineStr">
+    <row r="64" ht="45" customHeight="1">
+      <c r="A64" s="82" t="inlineStr">
         <is>
           <t>Producto</t>
         </is>
       </c>
-      <c r="B58" s="59" t="n"/>
-      <c r="C58" s="59" t="n"/>
-      <c r="D58" s="59" t="inlineStr">
+      <c r="B64" s="82" t="n"/>
+      <c r="C64" s="82" t="n"/>
+      <c r="D64" s="82" t="inlineStr">
         <is>
           <t>Tipo / material</t>
         </is>
       </c>
-      <c r="E58" s="59" t="n"/>
-      <c r="F58" s="59" t="n"/>
-      <c r="G58" s="59" t="inlineStr">
+      <c r="E64" s="82" t="n"/>
+      <c r="F64" s="82" t="n"/>
+      <c r="G64" s="82" t="inlineStr">
         <is>
           <t>Pros</t>
         </is>
       </c>
-      <c r="H58" s="59" t="n"/>
-      <c r="I58" s="59" t="n"/>
-      <c r="J58" s="59" t="inlineStr">
+      <c r="H64" s="82" t="n"/>
+      <c r="I64" s="82" t="n"/>
+      <c r="J64" s="82" t="inlineStr">
         <is>
           <t>Contras</t>
         </is>
       </c>
-      <c r="K58" s="59" t="n"/>
-      <c r="L58" s="59" t="n"/>
-      <c r="M58" s="59" t="inlineStr">
+      <c r="K64" s="82" t="n"/>
+      <c r="L64" s="82" t="n"/>
+      <c r="M64" s="82" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="N58" s="59" t="n"/>
-      <c r="O58" s="59" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="60" t="inlineStr">
+      <c r="N64" s="82" t="n"/>
+      <c r="O64" s="82" t="n"/>
+    </row>
+    <row r="65" ht="240" customHeight="1">
+      <c r="A65" s="83" t="inlineStr">
         <is>
           <t>Titus 50F / 50R</t>
         </is>
       </c>
-      <c r="B59" s="61" t="n"/>
-      <c r="C59" s="61" t="n"/>
-      <c r="D59" s="60" t="inlineStr">
+      <c r="B65" s="84" t="n"/>
+      <c r="C65" s="84" t="n"/>
+      <c r="D65" s="83" t="inlineStr">
         <is>
           <t>Eggcrate ½ in; aluminio, con versión íntegramente inox de fábrica</t>
         </is>
       </c>
-      <c r="E59" s="61" t="n"/>
-      <c r="F59" s="61" t="n"/>
-      <c r="G59" s="60" t="inlineStr">
+      <c r="E65" s="84" t="n"/>
+      <c r="F65" s="84" t="n"/>
+      <c r="G65" s="83" t="inlineStr">
         <is>
           <t>«Highest free area of any return grille»; única opción inox de catálogo</t>
         </is>
       </c>
-      <c r="H59" s="61" t="n"/>
-      <c r="I59" s="61" t="n"/>
-      <c r="J59" s="60" t="inlineStr">
+      <c r="H65" s="84" t="n"/>
+      <c r="I65" s="84" t="n"/>
+      <c r="J65" s="83" t="inlineStr">
         <is>
           <t>Importación; tamaño 353×336 por pedido</t>
         </is>
       </c>
-      <c r="K59" s="61" t="n"/>
-      <c r="L59" s="61" t="n"/>
-      <c r="M59" s="60" t="inlineStr">
+      <c r="K65" s="84" t="n"/>
+      <c r="L65" s="84" t="n"/>
+      <c r="M65" s="83" t="inlineStr">
         <is>
           <t>Titus 50F (PDF) (https://www.titus-hvac.com/file/1228/50F_50Rrprod_specialized_2017.pdf)</t>
         </is>
       </c>
-      <c r="N59" s="61" t="n"/>
-      <c r="O59" s="61" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="60" t="inlineStr">
+      <c r="N65" s="84" t="n"/>
+      <c r="O65" s="84" t="n"/>
+    </row>
+    <row r="66" ht="255" customHeight="1">
+      <c r="A66" s="83" t="inlineStr">
         <is>
           <t>Krueger EGC5</t>
         </is>
       </c>
-      <c r="B60" s="61" t="n"/>
-      <c r="C60" s="61" t="n"/>
-      <c r="D60" s="60" t="inlineStr">
+      <c r="B66" s="84" t="n"/>
+      <c r="C66" s="84" t="n"/>
+      <c r="D66" s="83" t="inlineStr">
         <is>
           <t>Eggcrate ½ in; aluminio</t>
         </is>
       </c>
-      <c r="E60" s="61" t="n"/>
-      <c r="F60" s="61" t="n"/>
-      <c r="G60" s="60" t="inlineStr">
+      <c r="E66" s="84" t="n"/>
+      <c r="F66" s="84" t="n"/>
+      <c r="G66" s="83" t="inlineStr">
         <is>
           <t>Amplia gama de tamaños (6×4 in a 96×96 in)</t>
         </is>
       </c>
-      <c r="H60" s="61" t="n"/>
-      <c r="I60" s="61" t="n"/>
-      <c r="J60" s="60" t="inlineStr">
+      <c r="H66" s="84" t="n"/>
+      <c r="I66" s="84" t="n"/>
+      <c r="J66" s="83" t="inlineStr">
         <is>
           <t>Sin ejecución inox</t>
         </is>
       </c>
-      <c r="K60" s="61" t="n"/>
-      <c r="L60" s="61" t="n"/>
-      <c r="M60" s="60" t="inlineStr">
+      <c r="K66" s="84" t="n"/>
+      <c r="L66" s="84" t="n"/>
+      <c r="M66" s="83" t="inlineStr">
         <is>
           <t>Krueger EGC5 (https://www.krueger-hvac.com/Catalog%20Home/Grilles/Grilles%20-%20Return/EGC5)</t>
         </is>
       </c>
-      <c r="N60" s="61" t="n"/>
-      <c r="O60" s="61" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="60" t="inlineStr">
+      <c r="N66" s="84" t="n"/>
+      <c r="O66" s="84" t="n"/>
+    </row>
+    <row r="67" ht="240" customHeight="1">
+      <c r="A67" s="83" t="inlineStr">
         <is>
           <t>ProAire S.A.S (Bogotá)</t>
         </is>
       </c>
-      <c r="B61" s="61" t="n"/>
-      <c r="C61" s="61" t="n"/>
-      <c r="D61" s="60" t="inlineStr">
+      <c r="B67" s="84" t="n"/>
+      <c r="C67" s="84" t="n"/>
+      <c r="D67" s="83" t="inlineStr">
         <is>
           <t>Fabricación a medida con corte láser, inox 316</t>
         </is>
       </c>
-      <c r="E61" s="61" t="n"/>
-      <c r="F61" s="61" t="n"/>
-      <c r="G61" s="60" t="inlineStr">
+      <c r="E67" s="84" t="n"/>
+      <c r="F67" s="84" t="n"/>
+      <c r="G67" s="83" t="inlineStr">
         <is>
           <t>Medida exacta 353×336 y ejecución inox 316L local; vía recomendada</t>
         </is>
       </c>
-      <c r="H61" s="61" t="n"/>
-      <c r="I61" s="61" t="n"/>
-      <c r="J61" s="60" t="inlineStr">
+      <c r="H67" s="84" t="n"/>
+      <c r="I67" s="84" t="n"/>
+      <c r="J67" s="83" t="inlineStr">
         <is>
           <t>Submittal y Ak por confirmar con proveedor</t>
         </is>
       </c>
-      <c r="K61" s="61" t="n"/>
-      <c r="L61" s="61" t="n"/>
-      <c r="M61" s="60" t="inlineStr">
+      <c r="K67" s="84" t="n"/>
+      <c r="L67" s="84" t="n"/>
+      <c r="M67" s="83" t="inlineStr">
         <is>
           <t>proairecolombia.com (https://www.proairecolombia.com/productos/rejillas-y-difusores.html)</t>
         </is>
       </c>
-      <c r="N61" s="61" t="n"/>
-      <c r="O61" s="61" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="60" t="inlineStr">
+      <c r="N67" s="84" t="n"/>
+      <c r="O67" s="84" t="n"/>
+    </row>
+    <row r="68" ht="195" customHeight="1">
+      <c r="A68" s="83" t="inlineStr">
         <is>
           <t>Laminaire (Colombia)</t>
         </is>
       </c>
-      <c r="B62" s="61" t="n"/>
-      <c r="C62" s="61" t="n"/>
-      <c r="D62" s="60" t="inlineStr">
+      <c r="B68" s="84" t="n"/>
+      <c r="C68" s="84" t="n"/>
+      <c r="D68" s="83" t="inlineStr">
         <is>
           <t>Rejillas y difusores en aluminio a pedido</t>
         </is>
       </c>
-      <c r="E62" s="61" t="n"/>
-      <c r="F62" s="61" t="n"/>
-      <c r="G62" s="60" t="inlineStr">
+      <c r="E68" s="84" t="n"/>
+      <c r="F68" s="84" t="n"/>
+      <c r="G68" s="83" t="inlineStr">
         <is>
           <t>Fabricación local con software de selección; marco para malla a pedido</t>
         </is>
       </c>
-      <c r="H62" s="61" t="n"/>
-      <c r="I62" s="61" t="n"/>
-      <c r="J62" s="60" t="inlineStr">
+      <c r="H68" s="84" t="n"/>
+      <c r="I68" s="84" t="n"/>
+      <c r="J68" s="83" t="inlineStr">
         <is>
           <t>Confirmar ejecución inox</t>
         </is>
       </c>
-      <c r="K62" s="61" t="n"/>
-      <c r="L62" s="61" t="n"/>
-      <c r="M62" s="60" t="inlineStr">
+      <c r="K68" s="84" t="n"/>
+      <c r="L68" s="84" t="n"/>
+      <c r="M68" s="83" t="inlineStr">
         <is>
           <t>laminaire.net (https://laminaire.net/)</t>
         </is>
       </c>
-      <c r="N62" s="61" t="n"/>
-      <c r="O62" s="61" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="60" t="inlineStr">
+      <c r="N68" s="84" t="n"/>
+      <c r="O68" s="84" t="n"/>
+    </row>
+    <row r="69" ht="120" customHeight="1">
+      <c r="A69" s="83" t="inlineStr">
         <is>
           <t>CL Ingeniería (Bogotá)</t>
         </is>
       </c>
-      <c r="B63" s="61" t="n"/>
-      <c r="C63" s="61" t="n"/>
-      <c r="D63" s="60" t="inlineStr">
+      <c r="B69" s="84" t="n"/>
+      <c r="C69" s="84" t="n"/>
+      <c r="D69" s="83" t="inlineStr">
         <is>
           <t>Rejillas y accesorios HVAC</t>
         </is>
       </c>
-      <c r="E63" s="61" t="n"/>
-      <c r="F63" s="61" t="n"/>
-      <c r="G63" s="60" t="inlineStr">
+      <c r="E69" s="84" t="n"/>
+      <c r="F69" s="84" t="n"/>
+      <c r="G69" s="83" t="inlineStr">
         <is>
           <t>Canal local adicional</t>
         </is>
       </c>
-      <c r="H63" s="61" t="n"/>
-      <c r="I63" s="61" t="n"/>
-      <c r="J63" s="60" t="inlineStr">
+      <c r="H69" s="84" t="n"/>
+      <c r="I69" s="84" t="n"/>
+      <c r="J69" s="83" t="inlineStr">
         <is>
           <t>Catálogo genérico</t>
         </is>
       </c>
-      <c r="K63" s="61" t="n"/>
-      <c r="L63" s="61" t="n"/>
-      <c r="M63" s="60" t="inlineStr">
+      <c r="K69" s="84" t="n"/>
+      <c r="L69" s="84" t="n"/>
+      <c r="M69" s="83" t="inlineStr">
         <is>
           <t>clingenieria.co (https://clingenieria.co/)</t>
         </is>
       </c>
-      <c r="N63" s="61" t="n"/>
-      <c r="O63" s="61" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="62" t="inlineStr">
+      <c r="N69" s="84" t="n"/>
+      <c r="O69" s="84" t="n"/>
+    </row>
+    <row r="70" ht="15" customHeight="1"/>
+    <row r="71" ht="15" customHeight="1"/>
+    <row r="72" ht="45" customHeight="1">
+      <c r="A72" s="85" t="inlineStr">
         <is>
           <t>5. Instalación</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="63" t="inlineStr">
+    <row r="73" ht="150" customHeight="1">
+      <c r="A73" s="86" t="inlineStr">
         <is>
           <t>5.1. Montaje a ras de muro exterior con marco perimetral sellado con silicona RTV neutra (compatible con hipoclorito; Chemical Resistance of RTV Silicone Sealants (PDF) (https://irp.cdn-website.com/63168859/files/uploaded/Chemical%20Resistance%20of%20RTV%20Silicone%20Sealants%20Chart.pdf), consulta 2026-07-23) y ferretería inox 316 (A4).</t>
         </is>
       </c>
     </row>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70">
-      <c r="A70" s="63" t="inlineStr">
+    <row r="74" ht="15" customHeight="1"/>
+    <row r="75" ht="15" customHeight="1"/>
+    <row r="76" ht="15" customHeight="1"/>
+    <row r="77" ht="15" customHeight="1"/>
+    <row r="78" ht="15" customHeight="1"/>
+    <row r="79" ht="150" customHeight="1">
+      <c r="A79" s="86" t="inlineStr">
         <is>
           <t>5.2. Las bocas exteriores se orientan preferentemente a sotavento respecto de las fuentes de cloro de la planta.</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="63" t="inlineStr">
+    <row r="80" ht="15" customHeight="1"/>
+    <row r="81" ht="165" customHeight="1">
+      <c r="A81" s="86" t="inlineStr">
         <is>
           <t>5.3. Programa de limpieza de la malla según carga de polvo observada en comisionamiento (dato típico de operación).</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="62" t="inlineStr">
+    <row r="82" ht="15" customHeight="1"/>
+    <row r="83" ht="15" customHeight="1"/>
+    <row r="84" ht="60" customHeight="1">
+      <c r="A84" s="85" t="inlineStr">
         <is>
           <t>6. Normas aplicables</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="63" t="inlineStr">
+    <row r="85" ht="165" customHeight="1">
+      <c r="A85" s="86" t="inlineStr">
         <is>
           <t>6.1. ASHRAE 70 (método de ensayo y reporte de desempeño de rejillas); correlación de área libre para transferencia de aire según Building Science BA-0006 (https://buildingscience.com/sites/default/files/migrate/pdf/BA-0006_Discuss_transfer_grilles.pdf) (consulta 2026-07-23); ISO 12944 / NACE-AMPP para la selección de materiales en el ambiente clorado.</t>
         </is>
       </c>
     </row>
-    <row r="75"/>
-    <row r="76"/>
+    <row r="86" ht="15" customHeight="1"/>
+    <row r="87" ht="15" customHeight="1"/>
+    <row r="88" ht="15" customHeight="1"/>
+    <row r="89" ht="15" customHeight="1"/>
+    <row r="90" ht="15" customHeight="1"/>
   </sheetData>
-  <mergeCells count="101">
-    <mergeCell ref="A66:O66"/>
-    <mergeCell ref="I44:O44"/>
-    <mergeCell ref="G62:I62"/>
+  <mergeCells count="104">
+    <mergeCell ref="I52:O52"/>
+    <mergeCell ref="A85:O90"/>
+    <mergeCell ref="D66:F66"/>
     <mergeCell ref="A49:H49"/>
-    <mergeCell ref="A19:O22"/>
     <mergeCell ref="N3:O3"/>
+    <mergeCell ref="A19:O24"/>
+    <mergeCell ref="G65:I65"/>
+    <mergeCell ref="J66:L66"/>
     <mergeCell ref="I30:O30"/>
+    <mergeCell ref="A79:O80"/>
     <mergeCell ref="N5:O5"/>
     <mergeCell ref="I46:O46"/>
     <mergeCell ref="C2:L3"/>
-    <mergeCell ref="G63:I63"/>
     <mergeCell ref="A50:H50"/>
-    <mergeCell ref="A63:C63"/>
-    <mergeCell ref="J61:L61"/>
+    <mergeCell ref="A55:H55"/>
+    <mergeCell ref="M66:O66"/>
+    <mergeCell ref="A44:O44"/>
+    <mergeCell ref="I54:O54"/>
     <mergeCell ref="A32:H32"/>
     <mergeCell ref="I32:O32"/>
-    <mergeCell ref="I41:O41"/>
-    <mergeCell ref="A24:O24"/>
-    <mergeCell ref="A73:O73"/>
+    <mergeCell ref="M68:O68"/>
     <mergeCell ref="A29:H29"/>
-    <mergeCell ref="I43:O43"/>
+    <mergeCell ref="M67:O67"/>
     <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A44:H44"/>
+    <mergeCell ref="A69:C69"/>
     <mergeCell ref="A31:H31"/>
     <mergeCell ref="B1:B5"/>
     <mergeCell ref="I33:O33"/>
+    <mergeCell ref="M69:O69"/>
+    <mergeCell ref="A66:C66"/>
     <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A51:H51"/>
+    <mergeCell ref="J65:L65"/>
+    <mergeCell ref="A57:O60"/>
+    <mergeCell ref="G69:I69"/>
+    <mergeCell ref="I35:O35"/>
+    <mergeCell ref="A84:O84"/>
     <mergeCell ref="I10:O10"/>
     <mergeCell ref="A18:O18"/>
-    <mergeCell ref="A74:O76"/>
     <mergeCell ref="I50:O50"/>
-    <mergeCell ref="J63:L63"/>
     <mergeCell ref="N2:O2"/>
-    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="G64:I64"/>
+    <mergeCell ref="D68:F68"/>
+    <mergeCell ref="A62:O62"/>
     <mergeCell ref="I11:O11"/>
-    <mergeCell ref="I45:O45"/>
-    <mergeCell ref="A58:C58"/>
-    <mergeCell ref="A42:H42"/>
-    <mergeCell ref="D60:F60"/>
+    <mergeCell ref="D67:F67"/>
+    <mergeCell ref="A72:O72"/>
+    <mergeCell ref="A67:C67"/>
     <mergeCell ref="A47:H47"/>
     <mergeCell ref="I47:O47"/>
-    <mergeCell ref="M58:O58"/>
-    <mergeCell ref="I28:O28"/>
-    <mergeCell ref="A60:C60"/>
+    <mergeCell ref="D69:F69"/>
+    <mergeCell ref="J67:L67"/>
     <mergeCell ref="N6:O6"/>
-    <mergeCell ref="J60:L60"/>
-    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="J69:L69"/>
     <mergeCell ref="N4:O4"/>
     <mergeCell ref="A48:H48"/>
     <mergeCell ref="A30:H30"/>
-    <mergeCell ref="A56:O56"/>
-    <mergeCell ref="G58:I58"/>
-    <mergeCell ref="D58:F58"/>
-    <mergeCell ref="A41:H41"/>
-    <mergeCell ref="M61:O61"/>
-    <mergeCell ref="A62:C62"/>
-    <mergeCell ref="M62:O62"/>
+    <mergeCell ref="G66:I66"/>
+    <mergeCell ref="I51:O51"/>
+    <mergeCell ref="G68:I68"/>
+    <mergeCell ref="A54:H54"/>
+    <mergeCell ref="I34:O34"/>
     <mergeCell ref="I49:O49"/>
-    <mergeCell ref="I27:O27"/>
-    <mergeCell ref="A26:H26"/>
-    <mergeCell ref="J58:L58"/>
+    <mergeCell ref="A73:O78"/>
+    <mergeCell ref="I36:O36"/>
     <mergeCell ref="A33:H33"/>
-    <mergeCell ref="D59:F59"/>
-    <mergeCell ref="A35:O37"/>
-    <mergeCell ref="A59:C59"/>
+    <mergeCell ref="A1:A5"/>
     <mergeCell ref="A9:O9"/>
-    <mergeCell ref="A67:O69"/>
-    <mergeCell ref="A1:A5"/>
     <mergeCell ref="C1:L1"/>
-    <mergeCell ref="A39:O39"/>
-    <mergeCell ref="M59:O59"/>
-    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="A53:H53"/>
+    <mergeCell ref="I53:O53"/>
+    <mergeCell ref="A35:H35"/>
     <mergeCell ref="A10:H10"/>
-    <mergeCell ref="J59:L59"/>
     <mergeCell ref="I12:O12"/>
-    <mergeCell ref="M60:O60"/>
+    <mergeCell ref="I55:O55"/>
+    <mergeCell ref="J68:L68"/>
+    <mergeCell ref="A34:H34"/>
     <mergeCell ref="I14:O14"/>
+    <mergeCell ref="A81:O82"/>
     <mergeCell ref="I48:O48"/>
-    <mergeCell ref="D61:F61"/>
     <mergeCell ref="I29:O29"/>
+    <mergeCell ref="A36:H36"/>
     <mergeCell ref="A11:H11"/>
-    <mergeCell ref="A45:H45"/>
+    <mergeCell ref="M65:O65"/>
+    <mergeCell ref="M64:O64"/>
     <mergeCell ref="I13:O13"/>
+    <mergeCell ref="A26:O26"/>
     <mergeCell ref="I31:O31"/>
-    <mergeCell ref="D62:F62"/>
     <mergeCell ref="I15:O15"/>
     <mergeCell ref="A46:H46"/>
     <mergeCell ref="N1:O1"/>
     <mergeCell ref="A12:H12"/>
-    <mergeCell ref="J62:L62"/>
-    <mergeCell ref="M63:O63"/>
-    <mergeCell ref="G60:I60"/>
-    <mergeCell ref="I26:O26"/>
+    <mergeCell ref="D64:F64"/>
+    <mergeCell ref="A68:C68"/>
     <mergeCell ref="A14:H14"/>
-    <mergeCell ref="G59:I59"/>
-    <mergeCell ref="D63:F63"/>
-    <mergeCell ref="A52:O54"/>
+    <mergeCell ref="A27:O28"/>
+    <mergeCell ref="J64:L64"/>
+    <mergeCell ref="A38:O42"/>
     <mergeCell ref="C4:L6"/>
-    <mergeCell ref="A43:H43"/>
-    <mergeCell ref="G61:I61"/>
-    <mergeCell ref="I42:O42"/>
+    <mergeCell ref="G67:I67"/>
+    <mergeCell ref="D65:F65"/>
+    <mergeCell ref="A52:H52"/>
+    <mergeCell ref="A65:C65"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/build/dts/P2437-HV-DTS-003 REV0.xlsx
+++ b/build/dts/P2437-HV-DTS-003 REV0.xlsx
@@ -22,7 +22,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.00000000000000"/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="30">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -135,35 +135,23 @@
     <font>
       <name val="Times New Roman"/>
       <b val="1"/>
-      <color rgb="001F4E78"/>
-      <sz val="14"/>
+      <color rgb="00375623"/>
+      <sz val="28"/>
     </font>
     <font>
       <name val="Times New Roman"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Times New Roman"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Times New Roman"/>
-      <b val="1"/>
-      <color rgb="001F4E78"/>
-      <sz val="12"/>
+      <sz val="28"/>
     </font>
     <font>
       <name val="Times New Roman"/>
       <i val="1"/>
       <color rgb="00404040"/>
-      <sz val="10"/>
+      <sz val="28"/>
     </font>
     <font>
       <name val="Times New Roman"/>
       <b val="1"/>
-      <sz val="11"/>
+      <sz val="28"/>
     </font>
     <font>
       <name val="Times New Roman"/>
@@ -243,8 +231,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
-        <bgColor rgb="001F4E78"/>
+        <fgColor rgb="00C6E0B4"/>
+        <bgColor rgb="00C6E0B4"/>
       </patternFill>
     </fill>
   </fills>
@@ -401,7 +389,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
@@ -519,12 +507,12 @@
     <xf numFmtId="164" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -537,74 +525,71 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="1" hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="31" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="4"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3721,89 +3706,64 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O90"/>
+  <dimension ref="A1:O67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30.6" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="6" customWidth="1" min="5" max="5"/>
-    <col width="6" customWidth="1" min="6" max="6"/>
-    <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="49" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
     <col width="13" customWidth="1" min="18" max="18"/>
     <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="13" customWidth="1" min="20" max="20"/>
     <col width="13" customWidth="1" min="21" max="21"/>
-    <col width="13" customWidth="1" min="22" max="22"/>
     <col width="13" customWidth="1" min="23" max="23"/>
     <col width="13" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
     <col width="13" customWidth="1" min="26" max="26"/>
     <col width="13" customWidth="1" min="27" max="27"/>
     <col width="13" customWidth="1" min="28" max="28"/>
     <col width="13" customWidth="1" min="29" max="29"/>
     <col width="13" customWidth="1" min="30" max="30"/>
-    <col width="13" customWidth="1" min="31" max="31"/>
     <col width="13" customWidth="1" min="32" max="32"/>
     <col width="13" customWidth="1" min="33" max="33"/>
-    <col width="13" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
-    <col width="13" customWidth="1" min="36" max="36"/>
+    <col width="13" customWidth="1" min="37" max="37"/>
     <col width="13" customWidth="1" min="38" max="38"/>
     <col width="13" customWidth="1" min="39" max="39"/>
     <col width="13" customWidth="1" min="40" max="40"/>
     <col width="13" customWidth="1" min="41" max="41"/>
     <col width="13" customWidth="1" min="42" max="42"/>
+    <col width="13" customWidth="1" min="43" max="43"/>
     <col width="13" customWidth="1" min="44" max="44"/>
+    <col width="13" customWidth="1" min="45" max="45"/>
     <col width="13" customWidth="1" min="46" max="46"/>
-    <col width="13" customWidth="1" min="47" max="47"/>
-    <col width="13" customWidth="1" min="48" max="48"/>
-    <col width="13" customWidth="1" min="49" max="49"/>
     <col width="13" customWidth="1" min="50" max="50"/>
-    <col width="13" customWidth="1" min="51" max="51"/>
     <col width="13" customWidth="1" min="52" max="52"/>
     <col width="13" customWidth="1" min="53" max="53"/>
     <col width="13" customWidth="1" min="54" max="54"/>
     <col width="13" customWidth="1" min="55" max="55"/>
+    <col width="13" customWidth="1" min="56" max="56"/>
     <col width="13" customWidth="1" min="57" max="57"/>
-    <col width="13" customWidth="1" min="58" max="58"/>
     <col width="13" customWidth="1" min="59" max="59"/>
     <col width="13" customWidth="1" min="60" max="60"/>
-    <col width="13" customWidth="1" min="62" max="62"/>
-    <col width="13" customWidth="1" min="64" max="64"/>
+    <col width="13" customWidth="1" min="61" max="61"/>
     <col width="13" customWidth="1" min="65" max="65"/>
     <col width="13" customWidth="1" min="66" max="66"/>
     <col width="13" customWidth="1" min="67" max="67"/>
-    <col width="13" customWidth="1" min="68" max="68"/>
-    <col width="13" customWidth="1" min="69" max="69"/>
-    <col width="13" customWidth="1" min="72" max="72"/>
-    <col width="13" customWidth="1" min="73" max="73"/>
-    <col width="13" customWidth="1" min="74" max="74"/>
-    <col width="13" customWidth="1" min="75" max="75"/>
-    <col width="13" customWidth="1" min="76" max="76"/>
-    <col width="13" customWidth="1" min="77" max="77"/>
-    <col width="13" customWidth="1" min="78" max="78"/>
-    <col width="13" customWidth="1" min="79" max="79"/>
-    <col width="13" customWidth="1" min="80" max="80"/>
-    <col width="13" customWidth="1" min="81" max="81"/>
-    <col width="13" customWidth="1" min="82" max="82"/>
-    <col width="13" customWidth="1" min="84" max="84"/>
-    <col width="13" customWidth="1" min="85" max="85"/>
-    <col width="13" customWidth="1" min="86" max="86"/>
-    <col width="13" customWidth="1" min="87" max="87"/>
-    <col width="13" customWidth="1" min="88" max="88"/>
-    <col width="13" customWidth="1" min="89" max="89"/>
-    <col width="13" customWidth="1" min="90" max="90"/>
   </cols>
   <sheetData>
     <row r="1" ht="29.25" customHeight="1">
@@ -4013,14 +3973,14 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" ht="345" customHeight="1">
+    <row r="9" ht="228" customHeight="1">
       <c r="A9" s="81" t="inlineStr">
         <is>
           <t>Hoja de datos: rejillas de descarga con malla anti-insectos</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
+    <row r="10" ht="38" customHeight="1">
       <c r="A10" s="82" t="inlineStr">
         <is>
           <t>Campo</t>
@@ -4045,7 +4005,7 @@
       <c r="N10" s="82" t="n"/>
       <c r="O10" s="82" t="n"/>
     </row>
-    <row r="11" ht="45" customHeight="1">
+    <row r="11" ht="38" customHeight="1">
       <c r="A11" s="83" t="inlineStr">
         <is>
           <t>Código</t>
@@ -4070,7 +4030,7 @@
       <c r="N11" s="84" t="n"/>
       <c r="O11" s="84" t="n"/>
     </row>
-    <row r="12" ht="45" customHeight="1">
+    <row r="12" ht="38" customHeight="1">
       <c r="A12" s="83" t="inlineStr">
         <is>
           <t>Revisión</t>
@@ -4095,7 +4055,7 @@
       <c r="N12" s="84" t="n"/>
       <c r="O12" s="84" t="n"/>
     </row>
-    <row r="13" ht="45" customHeight="1">
+    <row r="13" ht="38" customHeight="1">
       <c r="A13" s="83" t="inlineStr">
         <is>
           <t>Fecha</t>
@@ -4120,7 +4080,7 @@
       <c r="N13" s="84" t="n"/>
       <c r="O13" s="84" t="n"/>
     </row>
-    <row r="14" ht="240" customHeight="1">
+    <row r="14" ht="152" customHeight="1">
       <c r="A14" s="83" t="inlineStr">
         <is>
           <t>Proyecto</t>
@@ -4145,7 +4105,7 @@
       <c r="N14" s="84" t="n"/>
       <c r="O14" s="84" t="n"/>
     </row>
-    <row r="15" ht="150" customHeight="1">
+    <row r="15" ht="114" customHeight="1">
       <c r="A15" s="83" t="inlineStr">
         <is>
           <t>Etiqueta de equipo</t>
@@ -4170,72 +4130,216 @@
       <c r="N15" s="84" t="n"/>
       <c r="O15" s="84" t="n"/>
     </row>
-    <row r="16" ht="15" customHeight="1"/>
-    <row r="17" ht="15" customHeight="1"/>
-    <row r="18" ht="30" customHeight="1">
+    <row r="16" ht="38" customHeight="1"/>
+    <row r="17" ht="38" customHeight="1">
+      <c r="A17" s="81" t="inlineStr">
+        <is>
+          <t>1. Servicio</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="494" customHeight="1">
       <c r="A18" s="85" t="inlineStr">
         <is>
-          <t>1. Servicio</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="165" customHeight="1">
-      <c r="A19" s="86" t="inlineStr">
-        <is>
           <t>1.1. Descarga libre a la atmósfera del caudal de ventilación del laboratorio, a través de la envolvente del recinto. Las rejillas son la trayectoria de salida permanente del aire y, con el sistema detenido, una vía potencial de ingreso: por ello incorporan malla anti-insectos. Ambiente exterior corrosivo (atmósfera clorada de planta de hipoclorito de calcio).</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1"/>
-    <row r="21" ht="15" customHeight="1"/>
-    <row r="22" ht="15" customHeight="1"/>
-    <row r="23" ht="15" customHeight="1"/>
-    <row r="24" ht="15" customHeight="1"/>
-    <row r="25" ht="15" customHeight="1"/>
-    <row r="26" ht="105" customHeight="1">
-      <c r="A26" s="85" t="inlineStr">
+    <row r="19" ht="38" customHeight="1"/>
+    <row r="20" ht="38" customHeight="1"/>
+    <row r="21" ht="114" customHeight="1">
+      <c r="A21" s="81" t="inlineStr">
         <is>
           <t>2. Condiciones de operación y desempeño</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="105" customHeight="1">
-      <c r="A27" s="87" t="inlineStr">
+    <row r="22" ht="76" customHeight="1">
+      <c r="A22" s="86" t="inlineStr">
         <is>
           <t>Tabla 1. Condiciones de diseño (valores congelados de la memoria de cálculo).</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1"/>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="82" t="inlineStr">
+    <row r="23" ht="38" customHeight="1">
+      <c r="A23" s="82" t="inlineStr">
         <is>
           <t>Parámetro</t>
         </is>
       </c>
-      <c r="B29" s="82" t="n"/>
-      <c r="C29" s="82" t="n"/>
-      <c r="D29" s="82" t="n"/>
-      <c r="E29" s="82" t="n"/>
-      <c r="F29" s="82" t="n"/>
-      <c r="G29" s="82" t="n"/>
-      <c r="H29" s="82" t="n"/>
-      <c r="I29" s="82" t="inlineStr">
+      <c r="B23" s="82" t="n"/>
+      <c r="C23" s="82" t="n"/>
+      <c r="D23" s="82" t="n"/>
+      <c r="E23" s="82" t="n"/>
+      <c r="F23" s="82" t="n"/>
+      <c r="G23" s="82" t="n"/>
+      <c r="H23" s="82" t="n"/>
+      <c r="I23" s="82" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
       </c>
-      <c r="J29" s="82" t="n"/>
-      <c r="K29" s="82" t="n"/>
-      <c r="L29" s="82" t="n"/>
-      <c r="M29" s="82" t="n"/>
-      <c r="N29" s="82" t="n"/>
-      <c r="O29" s="82" t="n"/>
-    </row>
-    <row r="30" ht="30" customHeight="1">
+      <c r="J23" s="82" t="n"/>
+      <c r="K23" s="82" t="n"/>
+      <c r="L23" s="82" t="n"/>
+      <c r="M23" s="82" t="n"/>
+      <c r="N23" s="82" t="n"/>
+      <c r="O23" s="82" t="n"/>
+    </row>
+    <row r="24" ht="38" customHeight="1">
+      <c r="A24" s="83" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="B24" s="84" t="n"/>
+      <c r="C24" s="84" t="n"/>
+      <c r="D24" s="84" t="n"/>
+      <c r="E24" s="84" t="n"/>
+      <c r="F24" s="84" t="n"/>
+      <c r="G24" s="84" t="n"/>
+      <c r="H24" s="84" t="n"/>
+      <c r="I24" s="83" t="inlineStr">
+        <is>
+          <t>3 unidades</t>
+        </is>
+      </c>
+      <c r="J24" s="84" t="n"/>
+      <c r="K24" s="84" t="n"/>
+      <c r="L24" s="84" t="n"/>
+      <c r="M24" s="84" t="n"/>
+      <c r="N24" s="84" t="n"/>
+      <c r="O24" s="84" t="n"/>
+    </row>
+    <row r="25" ht="114" customHeight="1">
+      <c r="A25" s="83" t="inlineStr">
+        <is>
+          <t>Dimensiones faciales (unitarias)</t>
+        </is>
+      </c>
+      <c r="B25" s="84" t="n"/>
+      <c r="C25" s="84" t="n"/>
+      <c r="D25" s="84" t="n"/>
+      <c r="E25" s="84" t="n"/>
+      <c r="F25" s="84" t="n"/>
+      <c r="G25" s="84" t="n"/>
+      <c r="H25" s="84" t="n"/>
+      <c r="I25" s="83" t="inlineStr">
+        <is>
+          <t>353×336 mm (área facial 0.1187 m²)</t>
+        </is>
+      </c>
+      <c r="J25" s="84" t="n"/>
+      <c r="K25" s="84" t="n"/>
+      <c r="L25" s="84" t="n"/>
+      <c r="M25" s="84" t="n"/>
+      <c r="N25" s="84" t="n"/>
+      <c r="O25" s="84" t="n"/>
+    </row>
+    <row r="26" ht="76" customHeight="1">
+      <c r="A26" s="83" t="inlineStr">
+        <is>
+          <t>Caudal total de descarga</t>
+        </is>
+      </c>
+      <c r="B26" s="84" t="n"/>
+      <c r="C26" s="84" t="n"/>
+      <c r="D26" s="84" t="n"/>
+      <c r="E26" s="84" t="n"/>
+      <c r="F26" s="84" t="n"/>
+      <c r="G26" s="84" t="n"/>
+      <c r="H26" s="84" t="n"/>
+      <c r="I26" s="83" t="inlineStr">
+        <is>
+          <t>3 840 m³/h (1.0667 m³/s)</t>
+        </is>
+      </c>
+      <c r="J26" s="84" t="n"/>
+      <c r="K26" s="84" t="n"/>
+      <c r="L26" s="84" t="n"/>
+      <c r="M26" s="84" t="n"/>
+      <c r="N26" s="84" t="n"/>
+      <c r="O26" s="84" t="n"/>
+    </row>
+    <row r="27" ht="76" customHeight="1">
+      <c r="A27" s="83" t="inlineStr">
+        <is>
+          <t>Velocidad facial</t>
+        </is>
+      </c>
+      <c r="B27" s="84" t="n"/>
+      <c r="C27" s="84" t="n"/>
+      <c r="D27" s="84" t="n"/>
+      <c r="E27" s="84" t="n"/>
+      <c r="F27" s="84" t="n"/>
+      <c r="G27" s="84" t="n"/>
+      <c r="H27" s="84" t="n"/>
+      <c r="I27" s="83" t="inlineStr">
+        <is>
+          <t>3 m/s</t>
+        </is>
+      </c>
+      <c r="J27" s="84" t="n"/>
+      <c r="K27" s="84" t="n"/>
+      <c r="L27" s="84" t="n"/>
+      <c r="M27" s="84" t="n"/>
+      <c r="N27" s="84" t="n"/>
+      <c r="O27" s="84" t="n"/>
+    </row>
+    <row r="28" ht="152" customHeight="1">
+      <c r="A28" s="83" t="inlineStr">
+        <is>
+          <t>ΔP unitaria (cierre de orificio, C_d = 0.60, en el sitio)</t>
+        </is>
+      </c>
+      <c r="B28" s="84" t="n"/>
+      <c r="C28" s="84" t="n"/>
+      <c r="D28" s="84" t="n"/>
+      <c r="E28" s="84" t="n"/>
+      <c r="F28" s="84" t="n"/>
+      <c r="G28" s="84" t="n"/>
+      <c r="H28" s="84" t="n"/>
+      <c r="I28" s="83" t="inlineStr">
+        <is>
+          <t>11 Pa</t>
+        </is>
+      </c>
+      <c r="J28" s="84" t="n"/>
+      <c r="K28" s="84" t="n"/>
+      <c r="L28" s="84" t="n"/>
+      <c r="M28" s="84" t="n"/>
+      <c r="N28" s="84" t="n"/>
+      <c r="O28" s="84" t="n"/>
+    </row>
+    <row r="29" ht="152" customHeight="1">
+      <c r="A29" s="83" t="inlineStr">
+        <is>
+          <t>ΔP equivalente a densidad estándar (ρ = 1.2 kg/m³)</t>
+        </is>
+      </c>
+      <c r="B29" s="84" t="n"/>
+      <c r="C29" s="84" t="n"/>
+      <c r="D29" s="84" t="n"/>
+      <c r="E29" s="84" t="n"/>
+      <c r="F29" s="84" t="n"/>
+      <c r="G29" s="84" t="n"/>
+      <c r="H29" s="84" t="n"/>
+      <c r="I29" s="83" t="inlineStr">
+        <is>
+          <t>15 Pa</t>
+        </is>
+      </c>
+      <c r="J29" s="84" t="n"/>
+      <c r="K29" s="84" t="n"/>
+      <c r="L29" s="84" t="n"/>
+      <c r="M29" s="84" t="n"/>
+      <c r="N29" s="84" t="n"/>
+      <c r="O29" s="84" t="n"/>
+    </row>
+    <row r="30" ht="114" customHeight="1">
       <c r="A30" s="83" t="inlineStr">
         <is>
-          <t>Cantidad</t>
+          <t>Densidad del aire de diseño</t>
         </is>
       </c>
       <c r="B30" s="84" t="n"/>
@@ -4247,7 +4351,7 @@
       <c r="H30" s="84" t="n"/>
       <c r="I30" s="83" t="inlineStr">
         <is>
-          <t>3 unidades</t>
+          <t>0.88 kg/m³ (2 558 msnm, 74.1 kPa)</t>
         </is>
       </c>
       <c r="J30" s="84" t="n"/>
@@ -4257,846 +4361,676 @@
       <c r="N30" s="84" t="n"/>
       <c r="O30" s="84" t="n"/>
     </row>
-    <row r="31" ht="105" customHeight="1">
-      <c r="A31" s="83" t="inlineStr">
-        <is>
-          <t>Dimensiones faciales (unitarias)</t>
-        </is>
-      </c>
-      <c r="B31" s="84" t="n"/>
-      <c r="C31" s="84" t="n"/>
-      <c r="D31" s="84" t="n"/>
-      <c r="E31" s="84" t="n"/>
-      <c r="F31" s="84" t="n"/>
-      <c r="G31" s="84" t="n"/>
-      <c r="H31" s="84" t="n"/>
-      <c r="I31" s="83" t="inlineStr">
-        <is>
-          <t>353×336 mm (área facial 0.1187 m²)</t>
-        </is>
-      </c>
-      <c r="J31" s="84" t="n"/>
-      <c r="K31" s="84" t="n"/>
-      <c r="L31" s="84" t="n"/>
-      <c r="M31" s="84" t="n"/>
-      <c r="N31" s="84" t="n"/>
-      <c r="O31" s="84" t="n"/>
-    </row>
-    <row r="32" ht="75" customHeight="1">
-      <c r="A32" s="83" t="inlineStr">
-        <is>
-          <t>Caudal total de descarga</t>
-        </is>
-      </c>
-      <c r="B32" s="84" t="n"/>
-      <c r="C32" s="84" t="n"/>
-      <c r="D32" s="84" t="n"/>
-      <c r="E32" s="84" t="n"/>
-      <c r="F32" s="84" t="n"/>
-      <c r="G32" s="84" t="n"/>
-      <c r="H32" s="84" t="n"/>
-      <c r="I32" s="83" t="inlineStr">
-        <is>
-          <t>3 840 m³/h (1.0667 m³/s)</t>
-        </is>
-      </c>
-      <c r="J32" s="84" t="n"/>
-      <c r="K32" s="84" t="n"/>
-      <c r="L32" s="84" t="n"/>
-      <c r="M32" s="84" t="n"/>
-      <c r="N32" s="84" t="n"/>
-      <c r="O32" s="84" t="n"/>
-    </row>
-    <row r="33" ht="45" customHeight="1">
-      <c r="A33" s="83" t="inlineStr">
-        <is>
-          <t>Velocidad facial</t>
-        </is>
-      </c>
-      <c r="B33" s="84" t="n"/>
-      <c r="C33" s="84" t="n"/>
-      <c r="D33" s="84" t="n"/>
-      <c r="E33" s="84" t="n"/>
-      <c r="F33" s="84" t="n"/>
-      <c r="G33" s="84" t="n"/>
-      <c r="H33" s="84" t="n"/>
-      <c r="I33" s="83" t="inlineStr">
-        <is>
-          <t>3 m/s</t>
-        </is>
-      </c>
-      <c r="J33" s="84" t="n"/>
-      <c r="K33" s="84" t="n"/>
-      <c r="L33" s="84" t="n"/>
-      <c r="M33" s="84" t="n"/>
-      <c r="N33" s="84" t="n"/>
-      <c r="O33" s="84" t="n"/>
-    </row>
-    <row r="34" ht="165" customHeight="1">
-      <c r="A34" s="83" t="inlineStr">
-        <is>
-          <t>ΔP unitaria (cierre de orificio, C_d = 0.60, en el sitio)</t>
-        </is>
-      </c>
-      <c r="B34" s="84" t="n"/>
-      <c r="C34" s="84" t="n"/>
-      <c r="D34" s="84" t="n"/>
-      <c r="E34" s="84" t="n"/>
-      <c r="F34" s="84" t="n"/>
-      <c r="G34" s="84" t="n"/>
-      <c r="H34" s="84" t="n"/>
-      <c r="I34" s="83" t="inlineStr">
-        <is>
-          <t>11 Pa</t>
-        </is>
-      </c>
-      <c r="J34" s="84" t="n"/>
-      <c r="K34" s="84" t="n"/>
-      <c r="L34" s="84" t="n"/>
-      <c r="M34" s="84" t="n"/>
-      <c r="N34" s="84" t="n"/>
-      <c r="O34" s="84" t="n"/>
-    </row>
-    <row r="35" ht="135" customHeight="1">
-      <c r="A35" s="83" t="inlineStr">
-        <is>
-          <t>ΔP equivalente a densidad estándar (ρ = 1.2 kg/m³)</t>
-        </is>
-      </c>
-      <c r="B35" s="84" t="n"/>
-      <c r="C35" s="84" t="n"/>
-      <c r="D35" s="84" t="n"/>
-      <c r="E35" s="84" t="n"/>
-      <c r="F35" s="84" t="n"/>
-      <c r="G35" s="84" t="n"/>
-      <c r="H35" s="84" t="n"/>
-      <c r="I35" s="83" t="inlineStr">
-        <is>
-          <t>15 Pa</t>
-        </is>
-      </c>
-      <c r="J35" s="84" t="n"/>
-      <c r="K35" s="84" t="n"/>
-      <c r="L35" s="84" t="n"/>
-      <c r="M35" s="84" t="n"/>
-      <c r="N35" s="84" t="n"/>
-      <c r="O35" s="84" t="n"/>
-    </row>
-    <row r="36" ht="90" customHeight="1">
-      <c r="A36" s="83" t="inlineStr">
-        <is>
-          <t>Densidad del aire de diseño</t>
-        </is>
-      </c>
-      <c r="B36" s="84" t="n"/>
-      <c r="C36" s="84" t="n"/>
-      <c r="D36" s="84" t="n"/>
-      <c r="E36" s="84" t="n"/>
-      <c r="F36" s="84" t="n"/>
-      <c r="G36" s="84" t="n"/>
-      <c r="H36" s="84" t="n"/>
-      <c r="I36" s="83" t="inlineStr">
-        <is>
-          <t>0.88 kg/m³ (2 558 msnm, 74.1 kPa)</t>
-        </is>
-      </c>
-      <c r="J36" s="84" t="n"/>
-      <c r="K36" s="84" t="n"/>
-      <c r="L36" s="84" t="n"/>
-      <c r="M36" s="84" t="n"/>
-      <c r="N36" s="84" t="n"/>
-      <c r="O36" s="84" t="n"/>
-    </row>
-    <row r="37" ht="15" customHeight="1"/>
-    <row r="38" ht="165" customHeight="1">
-      <c r="A38" s="86" t="inlineStr">
+    <row r="31" ht="38" customHeight="1"/>
+    <row r="32" ht="418" customHeight="1">
+      <c r="A32" s="85" t="inlineStr">
         <is>
           <t>2.1. Nota de contexto: la ΔP unitaria de 11 Pa (cierre de orificio, C_d = 0.60, a 3 m/s) es la pérdida de descarga libre a la atmósfera y se suma a la caída de presión de la etapa filtrante para definir el punto de trabajo del ventilador; no existe consigna de presión interior que sostener.</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="15" customHeight="1"/>
-    <row r="40" ht="15" customHeight="1"/>
-    <row r="41" ht="15" customHeight="1"/>
-    <row r="42" ht="15" customHeight="1"/>
-    <row r="43" ht="15" customHeight="1"/>
-    <row r="44" ht="90" customHeight="1">
-      <c r="A44" s="85" t="inlineStr">
+    <row r="33" ht="38" customHeight="1"/>
+    <row r="34" ht="38" customHeight="1"/>
+    <row r="35" ht="114" customHeight="1">
+      <c r="A35" s="81" t="inlineStr">
         <is>
           <t>3. Construcción y áreas netas</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="45" customHeight="1">
-      <c r="A45" s="87" t="inlineStr">
+    <row r="36" ht="38" customHeight="1">
+      <c r="A36" s="86" t="inlineStr">
         <is>
           <t>Tabla 2. Especificación constructiva.</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="45" customHeight="1">
-      <c r="A46" s="82" t="inlineStr">
+    <row r="37" ht="38" customHeight="1">
+      <c r="A37" s="82" t="inlineStr">
         <is>
           <t>Característica</t>
         </is>
       </c>
-      <c r="B46" s="82" t="n"/>
-      <c r="C46" s="82" t="n"/>
-      <c r="D46" s="82" t="n"/>
-      <c r="E46" s="82" t="n"/>
-      <c r="F46" s="82" t="n"/>
-      <c r="G46" s="82" t="n"/>
-      <c r="H46" s="82" t="n"/>
-      <c r="I46" s="82" t="inlineStr">
+      <c r="B37" s="82" t="n"/>
+      <c r="C37" s="82" t="n"/>
+      <c r="D37" s="82" t="n"/>
+      <c r="E37" s="82" t="n"/>
+      <c r="F37" s="82" t="n"/>
+      <c r="G37" s="82" t="n"/>
+      <c r="H37" s="82" t="n"/>
+      <c r="I37" s="82" t="inlineStr">
         <is>
           <t>Especificación</t>
         </is>
       </c>
-      <c r="J46" s="82" t="n"/>
-      <c r="K46" s="82" t="n"/>
-      <c r="L46" s="82" t="n"/>
-      <c r="M46" s="82" t="n"/>
-      <c r="N46" s="82" t="n"/>
-      <c r="O46" s="82" t="n"/>
-    </row>
-    <row r="47" ht="150" customHeight="1">
-      <c r="A47" s="83" t="inlineStr">
+      <c r="J37" s="82" t="n"/>
+      <c r="K37" s="82" t="n"/>
+      <c r="L37" s="82" t="n"/>
+      <c r="M37" s="82" t="n"/>
+      <c r="N37" s="82" t="n"/>
+      <c r="O37" s="82" t="n"/>
+    </row>
+    <row r="38" ht="152" customHeight="1">
+      <c r="A38" s="83" t="inlineStr">
         <is>
           <t>Tipo de núcleo</t>
         </is>
       </c>
-      <c r="B47" s="84" t="n"/>
-      <c r="C47" s="84" t="n"/>
-      <c r="D47" s="84" t="n"/>
-      <c r="E47" s="84" t="n"/>
-      <c r="F47" s="84" t="n"/>
-      <c r="G47" s="84" t="n"/>
-      <c r="H47" s="84" t="n"/>
-      <c r="I47" s="83" t="inlineStr">
+      <c r="B38" s="84" t="n"/>
+      <c r="C38" s="84" t="n"/>
+      <c r="D38" s="84" t="n"/>
+      <c r="E38" s="84" t="n"/>
+      <c r="F38" s="84" t="n"/>
+      <c r="G38" s="84" t="n"/>
+      <c r="H38" s="84" t="n"/>
+      <c r="I38" s="83" t="inlineStr">
         <is>
           <t>Eggcrate (panal) ½×½×½ in (12.7 mm), máxima área libre</t>
         </is>
       </c>
-      <c r="J47" s="84" t="n"/>
-      <c r="K47" s="84" t="n"/>
-      <c r="L47" s="84" t="n"/>
-      <c r="M47" s="84" t="n"/>
-      <c r="N47" s="84" t="n"/>
-      <c r="O47" s="84" t="n"/>
-    </row>
-    <row r="48" ht="450" customHeight="1">
-      <c r="A48" s="83" t="inlineStr">
+      <c r="J38" s="84" t="n"/>
+      <c r="K38" s="84" t="n"/>
+      <c r="L38" s="84" t="n"/>
+      <c r="M38" s="84" t="n"/>
+      <c r="N38" s="84" t="n"/>
+      <c r="O38" s="84" t="n"/>
+    </row>
+    <row r="39" ht="456" customHeight="1">
+      <c r="A39" s="83" t="inlineStr">
         <is>
           <t>Área libre del núcleo</t>
         </is>
       </c>
-      <c r="B48" s="84" t="n"/>
-      <c r="C48" s="84" t="n"/>
-      <c r="D48" s="84" t="n"/>
-      <c r="E48" s="84" t="n"/>
-      <c r="F48" s="84" t="n"/>
-      <c r="G48" s="84" t="n"/>
-      <c r="H48" s="84" t="n"/>
-      <c r="I48" s="83" t="inlineStr">
+      <c r="B39" s="84" t="n"/>
+      <c r="C39" s="84" t="n"/>
+      <c r="D39" s="84" t="n"/>
+      <c r="E39" s="84" t="n"/>
+      <c r="F39" s="84" t="n"/>
+      <c r="G39" s="84" t="n"/>
+      <c r="H39" s="84" t="n"/>
+      <c r="I39" s="83" t="inlineStr">
         <is>
           <t>≥ 90 % (cifra repetida en catálogos del tipo; Airfoil RC-FCR5 (https://airfoil.com.au/product/removable-core-fixing-clip-eggcrate-grille-rc-fcr5/), consulta 2026-07-23)</t>
         </is>
       </c>
-      <c r="J48" s="84" t="n"/>
-      <c r="K48" s="84" t="n"/>
-      <c r="L48" s="84" t="n"/>
-      <c r="M48" s="84" t="n"/>
-      <c r="N48" s="84" t="n"/>
-      <c r="O48" s="84" t="n"/>
-    </row>
-    <row r="49" ht="705" customHeight="1">
-      <c r="A49" s="83" t="inlineStr">
+      <c r="J39" s="84" t="n"/>
+      <c r="K39" s="84" t="n"/>
+      <c r="L39" s="84" t="n"/>
+      <c r="M39" s="84" t="n"/>
+      <c r="N39" s="84" t="n"/>
+      <c r="O39" s="84" t="n"/>
+    </row>
+    <row r="40" ht="722" customHeight="1">
+      <c r="A40" s="83" t="inlineStr">
         <is>
           <t>Malla anti-insectos</t>
         </is>
       </c>
-      <c r="B49" s="84" t="n"/>
-      <c r="C49" s="84" t="n"/>
-      <c r="D49" s="84" t="n"/>
-      <c r="E49" s="84" t="n"/>
-      <c r="F49" s="84" t="n"/>
-      <c r="G49" s="84" t="n"/>
-      <c r="H49" s="84" t="n"/>
-      <c r="I49" s="83" t="inlineStr">
+      <c r="B40" s="84" t="n"/>
+      <c r="C40" s="84" t="n"/>
+      <c r="D40" s="84" t="n"/>
+      <c r="E40" s="84" t="n"/>
+      <c r="F40" s="84" t="n"/>
+      <c r="G40" s="84" t="n"/>
+      <c r="H40" s="84" t="n"/>
+      <c r="I40" s="83" t="inlineStr">
         <is>
           <t>Tejido 18×18, abertura ≈1 mm, alambre 0.45 mm, área abierta ≥ 48 % (tabla Industrial Metal Mesh (https://www.industrialmetalmesh.com/sale-54819921-micron-304-316l-stainless-steel-wire-mesh-screen-filter-mesh.html), consulta 2026-07-23); excluye insectos comunes</t>
         </is>
       </c>
-      <c r="J49" s="84" t="n"/>
-      <c r="K49" s="84" t="n"/>
-      <c r="L49" s="84" t="n"/>
-      <c r="M49" s="84" t="n"/>
-      <c r="N49" s="84" t="n"/>
-      <c r="O49" s="84" t="n"/>
-    </row>
-    <row r="50" ht="135" customHeight="1">
-      <c r="A50" s="83" t="inlineStr">
+      <c r="J40" s="84" t="n"/>
+      <c r="K40" s="84" t="n"/>
+      <c r="L40" s="84" t="n"/>
+      <c r="M40" s="84" t="n"/>
+      <c r="N40" s="84" t="n"/>
+      <c r="O40" s="84" t="n"/>
+    </row>
+    <row r="41" ht="152" customHeight="1">
+      <c r="A41" s="83" t="inlineStr">
         <is>
           <t>Área neta combinada (núcleo + malla)</t>
         </is>
       </c>
-      <c r="B50" s="84" t="n"/>
-      <c r="C50" s="84" t="n"/>
-      <c r="D50" s="84" t="n"/>
-      <c r="E50" s="84" t="n"/>
-      <c r="F50" s="84" t="n"/>
-      <c r="G50" s="84" t="n"/>
-      <c r="H50" s="84" t="n"/>
-      <c r="I50" s="83" t="inlineStr">
+      <c r="B41" s="84" t="n"/>
+      <c r="C41" s="84" t="n"/>
+      <c r="D41" s="84" t="n"/>
+      <c r="E41" s="84" t="n"/>
+      <c r="F41" s="84" t="n"/>
+      <c r="G41" s="84" t="n"/>
+      <c r="H41" s="84" t="n"/>
+      <c r="I41" s="83" t="inlineStr">
         <is>
           <t>≈ 45 % del área facial (dato típico: 0.90 × 0.50)</t>
         </is>
       </c>
-      <c r="J50" s="84" t="n"/>
-      <c r="K50" s="84" t="n"/>
-      <c r="L50" s="84" t="n"/>
-      <c r="M50" s="84" t="n"/>
-      <c r="N50" s="84" t="n"/>
-      <c r="O50" s="84" t="n"/>
-    </row>
-    <row r="51" ht="195" customHeight="1">
-      <c r="A51" s="83" t="inlineStr">
+      <c r="J41" s="84" t="n"/>
+      <c r="K41" s="84" t="n"/>
+      <c r="L41" s="84" t="n"/>
+      <c r="M41" s="84" t="n"/>
+      <c r="N41" s="84" t="n"/>
+      <c r="O41" s="84" t="n"/>
+    </row>
+    <row r="42" ht="190" customHeight="1">
+      <c r="A42" s="83" t="inlineStr">
         <is>
           <t>Material de la rejilla</t>
         </is>
       </c>
-      <c r="B51" s="84" t="n"/>
-      <c r="C51" s="84" t="n"/>
-      <c r="D51" s="84" t="n"/>
-      <c r="E51" s="84" t="n"/>
-      <c r="F51" s="84" t="n"/>
-      <c r="G51" s="84" t="n"/>
-      <c r="H51" s="84" t="n"/>
-      <c r="I51" s="83" t="inlineStr">
+      <c r="B42" s="84" t="n"/>
+      <c r="C42" s="84" t="n"/>
+      <c r="D42" s="84" t="n"/>
+      <c r="E42" s="84" t="n"/>
+      <c r="F42" s="84" t="n"/>
+      <c r="G42" s="84" t="n"/>
+      <c r="H42" s="84" t="n"/>
+      <c r="I42" s="83" t="inlineStr">
         <is>
           <t>Inox 316L (primera opción) o aluminio anodizado 6063-T5 (alternativa)</t>
         </is>
       </c>
-      <c r="J51" s="84" t="n"/>
-      <c r="K51" s="84" t="n"/>
-      <c r="L51" s="84" t="n"/>
-      <c r="M51" s="84" t="n"/>
-      <c r="N51" s="84" t="n"/>
-      <c r="O51" s="84" t="n"/>
-    </row>
-    <row r="52" ht="60" customHeight="1">
-      <c r="A52" s="83" t="inlineStr">
+      <c r="J42" s="84" t="n"/>
+      <c r="K42" s="84" t="n"/>
+      <c r="L42" s="84" t="n"/>
+      <c r="M42" s="84" t="n"/>
+      <c r="N42" s="84" t="n"/>
+      <c r="O42" s="84" t="n"/>
+    </row>
+    <row r="43" ht="76" customHeight="1">
+      <c r="A43" s="83" t="inlineStr">
         <is>
           <t>Material de la malla</t>
         </is>
       </c>
-      <c r="B52" s="84" t="n"/>
-      <c r="C52" s="84" t="n"/>
-      <c r="D52" s="84" t="n"/>
-      <c r="E52" s="84" t="n"/>
-      <c r="F52" s="84" t="n"/>
-      <c r="G52" s="84" t="n"/>
-      <c r="H52" s="84" t="n"/>
-      <c r="I52" s="83" t="inlineStr">
+      <c r="B43" s="84" t="n"/>
+      <c r="C43" s="84" t="n"/>
+      <c r="D43" s="84" t="n"/>
+      <c r="E43" s="84" t="n"/>
+      <c r="F43" s="84" t="n"/>
+      <c r="G43" s="84" t="n"/>
+      <c r="H43" s="84" t="n"/>
+      <c r="I43" s="83" t="inlineStr">
         <is>
           <t>Inox 316</t>
         </is>
       </c>
-      <c r="J52" s="84" t="n"/>
-      <c r="K52" s="84" t="n"/>
-      <c r="L52" s="84" t="n"/>
-      <c r="M52" s="84" t="n"/>
-      <c r="N52" s="84" t="n"/>
-      <c r="O52" s="84" t="n"/>
-    </row>
-    <row r="53" ht="120" customHeight="1">
+      <c r="J43" s="84" t="n"/>
+      <c r="K43" s="84" t="n"/>
+      <c r="L43" s="84" t="n"/>
+      <c r="M43" s="84" t="n"/>
+      <c r="N43" s="84" t="n"/>
+      <c r="O43" s="84" t="n"/>
+    </row>
+    <row r="44" ht="114" customHeight="1">
+      <c r="A44" s="83" t="inlineStr">
+        <is>
+          <t>Montaje de la malla</t>
+        </is>
+      </c>
+      <c r="B44" s="84" t="n"/>
+      <c r="C44" s="84" t="n"/>
+      <c r="D44" s="84" t="n"/>
+      <c r="E44" s="84" t="n"/>
+      <c r="F44" s="84" t="n"/>
+      <c r="G44" s="84" t="n"/>
+      <c r="H44" s="84" t="n"/>
+      <c r="I44" s="83" t="inlineStr">
+        <is>
+          <t>Marco desmontable para limpieza periódica</t>
+        </is>
+      </c>
+      <c r="J44" s="84" t="n"/>
+      <c r="K44" s="84" t="n"/>
+      <c r="L44" s="84" t="n"/>
+      <c r="M44" s="84" t="n"/>
+      <c r="N44" s="84" t="n"/>
+      <c r="O44" s="84" t="n"/>
+    </row>
+    <row r="45" ht="266" customHeight="1">
+      <c r="A45" s="83" t="inlineStr">
+        <is>
+          <t>Par galvánico</t>
+        </is>
+      </c>
+      <c r="B45" s="84" t="n"/>
+      <c r="C45" s="84" t="n"/>
+      <c r="D45" s="84" t="n"/>
+      <c r="E45" s="84" t="n"/>
+      <c r="F45" s="84" t="n"/>
+      <c r="G45" s="84" t="n"/>
+      <c r="H45" s="84" t="n"/>
+      <c r="I45" s="83" t="inlineStr">
+        <is>
+          <t>Si se combina marco de aluminio con malla inox, aislamiento dieléctrico (dato típico de ingeniería)</t>
+        </is>
+      </c>
+      <c r="J45" s="84" t="n"/>
+      <c r="K45" s="84" t="n"/>
+      <c r="L45" s="84" t="n"/>
+      <c r="M45" s="84" t="n"/>
+      <c r="N45" s="84" t="n"/>
+      <c r="O45" s="84" t="n"/>
+    </row>
+    <row r="46" ht="114" customHeight="1">
+      <c r="A46" s="83" t="inlineStr">
+        <is>
+          <t>Ensayo de desempeño</t>
+        </is>
+      </c>
+      <c r="B46" s="84" t="n"/>
+      <c r="C46" s="84" t="n"/>
+      <c r="D46" s="84" t="n"/>
+      <c r="E46" s="84" t="n"/>
+      <c r="F46" s="84" t="n"/>
+      <c r="G46" s="84" t="n"/>
+      <c r="H46" s="84" t="n"/>
+      <c r="I46" s="83" t="inlineStr">
+        <is>
+          <t>ASHRAE 70 (medición de rejillas)</t>
+        </is>
+      </c>
+      <c r="J46" s="84" t="n"/>
+      <c r="K46" s="84" t="n"/>
+      <c r="L46" s="84" t="n"/>
+      <c r="M46" s="84" t="n"/>
+      <c r="N46" s="84" t="n"/>
+      <c r="O46" s="84" t="n"/>
+    </row>
+    <row r="47" ht="38" customHeight="1"/>
+    <row r="48" ht="190" customHeight="1">
+      <c r="A48" s="85" t="inlineStr">
+        <is>
+          <t>3.1. La malla domina la pérdida del conjunto; el dimensionamiento por área neta combinada y la ΔP calculada por cierre de orificio (11 Pa) deben verificarse contra el área efectiva (Ak) del fabricante seleccionado (por confirmar con proveedor).</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="38" customHeight="1"/>
+    <row r="50" ht="76" customHeight="1">
+      <c r="A50" s="81" t="inlineStr">
+        <is>
+          <t>4. Candidatos comerciales</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="38" customHeight="1">
+      <c r="A51" s="86" t="inlineStr">
+        <is>
+          <t>Tabla 3. Candidatos (consulta 2026-07-23).</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="76" customHeight="1">
+      <c r="A52" s="82" t="inlineStr">
+        <is>
+          <t>Producto</t>
+        </is>
+      </c>
+      <c r="B52" s="82" t="n"/>
+      <c r="C52" s="82" t="n"/>
+      <c r="D52" s="82" t="inlineStr">
+        <is>
+          <t>Tipo / material</t>
+        </is>
+      </c>
+      <c r="E52" s="82" t="n"/>
+      <c r="F52" s="82" t="n"/>
+      <c r="G52" s="82" t="inlineStr">
+        <is>
+          <t>Pros</t>
+        </is>
+      </c>
+      <c r="H52" s="82" t="n"/>
+      <c r="I52" s="82" t="n"/>
+      <c r="J52" s="82" t="inlineStr">
+        <is>
+          <t>Contras</t>
+        </is>
+      </c>
+      <c r="K52" s="82" t="n"/>
+      <c r="L52" s="82" t="n"/>
+      <c r="M52" s="82" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="N52" s="82" t="n"/>
+      <c r="O52" s="82" t="n"/>
+    </row>
+    <row r="53" ht="266" customHeight="1">
       <c r="A53" s="83" t="inlineStr">
         <is>
-          <t>Montaje de la malla</t>
+          <t>Titus 50F / 50R</t>
         </is>
       </c>
       <c r="B53" s="84" t="n"/>
       <c r="C53" s="84" t="n"/>
-      <c r="D53" s="84" t="n"/>
+      <c r="D53" s="83" t="inlineStr">
+        <is>
+          <t>Eggcrate ½ in; aluminio, con versión íntegramente inox de fábrica</t>
+        </is>
+      </c>
       <c r="E53" s="84" t="n"/>
       <c r="F53" s="84" t="n"/>
-      <c r="G53" s="84" t="n"/>
+      <c r="G53" s="83" t="inlineStr">
+        <is>
+          <t>«Highest free area of any return grille»; única opción inox de catálogo</t>
+        </is>
+      </c>
       <c r="H53" s="84" t="n"/>
-      <c r="I53" s="83" t="inlineStr">
-        <is>
-          <t>Marco desmontable para limpieza periódica</t>
-        </is>
-      </c>
-      <c r="J53" s="84" t="n"/>
+      <c r="I53" s="84" t="n"/>
+      <c r="J53" s="83" t="inlineStr">
+        <is>
+          <t>Importación; tamaño 353×336 por pedido</t>
+        </is>
+      </c>
       <c r="K53" s="84" t="n"/>
       <c r="L53" s="84" t="n"/>
-      <c r="M53" s="84" t="n"/>
+      <c r="M53" s="83" t="inlineStr">
+        <is>
+          <t>Titus 50F (PDF) (https://www.titus-hvac.com/file/1228/50F_50Rrprod_specialized_2017.pdf)</t>
+        </is>
+      </c>
       <c r="N53" s="84" t="n"/>
       <c r="O53" s="84" t="n"/>
     </row>
-    <row r="54" ht="270" customHeight="1">
+    <row r="54" ht="266" customHeight="1">
       <c r="A54" s="83" t="inlineStr">
         <is>
-          <t>Par galvánico</t>
+          <t>Krueger EGC5</t>
         </is>
       </c>
       <c r="B54" s="84" t="n"/>
       <c r="C54" s="84" t="n"/>
-      <c r="D54" s="84" t="n"/>
+      <c r="D54" s="83" t="inlineStr">
+        <is>
+          <t>Eggcrate ½ in; aluminio</t>
+        </is>
+      </c>
       <c r="E54" s="84" t="n"/>
       <c r="F54" s="84" t="n"/>
-      <c r="G54" s="84" t="n"/>
+      <c r="G54" s="83" t="inlineStr">
+        <is>
+          <t>Amplia gama de tamaños (6×4 in a 96×96 in)</t>
+        </is>
+      </c>
       <c r="H54" s="84" t="n"/>
-      <c r="I54" s="83" t="inlineStr">
-        <is>
-          <t>Si se combina marco de aluminio con malla inox, aislamiento dieléctrico (dato típico de ingeniería)</t>
-        </is>
-      </c>
-      <c r="J54" s="84" t="n"/>
+      <c r="I54" s="84" t="n"/>
+      <c r="J54" s="83" t="inlineStr">
+        <is>
+          <t>Sin ejecución inox</t>
+        </is>
+      </c>
       <c r="K54" s="84" t="n"/>
       <c r="L54" s="84" t="n"/>
-      <c r="M54" s="84" t="n"/>
+      <c r="M54" s="83" t="inlineStr">
+        <is>
+          <t>Krueger EGC5 (https://www.krueger-hvac.com/Catalog%20Home/Grilles/Grilles%20-%20Return/EGC5)</t>
+        </is>
+      </c>
       <c r="N54" s="84" t="n"/>
       <c r="O54" s="84" t="n"/>
     </row>
-    <row r="55" ht="90" customHeight="1">
+    <row r="55" ht="266" customHeight="1">
       <c r="A55" s="83" t="inlineStr">
         <is>
-          <t>Ensayo de desempeño</t>
+          <t>ProAire S.A.S (Bogotá)</t>
         </is>
       </c>
       <c r="B55" s="84" t="n"/>
       <c r="C55" s="84" t="n"/>
-      <c r="D55" s="84" t="n"/>
+      <c r="D55" s="83" t="inlineStr">
+        <is>
+          <t>Fabricación a medida con corte láser, inox 316</t>
+        </is>
+      </c>
       <c r="E55" s="84" t="n"/>
       <c r="F55" s="84" t="n"/>
-      <c r="G55" s="84" t="n"/>
+      <c r="G55" s="83" t="inlineStr">
+        <is>
+          <t>Medida exacta 353×336 y ejecución inox 316L local; vía recomendada</t>
+        </is>
+      </c>
       <c r="H55" s="84" t="n"/>
-      <c r="I55" s="83" t="inlineStr">
-        <is>
-          <t>ASHRAE 70 (medición de rejillas)</t>
-        </is>
-      </c>
-      <c r="J55" s="84" t="n"/>
+      <c r="I55" s="84" t="n"/>
+      <c r="J55" s="83" t="inlineStr">
+        <is>
+          <t>Submittal y Ak por confirmar con proveedor</t>
+        </is>
+      </c>
       <c r="K55" s="84" t="n"/>
       <c r="L55" s="84" t="n"/>
-      <c r="M55" s="84" t="n"/>
+      <c r="M55" s="83" t="inlineStr">
+        <is>
+          <t>proairecolombia.com (https://www.proairecolombia.com/productos/rejillas-y-difusores.html)</t>
+        </is>
+      </c>
       <c r="N55" s="84" t="n"/>
       <c r="O55" s="84" t="n"/>
     </row>
-    <row r="56" ht="15" customHeight="1"/>
-    <row r="57" ht="165" customHeight="1">
-      <c r="A57" s="86" t="inlineStr">
-        <is>
-          <t>3.1. La malla domina la pérdida del conjunto; el dimensionamiento por área neta combinada y la ΔP calculada por cierre de orificio (11 Pa) deben verificarse contra el área efectiva (Ak) del fabricante seleccionado (por confirmar con proveedor).</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="15" customHeight="1"/>
-    <row r="59" ht="15" customHeight="1"/>
-    <row r="60" ht="15" customHeight="1"/>
-    <row r="61" ht="15" customHeight="1"/>
-    <row r="62" ht="75" customHeight="1">
+    <row r="56" ht="190" customHeight="1">
+      <c r="A56" s="83" t="inlineStr">
+        <is>
+          <t>Laminaire (Colombia)</t>
+        </is>
+      </c>
+      <c r="B56" s="84" t="n"/>
+      <c r="C56" s="84" t="n"/>
+      <c r="D56" s="83" t="inlineStr">
+        <is>
+          <t>Rejillas y difusores en aluminio a pedido</t>
+        </is>
+      </c>
+      <c r="E56" s="84" t="n"/>
+      <c r="F56" s="84" t="n"/>
+      <c r="G56" s="83" t="inlineStr">
+        <is>
+          <t>Fabricación local con software de selección; marco para malla a pedido</t>
+        </is>
+      </c>
+      <c r="H56" s="84" t="n"/>
+      <c r="I56" s="84" t="n"/>
+      <c r="J56" s="83" t="inlineStr">
+        <is>
+          <t>Confirmar ejecución inox</t>
+        </is>
+      </c>
+      <c r="K56" s="84" t="n"/>
+      <c r="L56" s="84" t="n"/>
+      <c r="M56" s="83" t="inlineStr">
+        <is>
+          <t>laminaire.net (https://laminaire.net/)</t>
+        </is>
+      </c>
+      <c r="N56" s="84" t="n"/>
+      <c r="O56" s="84" t="n"/>
+    </row>
+    <row r="57" ht="114" customHeight="1">
+      <c r="A57" s="83" t="inlineStr">
+        <is>
+          <t>CL Ingeniería (Bogotá)</t>
+        </is>
+      </c>
+      <c r="B57" s="84" t="n"/>
+      <c r="C57" s="84" t="n"/>
+      <c r="D57" s="83" t="inlineStr">
+        <is>
+          <t>Rejillas y accesorios HVAC</t>
+        </is>
+      </c>
+      <c r="E57" s="84" t="n"/>
+      <c r="F57" s="84" t="n"/>
+      <c r="G57" s="83" t="inlineStr">
+        <is>
+          <t>Canal local adicional</t>
+        </is>
+      </c>
+      <c r="H57" s="84" t="n"/>
+      <c r="I57" s="84" t="n"/>
+      <c r="J57" s="83" t="inlineStr">
+        <is>
+          <t>Catálogo genérico</t>
+        </is>
+      </c>
+      <c r="K57" s="84" t="n"/>
+      <c r="L57" s="84" t="n"/>
+      <c r="M57" s="83" t="inlineStr">
+        <is>
+          <t>clingenieria.co (https://clingenieria.co/)</t>
+        </is>
+      </c>
+      <c r="N57" s="84" t="n"/>
+      <c r="O57" s="84" t="n"/>
+    </row>
+    <row r="58" ht="38" customHeight="1"/>
+    <row r="59" ht="38" customHeight="1">
+      <c r="A59" s="81" t="inlineStr">
+        <is>
+          <t>5. Instalación</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="456" customHeight="1">
+      <c r="A60" s="85" t="inlineStr">
+        <is>
+          <t>5.1. Montaje a ras de muro exterior con marco perimetral sellado con silicona RTV neutra (compatible con hipoclorito; Chemical Resistance of RTV Silicone Sealants (PDF) (https://irp.cdn-website.com/63168859/files/uploaded/Chemical%20Resistance%20of%20RTV%20Silicone%20Sealants%20Chart.pdf), consulta 2026-07-23) y ferretería inox 316 (A4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="38" customHeight="1"/>
+    <row r="62" ht="114" customHeight="1">
       <c r="A62" s="85" t="inlineStr">
         <is>
-          <t>4. Candidatos comerciales</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="60" customHeight="1">
-      <c r="A63" s="87" t="inlineStr">
-        <is>
-          <t>Tabla 3. Candidatos (consulta 2026-07-23).</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="45" customHeight="1">
-      <c r="A64" s="82" t="inlineStr">
-        <is>
-          <t>Producto</t>
-        </is>
-      </c>
-      <c r="B64" s="82" t="n"/>
-      <c r="C64" s="82" t="n"/>
-      <c r="D64" s="82" t="inlineStr">
-        <is>
-          <t>Tipo / material</t>
-        </is>
-      </c>
-      <c r="E64" s="82" t="n"/>
-      <c r="F64" s="82" t="n"/>
-      <c r="G64" s="82" t="inlineStr">
-        <is>
-          <t>Pros</t>
-        </is>
-      </c>
-      <c r="H64" s="82" t="n"/>
-      <c r="I64" s="82" t="n"/>
-      <c r="J64" s="82" t="inlineStr">
-        <is>
-          <t>Contras</t>
-        </is>
-      </c>
-      <c r="K64" s="82" t="n"/>
-      <c r="L64" s="82" t="n"/>
-      <c r="M64" s="82" t="inlineStr">
-        <is>
-          <t>Fuente</t>
-        </is>
-      </c>
-      <c r="N64" s="82" t="n"/>
-      <c r="O64" s="82" t="n"/>
-    </row>
-    <row r="65" ht="240" customHeight="1">
-      <c r="A65" s="83" t="inlineStr">
-        <is>
-          <t>Titus 50F / 50R</t>
-        </is>
-      </c>
-      <c r="B65" s="84" t="n"/>
-      <c r="C65" s="84" t="n"/>
-      <c r="D65" s="83" t="inlineStr">
-        <is>
-          <t>Eggcrate ½ in; aluminio, con versión íntegramente inox de fábrica</t>
-        </is>
-      </c>
-      <c r="E65" s="84" t="n"/>
-      <c r="F65" s="84" t="n"/>
-      <c r="G65" s="83" t="inlineStr">
-        <is>
-          <t>«Highest free area of any return grille»; única opción inox de catálogo</t>
-        </is>
-      </c>
-      <c r="H65" s="84" t="n"/>
-      <c r="I65" s="84" t="n"/>
-      <c r="J65" s="83" t="inlineStr">
-        <is>
-          <t>Importación; tamaño 353×336 por pedido</t>
-        </is>
-      </c>
-      <c r="K65" s="84" t="n"/>
-      <c r="L65" s="84" t="n"/>
-      <c r="M65" s="83" t="inlineStr">
-        <is>
-          <t>Titus 50F (PDF) (https://www.titus-hvac.com/file/1228/50F_50Rrprod_specialized_2017.pdf)</t>
-        </is>
-      </c>
-      <c r="N65" s="84" t="n"/>
-      <c r="O65" s="84" t="n"/>
-    </row>
-    <row r="66" ht="255" customHeight="1">
-      <c r="A66" s="83" t="inlineStr">
-        <is>
-          <t>Krueger EGC5</t>
-        </is>
-      </c>
-      <c r="B66" s="84" t="n"/>
-      <c r="C66" s="84" t="n"/>
-      <c r="D66" s="83" t="inlineStr">
-        <is>
-          <t>Eggcrate ½ in; aluminio</t>
-        </is>
-      </c>
-      <c r="E66" s="84" t="n"/>
-      <c r="F66" s="84" t="n"/>
-      <c r="G66" s="83" t="inlineStr">
-        <is>
-          <t>Amplia gama de tamaños (6×4 in a 96×96 in)</t>
-        </is>
-      </c>
-      <c r="H66" s="84" t="n"/>
-      <c r="I66" s="84" t="n"/>
-      <c r="J66" s="83" t="inlineStr">
-        <is>
-          <t>Sin ejecución inox</t>
-        </is>
-      </c>
-      <c r="K66" s="84" t="n"/>
-      <c r="L66" s="84" t="n"/>
-      <c r="M66" s="83" t="inlineStr">
-        <is>
-          <t>Krueger EGC5 (https://www.krueger-hvac.com/Catalog%20Home/Grilles/Grilles%20-%20Return/EGC5)</t>
-        </is>
-      </c>
-      <c r="N66" s="84" t="n"/>
-      <c r="O66" s="84" t="n"/>
-    </row>
-    <row r="67" ht="240" customHeight="1">
-      <c r="A67" s="83" t="inlineStr">
-        <is>
-          <t>ProAire S.A.S (Bogotá)</t>
-        </is>
-      </c>
-      <c r="B67" s="84" t="n"/>
-      <c r="C67" s="84" t="n"/>
-      <c r="D67" s="83" t="inlineStr">
-        <is>
-          <t>Fabricación a medida con corte láser, inox 316</t>
-        </is>
-      </c>
-      <c r="E67" s="84" t="n"/>
-      <c r="F67" s="84" t="n"/>
-      <c r="G67" s="83" t="inlineStr">
-        <is>
-          <t>Medida exacta 353×336 y ejecución inox 316L local; vía recomendada</t>
-        </is>
-      </c>
-      <c r="H67" s="84" t="n"/>
-      <c r="I67" s="84" t="n"/>
-      <c r="J67" s="83" t="inlineStr">
-        <is>
-          <t>Submittal y Ak por confirmar con proveedor</t>
-        </is>
-      </c>
-      <c r="K67" s="84" t="n"/>
-      <c r="L67" s="84" t="n"/>
-      <c r="M67" s="83" t="inlineStr">
-        <is>
-          <t>proairecolombia.com (https://www.proairecolombia.com/productos/rejillas-y-difusores.html)</t>
-        </is>
-      </c>
-      <c r="N67" s="84" t="n"/>
-      <c r="O67" s="84" t="n"/>
-    </row>
-    <row r="68" ht="195" customHeight="1">
-      <c r="A68" s="83" t="inlineStr">
-        <is>
-          <t>Laminaire (Colombia)</t>
-        </is>
-      </c>
-      <c r="B68" s="84" t="n"/>
-      <c r="C68" s="84" t="n"/>
-      <c r="D68" s="83" t="inlineStr">
-        <is>
-          <t>Rejillas y difusores en aluminio a pedido</t>
-        </is>
-      </c>
-      <c r="E68" s="84" t="n"/>
-      <c r="F68" s="84" t="n"/>
-      <c r="G68" s="83" t="inlineStr">
-        <is>
-          <t>Fabricación local con software de selección; marco para malla a pedido</t>
-        </is>
-      </c>
-      <c r="H68" s="84" t="n"/>
-      <c r="I68" s="84" t="n"/>
-      <c r="J68" s="83" t="inlineStr">
-        <is>
-          <t>Confirmar ejecución inox</t>
-        </is>
-      </c>
-      <c r="K68" s="84" t="n"/>
-      <c r="L68" s="84" t="n"/>
-      <c r="M68" s="83" t="inlineStr">
-        <is>
-          <t>laminaire.net (https://laminaire.net/)</t>
-        </is>
-      </c>
-      <c r="N68" s="84" t="n"/>
-      <c r="O68" s="84" t="n"/>
-    </row>
-    <row r="69" ht="120" customHeight="1">
-      <c r="A69" s="83" t="inlineStr">
-        <is>
-          <t>CL Ingeniería (Bogotá)</t>
-        </is>
-      </c>
-      <c r="B69" s="84" t="n"/>
-      <c r="C69" s="84" t="n"/>
-      <c r="D69" s="83" t="inlineStr">
-        <is>
-          <t>Rejillas y accesorios HVAC</t>
-        </is>
-      </c>
-      <c r="E69" s="84" t="n"/>
-      <c r="F69" s="84" t="n"/>
-      <c r="G69" s="83" t="inlineStr">
-        <is>
-          <t>Canal local adicional</t>
-        </is>
-      </c>
-      <c r="H69" s="84" t="n"/>
-      <c r="I69" s="84" t="n"/>
-      <c r="J69" s="83" t="inlineStr">
-        <is>
-          <t>Catálogo genérico</t>
-        </is>
-      </c>
-      <c r="K69" s="84" t="n"/>
-      <c r="L69" s="84" t="n"/>
-      <c r="M69" s="83" t="inlineStr">
-        <is>
-          <t>clingenieria.co (https://clingenieria.co/)</t>
-        </is>
-      </c>
-      <c r="N69" s="84" t="n"/>
-      <c r="O69" s="84" t="n"/>
-    </row>
-    <row r="70" ht="15" customHeight="1"/>
-    <row r="71" ht="15" customHeight="1"/>
-    <row r="72" ht="45" customHeight="1">
-      <c r="A72" s="85" t="inlineStr">
-        <is>
-          <t>5. Instalación</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="150" customHeight="1">
-      <c r="A73" s="86" t="inlineStr">
-        <is>
-          <t>5.1. Montaje a ras de muro exterior con marco perimetral sellado con silicona RTV neutra (compatible con hipoclorito; Chemical Resistance of RTV Silicone Sealants (PDF) (https://irp.cdn-website.com/63168859/files/uploaded/Chemical%20Resistance%20of%20RTV%20Silicone%20Sealants%20Chart.pdf), consulta 2026-07-23) y ferretería inox 316 (A4).</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="15" customHeight="1"/>
-    <row r="75" ht="15" customHeight="1"/>
-    <row r="76" ht="15" customHeight="1"/>
-    <row r="77" ht="15" customHeight="1"/>
-    <row r="78" ht="15" customHeight="1"/>
-    <row r="79" ht="150" customHeight="1">
-      <c r="A79" s="86" t="inlineStr">
-        <is>
           <t>5.2. Las bocas exteriores se orientan preferentemente a sotavento respecto de las fuentes de cloro de la planta.</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="15" customHeight="1"/>
-    <row r="81" ht="165" customHeight="1">
-      <c r="A81" s="86" t="inlineStr">
+    <row r="63" ht="114" customHeight="1">
+      <c r="A63" s="85" t="inlineStr">
         <is>
           <t>5.3. Programa de limpieza de la malla según carga de polvo observada en comisionamiento (dato típico de operación).</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="15" customHeight="1"/>
-    <row r="83" ht="15" customHeight="1"/>
-    <row r="84" ht="60" customHeight="1">
-      <c r="A84" s="85" t="inlineStr">
+    <row r="64" ht="38" customHeight="1"/>
+    <row r="65" ht="76" customHeight="1">
+      <c r="A65" s="81" t="inlineStr">
         <is>
           <t>6. Normas aplicables</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="165" customHeight="1">
-      <c r="A85" s="86" t="inlineStr">
+    <row r="66" ht="494" customHeight="1">
+      <c r="A66" s="85" t="inlineStr">
         <is>
           <t>6.1. ASHRAE 70 (método de ensayo y reporte de desempeño de rejillas); correlación de área libre para transferencia de aire según Building Science BA-0006 (https://buildingscience.com/sites/default/files/migrate/pdf/BA-0006_Discuss_transfer_grilles.pdf) (consulta 2026-07-23); ISO 12944 / NACE-AMPP para la selección de materiales en el ambiente clorado.</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="15" customHeight="1"/>
-    <row r="87" ht="15" customHeight="1"/>
-    <row r="88" ht="15" customHeight="1"/>
-    <row r="89" ht="15" customHeight="1"/>
-    <row r="90" ht="15" customHeight="1"/>
+    <row r="67" ht="38" customHeight="1"/>
   </sheetData>
-  <mergeCells count="104">
-    <mergeCell ref="I52:O52"/>
-    <mergeCell ref="A85:O90"/>
-    <mergeCell ref="D66:F66"/>
-    <mergeCell ref="A49:H49"/>
+  <mergeCells count="100">
+    <mergeCell ref="I44:O44"/>
+    <mergeCell ref="D53:F53"/>
+    <mergeCell ref="A50:O50"/>
+    <mergeCell ref="A57:C57"/>
     <mergeCell ref="N3:O3"/>
-    <mergeCell ref="A19:O24"/>
-    <mergeCell ref="G65:I65"/>
-    <mergeCell ref="J66:L66"/>
+    <mergeCell ref="A25:H25"/>
     <mergeCell ref="I30:O30"/>
-    <mergeCell ref="A79:O80"/>
     <mergeCell ref="N5:O5"/>
     <mergeCell ref="I46:O46"/>
     <mergeCell ref="C2:L3"/>
-    <mergeCell ref="A50:H50"/>
-    <mergeCell ref="A55:H55"/>
-    <mergeCell ref="M66:O66"/>
-    <mergeCell ref="A44:O44"/>
-    <mergeCell ref="I54:O54"/>
-    <mergeCell ref="A32:H32"/>
-    <mergeCell ref="I32:O32"/>
-    <mergeCell ref="M68:O68"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="J52:L52"/>
+    <mergeCell ref="M53:O53"/>
+    <mergeCell ref="G52:I52"/>
+    <mergeCell ref="I41:O41"/>
+    <mergeCell ref="M55:O55"/>
     <mergeCell ref="A29:H29"/>
-    <mergeCell ref="M67:O67"/>
+    <mergeCell ref="A38:H38"/>
+    <mergeCell ref="M52:O52"/>
+    <mergeCell ref="I43:O43"/>
     <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A69:C69"/>
-    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A44:H44"/>
+    <mergeCell ref="I24:O24"/>
     <mergeCell ref="B1:B5"/>
-    <mergeCell ref="I33:O33"/>
-    <mergeCell ref="M69:O69"/>
-    <mergeCell ref="A66:C66"/>
+    <mergeCell ref="D57:F57"/>
+    <mergeCell ref="A40:H40"/>
     <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A51:H51"/>
-    <mergeCell ref="J65:L65"/>
-    <mergeCell ref="A57:O60"/>
-    <mergeCell ref="G69:I69"/>
-    <mergeCell ref="I35:O35"/>
-    <mergeCell ref="A84:O84"/>
+    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="A55:C55"/>
     <mergeCell ref="I10:O10"/>
-    <mergeCell ref="A18:O18"/>
-    <mergeCell ref="I50:O50"/>
     <mergeCell ref="N2:O2"/>
-    <mergeCell ref="G64:I64"/>
-    <mergeCell ref="D68:F68"/>
-    <mergeCell ref="A62:O62"/>
+    <mergeCell ref="G55:I55"/>
+    <mergeCell ref="M57:O57"/>
+    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="D55:F55"/>
     <mergeCell ref="I11:O11"/>
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="A72:O72"/>
-    <mergeCell ref="A67:C67"/>
-    <mergeCell ref="A47:H47"/>
-    <mergeCell ref="I47:O47"/>
-    <mergeCell ref="D69:F69"/>
-    <mergeCell ref="J67:L67"/>
+    <mergeCell ref="I45:O45"/>
+    <mergeCell ref="G54:I54"/>
+    <mergeCell ref="D54:F54"/>
+    <mergeCell ref="A42:H42"/>
+    <mergeCell ref="M56:O56"/>
+    <mergeCell ref="G56:I56"/>
+    <mergeCell ref="I28:O28"/>
+    <mergeCell ref="A59:O59"/>
+    <mergeCell ref="I37:O37"/>
     <mergeCell ref="N6:O6"/>
-    <mergeCell ref="J69:L69"/>
+    <mergeCell ref="A28:H28"/>
     <mergeCell ref="N4:O4"/>
-    <mergeCell ref="A48:H48"/>
+    <mergeCell ref="J53:L53"/>
+    <mergeCell ref="I23:O23"/>
     <mergeCell ref="A30:H30"/>
-    <mergeCell ref="G66:I66"/>
-    <mergeCell ref="I51:O51"/>
-    <mergeCell ref="G68:I68"/>
-    <mergeCell ref="A54:H54"/>
-    <mergeCell ref="I34:O34"/>
-    <mergeCell ref="I49:O49"/>
-    <mergeCell ref="A73:O78"/>
-    <mergeCell ref="I36:O36"/>
-    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="G53:I53"/>
+    <mergeCell ref="J55:L55"/>
+    <mergeCell ref="J54:L54"/>
+    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="J56:L56"/>
+    <mergeCell ref="A17:O17"/>
+    <mergeCell ref="A60:O61"/>
+    <mergeCell ref="I27:O27"/>
+    <mergeCell ref="A35:O35"/>
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A66:O67"/>
     <mergeCell ref="A1:A5"/>
     <mergeCell ref="A9:O9"/>
     <mergeCell ref="C1:L1"/>
-    <mergeCell ref="A64:C64"/>
-    <mergeCell ref="A53:H53"/>
-    <mergeCell ref="I53:O53"/>
-    <mergeCell ref="A35:H35"/>
+    <mergeCell ref="J57:L57"/>
+    <mergeCell ref="A18:O19"/>
     <mergeCell ref="A10:H10"/>
     <mergeCell ref="I12:O12"/>
-    <mergeCell ref="I55:O55"/>
-    <mergeCell ref="J68:L68"/>
-    <mergeCell ref="A34:H34"/>
+    <mergeCell ref="A32:O33"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A65:O65"/>
+    <mergeCell ref="A39:H39"/>
     <mergeCell ref="I14:O14"/>
-    <mergeCell ref="A81:O82"/>
-    <mergeCell ref="I48:O48"/>
+    <mergeCell ref="I39:O39"/>
+    <mergeCell ref="M54:O54"/>
+    <mergeCell ref="G57:I57"/>
+    <mergeCell ref="A56:C56"/>
     <mergeCell ref="I29:O29"/>
-    <mergeCell ref="A36:H36"/>
     <mergeCell ref="A11:H11"/>
-    <mergeCell ref="M65:O65"/>
-    <mergeCell ref="M64:O64"/>
+    <mergeCell ref="I38:O38"/>
+    <mergeCell ref="A45:H45"/>
+    <mergeCell ref="A21:O21"/>
     <mergeCell ref="I13:O13"/>
-    <mergeCell ref="A26:O26"/>
-    <mergeCell ref="I31:O31"/>
+    <mergeCell ref="I40:O40"/>
+    <mergeCell ref="D56:F56"/>
     <mergeCell ref="I15:O15"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="A37:H37"/>
     <mergeCell ref="A46:H46"/>
     <mergeCell ref="N1:O1"/>
     <mergeCell ref="A12:H12"/>
-    <mergeCell ref="D64:F64"/>
-    <mergeCell ref="A68:C68"/>
+    <mergeCell ref="I26:O26"/>
     <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A27:O28"/>
-    <mergeCell ref="J64:L64"/>
-    <mergeCell ref="A38:O42"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="I25:O25"/>
     <mergeCell ref="C4:L6"/>
-    <mergeCell ref="G67:I67"/>
-    <mergeCell ref="D65:F65"/>
-    <mergeCell ref="A52:H52"/>
-    <mergeCell ref="A65:C65"/>
+    <mergeCell ref="A43:H43"/>
+    <mergeCell ref="D52:F52"/>
+    <mergeCell ref="I42:O42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/build/dts/P2437-HV-DTS-003 REV0.xlsx
+++ b/build/dts/P2437-HV-DTS-003 REV0.xlsx
@@ -3708,28 +3708,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O67"/>
+  <dimension ref="A1:O63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="49" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="6" max="6"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="35" customWidth="1" min="9" max="9"/>
+    <col width="35" customWidth="1" min="10" max="10"/>
+    <col width="35" customWidth="1" min="11" max="11"/>
+    <col width="35" customWidth="1" min="12" max="12"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="14" max="14"/>
+    <col width="35" customWidth="1" min="15" max="15"/>
     <col width="13" customWidth="1" min="17" max="17"/>
-    <col width="13" customWidth="1" min="18" max="18"/>
-    <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
     <col width="13" customWidth="1" min="23" max="23"/>
     <col width="13" customWidth="1" min="24" max="24"/>
     <col width="13" customWidth="1" min="25" max="25"/>
@@ -3737,10 +3736,9 @@
     <col width="13" customWidth="1" min="27" max="27"/>
     <col width="13" customWidth="1" min="28" max="28"/>
     <col width="13" customWidth="1" min="29" max="29"/>
-    <col width="13" customWidth="1" min="30" max="30"/>
-    <col width="13" customWidth="1" min="32" max="32"/>
     <col width="13" customWidth="1" min="33" max="33"/>
     <col width="13" customWidth="1" min="35" max="35"/>
+    <col width="13" customWidth="1" min="36" max="36"/>
     <col width="13" customWidth="1" min="37" max="37"/>
     <col width="13" customWidth="1" min="38" max="38"/>
     <col width="13" customWidth="1" min="39" max="39"/>
@@ -3749,21 +3747,15 @@
     <col width="13" customWidth="1" min="42" max="42"/>
     <col width="13" customWidth="1" min="43" max="43"/>
     <col width="13" customWidth="1" min="44" max="44"/>
-    <col width="13" customWidth="1" min="45" max="45"/>
-    <col width="13" customWidth="1" min="46" max="46"/>
+    <col width="13" customWidth="1" min="48" max="48"/>
     <col width="13" customWidth="1" min="50" max="50"/>
+    <col width="13" customWidth="1" min="51" max="51"/>
     <col width="13" customWidth="1" min="52" max="52"/>
     <col width="13" customWidth="1" min="53" max="53"/>
     <col width="13" customWidth="1" min="54" max="54"/>
     <col width="13" customWidth="1" min="55" max="55"/>
-    <col width="13" customWidth="1" min="56" max="56"/>
     <col width="13" customWidth="1" min="57" max="57"/>
-    <col width="13" customWidth="1" min="59" max="59"/>
-    <col width="13" customWidth="1" min="60" max="60"/>
-    <col width="13" customWidth="1" min="61" max="61"/>
-    <col width="13" customWidth="1" min="65" max="65"/>
-    <col width="13" customWidth="1" min="66" max="66"/>
-    <col width="13" customWidth="1" min="67" max="67"/>
+    <col width="13" customWidth="1" min="62" max="62"/>
   </cols>
   <sheetData>
     <row r="1" ht="29.25" customHeight="1">
@@ -3973,14 +3965,14 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" ht="228" customHeight="1">
+    <row r="9" ht="100" customHeight="1">
       <c r="A9" s="81" t="inlineStr">
         <is>
           <t>Hoja de datos: rejillas de descarga con malla anti-insectos</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="38" customHeight="1">
+    <row r="10" ht="50" customHeight="1">
       <c r="A10" s="82" t="inlineStr">
         <is>
           <t>Campo</t>
@@ -4005,7 +3997,7 @@
       <c r="N10" s="82" t="n"/>
       <c r="O10" s="82" t="n"/>
     </row>
-    <row r="11" ht="38" customHeight="1">
+    <row r="11" ht="50" customHeight="1">
       <c r="A11" s="83" t="inlineStr">
         <is>
           <t>Código</t>
@@ -4030,7 +4022,7 @@
       <c r="N11" s="84" t="n"/>
       <c r="O11" s="84" t="n"/>
     </row>
-    <row r="12" ht="38" customHeight="1">
+    <row r="12" ht="50" customHeight="1">
       <c r="A12" s="83" t="inlineStr">
         <is>
           <t>Revisión</t>
@@ -4055,7 +4047,7 @@
       <c r="N12" s="84" t="n"/>
       <c r="O12" s="84" t="n"/>
     </row>
-    <row r="13" ht="38" customHeight="1">
+    <row r="13" ht="50" customHeight="1">
       <c r="A13" s="83" t="inlineStr">
         <is>
           <t>Fecha</t>
@@ -4080,7 +4072,7 @@
       <c r="N13" s="84" t="n"/>
       <c r="O13" s="84" t="n"/>
     </row>
-    <row r="14" ht="152" customHeight="1">
+    <row r="14" ht="100" customHeight="1">
       <c r="A14" s="83" t="inlineStr">
         <is>
           <t>Proyecto</t>
@@ -4105,7 +4097,7 @@
       <c r="N14" s="84" t="n"/>
       <c r="O14" s="84" t="n"/>
     </row>
-    <row r="15" ht="114" customHeight="1">
+    <row r="15" ht="100" customHeight="1">
       <c r="A15" s="83" t="inlineStr">
         <is>
           <t>Etiqueta de equipo</t>
@@ -4130,66 +4122,90 @@
       <c r="N15" s="84" t="n"/>
       <c r="O15" s="84" t="n"/>
     </row>
-    <row r="16" ht="38" customHeight="1"/>
-    <row r="17" ht="38" customHeight="1">
+    <row r="16" ht="50" customHeight="1"/>
+    <row r="17" ht="50" customHeight="1">
       <c r="A17" s="81" t="inlineStr">
         <is>
           <t>1. Servicio</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="494" customHeight="1">
+    <row r="18" ht="500" customHeight="1">
       <c r="A18" s="85" t="inlineStr">
         <is>
           <t>1.1. Descarga libre a la atmósfera del caudal de ventilación del laboratorio, a través de la envolvente del recinto. Las rejillas son la trayectoria de salida permanente del aire y, con el sistema detenido, una vía potencial de ingreso: por ello incorporan malla anti-insectos. Ambiente exterior corrosivo (atmósfera clorada de planta de hipoclorito de calcio).</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="38" customHeight="1"/>
-    <row r="20" ht="38" customHeight="1"/>
-    <row r="21" ht="114" customHeight="1">
-      <c r="A21" s="81" t="inlineStr">
+    <row r="19" ht="50" customHeight="1"/>
+    <row r="20" ht="150" customHeight="1">
+      <c r="A20" s="81" t="inlineStr">
         <is>
           <t>2. Condiciones de operación y desempeño</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="76" customHeight="1">
-      <c r="A22" s="86" t="inlineStr">
+    <row r="21" ht="100" customHeight="1">
+      <c r="A21" s="86" t="inlineStr">
         <is>
           <t>Tabla 1. Condiciones de diseño (valores congelados de la memoria de cálculo).</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="38" customHeight="1">
-      <c r="A23" s="82" t="inlineStr">
+    <row r="22" ht="50" customHeight="1">
+      <c r="A22" s="82" t="inlineStr">
         <is>
           <t>Parámetro</t>
         </is>
       </c>
-      <c r="B23" s="82" t="n"/>
-      <c r="C23" s="82" t="n"/>
-      <c r="D23" s="82" t="n"/>
-      <c r="E23" s="82" t="n"/>
-      <c r="F23" s="82" t="n"/>
-      <c r="G23" s="82" t="n"/>
-      <c r="H23" s="82" t="n"/>
-      <c r="I23" s="82" t="inlineStr">
+      <c r="B22" s="82" t="n"/>
+      <c r="C22" s="82" t="n"/>
+      <c r="D22" s="82" t="n"/>
+      <c r="E22" s="82" t="n"/>
+      <c r="F22" s="82" t="n"/>
+      <c r="G22" s="82" t="n"/>
+      <c r="H22" s="82" t="n"/>
+      <c r="I22" s="82" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
       </c>
-      <c r="J23" s="82" t="n"/>
-      <c r="K23" s="82" t="n"/>
-      <c r="L23" s="82" t="n"/>
-      <c r="M23" s="82" t="n"/>
-      <c r="N23" s="82" t="n"/>
-      <c r="O23" s="82" t="n"/>
-    </row>
-    <row r="24" ht="38" customHeight="1">
+      <c r="J22" s="82" t="n"/>
+      <c r="K22" s="82" t="n"/>
+      <c r="L22" s="82" t="n"/>
+      <c r="M22" s="82" t="n"/>
+      <c r="N22" s="82" t="n"/>
+      <c r="O22" s="82" t="n"/>
+    </row>
+    <row r="23" ht="50" customHeight="1">
+      <c r="A23" s="83" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="B23" s="84" t="n"/>
+      <c r="C23" s="84" t="n"/>
+      <c r="D23" s="84" t="n"/>
+      <c r="E23" s="84" t="n"/>
+      <c r="F23" s="84" t="n"/>
+      <c r="G23" s="84" t="n"/>
+      <c r="H23" s="84" t="n"/>
+      <c r="I23" s="83" t="inlineStr">
+        <is>
+          <t>3 unidades</t>
+        </is>
+      </c>
+      <c r="J23" s="84" t="n"/>
+      <c r="K23" s="84" t="n"/>
+      <c r="L23" s="84" t="n"/>
+      <c r="M23" s="84" t="n"/>
+      <c r="N23" s="84" t="n"/>
+      <c r="O23" s="84" t="n"/>
+    </row>
+    <row r="24" ht="150" customHeight="1">
       <c r="A24" s="83" t="inlineStr">
         <is>
-          <t>Cantidad</t>
+          <t>Dimensiones faciales (unitarias)</t>
         </is>
       </c>
       <c r="B24" s="84" t="n"/>
@@ -4201,7 +4217,7 @@
       <c r="H24" s="84" t="n"/>
       <c r="I24" s="83" t="inlineStr">
         <is>
-          <t>3 unidades</t>
+          <t>353×336 mm (área facial 0.1187 m²)</t>
         </is>
       </c>
       <c r="J24" s="84" t="n"/>
@@ -4211,10 +4227,10 @@
       <c r="N24" s="84" t="n"/>
       <c r="O24" s="84" t="n"/>
     </row>
-    <row r="25" ht="114" customHeight="1">
+    <row r="25" ht="100" customHeight="1">
       <c r="A25" s="83" t="inlineStr">
         <is>
-          <t>Dimensiones faciales (unitarias)</t>
+          <t>Caudal total de descarga</t>
         </is>
       </c>
       <c r="B25" s="84" t="n"/>
@@ -4226,7 +4242,7 @@
       <c r="H25" s="84" t="n"/>
       <c r="I25" s="83" t="inlineStr">
         <is>
-          <t>353×336 mm (área facial 0.1187 m²)</t>
+          <t>3 840 m³/h (1.0667 m³/s)</t>
         </is>
       </c>
       <c r="J25" s="84" t="n"/>
@@ -4236,10 +4252,10 @@
       <c r="N25" s="84" t="n"/>
       <c r="O25" s="84" t="n"/>
     </row>
-    <row r="26" ht="76" customHeight="1">
+    <row r="26" ht="100" customHeight="1">
       <c r="A26" s="83" t="inlineStr">
         <is>
-          <t>Caudal total de descarga</t>
+          <t>Velocidad facial</t>
         </is>
       </c>
       <c r="B26" s="84" t="n"/>
@@ -4251,7 +4267,7 @@
       <c r="H26" s="84" t="n"/>
       <c r="I26" s="83" t="inlineStr">
         <is>
-          <t>3 840 m³/h (1.0667 m³/s)</t>
+          <t>3 m/s</t>
         </is>
       </c>
       <c r="J26" s="84" t="n"/>
@@ -4261,10 +4277,10 @@
       <c r="N26" s="84" t="n"/>
       <c r="O26" s="84" t="n"/>
     </row>
-    <row r="27" ht="76" customHeight="1">
+    <row r="27" ht="200" customHeight="1">
       <c r="A27" s="83" t="inlineStr">
         <is>
-          <t>Velocidad facial</t>
+          <t>ΔP unitaria (cierre de orificio, C_d = 0.60, en el sitio)</t>
         </is>
       </c>
       <c r="B27" s="84" t="n"/>
@@ -4276,7 +4292,7 @@
       <c r="H27" s="84" t="n"/>
       <c r="I27" s="83" t="inlineStr">
         <is>
-          <t>3 m/s</t>
+          <t>11 Pa</t>
         </is>
       </c>
       <c r="J27" s="84" t="n"/>
@@ -4286,10 +4302,10 @@
       <c r="N27" s="84" t="n"/>
       <c r="O27" s="84" t="n"/>
     </row>
-    <row r="28" ht="152" customHeight="1">
+    <row r="28" ht="200" customHeight="1">
       <c r="A28" s="83" t="inlineStr">
         <is>
-          <t>ΔP unitaria (cierre de orificio, C_d = 0.60, en el sitio)</t>
+          <t>ΔP equivalente a densidad estándar (ρ = 1.2 kg/m³)</t>
         </is>
       </c>
       <c r="B28" s="84" t="n"/>
@@ -4301,7 +4317,7 @@
       <c r="H28" s="84" t="n"/>
       <c r="I28" s="83" t="inlineStr">
         <is>
-          <t>11 Pa</t>
+          <t>15 Pa</t>
         </is>
       </c>
       <c r="J28" s="84" t="n"/>
@@ -4311,10 +4327,10 @@
       <c r="N28" s="84" t="n"/>
       <c r="O28" s="84" t="n"/>
     </row>
-    <row r="29" ht="152" customHeight="1">
+    <row r="29" ht="150" customHeight="1">
       <c r="A29" s="83" t="inlineStr">
         <is>
-          <t>ΔP equivalente a densidad estándar (ρ = 1.2 kg/m³)</t>
+          <t>Densidad del aire de diseño</t>
         </is>
       </c>
       <c r="B29" s="84" t="n"/>
@@ -4326,7 +4342,7 @@
       <c r="H29" s="84" t="n"/>
       <c r="I29" s="83" t="inlineStr">
         <is>
-          <t>15 Pa</t>
+          <t>0.88 kg/m³ (2 558 msnm, 74.1 kPa)</t>
         </is>
       </c>
       <c r="J29" s="84" t="n"/>
@@ -4336,84 +4352,108 @@
       <c r="N29" s="84" t="n"/>
       <c r="O29" s="84" t="n"/>
     </row>
-    <row r="30" ht="114" customHeight="1">
-      <c r="A30" s="83" t="inlineStr">
-        <is>
-          <t>Densidad del aire de diseño</t>
-        </is>
-      </c>
-      <c r="B30" s="84" t="n"/>
-      <c r="C30" s="84" t="n"/>
-      <c r="D30" s="84" t="n"/>
-      <c r="E30" s="84" t="n"/>
-      <c r="F30" s="84" t="n"/>
-      <c r="G30" s="84" t="n"/>
-      <c r="H30" s="84" t="n"/>
-      <c r="I30" s="83" t="inlineStr">
-        <is>
-          <t>0.88 kg/m³ (2 558 msnm, 74.1 kPa)</t>
-        </is>
-      </c>
-      <c r="J30" s="84" t="n"/>
-      <c r="K30" s="84" t="n"/>
-      <c r="L30" s="84" t="n"/>
-      <c r="M30" s="84" t="n"/>
-      <c r="N30" s="84" t="n"/>
-      <c r="O30" s="84" t="n"/>
-    </row>
-    <row r="31" ht="38" customHeight="1"/>
-    <row r="32" ht="418" customHeight="1">
-      <c r="A32" s="85" t="inlineStr">
+    <row r="30" ht="50" customHeight="1"/>
+    <row r="31" ht="400" customHeight="1">
+      <c r="A31" s="85" t="inlineStr">
         <is>
           <t>2.1. Nota de contexto: la ΔP unitaria de 11 Pa (cierre de orificio, C_d = 0.60, a 3 m/s) es la pérdida de descarga libre a la atmósfera y se suma a la caída de presión de la etapa filtrante para definir el punto de trabajo del ventilador; no existe consigna de presión interior que sostener.</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="38" customHeight="1"/>
-    <row r="34" ht="38" customHeight="1"/>
-    <row r="35" ht="114" customHeight="1">
-      <c r="A35" s="81" t="inlineStr">
+    <row r="32" ht="50" customHeight="1"/>
+    <row r="33" ht="150" customHeight="1">
+      <c r="A33" s="81" t="inlineStr">
         <is>
           <t>3. Construcción y áreas netas</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="38" customHeight="1">
-      <c r="A36" s="86" t="inlineStr">
+    <row r="34" ht="50" customHeight="1">
+      <c r="A34" s="86" t="inlineStr">
         <is>
           <t>Tabla 2. Especificación constructiva.</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="38" customHeight="1">
-      <c r="A37" s="82" t="inlineStr">
+    <row r="35" ht="50" customHeight="1">
+      <c r="A35" s="82" t="inlineStr">
         <is>
           <t>Característica</t>
         </is>
       </c>
-      <c r="B37" s="82" t="n"/>
-      <c r="C37" s="82" t="n"/>
-      <c r="D37" s="82" t="n"/>
-      <c r="E37" s="82" t="n"/>
-      <c r="F37" s="82" t="n"/>
-      <c r="G37" s="82" t="n"/>
-      <c r="H37" s="82" t="n"/>
-      <c r="I37" s="82" t="inlineStr">
+      <c r="B35" s="82" t="n"/>
+      <c r="C35" s="82" t="n"/>
+      <c r="D35" s="82" t="n"/>
+      <c r="E35" s="82" t="n"/>
+      <c r="F35" s="82" t="n"/>
+      <c r="G35" s="82" t="n"/>
+      <c r="H35" s="82" t="n"/>
+      <c r="I35" s="82" t="inlineStr">
         <is>
           <t>Especificación</t>
         </is>
       </c>
-      <c r="J37" s="82" t="n"/>
-      <c r="K37" s="82" t="n"/>
-      <c r="L37" s="82" t="n"/>
-      <c r="M37" s="82" t="n"/>
-      <c r="N37" s="82" t="n"/>
-      <c r="O37" s="82" t="n"/>
-    </row>
-    <row r="38" ht="152" customHeight="1">
+      <c r="J35" s="82" t="n"/>
+      <c r="K35" s="82" t="n"/>
+      <c r="L35" s="82" t="n"/>
+      <c r="M35" s="82" t="n"/>
+      <c r="N35" s="82" t="n"/>
+      <c r="O35" s="82" t="n"/>
+    </row>
+    <row r="36" ht="200" customHeight="1">
+      <c r="A36" s="83" t="inlineStr">
+        <is>
+          <t>Tipo de núcleo</t>
+        </is>
+      </c>
+      <c r="B36" s="84" t="n"/>
+      <c r="C36" s="84" t="n"/>
+      <c r="D36" s="84" t="n"/>
+      <c r="E36" s="84" t="n"/>
+      <c r="F36" s="84" t="n"/>
+      <c r="G36" s="84" t="n"/>
+      <c r="H36" s="84" t="n"/>
+      <c r="I36" s="83" t="inlineStr">
+        <is>
+          <t>Eggcrate (panal) ½×½×½ in (12.7 mm), máxima área libre</t>
+        </is>
+      </c>
+      <c r="J36" s="84" t="n"/>
+      <c r="K36" s="84" t="n"/>
+      <c r="L36" s="84" t="n"/>
+      <c r="M36" s="84" t="n"/>
+      <c r="N36" s="84" t="n"/>
+      <c r="O36" s="84" t="n"/>
+    </row>
+    <row r="37" ht="600" customHeight="1">
+      <c r="A37" s="83" t="inlineStr">
+        <is>
+          <t>Área libre del núcleo</t>
+        </is>
+      </c>
+      <c r="B37" s="84" t="n"/>
+      <c r="C37" s="84" t="n"/>
+      <c r="D37" s="84" t="n"/>
+      <c r="E37" s="84" t="n"/>
+      <c r="F37" s="84" t="n"/>
+      <c r="G37" s="84" t="n"/>
+      <c r="H37" s="84" t="n"/>
+      <c r="I37" s="83" t="inlineStr">
+        <is>
+          <t>≥ 90 % (cifra repetida en catálogos del tipo; Airfoil RC-FCR5 (https://airfoil.com.au/product/removable-core-fixing-clip-eggcrate-grille-rc-fcr5/), consulta 2026-07-23)</t>
+        </is>
+      </c>
+      <c r="J37" s="84" t="n"/>
+      <c r="K37" s="84" t="n"/>
+      <c r="L37" s="84" t="n"/>
+      <c r="M37" s="84" t="n"/>
+      <c r="N37" s="84" t="n"/>
+      <c r="O37" s="84" t="n"/>
+    </row>
+    <row r="38" ht="950" customHeight="1">
       <c r="A38" s="83" t="inlineStr">
         <is>
-          <t>Tipo de núcleo</t>
+          <t>Malla anti-insectos</t>
         </is>
       </c>
       <c r="B38" s="84" t="n"/>
@@ -4425,7 +4465,7 @@
       <c r="H38" s="84" t="n"/>
       <c r="I38" s="83" t="inlineStr">
         <is>
-          <t>Eggcrate (panal) ½×½×½ in (12.7 mm), máxima área libre</t>
+          <t>Tejido 18×18, abertura ≈1 mm, alambre 0.45 mm, área abierta ≥ 48 % (tabla Industrial Metal Mesh (https://www.industrialmetalmesh.com/sale-54819921-micron-304-316l-stainless-steel-wire-mesh-screen-filter-mesh.html), consulta 2026-07-23); excluye insectos comunes</t>
         </is>
       </c>
       <c r="J38" s="84" t="n"/>
@@ -4435,10 +4475,10 @@
       <c r="N38" s="84" t="n"/>
       <c r="O38" s="84" t="n"/>
     </row>
-    <row r="39" ht="456" customHeight="1">
+    <row r="39" ht="200" customHeight="1">
       <c r="A39" s="83" t="inlineStr">
         <is>
-          <t>Área libre del núcleo</t>
+          <t>Área neta combinada (núcleo + malla)</t>
         </is>
       </c>
       <c r="B39" s="84" t="n"/>
@@ -4450,7 +4490,7 @@
       <c r="H39" s="84" t="n"/>
       <c r="I39" s="83" t="inlineStr">
         <is>
-          <t>≥ 90 % (cifra repetida en catálogos del tipo; Airfoil RC-FCR5 (https://airfoil.com.au/product/removable-core-fixing-clip-eggcrate-grille-rc-fcr5/), consulta 2026-07-23)</t>
+          <t>≈ 45 % del área facial (dato típico: 0.90 × 0.50)</t>
         </is>
       </c>
       <c r="J39" s="84" t="n"/>
@@ -4460,10 +4500,10 @@
       <c r="N39" s="84" t="n"/>
       <c r="O39" s="84" t="n"/>
     </row>
-    <row r="40" ht="722" customHeight="1">
+    <row r="40" ht="250" customHeight="1">
       <c r="A40" s="83" t="inlineStr">
         <is>
-          <t>Malla anti-insectos</t>
+          <t>Material de la rejilla</t>
         </is>
       </c>
       <c r="B40" s="84" t="n"/>
@@ -4475,7 +4515,7 @@
       <c r="H40" s="84" t="n"/>
       <c r="I40" s="83" t="inlineStr">
         <is>
-          <t>Tejido 18×18, abertura ≈1 mm, alambre 0.45 mm, área abierta ≥ 48 % (tabla Industrial Metal Mesh (https://www.industrialmetalmesh.com/sale-54819921-micron-304-316l-stainless-steel-wire-mesh-screen-filter-mesh.html), consulta 2026-07-23); excluye insectos comunes</t>
+          <t>Inox 316L (primera opción) o aluminio anodizado 6063-T5 (alternativa)</t>
         </is>
       </c>
       <c r="J40" s="84" t="n"/>
@@ -4485,10 +4525,10 @@
       <c r="N40" s="84" t="n"/>
       <c r="O40" s="84" t="n"/>
     </row>
-    <row r="41" ht="152" customHeight="1">
+    <row r="41" ht="100" customHeight="1">
       <c r="A41" s="83" t="inlineStr">
         <is>
-          <t>Área neta combinada (núcleo + malla)</t>
+          <t>Material de la malla</t>
         </is>
       </c>
       <c r="B41" s="84" t="n"/>
@@ -4500,7 +4540,7 @@
       <c r="H41" s="84" t="n"/>
       <c r="I41" s="83" t="inlineStr">
         <is>
-          <t>≈ 45 % del área facial (dato típico: 0.90 × 0.50)</t>
+          <t>Inox 316</t>
         </is>
       </c>
       <c r="J41" s="84" t="n"/>
@@ -4510,10 +4550,10 @@
       <c r="N41" s="84" t="n"/>
       <c r="O41" s="84" t="n"/>
     </row>
-    <row r="42" ht="190" customHeight="1">
+    <row r="42" ht="150" customHeight="1">
       <c r="A42" s="83" t="inlineStr">
         <is>
-          <t>Material de la rejilla</t>
+          <t>Montaje de la malla</t>
         </is>
       </c>
       <c r="B42" s="84" t="n"/>
@@ -4525,7 +4565,7 @@
       <c r="H42" s="84" t="n"/>
       <c r="I42" s="83" t="inlineStr">
         <is>
-          <t>Inox 316L (primera opción) o aluminio anodizado 6063-T5 (alternativa)</t>
+          <t>Marco desmontable para limpieza periódica</t>
         </is>
       </c>
       <c r="J42" s="84" t="n"/>
@@ -4535,10 +4575,10 @@
       <c r="N42" s="84" t="n"/>
       <c r="O42" s="84" t="n"/>
     </row>
-    <row r="43" ht="76" customHeight="1">
+    <row r="43" ht="350" customHeight="1">
       <c r="A43" s="83" t="inlineStr">
         <is>
-          <t>Material de la malla</t>
+          <t>Par galvánico</t>
         </is>
       </c>
       <c r="B43" s="84" t="n"/>
@@ -4550,7 +4590,7 @@
       <c r="H43" s="84" t="n"/>
       <c r="I43" s="83" t="inlineStr">
         <is>
-          <t>Inox 316</t>
+          <t>Si se combina marco de aluminio con malla inox, aislamiento dieléctrico (dato típico de ingeniería)</t>
         </is>
       </c>
       <c r="J43" s="84" t="n"/>
@@ -4560,10 +4600,10 @@
       <c r="N43" s="84" t="n"/>
       <c r="O43" s="84" t="n"/>
     </row>
-    <row r="44" ht="114" customHeight="1">
+    <row r="44" ht="150" customHeight="1">
       <c r="A44" s="83" t="inlineStr">
         <is>
-          <t>Montaje de la malla</t>
+          <t>Ensayo de desempeño</t>
         </is>
       </c>
       <c r="B44" s="84" t="n"/>
@@ -4575,7 +4615,7 @@
       <c r="H44" s="84" t="n"/>
       <c r="I44" s="83" t="inlineStr">
         <is>
-          <t>Marco desmontable para limpieza periódica</t>
+          <t>ASHRAE 70 (medición de rejillas)</t>
         </is>
       </c>
       <c r="J44" s="84" t="n"/>
@@ -4585,360 +4625,306 @@
       <c r="N44" s="84" t="n"/>
       <c r="O44" s="84" t="n"/>
     </row>
-    <row r="45" ht="266" customHeight="1">
-      <c r="A45" s="83" t="inlineStr">
-        <is>
-          <t>Par galvánico</t>
-        </is>
-      </c>
-      <c r="B45" s="84" t="n"/>
-      <c r="C45" s="84" t="n"/>
-      <c r="D45" s="84" t="n"/>
-      <c r="E45" s="84" t="n"/>
-      <c r="F45" s="84" t="n"/>
-      <c r="G45" s="84" t="n"/>
-      <c r="H45" s="84" t="n"/>
-      <c r="I45" s="83" t="inlineStr">
-        <is>
-          <t>Si se combina marco de aluminio con malla inox, aislamiento dieléctrico (dato típico de ingeniería)</t>
-        </is>
-      </c>
-      <c r="J45" s="84" t="n"/>
-      <c r="K45" s="84" t="n"/>
-      <c r="L45" s="84" t="n"/>
-      <c r="M45" s="84" t="n"/>
-      <c r="N45" s="84" t="n"/>
-      <c r="O45" s="84" t="n"/>
-    </row>
-    <row r="46" ht="114" customHeight="1">
-      <c r="A46" s="83" t="inlineStr">
-        <is>
-          <t>Ensayo de desempeño</t>
-        </is>
-      </c>
-      <c r="B46" s="84" t="n"/>
-      <c r="C46" s="84" t="n"/>
-      <c r="D46" s="84" t="n"/>
-      <c r="E46" s="84" t="n"/>
-      <c r="F46" s="84" t="n"/>
-      <c r="G46" s="84" t="n"/>
-      <c r="H46" s="84" t="n"/>
-      <c r="I46" s="83" t="inlineStr">
-        <is>
-          <t>ASHRAE 70 (medición de rejillas)</t>
-        </is>
-      </c>
-      <c r="J46" s="84" t="n"/>
-      <c r="K46" s="84" t="n"/>
-      <c r="L46" s="84" t="n"/>
-      <c r="M46" s="84" t="n"/>
-      <c r="N46" s="84" t="n"/>
-      <c r="O46" s="84" t="n"/>
-    </row>
-    <row r="47" ht="38" customHeight="1"/>
-    <row r="48" ht="190" customHeight="1">
-      <c r="A48" s="85" t="inlineStr">
+    <row r="45" ht="50" customHeight="1"/>
+    <row r="46" ht="350" customHeight="1">
+      <c r="A46" s="85" t="inlineStr">
         <is>
           <t>3.1. La malla domina la pérdida del conjunto; el dimensionamiento por área neta combinada y la ΔP calculada por cierre de orificio (11 Pa) deben verificarse contra el área efectiva (Ak) del fabricante seleccionado (por confirmar con proveedor).</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="38" customHeight="1"/>
-    <row r="50" ht="76" customHeight="1">
-      <c r="A50" s="81" t="inlineStr">
+    <row r="47" ht="50" customHeight="1"/>
+    <row r="48" ht="100" customHeight="1">
+      <c r="A48" s="81" t="inlineStr">
         <is>
           <t>4. Candidatos comerciales</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="38" customHeight="1">
-      <c r="A51" s="86" t="inlineStr">
+    <row r="49" ht="100" customHeight="1">
+      <c r="A49" s="86" t="inlineStr">
         <is>
           <t>Tabla 3. Candidatos (consulta 2026-07-23).</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="76" customHeight="1">
-      <c r="A52" s="82" t="inlineStr">
+    <row r="50" ht="100" customHeight="1">
+      <c r="A50" s="82" t="inlineStr">
         <is>
           <t>Producto</t>
         </is>
       </c>
-      <c r="B52" s="82" t="n"/>
-      <c r="C52" s="82" t="n"/>
-      <c r="D52" s="82" t="inlineStr">
+      <c r="B50" s="82" t="n"/>
+      <c r="C50" s="82" t="n"/>
+      <c r="D50" s="82" t="inlineStr">
         <is>
           <t>Tipo / material</t>
         </is>
       </c>
-      <c r="E52" s="82" t="n"/>
-      <c r="F52" s="82" t="n"/>
-      <c r="G52" s="82" t="inlineStr">
+      <c r="E50" s="82" t="n"/>
+      <c r="F50" s="82" t="n"/>
+      <c r="G50" s="82" t="inlineStr">
         <is>
           <t>Pros</t>
         </is>
       </c>
-      <c r="H52" s="82" t="n"/>
-      <c r="I52" s="82" t="n"/>
-      <c r="J52" s="82" t="inlineStr">
+      <c r="H50" s="82" t="n"/>
+      <c r="I50" s="82" t="n"/>
+      <c r="J50" s="82" t="inlineStr">
         <is>
           <t>Contras</t>
         </is>
       </c>
-      <c r="K52" s="82" t="n"/>
-      <c r="L52" s="82" t="n"/>
-      <c r="M52" s="82" t="inlineStr">
+      <c r="K50" s="82" t="n"/>
+      <c r="L50" s="82" t="n"/>
+      <c r="M50" s="82" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="N52" s="82" t="n"/>
-      <c r="O52" s="82" t="n"/>
-    </row>
-    <row r="53" ht="266" customHeight="1">
+      <c r="N50" s="82" t="n"/>
+      <c r="O50" s="82" t="n"/>
+    </row>
+    <row r="51" ht="350" customHeight="1">
+      <c r="A51" s="83" t="inlineStr">
+        <is>
+          <t>Titus 50F / 50R</t>
+        </is>
+      </c>
+      <c r="B51" s="84" t="n"/>
+      <c r="C51" s="84" t="n"/>
+      <c r="D51" s="83" t="inlineStr">
+        <is>
+          <t>Eggcrate ½ in; aluminio, con versión íntegramente inox de fábrica</t>
+        </is>
+      </c>
+      <c r="E51" s="84" t="n"/>
+      <c r="F51" s="84" t="n"/>
+      <c r="G51" s="83" t="inlineStr">
+        <is>
+          <t>«Highest free area of any return grille»; única opción inox de catálogo</t>
+        </is>
+      </c>
+      <c r="H51" s="84" t="n"/>
+      <c r="I51" s="84" t="n"/>
+      <c r="J51" s="83" t="inlineStr">
+        <is>
+          <t>Importación; tamaño 353×336 por pedido</t>
+        </is>
+      </c>
+      <c r="K51" s="84" t="n"/>
+      <c r="L51" s="84" t="n"/>
+      <c r="M51" s="83" t="inlineStr">
+        <is>
+          <t>Titus 50F (PDF) (https://www.titus-hvac.com/file/1228/50F_50Rrprod_specialized_2017.pdf)</t>
+        </is>
+      </c>
+      <c r="N51" s="84" t="n"/>
+      <c r="O51" s="84" t="n"/>
+    </row>
+    <row r="52" ht="350" customHeight="1">
+      <c r="A52" s="83" t="inlineStr">
+        <is>
+          <t>Krueger EGC5</t>
+        </is>
+      </c>
+      <c r="B52" s="84" t="n"/>
+      <c r="C52" s="84" t="n"/>
+      <c r="D52" s="83" t="inlineStr">
+        <is>
+          <t>Eggcrate ½ in; aluminio</t>
+        </is>
+      </c>
+      <c r="E52" s="84" t="n"/>
+      <c r="F52" s="84" t="n"/>
+      <c r="G52" s="83" t="inlineStr">
+        <is>
+          <t>Amplia gama de tamaños (6×4 in a 96×96 in)</t>
+        </is>
+      </c>
+      <c r="H52" s="84" t="n"/>
+      <c r="I52" s="84" t="n"/>
+      <c r="J52" s="83" t="inlineStr">
+        <is>
+          <t>Sin ejecución inox</t>
+        </is>
+      </c>
+      <c r="K52" s="84" t="n"/>
+      <c r="L52" s="84" t="n"/>
+      <c r="M52" s="83" t="inlineStr">
+        <is>
+          <t>Krueger EGC5 (https://www.krueger-hvac.com/Catalog%20Home/Grilles/Grilles%20-%20Return/EGC5)</t>
+        </is>
+      </c>
+      <c r="N52" s="84" t="n"/>
+      <c r="O52" s="84" t="n"/>
+    </row>
+    <row r="53" ht="350" customHeight="1">
       <c r="A53" s="83" t="inlineStr">
         <is>
-          <t>Titus 50F / 50R</t>
+          <t>ProAire S.A.S (Bogotá)</t>
         </is>
       </c>
       <c r="B53" s="84" t="n"/>
       <c r="C53" s="84" t="n"/>
       <c r="D53" s="83" t="inlineStr">
         <is>
-          <t>Eggcrate ½ in; aluminio, con versión íntegramente inox de fábrica</t>
+          <t>Fabricación a medida con corte láser, inox 316</t>
         </is>
       </c>
       <c r="E53" s="84" t="n"/>
       <c r="F53" s="84" t="n"/>
       <c r="G53" s="83" t="inlineStr">
         <is>
-          <t>«Highest free area of any return grille»; única opción inox de catálogo</t>
+          <t>Medida exacta 353×336 y ejecución inox 316L local; vía recomendada</t>
         </is>
       </c>
       <c r="H53" s="84" t="n"/>
       <c r="I53" s="84" t="n"/>
       <c r="J53" s="83" t="inlineStr">
         <is>
-          <t>Importación; tamaño 353×336 por pedido</t>
+          <t>Submittal y Ak por confirmar con proveedor</t>
         </is>
       </c>
       <c r="K53" s="84" t="n"/>
       <c r="L53" s="84" t="n"/>
       <c r="M53" s="83" t="inlineStr">
         <is>
-          <t>Titus 50F (PDF) (https://www.titus-hvac.com/file/1228/50F_50Rrprod_specialized_2017.pdf)</t>
+          <t>proairecolombia.com (https://www.proairecolombia.com/productos/rejillas-y-difusores.html)</t>
         </is>
       </c>
       <c r="N53" s="84" t="n"/>
       <c r="O53" s="84" t="n"/>
     </row>
-    <row r="54" ht="266" customHeight="1">
+    <row r="54" ht="250" customHeight="1">
       <c r="A54" s="83" t="inlineStr">
         <is>
-          <t>Krueger EGC5</t>
+          <t>Laminaire (Colombia)</t>
         </is>
       </c>
       <c r="B54" s="84" t="n"/>
       <c r="C54" s="84" t="n"/>
       <c r="D54" s="83" t="inlineStr">
         <is>
-          <t>Eggcrate ½ in; aluminio</t>
+          <t>Rejillas y difusores en aluminio a pedido</t>
         </is>
       </c>
       <c r="E54" s="84" t="n"/>
       <c r="F54" s="84" t="n"/>
       <c r="G54" s="83" t="inlineStr">
         <is>
-          <t>Amplia gama de tamaños (6×4 in a 96×96 in)</t>
+          <t>Fabricación local con software de selección; marco para malla a pedido</t>
         </is>
       </c>
       <c r="H54" s="84" t="n"/>
       <c r="I54" s="84" t="n"/>
       <c r="J54" s="83" t="inlineStr">
         <is>
-          <t>Sin ejecución inox</t>
+          <t>Confirmar ejecución inox</t>
         </is>
       </c>
       <c r="K54" s="84" t="n"/>
       <c r="L54" s="84" t="n"/>
       <c r="M54" s="83" t="inlineStr">
         <is>
-          <t>Krueger EGC5 (https://www.krueger-hvac.com/Catalog%20Home/Grilles/Grilles%20-%20Return/EGC5)</t>
+          <t>laminaire.net (https://laminaire.net/)</t>
         </is>
       </c>
       <c r="N54" s="84" t="n"/>
       <c r="O54" s="84" t="n"/>
     </row>
-    <row r="55" ht="266" customHeight="1">
+    <row r="55" ht="150" customHeight="1">
       <c r="A55" s="83" t="inlineStr">
         <is>
-          <t>ProAire S.A.S (Bogotá)</t>
+          <t>CL Ingeniería (Bogotá)</t>
         </is>
       </c>
       <c r="B55" s="84" t="n"/>
       <c r="C55" s="84" t="n"/>
       <c r="D55" s="83" t="inlineStr">
         <is>
-          <t>Fabricación a medida con corte láser, inox 316</t>
+          <t>Rejillas y accesorios HVAC</t>
         </is>
       </c>
       <c r="E55" s="84" t="n"/>
       <c r="F55" s="84" t="n"/>
       <c r="G55" s="83" t="inlineStr">
         <is>
-          <t>Medida exacta 353×336 y ejecución inox 316L local; vía recomendada</t>
+          <t>Canal local adicional</t>
         </is>
       </c>
       <c r="H55" s="84" t="n"/>
       <c r="I55" s="84" t="n"/>
       <c r="J55" s="83" t="inlineStr">
         <is>
-          <t>Submittal y Ak por confirmar con proveedor</t>
+          <t>Catálogo genérico</t>
         </is>
       </c>
       <c r="K55" s="84" t="n"/>
       <c r="L55" s="84" t="n"/>
       <c r="M55" s="83" t="inlineStr">
         <is>
-          <t>proairecolombia.com (https://www.proairecolombia.com/productos/rejillas-y-difusores.html)</t>
+          <t>clingenieria.co (https://clingenieria.co/)</t>
         </is>
       </c>
       <c r="N55" s="84" t="n"/>
       <c r="O55" s="84" t="n"/>
     </row>
-    <row r="56" ht="190" customHeight="1">
-      <c r="A56" s="83" t="inlineStr">
-        <is>
-          <t>Laminaire (Colombia)</t>
-        </is>
-      </c>
-      <c r="B56" s="84" t="n"/>
-      <c r="C56" s="84" t="n"/>
-      <c r="D56" s="83" t="inlineStr">
-        <is>
-          <t>Rejillas y difusores en aluminio a pedido</t>
-        </is>
-      </c>
-      <c r="E56" s="84" t="n"/>
-      <c r="F56" s="84" t="n"/>
-      <c r="G56" s="83" t="inlineStr">
-        <is>
-          <t>Fabricación local con software de selección; marco para malla a pedido</t>
-        </is>
-      </c>
-      <c r="H56" s="84" t="n"/>
-      <c r="I56" s="84" t="n"/>
-      <c r="J56" s="83" t="inlineStr">
-        <is>
-          <t>Confirmar ejecución inox</t>
-        </is>
-      </c>
-      <c r="K56" s="84" t="n"/>
-      <c r="L56" s="84" t="n"/>
-      <c r="M56" s="83" t="inlineStr">
-        <is>
-          <t>laminaire.net (https://laminaire.net/)</t>
-        </is>
-      </c>
-      <c r="N56" s="84" t="n"/>
-      <c r="O56" s="84" t="n"/>
-    </row>
-    <row r="57" ht="114" customHeight="1">
-      <c r="A57" s="83" t="inlineStr">
-        <is>
-          <t>CL Ingeniería (Bogotá)</t>
-        </is>
-      </c>
-      <c r="B57" s="84" t="n"/>
-      <c r="C57" s="84" t="n"/>
-      <c r="D57" s="83" t="inlineStr">
-        <is>
-          <t>Rejillas y accesorios HVAC</t>
-        </is>
-      </c>
-      <c r="E57" s="84" t="n"/>
-      <c r="F57" s="84" t="n"/>
-      <c r="G57" s="83" t="inlineStr">
-        <is>
-          <t>Canal local adicional</t>
-        </is>
-      </c>
-      <c r="H57" s="84" t="n"/>
-      <c r="I57" s="84" t="n"/>
-      <c r="J57" s="83" t="inlineStr">
-        <is>
-          <t>Catálogo genérico</t>
-        </is>
-      </c>
-      <c r="K57" s="84" t="n"/>
-      <c r="L57" s="84" t="n"/>
-      <c r="M57" s="83" t="inlineStr">
-        <is>
-          <t>clingenieria.co (https://clingenieria.co/)</t>
-        </is>
-      </c>
-      <c r="N57" s="84" t="n"/>
-      <c r="O57" s="84" t="n"/>
-    </row>
-    <row r="58" ht="38" customHeight="1"/>
-    <row r="59" ht="38" customHeight="1">
-      <c r="A59" s="81" t="inlineStr">
+    <row r="56" ht="50" customHeight="1"/>
+    <row r="57" ht="50" customHeight="1">
+      <c r="A57" s="81" t="inlineStr">
         <is>
           <t>5. Instalación</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="456" customHeight="1">
+    <row r="58" ht="450" customHeight="1">
+      <c r="A58" s="85" t="inlineStr">
+        <is>
+          <t>5.1. Montaje a ras de muro exterior con marco perimetral sellado con silicona RTV neutra (compatible con hipoclorito; Chemical Resistance of RTV Silicone Sealants (PDF) (https://irp.cdn-website.com/63168859/files/uploaded/Chemical%20Resistance%20of%20RTV%20Silicone%20Sealants%20Chart.pdf), consulta 2026-07-23) y ferretería inox 316 (A4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="150" customHeight="1">
+      <c r="A59" s="85" t="inlineStr">
+        <is>
+          <t>5.2. Las bocas exteriores se orientan preferentemente a sotavento respecto de las fuentes de cloro de la planta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="150" customHeight="1">
       <c r="A60" s="85" t="inlineStr">
         <is>
-          <t>5.1. Montaje a ras de muro exterior con marco perimetral sellado con silicona RTV neutra (compatible con hipoclorito; Chemical Resistance of RTV Silicone Sealants (PDF) (https://irp.cdn-website.com/63168859/files/uploaded/Chemical%20Resistance%20of%20RTV%20Silicone%20Sealants%20Chart.pdf), consulta 2026-07-23) y ferretería inox 316 (A4).</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="38" customHeight="1"/>
-    <row r="62" ht="114" customHeight="1">
-      <c r="A62" s="85" t="inlineStr">
-        <is>
-          <t>5.2. Las bocas exteriores se orientan preferentemente a sotavento respecto de las fuentes de cloro de la planta.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="114" customHeight="1">
+          <t>5.3. Programa de limpieza de la malla según carga de polvo observada en comisionamiento (dato típico de operación).</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="50" customHeight="1"/>
+    <row r="62" ht="100" customHeight="1">
+      <c r="A62" s="81" t="inlineStr">
+        <is>
+          <t>6. Normas aplicables</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="500" customHeight="1">
       <c r="A63" s="85" t="inlineStr">
         <is>
-          <t>5.3. Programa de limpieza de la malla según carga de polvo observada en comisionamiento (dato típico de operación).</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="38" customHeight="1"/>
-    <row r="65" ht="76" customHeight="1">
-      <c r="A65" s="81" t="inlineStr">
-        <is>
-          <t>6. Normas aplicables</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="494" customHeight="1">
-      <c r="A66" s="85" t="inlineStr">
-        <is>
           <t>6.1. ASHRAE 70 (método de ensayo y reporte de desempeño de rejillas); correlación de área libre para transferencia de aire según Building Science BA-0006 (https://buildingscience.com/sites/default/files/migrate/pdf/BA-0006_Discuss_transfer_grilles.pdf) (consulta 2026-07-23); ISO 12944 / NACE-AMPP para la selección de materiales en el ambiente clorado.</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="38" customHeight="1"/>
   </sheetData>
-  <mergeCells count="100">
+  <mergeCells count="96">
     <mergeCell ref="I44:O44"/>
     <mergeCell ref="D53:F53"/>
-    <mergeCell ref="A50:O50"/>
-    <mergeCell ref="A57:C57"/>
     <mergeCell ref="N3:O3"/>
     <mergeCell ref="A25:H25"/>
-    <mergeCell ref="I30:O30"/>
+    <mergeCell ref="J50:L50"/>
     <mergeCell ref="N5:O5"/>
-    <mergeCell ref="I46:O46"/>
     <mergeCell ref="C2:L3"/>
     <mergeCell ref="A52:C52"/>
+    <mergeCell ref="G50:I50"/>
     <mergeCell ref="J52:L52"/>
     <mergeCell ref="M53:O53"/>
     <mergeCell ref="G52:I52"/>
@@ -4952,75 +4938,73 @@
     <mergeCell ref="A44:H44"/>
     <mergeCell ref="I24:O24"/>
     <mergeCell ref="B1:B5"/>
-    <mergeCell ref="D57:F57"/>
     <mergeCell ref="A40:H40"/>
     <mergeCell ref="A15:H15"/>
     <mergeCell ref="A24:H24"/>
+    <mergeCell ref="I35:O35"/>
     <mergeCell ref="A55:C55"/>
     <mergeCell ref="I10:O10"/>
     <mergeCell ref="N2:O2"/>
     <mergeCell ref="G55:I55"/>
-    <mergeCell ref="M57:O57"/>
     <mergeCell ref="A27:H27"/>
+    <mergeCell ref="G51:I51"/>
+    <mergeCell ref="A62:O62"/>
     <mergeCell ref="D55:F55"/>
     <mergeCell ref="I11:O11"/>
-    <mergeCell ref="I45:O45"/>
     <mergeCell ref="G54:I54"/>
+    <mergeCell ref="A20:O20"/>
     <mergeCell ref="D54:F54"/>
     <mergeCell ref="A42:H42"/>
-    <mergeCell ref="M56:O56"/>
-    <mergeCell ref="G56:I56"/>
+    <mergeCell ref="A48:O48"/>
+    <mergeCell ref="A22:H22"/>
     <mergeCell ref="I28:O28"/>
-    <mergeCell ref="A59:O59"/>
+    <mergeCell ref="A51:C51"/>
     <mergeCell ref="I37:O37"/>
     <mergeCell ref="N6:O6"/>
     <mergeCell ref="A28:H28"/>
     <mergeCell ref="N4:O4"/>
     <mergeCell ref="J53:L53"/>
     <mergeCell ref="I23:O23"/>
-    <mergeCell ref="A30:H30"/>
     <mergeCell ref="G53:I53"/>
     <mergeCell ref="J55:L55"/>
+    <mergeCell ref="A50:C50"/>
     <mergeCell ref="J54:L54"/>
+    <mergeCell ref="A33:O33"/>
     <mergeCell ref="A41:H41"/>
-    <mergeCell ref="J56:L56"/>
     <mergeCell ref="A17:O17"/>
-    <mergeCell ref="A60:O61"/>
+    <mergeCell ref="D51:F51"/>
     <mergeCell ref="I27:O27"/>
-    <mergeCell ref="A35:O35"/>
     <mergeCell ref="A26:H26"/>
-    <mergeCell ref="A66:O67"/>
+    <mergeCell ref="I36:O36"/>
+    <mergeCell ref="D50:F50"/>
     <mergeCell ref="A1:A5"/>
     <mergeCell ref="A9:O9"/>
     <mergeCell ref="C1:L1"/>
-    <mergeCell ref="J57:L57"/>
-    <mergeCell ref="A18:O19"/>
+    <mergeCell ref="I22:O22"/>
+    <mergeCell ref="A35:H35"/>
     <mergeCell ref="A10:H10"/>
     <mergeCell ref="I12:O12"/>
-    <mergeCell ref="A32:O33"/>
+    <mergeCell ref="M51:O51"/>
     <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A65:O65"/>
     <mergeCell ref="A39:H39"/>
     <mergeCell ref="I14:O14"/>
     <mergeCell ref="I39:O39"/>
     <mergeCell ref="M54:O54"/>
-    <mergeCell ref="G57:I57"/>
-    <mergeCell ref="A56:C56"/>
     <mergeCell ref="I29:O29"/>
+    <mergeCell ref="A36:H36"/>
     <mergeCell ref="A11:H11"/>
     <mergeCell ref="I38:O38"/>
-    <mergeCell ref="A45:H45"/>
-    <mergeCell ref="A21:O21"/>
     <mergeCell ref="I13:O13"/>
+    <mergeCell ref="A57:O57"/>
     <mergeCell ref="I40:O40"/>
-    <mergeCell ref="D56:F56"/>
     <mergeCell ref="I15:O15"/>
     <mergeCell ref="A53:C53"/>
     <mergeCell ref="A37:H37"/>
-    <mergeCell ref="A46:H46"/>
     <mergeCell ref="N1:O1"/>
     <mergeCell ref="A12:H12"/>
+    <mergeCell ref="J51:L51"/>
     <mergeCell ref="I26:O26"/>
+    <mergeCell ref="M50:O50"/>
     <mergeCell ref="A14:H14"/>
     <mergeCell ref="A23:H23"/>
     <mergeCell ref="I25:O25"/>
